--- a/tools/excel/owasp/owasp-top-10-web_2025.xlsx
+++ b/tools/excel/owasp/owasp-top-10-web_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\owasp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3413A75-EE7C-4BF5-8441-D5798469F514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F5AF1F-7CFE-4CA5-8CC4-7BED21A95881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="387">
   <si>
     <t>type</t>
   </si>
@@ -7946,12 +7946,683 @@
 Un logiciel sécurisé nécessite un cycle de développement sécurisé, un modèle de conception sécurisé, une méthodologie pavée, une bibliothèque de composants sécurisée, des outils appropriés, une modélisation des menaces et des post-mortem d’incidents utilisés pour améliorer le processus. Contactez vos spécialistes de la sécurité au début d’un projet logiciel, tout au long du projet, et pour la maintenance logicielle continue. Envisagez d’utiliser le [Modèle de Maturité d’Assurance Logicielle OWASP (SAMM)](https://owaspsamm.org/) pour structurer vos efforts de développement logiciel sécurisé. 
 Souvent, l’autoresponsabilité des développeurs est sous-estimée. Favoriser une culture de conscience, de responsabilité et d’atténuation proactive des risques. Des échanges réguliers sur la sécurité (par exemple lors de séances de modélisation des menaces) peuvent générer un état d’esprit visant à inclure la sécurité dans toutes les décisions de conception importantes.</t>
   </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;40
+   &lt;/td&gt;
+   &lt;td&gt;20,15 % 
+   &lt;/td&gt;
+   &lt;td&gt;3,74 % 
+   &lt;/td&gt;
+   &lt;td&gt;100,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;42,93 % 
+   &lt;/td&gt;
+   &lt;td&gt;7.04
+   &lt;/td&gt;
+   &lt;td&gt;3,84
+   &lt;/td&gt;
+   &lt;td&gt;1 839 701
+   &lt;/td&gt;
+   &lt;td&gt;32 654
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+Le contrôle d’accès n’est efficace que lorsqu’il est implémenté dans du code serveur de confiance ou dans des API serverless, où l’attaquant ne peut pas modifier la vérification ou les métadonnées de contrôle d’accès. 
+* Sauf pour les ressources publiques, refuser par défaut. 
+* Implémenter les mécanismes de contrôle d’accès une fois et les réutiliser dans toute l’application, y compris en minimisant l’utilisation du partage de ressources inter-origine (CORS). 
+* Les contrôles d’accès aux modèles devraient imposer la propriété des enregistrements plutôt que de permettre aux utilisateurs de créer, lire, mettre à jour ou supprimer un enregistrement. 
+* Les exigences uniques de limite d’activité des applications doivent être appliquées par les modèles de domaine. 
+* Désactivez la liste des répertoires des serveurs web et assurez-vous que les métadonnées de fichiers (par exemple, .git) et les fichiers de sauvegarde ne sont pas présents dans les racines web. 
+* Échecs de contrôle d’accès aux journaux, alerter les administrateurs lorsque cela est approprié (par exemple, échecs répétés). 
+* Mettre en place des limites de vitesse sur l’accès à l’API et aux contrôleurs afin de minimiser les dommages causés par les outils d’attaque automatisés. 
+* Les identifiants de session avec état doivent être invalidés sur le serveur après la déconnexion. Les jetons JWT sans état doivent être de courte durée afin de minimiser la fenêtre d’opportunité pour un attaquant. Pour les JWT à durée de vie plus longue, envisagez d’utiliser des jetons de rafraîchissement et de suivre les normes OAuth pour révoquer l’accès. 
+* Utilisez des kits à outils ou des motifs bien établis qui fournissent des contrôles d’accès simples et déclaratifs. 
+Les développeurs et le personnel QA devraient inclure le contrôle d’accès fonctionnel dans leurs tests unitaires et d’intégration.
+## Exemples de scénarios d’attaque
+**Scénario #1 :** L’application utilise des données non vérifiées dans un appel SQL qui accédent aux informations du compte : 
+```
+pstmt.setString(1, request.getParameter(« acct »)) ; 
+ResultSet results = pstmt.executeQuery( ) ; 
+```
+Un attaquant peut simplement modifier le paramètre « compte » du navigateur pour envoyer n’importe quel numéro de compte souhaité. Si ce n’est pas correctement vérifié, l’attaquant peut accéder au compte de n’importe quel utilisateur. 
+```
+https://example.com/app/accountInfo?acct=notmyacct
+```
+**Scénario #2 :** Un attaquant force simplement les navigateurs à cibler les URL. Des droits d’administrateur sont nécessaires pour accéder à la page d’administration. 
+```
+https://example.com/app/getappInfo
+https://example.com/app/admin_getappInfo
+```
+Si un utilisateur non authentifié peut accéder à l’une ou l’autre des pages, c’est un défaut. Si un non-administrateur peut accéder à la page d’administration, c’est un défaut. 
+**Scénario #3 :** Une application met tout son contrôle d’accès dans son front-end. Bien que l’attaquant ne puisse pas accéder à « https://example.com/app/admin_getappInfo » en raison du code JavaScript qui tourne dans le navigateur, il peut simplement exécuter : 
+```
+$ curl https://example.com/app/admin_getappInfo
+```
+depuis la ligne de commande. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A01_2025-Broken_Access_Control/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16
+   &lt;/td&gt;
+   &lt;td&gt;27,70 % 
+   &lt;/td&gt;
+   &lt;td&gt;3,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;100,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;52,35 % 
+   &lt;/td&gt;
+   &lt;td&gt;7,96
+   &lt;/td&gt;
+   &lt;td&gt;3,97
+   &lt;/td&gt;
+   &lt;td&gt;719 084
+   &lt;/td&gt;
+   &lt;td&gt;1 375
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+Des processus d’installation sécurisés doivent être mis en œuvre, notamment : 
+* Un processus de durcissement répétable permettant un déploiement rapide et facile d’un autre environnement suffisamment verrouillé. Les environnements de développement, d’assurance qualité et de production doivent tous être configurés de manière identique, avec des identifiants différents utilisés dans chaque environnement. Ce processus doit être automatisé pour minimiser l’effort nécessaire à la mise en place d’un nouvel environnement sécurisé. 
+* Une plateforme minimale sans fonctionnalités, composants, documentations ou exemples inutiles. Supprimez ou n’installez pas les fonctionnalités et frameworks inutilisés. 
+* Une tâche visant à revoir et mettre à jour les configurations appropriées à toutes les notes de sécurité, mises à jour et correctifs dans le cadre du processus de gestion des correctifs (voir [A03 Défaillances de la chaîne d’approvisionnement logicielle](A03_2025-Software_Supply_Chain_Failures.md)). Revoir les permissions de stockage cloud (par exemple, les permissions de bucket S3). 
+* Une architecture d’application segmentée offre une séparation efficace et sécurisée entre composants ou locataires, avec segmentation, conteneurisation ou groupes de sécurité cloud (ACL). 
+* Envoi de directives de sécurité aux clients, par exemple, les en-têtes de sécurité. 
+* Un processus automatisé pour vérifier l’efficacité des configurations et des réglages dans tous les environnements. 
+* Ajouter proactivement une configuration centrale pour intercepter les messages d’erreur excessifs en tant que sauvegarde. 
+* Si ces vérifications ne sont pas automatisées, elles doivent être vérifiées manuellement au minimum chaque année. 
+* Utiliser la fédération d’identité, des identifiants de courte durée ou des mécanismes d’accès basés sur des rôles fournis par la plateforme sous-jacente au lieu d’intégrer des clés statiques ou des secrets dans le code, les fichiers de configuration ou les pipelines.
+## Exemples de scénarios d’attaque
+**Scénario #1 :** Le serveur d’applications d’applications d’exemple n’est pas supprimé du serveur de production. Ces applications d’exemple présentent des failles de sécurité connues que les attaquants utilisent pour compromettre le serveur. Supposons que l’une de ces applications soit la console d’administration, et que les comptes par défaut n’aient pas été modifiés. Dans ce cas, l’attaquant se connecte avec le mot de passe par défaut et prend le relais. 
+**Scénario #2 :** La liste des répertoires n’est pas désactivée sur le serveur. Un attaquant découvre qu’il peut simplement lister les répertoires. L’attaquant trouve et télécharge les classes Java compilées, qu’il décompile et rétro-ingénierie pour visualiser le code. L’attaquant découvre alors une grave faille de contrôle d’accès dans l’application. 
+**Scénario #3 :** La configuration du serveur d’applications permet de renvoyer des messages d’erreur détaillés, tels que des traces de pile. Cela expose potentiellement des informations sensibles ou des failles sous-jacentes, comme des versions de composants connues pour être vulnérables. 
+**Scénario #4 :** Un fournisseur de services cloud (CSP) a par défaut des permissions de partage ouvertes à Internet. Cela permet d’accéder aux données sensibles stockées dans le stockage cloud. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;32
+   &lt;/td&gt;
+   &lt;td&gt;13,77 % 
+   &lt;/td&gt;
+   &lt;td&gt;3,80 % 
+   &lt;/td&gt;
+   &lt;td&gt;100,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;47,74 % 
+   &lt;/td&gt;
+   &lt;td&gt;7.23
+   &lt;/td&gt;
+   &lt;td&gt;3,90
+   &lt;/td&gt;
+   &lt;td&gt;1 665 348
+   &lt;/td&gt;
+   &lt;td&gt;2 185
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+Faites au minimum ce qui suit et consultez les références : 
+* Classifier et étiqueter les données traitées, stockées ou transmises par une application. Identifier quelles données sont sensibles selon les lois sur la vie privée, les exigences réglementaires ou les besoins de l’entreprise. 
+* Stockez vos clés les plus sensibles dans un HSM matériel ou cloud. 
+* Utiliser des implémentations d’algorithmes cryptographiques bien fiables dans la mesure du possible. 
+* Ne stockez pas inutilement les données sensibles. Jetez-les dès que possible ou utilisez une tokenisation conforme PCI DSS, voire une troncature. Les données non conservées ne peuvent pas être volées. 
+* Assurez-vous de chiffrer toutes les données sensibles au repos. 
+* S’assurer que des algorithmes, protocoles et clés standards à jour et solides sont en place ; utiliser une gestion de clés appropriée. 
+* Chiffrer toutes les données en transit avec des protocoles &gt;= TLS 1.2 uniquement, avec des chiffrements de secret direct (FS), supprimer le support des chiffrements en chaîne de blocs de chiffrement (CBC), supporter les algorithmes de changement de clé quantique. Pour HTTPS, appliquer le chiffrement en utilisant HTTP Strict Transport Security (HSTS). Tout vérifier avec un outil. 
+* Désactivez la mise en cache pour les réponses contenant des données sensibles. Cela inclut la mise en cache dans votre CDN, votre serveur web et toute mise en cache d’application (par exemple : Redis). 
+* Appliquer les contrôles de sécurité requis selon la classification des données. 
+* N’utilisez pas de protocoles non chiffrés tels que FTP et STARTTLS. Évitez d’utiliser SMTP pour transmettre des données confidentielles. 
+* Stockez les mots de passe à l’aide de fonctions de hachage adaptatives fortes et salées avec un facteur de travail (facteur de retard), telles qu’Argon2, yescrypt, scrypt ou PBKDF2-HMAC-SHA-512. Pour les systèmes hérités utilisant bcrypt, obtenez plus de conseils sur [OWASP Cheat Sheet : Password Storage](https://cheatsheetseries.owasp.org/cheatsheets/Password_Storage_Cheat_Sheet.html)
+* Les vecteurs d’initialisation doivent être choisis en fonction du mode de fonctionnement. Cela peut signifier utiliser un CSPRNG (générateur de nombres pseudo aléatoires cryptographiquement sécurisé). Pour les modes nécessitant un nonce, le vecteur d’initialisation (IV) n’a pas besoin de CSPRNG. Dans tous les cas, l’IV ne doit jamais être utilisé deux fois pour une clé fixe. 
+* Utilisez toujours un chiffrement authentifié au lieu de simplement le chiffrement.
+* Les clés doivent être générées de manière cryptographique aléatoire et stockées en mémoire sous forme de tableaux d’octets. Si un mot de passe est utilisé, il doit alors être converti en clé via une fonction de dérivation de clé de base appropriée. 
+* S’assurer que l’aléa cryptographique est utilisée lorsque cela est approprié et qu’elle n’a pas été ensemencée de manière prévisible ou avec une faible entropie. La plupart des API modernes n’exigent pas que le développeur ensemence le CSPRNG pour être sécurisé. 
+* Éviter les fonctions cryptographiques obsolètes, les méthodes de construction de blocs et les schémas de remplissage, tels que MD5, SHA1, Cipher Block Chaining Mode (CBC), PKCS numéro 1 v1.5. 
+* Assurez-vous que les paramètres et configurations respectent les exigences de sécurité en les faisant examiner par des spécialistes de la sécurité, des outils conçus à cet effet, ou les deux. 
+* Vous devez vous préparer dès maintenant à la cryptographie post-quantique (PQC), voir référence (ENISA) afin que les systèmes à haut risque soient sûrs au plus tard fin 2030.
+## Exemples de scénarios d’attaque
+**Scénario #1** : Un site n’utilise pas et n’applique pas le TLS pour toutes les pages et ne supporte pas un chiffrement faible. Un attaquant surveille le trafic réseau (par exemple, sur un réseau sans fil non sécurisé), rétrograde les connexions de HTTPS à HTTP, intercepte les requêtes et vole le cookie de session de l’utilisateur. L’attaquant rejoue ensuite ce cookie et détourne la session (authentifiée) de l’utilisateur, accédant ou modifiant les données privées de l’utilisateur. Au lieu de ce qui précède, il pourrait modifier toutes les données transportées, par exemple le destinataire d’un transfert d’argent. 
+**Scénario #2** : La base de données de mots de passe utilise des hachages non salés ou simples pour stocker les mots de passe de chacun. Une faille de téléchargement de fichier permet à un attaquant de récupérer la base de mots de passe. Tous les hachages non salés peuvent être exposés avec une table arc-en-ciel de hachages pré-calculés. Les hachages générés par des fonctions de hachage simples ou rapides peuvent être cassés par des GPU, même s’ils ont été salés. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A04_2025-Cryptographic_Failures/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;37
+   &lt;/td&gt;
+   &lt;td&gt;13,77 % 
+   &lt;/td&gt;
+   &lt;td&gt;3,08 % 
+   &lt;/td&gt;
+   &lt;td&gt;100,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;42,93 % 
+   &lt;/td&gt;
+   &lt;td&gt;7.15
+   &lt;/td&gt;
+   &lt;td&gt;4.32
+   &lt;/td&gt;
+   &lt;td&gt;1 404 249
+   &lt;/td&gt;
+   &lt;td&gt;62 445
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+Le meilleur moyen d’éviter l’injection consiste à séparer les données des commandes et requêtes : 
+* L’option préférée est d’utiliser une API sécurisée, qui évite complètement d’utiliser l’interpréteur, fournit une interface paramétrée ou migre vers des outils de cartographie relationnelle d’objets (ORM).  
+**Note :** Même paramétrés, les procédures stockées peuvent encore introduire l’injection SQL si PL/SQL ou T-SQL concaténe requêtes et données ou exécute des données hostiles avec EXECUTE IMMEDIATE ou exec(). 
+Lorsqu’il n’est pas possible de séparer les données des commandes, vous pouvez réduire les menaces en utilisant les techniques suivantes.  
+* Utilisez une validation d’entrée positive côté serveur. Ce n’est pas une défense complète car de nombreuses applications nécessitent des caractères spéciaux, tels que des zones de texte ou des API pour les applications mobiles. 
+* Pour toute requête dynamique résiduelle, échappez les caractères spéciaux en utilisant la syntaxe d’échappement spécifique de cet interpréteur.  
+**Note :** Les structures SQL telles que les noms de tables, les noms de colonnes, etc., ne peuvent pas être contournées, et donc les noms de structures fournis par l’utilisateur sont dangereux. C’est un problème courant dans les logiciels de rédaction de rapports. 
+**Attention** ces techniques impliquent l’analyse et l’évacuation de chaînes complexes, les rendant sujettes à l’erreur et peu robustes face à de légers changements du système sous-jacent.
+## Exemples de scénarios d’attaque
+**Scénario #1 :** Une application utilise des données non fiables dans la construction de l’appel SQL vulnérable suivant : 
+```
+Requête de chaîne = « SELECT * FROM accounts WHERE custID=' » + request.getParameter(« id ») + « ' » ; 
+```
+Un attaquant modifie la valeur du paramètre 'id' dans son navigateur pour envoyer : '' OU '1'='1'. Par exemple : 
+```
+http://example.com/app/accountView?id=' OU '1'='1
+```
+Cela modifie la signification de la requête pour retourner tous les enregistrements de la table des comptes. Des attaques plus dangereuses pourraient modifier ou supprimer des données, voire invoquer des procédures stockées. 
+**Scénario #2 :** La confiance aveugle d’une application dans les frameworks peut entraîner des requêtes qui restent vulnérables. Par exemple, Hibernate Query Language (HQL) : 
+```
+Requête HQLQuery = session.createQuery(« FROM accounts WHERE custID=' » + request.getParameter(« id ») + « ' ») ; 
+```
+Un attaquant fournit : « OR custID N’EST PAS NULL ni custID = ''. Cela contourne le filtre et renvoie tous les comptes. Bien que HQL ait moins de fonctions dangereuses que SQL brut, il permet toujours un accès non autorisé aux données lorsque les saisies de l’utilisateur sont concaténées en requêtes. 
+**Scénario #3 :** Une application transmet directement l’entrée utilisateur à une commande du système d’exploitation : 
+```
+String cmd = « nslookup " + request.getParameter(« domain ») ; 
+Runtime.getRuntime().exec(cmd) ; 
+```
+Un attaquant fournit des commandes arbitraires de type « example.com ; cat /etc/passwd » pour exécuter des commandes arbitraires sur le serveur. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A05_2025-Injection/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;36
+   &lt;/td&gt;
+   &lt;td&gt;15,80 % 
+   &lt;/td&gt;
+   &lt;td&gt;2,92 % 
+   &lt;/td&gt;
+   &lt;td&gt;100,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;37,14 % 
+   &lt;/td&gt;
+   &lt;td&gt;7,69
+   &lt;/td&gt;
+   &lt;td&gt;4,44
+   &lt;/td&gt;
+   &lt;td&gt;1 120 673
+   &lt;/td&gt;
+   &lt;td&gt;7 147
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+* Lorsque possible, implémenter et faire respecter l’utilisation de l’authentification multifactorielle pour prévenir le bourrage automatisé des identifiants, la force brute et les attaques de réutilisation de crédents volées. 
+* Lorsque possible, encourager et activer l’utilisation de gestionnaires de mots de passe pour aider les utilisateurs à faire de meilleurs choix. 
+* Ne pas livrer ni déployer avec des identifiants par défaut, en particulier pour les utilisateurs administrateurs. 
+* Mettre en place des vérifications de mots de passe faibles, comme tester de nouveaux mots de passe ou modifiés dans la liste des 10 000 pires mots de passe. 
+* Lors de la création d’un nouveau compte et des changements de mot de passe, validez contre les listes d’identifiants connus pour violation (par exemple : utiliser [haveibeenpwned.com](https://haveibeenpwned.com)). 
+* Aligner les politiques de longueur, de complexité et de rotation des mots de passe avec les directives du [National Institute of Standards and Technology (NIST) 800-63b dans la section 5.1.1] (https://pages.nist.gov/800-63-3/sp800-63b.html#:~:text=5.1.1%20Memorized%20Secrets) pour les secrets mémorisés ou d’autres politiques modernes fondées sur des mots de passe fondées sur des preuves. 
+* Ne forcez pas les êtres humains à faire tourner les mots de passe sauf si vous suspectez une faille. Si vous soupçonnez une fuite, forcez immédiatement la réinitialisation du mot de passe.  
+* S’assurer que l’enregistrement, la récupération des identifiants et les voies API sont renforcés contre les attaques d’énumération de comptes en utilisant les mêmes messages pour tous les résultats (« Nom d’utilisateur ou mot de passe invalides. »). 
+* Limiter ou retarder de plus en plus les tentatives de connexion ratées, mais veillez à ne pas créer un scénario de déni de service. Consignez toutes les défaillances et alertez les administrateurs lorsque des attaques de type « credentialsal stuffing, de force brute » ou d’autres attaques sont détectées ou suspectées. 
+* Utiliser un gestionnaire de session intégré sécurisé côté serveur qui génère un nouvel ID de session aléatoire avec une forte entropie après la connexion. Les identifiants de session ne doivent pas être dans l’URL, être stockés de manière sécurisée dans un cookie sécurisé, et invalidés après déconnexion, inactivité et délais absolus.  
+* Idéalement, utiliser un système préfabriqué et bien fiable pour gérer l’authentification, l’identité et la gestion des sessions. Transférez ce risque autant que possible en achetant et en utilisant un système renforcé et bien testé. 
+* Vérifier l’utilisation prévue des identifiants fournis, par exemple pour les JWT, valider les affirmations « aud », « iss » et les périmètres
+## Exemples de scénarios d’attaque
+**Scénario #1 :** Le remplissage de crédentiaux, l’utilisation de listes de combinaisons de noms d’utilisateur et de mots de passe connus, est désormais une attaque très courante. Plus récemment, les attaquants ont été observés « incrémentant » ou ajustant autrement les mots de passe, en fonction du comportement humain courant. Par exemple, changer « Winter2025 » en « Hiver 2026 », ou « ILoveMyDog6 » en « ILoveMyDog7 » ou « ILoveMyDog5 ». Cet ajustement des tentatives de mot de passe est appelé attaque hybride de remplissage de crédibles ou attaque par pulvérisation de mots de passe, et ils peuvent être encore plus efficaces que la version traditionnelle. Si une application ne met pas en place de défenses contre les menaces automatisées (force brute, scripts ou bots) ou bourrage de crédents, l’application peut être utilisée comme oracle de mot de passe pour déterminer si les identifiants sont valides et obtenir un accès non autorisé. 
+**Scénario #2 :** La plupart des attaques d’authentification réussies surviennent en raison de l’utilisation continue des mots de passe comme seul facteur d’authentification. Une fois considérées comme les meilleures pratiques, la rotation des mots de passe et les exigences de complexité encouragent les utilisateurs à réutiliser les mots de passe et à utiliser des mots de passe faibles. Il est recommandé aux organisations d’arrêter ces pratiques conformément au NIST 800-63 et d’imposer l’utilisation de l’authentification multifacteur sur tous les systèmes importants. 
+**Scénario #3 :** Les délais d’expiration des sessions d’application ne sont pas correctement implémentés. Un utilisateur utilise un ordinateur public pour accéder à une application et au lieu de sélectionner « déconnexion », il ferme simplement l’onglet du navigateur et s’en va. Un autre exemple est si une session de connexion unique (SSO) ne peut pas être fermée par un seul déconnexion (SLO). C’est-à-dire qu’une seule connexion vous connecte, par exemple, à votre lecteur de messagerie, à votre système de documents et à votre système de chat. Mais la déconnexion ne se produit qu’au système actuel. Si un attaquant utilise le même navigateur après que la victime pense s’être déconnectée avec succès, mais avec l’utilisateur toujours authentifié sur certaines applications, il peut alors accéder au compte de la victime. Le même problème peut survenir dans les bureaux et les entreprises lorsqu’une application sensible n’a pas été correctement fermée et qu’un collègue a un accès (temporaire) à l’ordinateur déverrouillé. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A07_2025-Authentication_Failures/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;14
+   &lt;/td&gt;
+   &lt;td&gt;8,98 % 
+   &lt;/td&gt;
+   &lt;td&gt;2,75 % 
+   &lt;/td&gt;
+   &lt;td&gt;78,52 % 
+   &lt;/td&gt;
+   &lt;td&gt;45,49 % 
+   &lt;/td&gt;
+   &lt;td&gt;7.11
+   &lt;/td&gt;
+   &lt;td&gt;4,79
+   &lt;/td&gt;
+   &lt;td&gt;501 327
+   &lt;/td&gt;
+   &lt;td&gt;3 331
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+* Utilisez des signatures numériques ou des mécanismes similaires pour vérifier que le logiciel ou les données proviennent de la source attendue et n’ont pas été modifiés. 
+* Assurez-vous que les bibliothèques et dépendances, telles que npm ou Maven, ne consomment que des dépôts fiables. Si votre profil de risque est plus élevé, envisagez d’héberger un dépôt interne de bien connu qui est vérifié. 
+* Assurez-vous qu’un processus de révision des modifications de code et de configuration est en place afin de minimiser le risque que du code ou une configuration malveillante soit introduit dans votre pipeline logiciel. 
+* Assurez-vous que votre pipeline CI/CD dispose d’une ségrégation, d’une configuration et d’un contrôle d’accès appropriés afin d’assurer l’intégrité du code circulant dans les processus de compilation et de déploiement. 
+* S’assurer que les données sérialisées non signées ou non chiffrées ne sont pas reçues de clients non fiables et utilisées par la suite sans aucune forme de vérification d’intégrité ou de signature numérique pour détecter toute falsification ou relecture des données sérialisées.
+## Exemples de scénarios d’attaque
+**Scénario #1 Inclusion de fonctionnalités Web provenant d’une source non fiable :** Une entreprise utilise un fournisseur de services externe pour fournir des fonctionnalités de support. Pour plus de commodité, elle dispose d’une correspondance DNS pour « myCompany.SupportProvider.com » vers « support.myCompany.com ». Cela signifie que tous les cookies, y compris ceux d’authentification, définis sur le domaine « myCompany.com » seront désormais envoyés au fournisseur de support. Toute personne ayant accès à l’infrastructure du fournisseur de support peut voler les cookies de tous vos utilisateurs ayant visité « support.myCompany.com » et effectuer une attaque de détournement de session. 
+**Scénario #2 Mise à jour sans signature :** De nombreux routeurs domestiques, décodeurs, firmwares d’appareils et autres ne vérifient pas les mises à jour via un firmware signé. Le firmware non signé est une cible croissante pour les attaquants et devrait ne faire qu’empirer. C’est une préoccupation majeure car il n’existe souvent aucun mécanisme à remédier autre que de corriger dans une version future et d’attendre que les versions précédentes se dépassent. 
+**Scénario #3 Utilisation d’un paquet à partir d’une source non fiable :** Un développeur a du mal à trouver la version mise à jour d’un paquet qu’il recherche, il la télécharge donc non pas depuis le gestionnaire de paquets fiable classique, mais depuis un site web en ligne. Le paquet n’est pas signé, et il n’y a donc aucune possibilité d’en garantir l’intégrité. Le paquet inclut du code malveillant. 
+**Scénario #4 Désérialisation insécurisée :** Une application React appelle un ensemble de microservices Spring Boot. En tant que programmeurs fonctionnels, ils ont essayé de s’assurer que leur code reste immuable. La solution qu’ils ont trouvée est de sérialiser l’état utilisateur et de le transmettre à chaque requête. Un attaquant remarque la signature d’objet Java « rO0 » (en base64) et utilise le [Java Deserialization Scanner](https://github.com/federicodotta/Java-Deserialization-Scanner) pour obtenir une exécution de code à distance sur le serveur d’applications. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A08_2025-Software_or_Data_Integrity_Failures/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20,67 % 
+   &lt;/td&gt;
+   &lt;td&gt;2,95 % 
+   &lt;/td&gt;
+   &lt;td&gt;100,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;37,95 % 
+   &lt;/td&gt;
+   &lt;td&gt;7.11
+   &lt;/td&gt;
+   &lt;td&gt;3.81
+   &lt;/td&gt;
+   &lt;td&gt;769 581
+   &lt;/td&gt;
+   &lt;td&gt;3 416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+Pour gérer correctement une condition exceptionnelle, nous devons planifier de telles situations (attendez-vous au pire). Nous devons « détecter » chaque erreur système possible directement à l’endroit où elle survient puis la traiter (ce qui signifie faire quelque chose de significatif pour résoudre le problème et nous assurer de nous en remettre). Dans le cadre de la gestion, nous devrions inclure l’envoi d’une erreur (pour informer l’utilisateur de manière compréhensible), la consignation de l’événement, ainsi que l’émission d’une alerte si cela est justifié. Nous devrions également avoir un gestionnaire global d’exceptions en place au cas où quelque chose serait manqué. Idéalement, nous aurions aussi des outils ou fonctionnalités de surveillance et/ou d’observabilité qui surveillent les erreurs répétées ou les schémas indiquant une attaque en cours, qui pourrait fournir une réponse, une défense ou un blocage quelconque. Cela peut nous aider à bloquer et à répondre aux scripts et bots qui se concentrent sur nos faiblesses en gestion des erreurs. 
+Détecter et gérer des conditions exceptionnelles garantit que l’infrastructure sous-jacente de nos programmes ne doit pas gérer des situations imprévisibles. Si vous êtes en cours de transaction de quelque nature que ce soit, il est extrêmement important de revenir en arrière sur chaque partie de la transaction et de recommencer (ce qu’on appelle également échec de clôture). Tenter de récupérer une transaction en cours de route est souvent l’occasion de créer des erreurs irrémédiables. 
+Dans la mesure du possible, ajoutez des limites de vitesse, des quotas de ressources, des limitations de puissance et d’autres limites autant que possible, pour prévenir des conditions exceptionnelles dès le départ. Rien dans les technologies de l’information ne devrait être illimité, car cela conduit à un manque de résilience des applications, au déni de service, à des attaques par force brute réussies et à des factures cloud extraordinaires. 
+Considérez si des erreurs répétées identiques, au-delà d’un certain débit, ne doivent être produites que sous forme de statistiques montrant la fréquence et dans quel délai ils se sont produits. Ces informations doivent être ajoutées au message original afin de ne pas interférer avec la journalisation et la surveillance automatisées, voir [A09:2025 Défaillances de journalisation et alertes de sécurité](A09_2025-Security_Logging_and_Alerting_Failures.md).
+En plus de cela, nous voudrions inclure une validation stricte des entrées (avec nettoyage ou échappement pour les caractères potentiellement dangereux que nous devons accepter), une gestion centralisée des erreurs, la journalisation, la surveillance et l’alerte, ainsi qu’un gestionnaire global d’exceptions. Une application ne doit pas avoir plusieurs fonctions pour gérer des conditions exceptionnelles, elle doit être effectuée en un seul endroit, de la même manière à chaque fois. Nous devrions également créer des exigences de sécurité du projet pour tous les conseils de cette section, effectuer la modélisation des menaces et/ou des activités de revue de conception sécurisée lors de la phase de conception de nos projets, effectuer des revues de code ou des analyses statiques, ainsi que réaliser des tests de stress, de performance et d’intrusion du système final. 
+Si possible, toute votre organisation devrait gérer les conditions exceptionnelles de la même manière, car cela facilite la relecture et l’audit du code pour détecter des erreurs dans ce contrôle de sécurité important.
+## Exemples de scénarios d’attaque
+**Scénario #1 : Une épuisement des ressources dû à une mauvaise gestion de conditions exceptionnelles (déni de service) peut être causé si l’application détecte des exceptions lors du téléchargement des fichiers, mais ne libère pas correctement les ressources ensuite. Chaque nouvelle exception laisse les ressources bloquées ou indisponibles, jusqu’à ce que toutes les ressources soient épuisées. 
+**Scénario #2 :** Exposition de données sensibles via une mauvaise gestion ou des erreurs de base de données qui révèlent l’erreur système complète à l’utilisateur. L’attaquant continue de forcer des erreurs afin d’utiliser les informations sensibles du système pour créer une meilleure attaque d’injection SQL. Les données sensibles dans les messages d’erreur utilisateur sont de la reconnaissance. 
+**Scénario #3 :** La corruption d’état dans les transactions financières pourrait être causée par un attaquant interrompant une transaction en plusieurs étapes via des perturbations réseau. Imaginez que l’ordre de la transaction soit : débiter un compte utilisateur, créditer le compte de destination, enregistrer la transaction. Si le système ne revient pas correctement sur l’intégralité de la transaction (échec fermé) en cas d’erreur en cours de route, l’attaquant pourrait potentiellement vider le compte de l’utilisateur, ou peut-être une condition de course permettant à l’attaquant d’envoyer de l’argent à destination plusieurs fois. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;6
+   &lt;/td&gt;
+   &lt;td&gt;9,56 % 
+   &lt;/td&gt;
+   &lt;td&gt;5,72 % 
+   &lt;/td&gt;
+   &lt;td&gt;65,42 % 
+   &lt;/td&gt;
+   &lt;td&gt;27,47 % 
+   &lt;/td&gt;
+   &lt;td&gt;8.17
+   &lt;/td&gt;
+   &lt;td&gt;5.23
+   &lt;/td&gt;
+   &lt;td&gt;215 248
+   &lt;/td&gt;
+   &lt;td&gt;11
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+Il devrait y avoir un processus de gestion des correctifs pour : 
+* Générer et gérer centralisément la liste des documents logiciels (SBOM) de l’ensemble de votre logiciel. 
+* Suivre non seulement vos dépendances directes, mais aussi leurs dépendances (transitives), et ainsi de suite. 
+* Réduire la surface d’attaque en supprimant les dépendances inutilisées, les fonctionnalités, les composants, les fichiers et la documentation inutiles. 
+* Inventorier continuellement les versions des composants côté client et côté serveur (par exemple, frameworks, bibliothèques) et leurs dépendances à l’aide d’outils comme OWASP Dependency Track, OWASP Dependency Check, retire.js, etc. 
+* Surveillez en continu des sources telles que Common Vulnerability and Exposures (CVE), National Vulnerability Database (NVD) et [Open Source Vulnerabilities (OSV)](https://osv.dev/) pour les vulnérabilités des composants que vous utilisez. Utilisez l’analyse de composition logicielle, la chaîne d’approvisionnement logicielle ou des outils SBOM axés sur la sécurité pour automatiser le processus. Abonnez-vous aux alertes concernant les vulnérabilités de sécurité liées aux composants que vous utilisez. 
+* N’obtenir les composants que de sources officielles (fiables) via des liens sécurisés. Privilégier les paquets signés pour réduire le risque d’inclure un composant modifié et malveillant (voir [A08:2025 - Défaillances d’intégrité logicielle et des données](https://owasp.org/Top10/2025/A08_2025-Software_or_Data_Integrity_Failures/)). 
+* Choisissez délibérément la version d’une dépendance que vous utilisez et ne mettez à jour que lorsqu’il y a un besoin. 
+* Surveillez les bibliothèques et composants non maintenus ou qui ne créent pas de correctifs de sécurité pour les versions précédentes. Si le patch n’est pas possible, envisagez de migrer vers une alternative. Si cela n’est pas possible, envisagez de déployer un correctif virtuel pour surveiller, détecter ou protéger contre le problème découvert. 
+* Mettez régulièrement à jour votre CI/CD, IDE et tout autre outil de développement
+* Éviter de déployer des mises à jour simultanément sur tous les systèmes. Utiliser des déploiements par étapes ou des déploiements canari pour limiter l’exposition au cas où un fournisseur de confiance serait compromis. 
+Il devrait y avoir un processus de gestion des changements ou un système de suivi pour suivre les modifications sur :
+* Paramètres CI/CD (tous les outils de compilation et pipelines)
+* Dépôts de code
+* Zones de bac à sable
+* IDE développeurs
+* Outils SBOM et artefacts créés
+* Systèmes de journalisation et journaux
+* Intégrations tierces, telles que le SaaS
+* Dépôts d’artefacts
+* Registres de conteneurs
+Renforcez les systèmes suivants, ce qui inclut la mise en service de la MFA et la fermeture de l’IAM : 
+* Votre dépôt de code (ce qui inclut de ne pas vérifier les secrets, protéger les branches, sauvegarder)
+* Stations de travail développeurs (correctifs réguliers, MFA, surveillance, et plus encore)
+* Votre serveur de compilation &amp; CI/CD (séparation des fonctions, contrôle d’accès, compilations signées, secrets à portée d’environnement, journaux inviolables, plus encore)
+* Vos artefacts (assurez l’intégrité via la provenance, la signature et l’horodatage, promouvez les artefacts plutôt que les reconstruisez pour chaque environnement, assurez-vous que les builds restent immuables)
+* Infrastructure en tant que code (géré comme tout le code, y compris l’utilisation des PR et le contrôle de versions)
+Chaque organisation doit s’assurer d’un plan continu pour la surveillance, le tri et l’application des mises à jour ou modifications de configuration tout au long de la durée de vie de l’application ou du portefeuille.
+## Exemples de scénarios d’attaque
+**Scénario #1 :** Un fournisseur de confiance est compromis par des logiciels malveillants, ce qui entraîne la compromission de vos systèmes informatiques lors de la mise à jour. L’exemple le plus célèbre est probablement : 
+* Le compromis SolarWinds de 2019 qui a conduit à la compromission de ~18 000 organisations. [https://www.npr.org/2021/04/16/985439655/a-worst-nightmare-cyberattack-the-untold-story-of-the-solarwinds-hack] (https://www.npr.org/2021/04/16/985439655/a-worst-nightmare-cyberattack-the-untold-story-of-the-solarwinds-hack)
+**Scénario #2 :** Un fournisseur de confiance est compromis au point de ne se comporter de manière malveillante que dans une condition spécifique. 
+* Le vol de 1,5 milliard de dollars par Bybit en 2025 a été causé par [une attaque de chaîne d’approvisionnement dans un logiciel de portefeuille](https://www.sygnia.co/blog/sygnia-investigation-bybit-hack/) qui ne s’est exécutée que lorsque le portefeuille cible était utilisé. 
+**Scénario #3 :** L’attaque de chaîne d’approvisionnement ['Shai-Hulud'](https://www.cisa.gov/news-events/alerts/2025/09/23/widespread-supply-chain-compromise-impacting-npm-ecosystem) en 2025 a été le premier ver npm auto-propagant réussi. Les attaques ont semé des versions malveillantes de paquets populaires, qui utilisaient un script post-installation pour récolter et exfiltrer des données sensibles vers des dépôts publics GitHub. Le malware détectait également les jetons npm dans l’environnement victime et les utilisait automatiquement pour diffuser des versions malveillantes de tout package accessible. Le ver a atteint plus de 500 versions de paquets avant d’être perturbé par npm. Cette attaque de chaîne d’approvisionnement était avancée, se propageait rapidement et causait des dommages, et en ciblant les machines développeurs, elle a démontré que les développeurs eux-mêmes sont désormais des cibles principales pour les attaques de la chaîne d’approvisionnement. 
+**Scénario #4 :** Les composants fonctionnent généralement avec les mêmes privilèges que l’application elle-même, donc des défauts dans n’importe quel composant peuvent avoir un impact sérieux. Ces défauts peuvent être accidentels (par exemple, une erreur de codage) ou intentionnels (par exemple, une porte dérobée dans un composant). Voici quelques exemples de vulnérabilités exploitables de composants découverts : 
+* CVE-2017-5638, une vulnérabilité d’exécution de code à distance Struts 2 qui permet l’exécution de code arbitraire sur le serveur, a été tenue responsable de violations importantes. 
+* CVE-2021-44228 (« Log4Shell »), une vulnérabilité zero-day d’exécution de code à distance Apache Log4j, a été tenue responsable de campagnes de ransomware, de cryptominage et d’autres attaques. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A03_2025-Software_Supply_Chain_Failures/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;39
+   &lt;/td&gt;
+   &lt;td&gt;22,18 % 
+   &lt;/td&gt;
+   &lt;td&gt;1,86 % 
+   &lt;/td&gt;
+   &lt;td&gt;88,76 % 
+   &lt;/td&gt;
+   &lt;td&gt;35,18 % 
+   &lt;/td&gt;
+   &lt;td&gt;6,96
+   &lt;/td&gt;
+   &lt;td&gt;4,05
+   &lt;/td&gt;
+   &lt;td&gt;729 882
+   &lt;/td&gt;
+   &lt;td&gt;7 647
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+* Établir et utiliser un cycle de développement sécurisé avec des professionnels AppSec pour aider à évaluer et concevoir des contrôles liés à la sécurité et à la confidentialité
+* Établir et utiliser une bibliothèque de modèles de conception sécurisés ou de composants de routes pavées
+* Utiliser la modélisation des menaces pour des parties critiques de l’application telles que l’authentification, le contrôle d’accès, la logique métier et les flux de clés
+* Utiliser la modélisation des menaces comme outil éducatif pour générer un état d’esprit de sécurité
+* Intégrer le langage de sécurité et les contrôles dans les histoires utilisateur
+* Intégrer des vérifications de plausibilité à chaque niveau de votre application (du frontend au backend)
+* Écrire des tests unitaires et d’intégration pour valider que tous les flux critiques sont résistants au modèle de menace. Compiler les cas d’utilisation *et* les cas d’utilisation inappropriés pour chaque niveau de votre application. 
+* Séparer les couches de niveaux sur le système et les couches réseau, en fonction des besoins d’exposition et de protection
+* Séparer les locataires de manière rigoureuse par conception sur tous les niveaux
+## Exemples de scénarios d’attaque
+**Scénario #1 :** Un flux de travail de récupération d’identifiants peut inclure des « questions et réponses », ce qui est interdit par le NIST 800-63b, l’OWASP ASVS et le OWASP Top 10. Les questions et réponses ne peuvent pas être dignes de confiance comme preuve d’identité, car plus d’une personne peut connaître les réponses. De telles fonctionnalités doivent être supprimées et remplacées par une conception plus sécurisée. 
+**Scénario #2 :** Une chaîne de cinémas permet des réductions de réservation de groupe et compte un maximum de quinze participants avant de devoir payer un acompte. Les attaquants pourraient modéliser ce flux de menaces et tester s’ils peuvent trouver un vecteur d’attaque dans la logique métier de l’application, par exemple réserver six cents sièges et tous les cinémas en même temps en quelques requêtes, entraînant une perte massive de revenus. 
+**Scénario #3 :** Le site e-commerce d’une chaîne de distribution ne dispose pas de protection contre les bots gérés par des revendeurs achetant des cartes vidéo haut de gamme pour les revendre sur des sites d’enchères. Cela crée une mauvaise publicité pour les fabricants de cartes vidéo et les propriétaires de chaînes de détail, et endure des tensions avec les passionnés qui ne peuvent obtenir ces cartes à aucun prix. Des règles strictes de conception anti-bots et de logique de domaine, comme les achats effectués dans quelques secondes de disponibilité, peuvent identifier des achats inauthentiques et rejeter ces transactions. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A06_2025-Insecure_Design/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;5
+   &lt;/td&gt;
+   &lt;td&gt;11,33 % 
+   &lt;/td&gt;
+   &lt;td&gt;3,91 % 
+   &lt;/td&gt;
+   &lt;td&gt;85,96 % 
+   &lt;/td&gt;
+   &lt;td&gt;46,48 % 
+   &lt;/td&gt;
+   &lt;td&gt;7.19
+   &lt;/td&gt;
+   &lt;td&gt;2,65
+   &lt;/td&gt;
+   &lt;td&gt;260 288
+   &lt;/td&gt;
+   &lt;td&gt;723
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+Les développeurs doivent implémenter certains ou tous les contrôles suivants, selon le risque de l’application : 
+* S’assurer que toutes les défaillances de connexion, de contrôle d’accès et de validation d’entrée côté serveur peuvent être enregistrées avec suffisamment de contexte utilisateur pour identifier les comptes suspects ou malveillants et conservées suffisamment longtemps pour permettre une analyse médico-légale retardée. 
+* Assurez-vous que chaque partie de votre application contenant un contrôle de sécurité est enregistrée, qu’elle réussisse ou non. 
+* S’assurer que les journaux sont générés dans un format que les solutions de gestion des journaux peuvent facilement consommer. 
+* S’assurer que les données de journal sont correctement encodées pour éviter les injections ou attaques sur les systèmes de journalisation ou de surveillance. 
+* Veiller à ce que toutes les transactions disposent d’une trace d’audit avec des contrôles d’intégrité pour éviter toute altération ou suppression, comme des tables de base de données à ajout uniquement ou autres. 
+* Assurez-vous que toutes les transactions qui génèrent une erreur soient annulées et recommencées. Échouez toujours à la clôture. 
+* Si votre application ou ses utilisateurs se comportent de manière suspecte, lancez une alerte. Créez des conseils pour vos développeurs sur ce sujet afin qu’ils puissent coder contre cela ou acheter un système pour cela. 
+* Les équipes DevSecOps et de sécurité doivent établir des cas d’utilisation efficaces de surveillance et d’alerte, y compris des playbooks afin que les activités suspectes soient détectées et traitées rapidement par l’équipe du Centre des Opérations de Sécurité (SOC). 
+* Ajoutez des « honeytokens » comme pièges pour les attaquants dans votre application, par exemple dans la base de données, les données, comme identité utilisateur réelle et/ou technique. Comme ils ne sont pas utilisés dans les affaires normales, tout accès génère des données de journalisation pouvant être alertées avec presque aucun faux positif. 
+* L’analyse comportementale et le support de l’IA pourraient être optionnellement une technique supplémentaire pour supporter de faibles taux de faux positifs lors des alertes. 
+* Établir ou adopter un plan de réponse et de rétablissement aux incidents, tel que le National Institute of Standards and Technology (NIST) 800-61r2 ou ultérieur. Enseignez à vos développeurs logiciels à quoi ressemblent les attaques et incidents d’applications, afin qu’ils puissent les signaler. 
+Il existe des produits commerciaux et open source de protection d’applications tels que le Mod Security Core Rule Set OWASP, ainsi que des logiciels open source de corrélation de journaux, tels que la pile Elasticsearch, Logstash, Kibana (ELK), qui proposent des tableaux de bord personnalisés et des alertes pouvant vous aider à lutter contre ces problèmes. Il existe également des outils commerciaux d’observabilité qui peuvent vous aider à répondre ou bloquer des attaques en temps quasi réel.
+## Exemples de scénarios d’attaque
+**Scénario #1 :** L’opérateur du site web d’un fournisseur de régime de santé pour enfants n’a pas pu détecter une violation en raison d’un manque de surveillance et de registration. Une partie externe a informé le prestataire du régime de santé qu’un attaquant avait accédé et modifié des milliers de dossiers médicaux sensibles de plus de 3,5 millions d’enfants. Une revue post-incident a révélé que les développeurs du site n’avaient pas corrigé de vulnérabilités significatives. Comme il n’y avait ni journalisation ni surveillance du système, la violation de données pouvait être en cours depuis 2013, soit plus de sept ans. 
+**Scénario #2 :** Une grande compagnie aérienne indienne a subi une violation de données impliquant plus de dix ans de données personnelles de millions de passagers, y compris des données de passeports et de cartes de crédit. La violation de données s’est produite chez un fournisseur tiers d’hébergement cloud, qui a informé la compagnie aérienne après un certain temps. 
+**Scénario #3 :** Une grande compagnie aérienne européenne a subi une violation déclarable selon le RGPD. La violation aurait été causée par des vulnérabilités de sécurité des applications de paiement exploitées par des attaquants, qui ont collecté plus de 400 000 relevés de paiement clients. La compagnie aérienne a été condamnée à une amende de 20 millions de livres sterling par le régulateur de la vie privée. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A09_2025-Security_Logging_and_Alerting_Failures/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7960,9 +8631,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -7979,7 +8659,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -8013,31 +8693,900 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="39">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -8048,6 +9597,49 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4F4D3D0-A75A-471A-9225-F8FBA886F341}" name="Tableau1" displayName="Tableau1" ref="A1:AH11" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
+  <autoFilter ref="A1:AH11" xr:uid="{F4F4D3D0-A75A-471A-9225-F8FBA886F341}"/>
+  <tableColumns count="34">
+    <tableColumn id="1" xr3:uid="{20C696B3-F3A9-4D52-B31D-9D8663D1DB71}" name="ref_id" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{17243304-7DCB-4BF7-9986-F4AD97FC78CA}" name="name" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{8B25493F-0F71-4BFE-85D4-F5984D21AC75}" name="description" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{F56F0116-19FC-4FCD-A303-1A21A8C96E11}" name="annotation" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{3D791354-91A9-4E1D-BEF6-A9A5A8A22998}" name="name[fr]" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{D8DCB7EE-CBDD-49D5-9BD8-2FDCA39C2393}" name="description[fr]" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{B3212763-7D29-4002-9509-0ADAB8E947E0}" name="annotation[fr]" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{97365EF5-4239-4299-8A88-4B94639A030B}" name="name[cs]" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{9332F77D-1BDC-4F84-9FFD-52FAAB99C0D6}" name="description[cs]" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{259AA177-2D77-4278-8FBC-668F9B2E632E}" name="annotation[cs]" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{56D7B82C-687D-409F-BDAD-82FB932587E2}" name="name[de]" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{923C63BC-ED04-4B8A-A8B2-62773BBB809C}" name="description[de]" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{3AC976CC-F767-49B0-9D10-C0E5E8BE141B}" name="annotation[de]" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{6173A9C3-34B7-428E-B72A-37056E1C1EBD}" name="name[es]" dataDxfId="22"/>
+    <tableColumn id="15" xr3:uid="{8D73EF1A-F638-4F88-B122-97E698A8F65C}" name="description[es]" dataDxfId="21"/>
+    <tableColumn id="16" xr3:uid="{D5227CA4-120B-4DB8-A829-E6A25EA72E35}" name="annotation[es]" dataDxfId="20"/>
+    <tableColumn id="17" xr3:uid="{001384B1-5401-40FC-B7BC-8DAAD7B8ED9C}" name="name[fa]" dataDxfId="19"/>
+    <tableColumn id="18" xr3:uid="{366720CD-3CB7-4463-8EAB-99966D51FFE4}" name="description[fa]" dataDxfId="18"/>
+    <tableColumn id="19" xr3:uid="{120801F2-CF30-48AF-95EB-A5FE039DC1D9}" name="annotation[fa]" dataDxfId="17"/>
+    <tableColumn id="20" xr3:uid="{1B122668-F94F-4389-9D8D-AF7A2AD03138}" name="name[it]" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{591B41BA-0086-434F-9574-480FAD5AB0EE}" name="description[it]" dataDxfId="15"/>
+    <tableColumn id="22" xr3:uid="{DBB49242-33A4-4CE6-8CDC-78B1BD2F8FEB}" name="annotation[it]" dataDxfId="14"/>
+    <tableColumn id="23" xr3:uid="{6BDA09A6-219F-4E16-8511-3587DB546C6D}" name="name[ja]" dataDxfId="13"/>
+    <tableColumn id="24" xr3:uid="{36F23F53-D49E-42CC-8CA2-B27DC821694D}" name="description[ja]" dataDxfId="12"/>
+    <tableColumn id="25" xr3:uid="{3039A195-B467-4670-9FA1-5C386D80016E}" name="annotation[ja]" dataDxfId="11"/>
+    <tableColumn id="26" xr3:uid="{E0AC4B3E-211E-472C-9504-4AEDFF7647EC}" name="name[ko]" dataDxfId="10"/>
+    <tableColumn id="27" xr3:uid="{A7ED36D1-478D-434A-BEE9-093D928BC94F}" name="description[ko]" dataDxfId="9"/>
+    <tableColumn id="28" xr3:uid="{AC28BFD9-D5BE-40D9-81E4-E43731706E28}" name="annotation[ko]" dataDxfId="8"/>
+    <tableColumn id="29" xr3:uid="{0C382B30-4F63-4555-994F-52EA358D7FCE}" name="name[pt]" dataDxfId="7"/>
+    <tableColumn id="30" xr3:uid="{750FC0D5-9907-4470-8CFC-AC612C3999FE}" name="description[pt]" dataDxfId="6"/>
+    <tableColumn id="31" xr3:uid="{E340CC54-AE05-44BA-88C2-7E381DA7CAA2}" name="annotation[pt]" dataDxfId="5"/>
+    <tableColumn id="32" xr3:uid="{8EDE774A-6638-496F-9CE5-7270A55EFEC3}" name="name[zh]" dataDxfId="4"/>
+    <tableColumn id="33" xr3:uid="{13B7C29B-1ADE-4CA4-9203-3612E8567D23}" name="description[zh]" dataDxfId="3"/>
+    <tableColumn id="34" xr3:uid="{6B4F0FB1-ECB4-4D63-B0EE-75B41FA57863}" name="annotation[zh]" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8350,8 +9942,8 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="3" t="s">
         <v>366</v>
       </c>
     </row>
@@ -8663,1131 +10255,1154 @@
     <col min="34" max="34" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:34" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Z2" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AA2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AD2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AE2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AF2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AG2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AH2" s="8" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Q3" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="S3" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="T3" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="U3" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="V3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="W3" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="X3" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Y3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="Z3" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AA3" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AB3" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AC3" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AD3" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AE3" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AF3" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AG3" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AH3" s="8" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
+      <c r="G4" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="P4" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="R4" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="S4" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="T4" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="U4" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="V4" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="W4" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="X4" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Y4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="Z4" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AA4" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AB4" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AC4" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AD4" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="AE4" s="1" t="s">
+      <c r="AE4" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="AF4" s="1" t="s">
+      <c r="AF4" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="AG4" s="1" t="s">
+      <c r="AG4" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="AH4" s="1" t="s">
+      <c r="AH4" s="8" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
+      <c r="G5" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="P5" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="Q5" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="S5" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="T5" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="U5" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="V5" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="W5" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="X5" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="Y5" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="Z5" s="1" t="s">
+      <c r="Z5" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="AA5" s="1" t="s">
+      <c r="AA5" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="AB5" s="1" t="s">
+      <c r="AB5" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="AC5" s="1" t="s">
+      <c r="AC5" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AD5" s="1" t="s">
+      <c r="AD5" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="AE5" s="1" t="s">
+      <c r="AE5" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="AF5" s="1" t="s">
+      <c r="AF5" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="AG5" s="1" t="s">
+      <c r="AG5" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="AH5" s="1" t="s">
+      <c r="AH5" s="8" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
+      <c r="G6" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="O6" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="P6" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="Q6" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="R6" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="S6" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="T6" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="U6" s="1" t="s">
+      <c r="U6" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="V6" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="W6" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="X6" s="1" t="s">
+      <c r="X6" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="Y6" s="1" t="s">
+      <c r="Y6" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="Z6" s="1" t="s">
+      <c r="Z6" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="AA6" s="1" t="s">
+      <c r="AA6" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="AB6" s="1" t="s">
+      <c r="AB6" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AC6" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="AD6" s="1" t="s">
+      <c r="AD6" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="AE6" s="1" t="s">
+      <c r="AE6" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="AF6" s="1" t="s">
+      <c r="AF6" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="AG6" s="1" t="s">
+      <c r="AG6" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="AH6" s="1" t="s">
+      <c r="AH6" s="8" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
+      <c r="G7" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="O7" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="P7" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="Q7" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="R7" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="S7" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="T7" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="U7" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="V7" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="W7" s="1" t="s">
+      <c r="W7" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="X7" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="Y7" s="1" t="s">
+      <c r="Y7" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="Z7" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="AA7" s="1" t="s">
+      <c r="AA7" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="AB7" s="1" t="s">
+      <c r="AB7" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="AC7" s="1" t="s">
+      <c r="AC7" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="AD7" s="1" t="s">
+      <c r="AD7" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="AE7" s="1" t="s">
+      <c r="AE7" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="AF7" s="1" t="s">
+      <c r="AF7" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="AG7" s="1" t="s">
+      <c r="AG7" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="AH7" s="1" t="s">
+      <c r="AH7" s="8" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
+      <c r="G8" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="O8" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="P8" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="Q8" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="R8" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="S8" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="T8" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="U8" s="1" t="s">
+      <c r="U8" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="V8" s="1" t="s">
+      <c r="V8" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="W8" s="1" t="s">
+      <c r="W8" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="X8" s="1" t="s">
+      <c r="X8" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="Y8" s="1" t="s">
+      <c r="Y8" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="Z8" s="1" t="s">
+      <c r="Z8" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="AA8" s="1" t="s">
+      <c r="AA8" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="AB8" s="1" t="s">
+      <c r="AB8" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="AC8" s="1" t="s">
+      <c r="AC8" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="AD8" s="1" t="s">
+      <c r="AD8" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="AE8" s="1" t="s">
+      <c r="AE8" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="AF8" s="1" t="s">
+      <c r="AF8" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="AG8" s="1" t="s">
+      <c r="AG8" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="AH8" s="1" t="s">
+      <c r="AH8" s="8" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1" t="s">
+      <c r="G9" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="O9" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="P9" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="Q9" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="R9" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="S9" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="T9" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="U9" s="1" t="s">
+      <c r="U9" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="V9" s="1" t="s">
+      <c r="V9" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="W9" s="1" t="s">
+      <c r="W9" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="X9" s="1" t="s">
+      <c r="X9" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="Y9" s="1" t="s">
+      <c r="Y9" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="Z9" s="1" t="s">
+      <c r="Z9" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="AA9" s="1" t="s">
+      <c r="AA9" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="AB9" s="1" t="s">
+      <c r="AB9" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="AC9" s="1" t="s">
+      <c r="AC9" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="AD9" s="1" t="s">
+      <c r="AD9" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="AE9" s="1" t="s">
+      <c r="AE9" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="AF9" s="1" t="s">
+      <c r="AF9" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="AG9" s="1" t="s">
+      <c r="AG9" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="AH9" s="1" t="s">
+      <c r="AH9" s="8" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1" t="s">
+      <c r="G10" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="N10" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="O10" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="P10" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="Q10" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="R10" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="S10" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="T10" s="1" t="s">
+      <c r="T10" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="U10" s="1" t="s">
+      <c r="U10" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="V10" s="1" t="s">
+      <c r="V10" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="W10" s="1" t="s">
+      <c r="W10" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="X10" s="1" t="s">
+      <c r="X10" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="Y10" s="1" t="s">
+      <c r="Y10" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="Z10" s="1" t="s">
+      <c r="Z10" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="AA10" s="1" t="s">
+      <c r="AA10" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="AB10" s="1" t="s">
+      <c r="AB10" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="AC10" s="1" t="s">
+      <c r="AC10" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="AD10" s="1" t="s">
+      <c r="AD10" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AE10" s="1" t="s">
+      <c r="AE10" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="AF10" s="1" t="s">
+      <c r="AF10" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="AG10" s="1" t="s">
+      <c r="AG10" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="AH10" s="1" t="s">
+      <c r="AH10" s="8" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1" t="s">
+      <c r="G11" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="N11" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="O11" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="P11" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="Q11" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="R11" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="S11" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="T11" s="1" t="s">
+      <c r="T11" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="U11" s="1" t="s">
+      <c r="U11" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="V11" s="1" t="s">
+      <c r="V11" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="W11" s="1" t="s">
+      <c r="W11" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="X11" s="1" t="s">
+      <c r="X11" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="Y11" s="1" t="s">
+      <c r="Y11" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="Z11" s="1" t="s">
+      <c r="Z11" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="AA11" s="1" t="s">
+      <c r="AA11" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="AB11" s="1" t="s">
+      <c r="AB11" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="AC11" s="1" t="s">
+      <c r="AC11" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="AD11" s="1" t="s">
+      <c r="AD11" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="AE11" s="1" t="s">
+      <c r="AE11" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="AF11" s="1" t="s">
+      <c r="AF11" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="AG11" s="1" t="s">
+      <c r="AG11" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="AH11" s="1" t="s">
+      <c r="AH11" s="13" t="s">
         <v>365</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/tools/excel/owasp/owasp-top-10-web_2025.xlsx
+++ b/tools/excel/owasp/owasp-top-10-web_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\owasp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F5AF1F-7CFE-4CA5-8CC4-7BED21A95881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFADF6E-28B9-4AB5-BBFD-DF0876D2B2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30696" yWindow="-9720" windowWidth="22824" windowHeight="16344" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="398">
   <si>
     <t>type</t>
   </si>
@@ -202,9 +202,6 @@
   </si>
   <si>
     <t>base_urn</t>
-  </si>
-  <si>
-    <t>urn:intuitem:risk:owasp-top-10-web_2025</t>
   </si>
   <si>
     <t>annotation</t>
@@ -8617,6 +8614,42 @@
 **Scénario #3 :** Une grande compagnie aérienne européenne a subi une violation déclarable selon le RGPD. La violation aurait été causée par des vulnérabilités de sécurité des applications de paiement exploitées par des attaquants, qui ont collecté plus de 400 000 relevés de paiement clients. La compagnie aérienne a été condamnée à une amende de 20 millions de livres sterling par le régulateur de la vie privée. 
 Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A09_2025-Security_Logging_and_Alerting_Failures/</t>
   </si>
+  <si>
+    <t>urn:intuitem:risk:threat:owasp-top-10-web_2025</t>
+  </si>
+  <si>
+    <t>node_id</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
 </sst>
 </file>
 
@@ -8645,7 +8678,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8658,8 +8691,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -8697,57 +8742,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -8755,12 +8750,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -8772,9 +8763,7 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -8782,14 +8771,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8798,48 +8788,29 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="38">
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -8849,27 +8820,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8880,534 +8835,860 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill patternType="solid">
@@ -9420,20 +9701,32 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -9445,129 +9738,203 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
+        <left style="thin">
           <color indexed="64"/>
-        </right>
+        </left>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -9586,6 +9953,60 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -9600,43 +10021,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4F4D3D0-A75A-471A-9225-F8FBA886F341}" name="Tableau1" displayName="Tableau1" ref="A1:AH11" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
-  <autoFilter ref="A1:AH11" xr:uid="{F4F4D3D0-A75A-471A-9225-F8FBA886F341}"/>
-  <tableColumns count="34">
-    <tableColumn id="1" xr3:uid="{20C696B3-F3A9-4D52-B31D-9D8663D1DB71}" name="ref_id" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{17243304-7DCB-4BF7-9986-F4AD97FC78CA}" name="name" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{8B25493F-0F71-4BFE-85D4-F5984D21AC75}" name="description" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{F56F0116-19FC-4FCD-A303-1A21A8C96E11}" name="annotation" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{3D791354-91A9-4E1D-BEF6-A9A5A8A22998}" name="name[fr]" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{D8DCB7EE-CBDD-49D5-9BD8-2FDCA39C2393}" name="description[fr]" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{B3212763-7D29-4002-9509-0ADAB8E947E0}" name="annotation[fr]" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{97365EF5-4239-4299-8A88-4B94639A030B}" name="name[cs]" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{9332F77D-1BDC-4F84-9FFD-52FAAB99C0D6}" name="description[cs]" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{259AA177-2D77-4278-8FBC-668F9B2E632E}" name="annotation[cs]" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{56D7B82C-687D-409F-BDAD-82FB932587E2}" name="name[de]" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{923C63BC-ED04-4B8A-A8B2-62773BBB809C}" name="description[de]" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{3AC976CC-F767-49B0-9D10-C0E5E8BE141B}" name="annotation[de]" dataDxfId="23"/>
-    <tableColumn id="14" xr3:uid="{6173A9C3-34B7-428E-B72A-37056E1C1EBD}" name="name[es]" dataDxfId="22"/>
-    <tableColumn id="15" xr3:uid="{8D73EF1A-F638-4F88-B122-97E698A8F65C}" name="description[es]" dataDxfId="21"/>
-    <tableColumn id="16" xr3:uid="{D5227CA4-120B-4DB8-A829-E6A25EA72E35}" name="annotation[es]" dataDxfId="20"/>
-    <tableColumn id="17" xr3:uid="{001384B1-5401-40FC-B7BC-8DAAD7B8ED9C}" name="name[fa]" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{366720CD-3CB7-4463-8EAB-99966D51FFE4}" name="description[fa]" dataDxfId="18"/>
-    <tableColumn id="19" xr3:uid="{120801F2-CF30-48AF-95EB-A5FE039DC1D9}" name="annotation[fa]" dataDxfId="17"/>
-    <tableColumn id="20" xr3:uid="{1B122668-F94F-4389-9D8D-AF7A2AD03138}" name="name[it]" dataDxfId="16"/>
-    <tableColumn id="21" xr3:uid="{591B41BA-0086-434F-9574-480FAD5AB0EE}" name="description[it]" dataDxfId="15"/>
-    <tableColumn id="22" xr3:uid="{DBB49242-33A4-4CE6-8CDC-78B1BD2F8FEB}" name="annotation[it]" dataDxfId="14"/>
-    <tableColumn id="23" xr3:uid="{6BDA09A6-219F-4E16-8511-3587DB546C6D}" name="name[ja]" dataDxfId="13"/>
-    <tableColumn id="24" xr3:uid="{36F23F53-D49E-42CC-8CA2-B27DC821694D}" name="description[ja]" dataDxfId="12"/>
-    <tableColumn id="25" xr3:uid="{3039A195-B467-4670-9FA1-5C386D80016E}" name="annotation[ja]" dataDxfId="11"/>
-    <tableColumn id="26" xr3:uid="{E0AC4B3E-211E-472C-9504-4AEDFF7647EC}" name="name[ko]" dataDxfId="10"/>
-    <tableColumn id="27" xr3:uid="{A7ED36D1-478D-434A-BEE9-093D928BC94F}" name="description[ko]" dataDxfId="9"/>
-    <tableColumn id="28" xr3:uid="{AC28BFD9-D5BE-40D9-81E4-E43731706E28}" name="annotation[ko]" dataDxfId="8"/>
-    <tableColumn id="29" xr3:uid="{0C382B30-4F63-4555-994F-52EA358D7FCE}" name="name[pt]" dataDxfId="7"/>
-    <tableColumn id="30" xr3:uid="{750FC0D5-9907-4470-8CFC-AC612C3999FE}" name="description[pt]" dataDxfId="6"/>
-    <tableColumn id="31" xr3:uid="{E340CC54-AE05-44BA-88C2-7E381DA7CAA2}" name="annotation[pt]" dataDxfId="5"/>
-    <tableColumn id="32" xr3:uid="{8EDE774A-6638-496F-9CE5-7270A55EFEC3}" name="name[zh]" dataDxfId="4"/>
-    <tableColumn id="33" xr3:uid="{13B7C29B-1ADE-4CA4-9203-3612E8567D23}" name="description[zh]" dataDxfId="3"/>
-    <tableColumn id="34" xr3:uid="{6B4F0FB1-ECB4-4D63-B0EE-75B41FA57863}" name="annotation[zh]" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A014C139-48ED-459E-8EFE-0F48BB944E29}" name="Tableau1" displayName="Tableau1" ref="A1:AI11" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36" tableBorderDxfId="35">
+  <autoFilter ref="A1:AI11" xr:uid="{A014C139-48ED-459E-8EFE-0F48BB944E29}"/>
+  <tableColumns count="35">
+    <tableColumn id="1" xr3:uid="{25AE8D30-3860-4111-8EA6-C4C7AEECC6EB}" name="ref_id" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{92E23933-32F2-41EA-BF91-455565D13AFD}" name="node_id" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{CD524151-5700-4186-A8E3-1B3BECA35D31}" name="name" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{0BFFD00C-098B-4E57-A16B-3C376911F0A6}" name="description" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{1031B7B0-FAC6-47EA-BF11-B9A35519FBFD}" name="annotation" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{FB68E663-983D-432F-8C12-C673829B1EE9}" name="name[fr]" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{E7898F1E-1574-4B4E-A4FD-758820DEADE4}" name="description[fr]" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{3CA9968D-8F68-4C21-95A2-FFD6FC8B7493}" name="annotation[fr]" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{93E9EC66-775C-4641-BD7A-A06C2F9D56B2}" name="name[cs]" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{51366F19-9468-42E8-90A9-B9C23225D7DD}" name="description[cs]" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{8C2133FF-64CE-4C7C-AEC1-7AFB9456E6CF}" name="annotation[cs]" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{DEA91A07-6088-4648-BC99-DBBE4BB97527}" name="name[de]" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{AB6F2498-4869-43FA-92E5-0EDAFE791BAD}" name="description[de]" dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{39519832-5547-4B8D-8CE3-A5F59F22EBAC}" name="annotation[de]" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{8460DD8D-47C6-4E87-AD01-F3AD20769748}" name="name[es]" dataDxfId="20"/>
+    <tableColumn id="16" xr3:uid="{5EAA485E-15DE-46C4-A9D2-97C138336F35}" name="description[es]" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{B3866A17-8967-4C4E-A5EE-56274B48C1F1}" name="annotation[es]" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{CC115383-C845-4A5F-BAF5-C6ABAC7C4E12}" name="name[fa]" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{552DBEA8-469F-4D67-9E2E-98218233E662}" name="description[fa]" dataDxfId="16"/>
+    <tableColumn id="20" xr3:uid="{31BF1538-369A-4B29-B01B-CB8C16854DB5}" name="annotation[fa]" dataDxfId="15"/>
+    <tableColumn id="21" xr3:uid="{5D79E7BE-5B52-46D7-B7A5-6104BC1A1D44}" name="name[it]" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{C8923F58-6252-4E60-AC02-E32CBC8BC741}" name="description[it]" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{F48E3656-A969-4E25-A065-330F8D08E7D2}" name="annotation[it]" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{32FDE793-892B-41C0-87A4-EE72BF642E10}" name="name[ja]" dataDxfId="11"/>
+    <tableColumn id="25" xr3:uid="{499C9F0B-0066-4FFD-B117-F2A167ABAA64}" name="description[ja]" dataDxfId="10"/>
+    <tableColumn id="26" xr3:uid="{F30E2A0D-2E40-4166-858A-B03C02C9B7E6}" name="annotation[ja]" dataDxfId="9"/>
+    <tableColumn id="27" xr3:uid="{9DFEFF6B-B495-4084-AF12-32844FFE1E6D}" name="name[ko]" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{89D67697-85DF-43A7-8ADC-439089931056}" name="description[ko]" dataDxfId="7"/>
+    <tableColumn id="29" xr3:uid="{1FA2710F-4C36-4270-94CF-7E241AC56D9D}" name="annotation[ko]" dataDxfId="6"/>
+    <tableColumn id="30" xr3:uid="{DB1A945B-B6AA-45F9-99F6-19E338C66ABE}" name="name[pt]" dataDxfId="5"/>
+    <tableColumn id="31" xr3:uid="{4044319C-6166-474F-A4F5-EB6FE072A4DA}" name="description[pt]" dataDxfId="4"/>
+    <tableColumn id="32" xr3:uid="{3D009E4C-699E-4946-A3CF-B80EEE277683}" name="annotation[pt]" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{84E7C3A7-8E19-474F-810B-09585BAC9C18}" name="name[zh]" dataDxfId="2"/>
+    <tableColumn id="34" xr3:uid="{891B07E7-E061-4AD2-B36B-74CA005DED85}" name="description[zh]" dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{AF75C4F6-F5AB-45F4-A48B-8353C10BDD88}" name="annotation[zh]" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9944,7 +10366,7 @@
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -10206,7 +10628,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>52</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -10216,1187 +10638,1221 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="100" customWidth="1"/>
-    <col min="4" max="4" width="120" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="100" customWidth="1"/>
-    <col min="7" max="7" width="120" customWidth="1"/>
-    <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="100" customWidth="1"/>
-    <col min="10" max="10" width="120" customWidth="1"/>
-    <col min="11" max="11" width="42" customWidth="1"/>
-    <col min="12" max="12" width="100" customWidth="1"/>
-    <col min="13" max="13" width="120" customWidth="1"/>
-    <col min="14" max="14" width="42" customWidth="1"/>
-    <col min="15" max="15" width="100" customWidth="1"/>
-    <col min="16" max="16" width="120" customWidth="1"/>
-    <col min="17" max="17" width="42" customWidth="1"/>
-    <col min="18" max="18" width="100" customWidth="1"/>
-    <col min="19" max="19" width="120" customWidth="1"/>
-    <col min="20" max="20" width="42" customWidth="1"/>
-    <col min="21" max="21" width="100" customWidth="1"/>
-    <col min="22" max="22" width="120" customWidth="1"/>
-    <col min="23" max="23" width="42" customWidth="1"/>
-    <col min="24" max="24" width="100" customWidth="1"/>
-    <col min="25" max="25" width="120" customWidth="1"/>
-    <col min="26" max="26" width="42" customWidth="1"/>
-    <col min="27" max="27" width="100" customWidth="1"/>
-    <col min="28" max="28" width="120" customWidth="1"/>
-    <col min="29" max="29" width="42" customWidth="1"/>
-    <col min="30" max="30" width="100" customWidth="1"/>
-    <col min="31" max="31" width="120" customWidth="1"/>
-    <col min="32" max="32" width="42" customWidth="1"/>
-    <col min="33" max="33" width="100" customWidth="1"/>
-    <col min="34" max="34" width="120" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="100" customWidth="1"/>
+    <col min="5" max="5" width="120" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="100" customWidth="1"/>
+    <col min="8" max="8" width="120" customWidth="1"/>
+    <col min="9" max="9" width="42" customWidth="1"/>
+    <col min="10" max="10" width="100" customWidth="1"/>
+    <col min="11" max="11" width="120" customWidth="1"/>
+    <col min="12" max="12" width="42" customWidth="1"/>
+    <col min="13" max="13" width="100" customWidth="1"/>
+    <col min="14" max="14" width="120" customWidth="1"/>
+    <col min="15" max="15" width="42" customWidth="1"/>
+    <col min="16" max="16" width="100" customWidth="1"/>
+    <col min="17" max="17" width="120" customWidth="1"/>
+    <col min="18" max="18" width="42" customWidth="1"/>
+    <col min="19" max="19" width="100" customWidth="1"/>
+    <col min="20" max="20" width="120" customWidth="1"/>
+    <col min="21" max="21" width="42" customWidth="1"/>
+    <col min="22" max="22" width="100" customWidth="1"/>
+    <col min="23" max="23" width="120" customWidth="1"/>
+    <col min="24" max="24" width="42" customWidth="1"/>
+    <col min="25" max="25" width="100" customWidth="1"/>
+    <col min="26" max="26" width="120" customWidth="1"/>
+    <col min="27" max="27" width="42" customWidth="1"/>
+    <col min="28" max="28" width="100" customWidth="1"/>
+    <col min="29" max="29" width="120" customWidth="1"/>
+    <col min="30" max="30" width="42" customWidth="1"/>
+    <col min="31" max="31" width="100" customWidth="1"/>
+    <col min="32" max="32" width="120" customWidth="1"/>
+    <col min="33" max="33" width="42" customWidth="1"/>
+    <col min="34" max="34" width="100" customWidth="1"/>
+    <col min="35" max="35" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:35" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="D1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="16" t="s">
+      <c r="I1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="15" t="s">
+      <c r="L1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="15" t="s">
+      <c r="O1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="15" t="s">
+      <c r="R1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="Q1" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="S1" s="15" t="s">
+      <c r="U1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="T1" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="V1" s="15" t="s">
+      <c r="X1" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="W1" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="X1" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y1" s="15" t="s">
+      <c r="AA1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC1" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="Z1" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB1" s="15" t="s">
+      <c r="AD1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF1" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="AC1" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD1" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE1" s="15" t="s">
+      <c r="AG1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI1" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="AF1" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG1" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH1" s="17" t="s">
+    </row>
+    <row r="2" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>63</v>
       </c>
+      <c r="B2" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG2" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI2" s="5" t="s">
+        <v>93</v>
+      </c>
     </row>
-    <row r="2" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="5" t="s">
+    <row r="3" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AF2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH2" s="8" t="s">
-        <v>94</v>
+      <c r="I3" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z3" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA3" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB3" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD3" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE3" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF3" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG3" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH3" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI3" s="8" t="s">
+        <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="5" t="s">
+    <row r="4" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H4" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AE4" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF4" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD3" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE3" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG3" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="AH3" s="8" t="s">
-        <v>125</v>
+      <c r="I5" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y5" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z5" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA5" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB5" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC5" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD5" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="AF5" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="AG5" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="AH5" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI5" s="8" t="s">
+        <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="G4" s="6" t="s">
+    <row r="6" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="AC6" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AD6" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="AE6" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="AF6" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG6" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="AH6" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="AI6" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="X4" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Z4" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB4" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC4" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="AD4" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE4" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="AF4" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="AG4" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AH4" s="8" t="s">
-        <v>154</v>
+      <c r="I7" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="X7" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y7" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z7" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="AA7" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB7" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC7" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="AD7" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="AE7" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF7" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG7" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="AH7" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI7" s="8" t="s">
+        <v>243</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y5" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z5" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA5" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB5" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="AC5" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="AD5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE5" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF5" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="AG5" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="AH5" s="8" t="s">
-        <v>185</v>
+    <row r="8" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB8" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="AC8" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="AD8" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="AE8" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="AF8" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="AG8" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="AH8" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="AI8" s="5" t="s">
+        <v>273</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="R6" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="U6" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="Z6" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB6" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AC6" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="AD6" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="AE6" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="AF6" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="AG6" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="AH6" s="8" t="s">
-        <v>214</v>
+    <row r="9" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="T9" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="W9" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="X9" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y9" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="Z9" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="AA9" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="AB9" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="AC9" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="AD9" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="AE9" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="AF9" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="AG9" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="AH9" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="AI9" s="8" t="s">
+        <v>303</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="G7" s="6" t="s">
+    <row r="10" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="W7" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="X7" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y7" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="Z7" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA7" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="AB7" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC7" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="AD7" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="AE7" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="AF7" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="AG7" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="AH7" s="8" t="s">
-        <v>244</v>
+      <c r="I10" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="AB10" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="AC10" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="AD10" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="AE10" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="AF10" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG10" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="AH10" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="AI10" s="5" t="s">
+        <v>334</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="X8" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="Y8" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z8" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="AA8" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="AB8" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="AC8" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="AD8" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="AE8" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="AF8" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="AG8" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="AH8" s="8" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="G9" s="6" t="s">
+    <row r="11" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="T9" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="V9" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="Y9" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="Z9" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="AA9" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="AB9" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="AC9" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="AD9" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="AE9" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="AF9" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="AG9" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="AH9" s="8" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="T10" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="W10" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="X10" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="Y10" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="Z10" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="AA10" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="AB10" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="AC10" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="AD10" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="AE10" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="AF10" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="AG10" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="AH10" s="8" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="I11" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="R11" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="P11" s="10" t="s">
+      <c r="S11" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="Q11" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="R11" s="10" t="s">
+      <c r="T11" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="S11" s="10" t="s">
+      <c r="U11" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="V11" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="T11" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="U11" s="10" t="s">
+      <c r="W11" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="V11" s="10" t="s">
+      <c r="X11" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="W11" s="10" t="s">
+      <c r="Y11" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="X11" s="10" t="s">
+      <c r="Z11" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="Y11" s="10" t="s">
+      <c r="AA11" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="Z11" s="10" t="s">
+      <c r="AB11" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="AA11" s="10" t="s">
+      <c r="AC11" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="AB11" s="10" t="s">
+      <c r="AD11" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="AC11" s="10" t="s">
+      <c r="AE11" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="AD11" s="10" t="s">
+      <c r="AF11" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="AE11" s="10" t="s">
+      <c r="AG11" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="AF11" s="10" t="s">
+      <c r="AH11" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="AG11" s="10" t="s">
+      <c r="AI11" s="8" t="s">
         <v>364</v>
-      </c>
-      <c r="AH11" s="13" t="s">
-        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/owasp/owasp-top-10-web_2025.xlsx
+++ b/tools/excel/owasp/owasp-top-10-web_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\owasp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFADF6E-28B9-4AB5-BBFD-DF0876D2B2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140E4654-EA3E-44CC-8C8A-81CCC0E8CBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30696" yWindow="-9720" windowWidth="22824" windowHeight="16344" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3045" yWindow="-14475" windowWidth="20280" windowHeight="11790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -1111,68 +1111,6 @@
 Without a concerted, repeatable application security configuration hardening process, systems are at a higher risk.</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWEs Mapped 
-   &lt;/td&gt;
-   &lt;td&gt;Max Incidence Rate
-   &lt;/td&gt;
-   &lt;td&gt;Avg Incidence Rate
-   &lt;/td&gt;
-   &lt;td&gt;Max Coverage
-   &lt;/td&gt;
-   &lt;td&gt;Avg Coverage
-   &lt;/td&gt;
-   &lt;td&gt;Avg Weighted Exploit
-   &lt;/td&gt;
-   &lt;td&gt;Avg Weighted Impact
-   &lt;/td&gt;
-   &lt;td&gt;Total Occurrences
-   &lt;/td&gt;
-   &lt;td&gt;Total CVEs
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;16
-   &lt;/td&gt;
-   &lt;td&gt;27.70%
-   &lt;/td&gt;
-   &lt;td&gt;3.00%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;52.35%
-   &lt;/td&gt;
-   &lt;td&gt;7.96
-   &lt;/td&gt;
-   &lt;td&gt;3.97
-   &lt;/td&gt;
-   &lt;td&gt;719,084
-   &lt;/td&gt;
-   &lt;td&gt;1,375
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Secure installation processes should be implemented, including:
-* A repeatable hardening process enabling the fast and easy deployment of another environment that is appropriately locked down. Development, QA, and production environments should all be configured identically, with different credentials used in each environment. This process should be automated to minimize the effort required to set up a new secure environment.
-* A minimal platform without any unnecessary features, components, documentation, or samples. Remove or do not install unused features and frameworks.
-* A task to review and update the configurations appropriate to all security notes, updates, and patches as part of the patch management process (see [A03 Software Supply Chain Failures](A03_2025-Software_Supply_Chain_Failures.md)). Review cloud storage permissions (e.g., S3 bucket permissions).
-* A segmented application architecture provides effective and secure separation between components or tenants, with segmentation, containerization, or cloud security groups (ACLs).
-* Sending security directives to clients, e.g., Security Headers.
-* An automated process to verify the effectiveness of the configurations and settings in all environments.
-* Proactively add a central configuration to intercept excessive error messages as a backup.
-* If these verifications are not automated, they should be manually verified annually at a minimum.
-* Use identity federation, short-lived credentials, or role-based access mechanisms provided by the underlying platform instead of embedding static keys or secrets in code, configuration files, or pipelines.
-## Example attack scenarios
-**Scenario #1:** The application server comes with sample applications not removed from the production server. These sample applications have known security flaws that attackers use to compromise the server. Suppose one of these applications is the admin console, and default accounts weren't changed. In that case, the attacker logs in with the default password and takes over.
-**Scenario #2:** Directory listing is not disabled on the server. An attacker discovers they can simply list directories. The attacker finds and downloads the compiled Java classes, which they decompile and reverse engineer to view the code. The attacker then finds a severe access control flaw in the application.
-**Scenario #3:** The application server's configuration allows detailed error messages, such as stack traces to be returned to users. This potentially exposes sensitive information or underlying flaws, such as component versions that are known to be vulnerable.
-**Scenario #4:** A cloud service provider (CSP) defaults to having sharing permissions open to the Internet. This allows sensitive data stored within cloud storage to be accessed.
-For more information about the references and the list of mapped CWEs: https://top10.owasp.org/2025/A02_2025-Security_Misconfiguration/</t>
-  </si>
-  <si>
     <t>Mauvaise configuration de sécurité</t>
   </si>
   <si>
@@ -1192,137 +1130,7 @@
 Bez koordinovaného a opakovatelného procesu bezpečnostního hardeningu konfigurace aplikací jsou systémy vystaveny zvýšenému riziku.</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;Počet mapovaných CWE 
-   &lt;/td&gt;
-   &lt;td&gt;Max míra výskytu
-   &lt;/td&gt;
-   &lt;td&gt;Průměrná míra výskytu
-   &lt;/td&gt;
-   &lt;td&gt;Max pokrytí
-   &lt;/td&gt;
-   &lt;td&gt;Průměrné pokrytí
-   &lt;/td&gt;
-   &lt;td&gt;Průměrná vážená zneužitelnost
-   &lt;/td&gt;
-   &lt;td&gt;Průměrný vážený dopad
-   &lt;/td&gt;
-   &lt;td&gt;Celkový počet výskytů
-   &lt;/td&gt;
-   &lt;td&gt;Celkový počet CVE
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;16
-   &lt;/td&gt;
-   &lt;td&gt;27,70 %
-   &lt;/td&gt;
-   &lt;td&gt;3,00 %
-   &lt;/td&gt;
-   &lt;td&gt;100,00 %
-   &lt;/td&gt;
-   &lt;td&gt;52,35 %
-   &lt;/td&gt;
-   &lt;td&gt;7,96
-   &lt;/td&gt;
-   &lt;td&gt;3,97
-   &lt;/td&gt;
-   &lt;td&gt;719 084
-   &lt;/td&gt;
-   &lt;td&gt;1 375
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Měly by být implementovány bezpečné instalační procesy, včetně:
-* Opakovatelný proces hardeningu umožňující rychlé a snadné nasazení dalšího prostředí s odpovídajícím zabezpečením. Vývojové, testovací (QA) a produkční prostředí by měla být konfigurována shodně, přičemž v každém prostředí by se měly používat odlišné přihlašovací údaje. Tento proces by měl být automatizován, aby se minimalizovalo úsilí potřebné k nastavení nového bezpečného prostředí.
-* Minimální platforma bez zbytečných funkcí, komponent, dokumentace nebo ukázek. Odstraňte nebo neinstalujte nepoužívané funkce a frameworky.
-* Revize a aktualizace konfigurací v návaznosti na všechna bezpečnostní upozornění, aktualizace a záplaty jako součást procesu správy záplat (viz [A03:2025 Selhání dodavatelského řetězce softwaru](A03_2025-Software_Supply_Chain_Failures.md)). Kontrola oprávnění cloudových úložišť (např. oprávnění S3 bucketů).
-* Segmentovanou architekturu aplikace, která zajišťuje účinné a bezpečné oddělení komponent nebo tenantů pomocí segmentace, kontejnerizace nebo cloudových bezpečnostních skupin (ACL).
-* Zasílání bezpečnostních direktiv klientům, např. bezpečnostních hlaviček (Security Headers).
-* Automatizovaný proces ověřování účinnosti konfigurací a nastavení ve všech prostředích.
-* Proaktivní zavedení centrální konfigurace pro zachytávání příliš informativních chybových hlášení jako záložního opatření.
-* Pokud tyto kontroly nejsou automatizované, měly by být alespoň jednou ročně prováděny manuálně.
-* Využívání federace identit, krátkodobě platných přihlašovacích údajů nebo mechanismů řízení přístupu založených na rolích poskytovaných podkladovou platformou namísto ukládání statických klíčů nebo tajných údajů (secrets) do zdrojového kódu, konfiguračních souborů nebo CI/CD pipeline.
-## Example attack scenarios
-**Scénář #1:** Na aplikačním serveru zůstaly nasazeny ukázkové aplikace, které nebyly z produkčního prostředí odstraněny. Tyto aplikace obsahují známé bezpečnostní chyby, které mohou útočníci zneužít ke kompromitaci serveru. Pokud je jednou z těchto aplikací administrační konzole a výchozí účty nebyly změněny, útočník se přihlásí pomocí výchozích přihlašovacích údajů a převezme kontrolu.
-**Scénář #2:** Na serveru není zakázán výpis adresářů. Útočník zjistí, že může zobrazit seznam adresářů, nalezne a stáhne zkompilované třídy Java, které následně dekompiluje a analyzuje. Na základě toho odhalí závažnou chybu v řízení přístupu aplikace.
-**Scénář #3:** Konfigurace aplikačního serveru umožňuje zobrazování detailních chybových informací, například výpisů zásobníku (stack trace). Tím může dojít ke zpřístupnění citlivých informací nebo vnitřních nedostatků, například verzí použitých komponent, o nichž je známo, že jsou zranitelné.
-**Scénář #4:** Poskytovatel cloudových služeb (CSP) má ve výchozím nastavení povolena oprávnění ke sdílení otevřená do Internetu. To umožňuje přístup k citlivým datům uloženým v cloudovém úložišti.
-Další informace o odkazech a seznamu namapovaných CWE: https://top10.owasp.org/2025/cs/A02_2025-Security_Misconfiguration/</t>
-  </si>
-  <si>
     <t>Sicherheitsrelevante Fehlkonfiguration</t>
-  </si>
-  <si>
-    <t>Die Anwendung besitzt möglicherweise Schwachstellen, wenn Folgendes zutrifft:
-* Mangelhafte Sicherheitshärtung des Anwendungsstacks oder ungeeignet konfigurierte Berechtigungen auf Cloud-Diensten.
-* Nicht benötigte Features sind aktiviert oder installiert (z. B. unnötige Ports, Dienste, Seiten, Accounts oder Rechte).
-* Standardkonten und -passwörter sind aktiviert bzw. unverändert.
-* Die Fehlerbehandlung gibt Stack-Traces oder andere interne technische Fehlermeldungen an Anwender:innen preis.
-* Für aktualisierte Systeme sind die neuesten Sicherheitsfeatures deaktiviert oder nicht sicher konfiguriert.
-* Die Sicherheitseinstellungen in den Anwendungsservern und -frameworks (z. B. Struts, Spring, ASP.NET), Bibliotheken, Datenbanken etc. sind nicht auf sichere Werte gesetzt.
-* Der Server sendet keine Sicherheits-Header oder -Direktiven, bzw. diese sind nicht sicher konfiguriert.
-* Die Software ist veraltet oder verwundbar (siehe [A06:2025-Unsichere oder veraltete Komponenten](A06_2025-Vulnerable_and_Outdated_Components.md)).
-Ohne einen abgestimmten und reproduzierbaren Prozess zur sicheren Konfiguration sind Systeme einem höheren Risiko ausgesetzt!</t>
-  </si>
-  <si>
-    <t>## Score table
-&lt;table&gt;
-&lt;tr&gt;
-   &lt;td&gt;Zugeordnete CWEs
-   &lt;/td&gt;
-   &lt;td&gt;Max. Häufigkeit
-   &lt;/td&gt;
-   &lt;td&gt;Durchschn. Häufigkeit
-   &lt;/td&gt;
-   &lt;td&gt;Max. Abdeckung
-   &lt;/td&gt;
-   &lt;td&gt;Durchschn. Abdeckung
-   &lt;/td&gt;
-   &lt;td&gt;Durchschn. gewichtete Ausnutzbarkeit
-   &lt;/td&gt;
-   &lt;td&gt;Durchschn. gewichtete Auswirkung
-   &lt;/td&gt;
-   &lt;td&gt;Gesamtanzahl
-   &lt;/td&gt;
-   &lt;td&gt;Summe CVEs
-   &lt;/td&gt;
-&lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;16
-   &lt;/td&gt;
-   &lt;td&gt;27.70%
-   &lt;/td&gt;
-   &lt;td&gt;3.00%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;52.35%
-   &lt;/td&gt;
-   &lt;td&gt;7.96
-   &lt;/td&gt;
-   &lt;td&gt;3.97
-   &lt;/td&gt;
-   &lt;td&gt;719,084
-   &lt;/td&gt;
-   &lt;td&gt;1,375
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Es sollten sichere Installationsprozesse implementiert werden, darunter:
-* Ein wiederholbarer Härtungsprozess, welcher die schnelle und einfache Bereitstellung zusätzlicher Umgebungen, die entsprechend abgesichert sind, ermöglicht. Entwicklungs-, Qualitätssicherungs- und Produktionsumgebungen sollten alle identisch konfiguriert sein, wobei in jeder Umgebung unterschiedliche Zugangsdaten verwendet werden sollten. Dieser Prozess sollte automatisiert werden, um den Aufwand für die Einrichtung einer neuen sicheren Umgebung zu minimieren.
-* Eine minimale Plattform ohne unnötige Funktionen, Komponenten, Dokumentation oder Beispiele: Entfernen Sie Funktionen und Frameworks die Sie nicht verwenden oder installieren Sie diese erst gar nicht.
-* Überprüfen und Aktualisieren der Konfigurationen, die für alle Sicherheitshinweise, Updates und Patches im Rahmen des Patch-Verwaltungsprozesses geeignet sind (siehe [A03:2025 – Schwachstellen in der Software-Lieferkette](A03_2025-Software_Supply_Chain_Failures.md)). Überprüfen Sie die Cloud-Speicherberechtigungen (z. B. S3-Bucket-Berechtigungen).
-## Example attack scenarios
-**Szenario Nr. 1:** Der Anwendungsserver wird mit Beispielanwendungen geliefert, die nicht vom Produktionsserver entfernt wurden. Diese Beispielanwendungen weisen bekannte Schwachstellen auf, die Angreifer:innen nutzen, um den Server zu gefährden. Angenommen, eine dieser Anwendungen ist die Admin-Konsole und die Standardkonten wurden nicht geändert. In diesem Fall meldet sich die/der Angreifer:in mit einem Standardkennwort an und übernimmt die Kontrolle.
-**Szenario Nr. 2:** Die Directory Listings wurden nicht auf dem Server deaktiviert. Angreifer:innen entdecken, dass Verzeichnisse einfach aufgelistet werden können. Die/Der Angreifer:in findet die kompilierten Java-Klassen und lädt sie herunter, dekompiliert sie und betreibt Reverse Engineering, um den Code anzuzeigen. Dies ermöglicht das Findet eines schwerwiegenden Fehlers in der Zugriffskontrolle in der Anwendung.
-**Szenario Nr. 3:** Die Konfiguration des Anwendungsservers ermöglicht die Rückgabe detaillierter Fehlermeldungen an Anwender:innen, wie z. B. Stack-Traces. Dadurch werden möglicherweise vertrauliche Informationen oder zugrunde liegende Fehler wie Komponentenversionen offengelegt, die als angreifbar bekannt sind.
-**Szenario Nr. 4:** Ein Cloud-Dienstanbieter (CSP) gewährt standardmäßig Freigabeberechtigungen zum Internet und ermöglicht dadurch Zugriff auf sensible Daten in der Cloud.
-Weitere Informationen zu den Referenzen und zur Liste der zugeordneten CWEs: https://top10.owasp.org/2025/de/A02_2025-Security_Misconfiguration/</t>
   </si>
   <si>
     <t>Configuración de Seguridad Incorrecta (Security Misconfiguration)</t>
@@ -1339,68 +1147,6 @@
 * Los ajustes de seguridad en los servidores de aplicaciones, frameworks de aplicaciones (por ejemplo, Struts, Spring, ASP.NET), bibliotecas, bases de datos, etc., no están establecidos en valores seguros.
 * El servidor no envía cabeceras o directivas de seguridad, o estas no están establecidas en valores seguros.
 Sin un proceso de bastionado (hardening) de la configuración de seguridad de las aplicaciones que sea concertado y repetible, los sistemas corren un mayor riesgo.</t>
-  </si>
-  <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWE Mapeados 
-   &lt;/td&gt;
-   &lt;td&gt;Tasa de Incidencia Máx.
-   &lt;/td&gt;
-   &lt;td&gt;Tasa de Incidencia Prom.
-   &lt;/td&gt;
-   &lt;td&gt;Cobertura Máx.
-   &lt;/td&gt;
-   &lt;td&gt;Cobertura Prom.
-   &lt;/td&gt;
-   &lt;td&gt;Explotación Ponderada Prom.
-   &lt;/td&gt;
-   &lt;td&gt;Impacto Ponderado Prom.
-   &lt;/td&gt;
-   &lt;td&gt;Ocurrencias Totales
-   &lt;/td&gt;
-   &lt;td&gt;CVE Totales
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;16
-   &lt;/td&gt;
-   &lt;td&gt;27.70%
-   &lt;/td&gt;
-   &lt;td&gt;3.00%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;52.35%
-   &lt;/td&gt;
-   &lt;td&gt;7.96
-   &lt;/td&gt;
-   &lt;td&gt;3.97
-   &lt;/td&gt;
-   &lt;td&gt;719,084
-   &lt;/td&gt;
-   &lt;td&gt;1,375
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Deben implementarse procesos de instalación seguros, que incluyan:
-* Un proceso de bastionado (hardening) repetible que permita el despliegue rápido y sencillo de otro entorno que esté bloqueado adecuadamente. Los entornos de desarrollo, QA y producción deben estar configurados de forma idéntica, con credenciales diferentes en cada uno. Este proceso debe estar automatizado para minimizar el esfuerzo requerido para configurar un nuevo entorno seguro.
-* Una plataforma mínima sin funciones, componentes, documentación o ejemplos innecesarios. Elimine o no instale funciones y frameworks que no utilice.
-* Una tarea para revisar y actualizar las configuraciones de acuerdo con todas las notas de seguridad, actualizaciones y parches como parte del proceso de gestión de parches (consulte [A03 Fallas en la Cadena de Suministro de Software](A03_2025-Software_Supply_Chain_Failures.md)). Revise los permisos de almacenamiento en la nube (por ejemplo, los permisos de los buckets S3).
-* Una arquitectura de aplicación segmentada que proporcione una separación efectiva y segura entre componentes o inquilinos (tenants), con segmentación, contenedorización o grupos de seguridad en la nube (ACLs).
-* Envío de directivas de seguridad a los clientes, por ejemplo, Cabeceras de Seguridad (Security Headers).
-* Un proceso automatizado para verificar la eficacia de las configuraciones y ajustes en todos los entornos.
-* Añadir proactivamente una configuración central para interceptar mensajes de error excesivos como medida de respaldo.
-* Si estas verificaciones no están automatizadas, deben verificarse manualmente al menos una vez al año.
-* Utilizar federación de identidades, credenciales de corta duración o mecanismos de acceso basados en roles proporcionados por la plataforma subyacente en lugar de incrustar claves estáticas o secretos en el código, los archivos de configuración o los flujos de trabajo (pipelines).
-## Example attack scenarios
-**Escenario #1:** El servidor de aplicaciones viene con aplicaciones de ejemplo que no se eliminaron del servidor de producción. Estas aplicaciones de ejemplo tienen fallas de seguridad conocidas que los atacantes utilizan para comprometer el servidor. Supongamos que una de estas aplicaciones es la consola de administración y las cuentas predeterminadas no se cambiaron. En ese caso, el atacante inicia sesión con la contraseña predeterminada y toma el control.
-**Escenario #2:** El listado de directorios no está desactivado en el servidor. Un atacante descubre que puede simplemente listar los directorios. El atacante encuentra y descarga las clases Java compiladas, las cuales descompila y les aplica ingeniería inversa para ver el código. El atacante encuentra entonces una falla grave de control de acceso en la aplicación.
-**Escenario #3:** La configuración del servidor de aplicaciones permite que se devuelvan mensajes de error detallados, como trazas de la pila, a los usuarios. Esto expone potencialmente información sensible o fallas subyacentes, como versiones de componentes que se sabe que son vulnerables.
-**Escenario #4:** Un proveedor de servicios en la nube (CSP) tiene por defecto permisos de compartición abiertos a Internet. Esto permite el acceso a datos sensibles almacenados en el almacenamiento en la nube.
-Para obtener más información sobre las referencias y la lista de CWE asociadas: https://top10.owasp.org/2025/es/A02_2025-Security_Misconfiguration/</t>
   </si>
   <si>
     <t>خطا در پیکربندی امنیتی (Security Misconfiguration)</t>
@@ -1452,68 +1198,6 @@
 Senza un processo ripetibile e concertato di hardening della configurazione della sicurezza applicativa, i sistemi sono a rischio più elevato.</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWE Mappate 
-   &lt;/td&gt;
-   &lt;td&gt;Tasso Massimo di Incidenza
-   &lt;/td&gt;
-   &lt;td&gt;Tasso Medio di Incidenza
-   &lt;/td&gt;
-   &lt;td&gt;Copertura Massima
-   &lt;/td&gt;
-   &lt;td&gt;Copertura Media
-   &lt;/td&gt;
-   &lt;td&gt;Exploit Medio Ponderato
-   &lt;/td&gt;
-   &lt;td&gt;Impatto Medio Ponderato
-   &lt;/td&gt;
-   &lt;td&gt;Totale Occorrenze
-   &lt;/td&gt;
-   &lt;td&gt;Totale CVE
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;16
-   &lt;/td&gt;
-   &lt;td&gt;27,70%
-   &lt;/td&gt;
-   &lt;td&gt;3,00%
-   &lt;/td&gt;
-   &lt;td&gt;100,00%
-   &lt;/td&gt;
-   &lt;td&gt;52,35%
-   &lt;/td&gt;
-   &lt;td&gt;7,96
-   &lt;/td&gt;
-   &lt;td&gt;3,97
-   &lt;/td&gt;
-   &lt;td&gt;719.084
-   &lt;/td&gt;
-   &lt;td&gt;1.375
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Devono essere implementati processi di installazione sicuri, incluso:
-* Un processo di hardening ripetibile che consenta la distribuzione rapida e semplice di un altro ambiente adeguatamente protetto. Gli ambienti di sviluppo, QA e produzione devono essere configurati in modo identico, con credenziali diverse utilizzate in ciascun ambiente. Questo processo deve essere automatizzato per minimizzare lo sforzo necessario per configurare un nuovo ambiente sicuro.
-* Una piattaforma minimale senza funzionalità, componenti, documentazione o campioni non necessari. Rimuovere o non installare funzionalità e framework non utilizzati.
-* Un'attività di revisione e aggiornamento delle configurazioni appropriate a tutte le note di sicurezza, aggiornamenti e patch come parte del processo di gestione delle patch (vedi [A03 Software Supply Chain Failures](A03_2025-Software_Supply_Chain_Failures.md)). Revisionare i permessi dello storage cloud (es. permessi dei bucket S3).
-* Un'architettura applicativa segmentata che fornisca una separazione efficace e sicura tra componenti o tenant, con segmentazione, containerizzazione o gruppi di sicurezza cloud (ACL).
-* Invio di direttive di sicurezza ai client, es. Security Headers.
-* Un processo automatizzato per verificare l'efficacia delle configurazioni e delle impostazioni in tutti gli ambienti.
-* Aggiungere proattivamente una configurazione centrale per intercettare messaggi di errore eccessivi come backup.
-* Se queste verifiche non sono automatizzate, devono essere verificate manualmente almeno annualmente.
-* Utilizzare la federazione di identità, credenziali di breve durata o meccanismi di accesso basati sui ruoli forniti dalla piattaforma sottostante anziché incorporare chiavi o segreti statici nel codice, nei file di configurazione o nelle pipeline.
-## Example attack scenarios
-**Scenario #1:** Il server applicativo include applicazioni di esempio non rimosse dal server di produzione. Queste applicazioni di esempio hanno falle di sicurezza note che gli attaccanti utilizzano per compromettere il server. Supponiamo che una di queste applicazioni sia la console di amministrazione e che le credenziali predefinite non siano state cambiate. In tal caso, l'attaccante accede con la password predefinita e prende il controllo.
-**Scenario #2:** Il directory listing non è disabilitato sul server. Un attaccante scopre che può semplicemente elencare le directory. L'attaccante trova e scarica le classi Java compilate, che decompila e fa reverse engineering per visualizzare il codice. L'attaccante trova quindi una grave falla nel controllo degli accessi nell'applicazione.
-**Scenario #3:** La configurazione del server applicativo consente la restituzione di messaggi di errore dettagliati, come stack trace, agli utenti. Ciò potrebbe esporre informazioni sensibili o falle sottostanti, come le versioni dei componenti note per essere vulnerabili.
-**Scenario #4:** Un cloud service provider (CSP) ha come default i permessi di condivisione aperti a Internet. Ciò consente l'accesso ai dati sensibili archiviati nello storage cloud.
-Per maggiori informazioni sui riferimenti e sull'elenco delle CWE mappate: https://top10.owasp.org/2025/it/A02_2025-Security_Misconfiguration/</t>
-  </si>
-  <si>
     <t>セキュリティ設定の不備 (Security Misconfiguration)</t>
   </si>
   <si>
@@ -1530,50 +1214,6 @@
 反復可能で一貫したアプリケーションセキュリティ設定の要塞化プロセスがなければ、システムのリスクは高まり続けます。</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;紐付けられた CWE 数&lt;/td&gt;
-   &lt;td&gt;最大出現率&lt;/td&gt;
-   &lt;td&gt;平均出現率&lt;/td&gt;
-   &lt;td&gt;最大網羅率&lt;/td&gt;
-   &lt;td&gt;平均網羅率&lt;/td&gt;
-   &lt;td&gt;平均加重悪用スコア&lt;/td&gt;
-   &lt;td&gt;平均加重影響スコア&lt;/td&gt;
-   &lt;td&gt;出現総数&lt;/td&gt;
-   &lt;td&gt;CVE 総数&lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;16&lt;/td&gt;
-   &lt;td&gt;27.70%&lt;/td&gt;
-   &lt;td&gt;3.00%&lt;/td&gt;
-   &lt;td&gt;100.00%&lt;/td&gt;
-   &lt;td&gt;52.35%&lt;/td&gt;
-   &lt;td&gt;7.96&lt;/td&gt;
-   &lt;td&gt;3.97&lt;/td&gt;
-   &lt;td&gt;719,084&lt;/td&gt;
-   &lt;td&gt;1,375&lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-安全なインストールプロセスを実装する必要があります。これには以下の対策が含まれます。
-* **反復可能な要塞化プロセス：** 適切にロックダウンされた環境を、迅速かつ容易にデプロイできるプロセスを確立してください。開発、QA、本番の各環境は同一の設定とし、認証情報のみを環境ごとに使い分けるべきです。このプロセスを自動化し、安全な環境構築の負荷を最小限に抑えてください。
-* **最小限のプラットフォーム：** 不要な機能、コンポーネント、ドキュメント、サンプルを含まない最小限のプラットフォームを構成してください。使用していない機能やフレームワークは削除するか、インストールしないでください。
-* **設定レビューとパッチ管理：** パッチ管理プロセスの一環として、セキュリティノートやアップデート、パッチに基づき設定をレビュー・更新してください（[A03 ソフトウェアサプライチェーンの不備](A03_2025-Software_Supply_Chain_Failures.md) を参照）。クラウドストレージ（S3 バケット等）の権限設定も定期的にレビューしてください。
-* **セグメント化されたアーキテクチャ：** コンテナ化、セグメンテーション、あるいはクラウドのセキュリティグループ (ACL) を活用し、コンポーネント間やテナント間を安全に分離してください。
-* **セキュリティディレクティブの送信：** セキュリティヘッダーなどのディレクティブをクライアントへ送信してください。
-* **自動検証プロセス：** すべての環境において、設定の有効性を自動で検証するプロセスを導入してください。
-* **中央集中型のエラー管理：** 過剰なエラーメッセージをインターセプトする中央設定を、バックアップとして事前に導入してください。
-* **手動検証の実施：** 検証が自動化されていない場合は、少なくとも年に一度は手動で検証を実施してください。
-* **プラットフォーム機能の活用：** コードや設定ファイル、パイプラインに静的なキーやシークレットを埋め込むのではなく、プラットフォームが提供するアイデンティティ連携 (Identity Federation)、短命な認証情報 (Short-lived Credentials)、またはロールベースのアクセス制御を活用してください。
-## Example attack scenarios
-**シナリオ #1：** 本番サーバーからサンプルアプリケーションが削除されていなかった。攻撃者は、これらのサンプルに含まれる既知の脆弱性を悪用してサーバーを侵害した。さらに、管理コンソールのデフォルトパスワードが変更されていなかったため、攻撃者は管理者としてログインし、システムを完全に乗っ取った。
-**シナリオ #2：** サーバーのディレクトリ一覧表示が無効化されていなかった。攻撃者はディレクトリ構造を把握し、コンパイル済みの Java クラスファイルをダウンロードした。これをデコンパイルしてソースコードをリバースエンジニアリングした結果、アプリケーションに重大なアクセス制御の欠陥があることを突き止めた。
-**シナリオ #3：** アプリケーションサーバーの設定により、スタックトレースを含む詳細なエラーメッセージがユーザーに返されていた。これにより、機密情報や、使用されているコンポーネントのバージョン（脆弱性が既知のものを含む）といった内部情報が攻撃者に露呈した。
-**シナリオ #4：** クラウドサービスプロバイダー (CSP) のデフォルト設定により、共有権限がインターネットに公開されていた。これにより、クラウドストレージ内に保存されていた機密データが第三者に奪取された。
-参考資料およびマッピングされたCWEの一覧について、詳しくはこちら： https://top10.owasp.org/2025/ja/A02_2025-Security_Misconfiguration/</t>
-  </si>
-  <si>
     <t>보안 설정 오류</t>
   </si>
   <si>
@@ -1590,68 +1230,6 @@
 일관되고 재사용 가능한 애플리케이션 보안 설정 하드닝 절차가 없다면 시스템은 더 높은 위험에 놓인다.</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;해당되는 CWE 개수
-   &lt;/td&gt;
-   &lt;td&gt;최대 취약점 발생률
-   &lt;/td&gt;
-   &lt;td&gt;평균 취약점 발생률
-   &lt;/td&gt;
-   &lt;td&gt;최대 테스트 커버리지
-   &lt;/td&gt;
-   &lt;td&gt;평균 테스트 커버리지
-   &lt;/td&gt;
-   &lt;td&gt;평균 가중 악용도
-   &lt;/td&gt;
-   &lt;td&gt;평균 가중 영향도
-   &lt;/td&gt;
-   &lt;td&gt;총 발생 건수
-   &lt;/td&gt;
-   &lt;td&gt;총 CVE 건수
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;16
-   &lt;/td&gt;
-   &lt;td&gt;27.70%
-   &lt;/td&gt;
-   &lt;td&gt;3.00%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;52.35%
-   &lt;/td&gt;
-   &lt;td&gt;7.96
-   &lt;/td&gt;
-   &lt;td&gt;3.97
-   &lt;/td&gt;
-   &lt;td&gt;719,084
-   &lt;/td&gt;
-   &lt;td&gt;1,375
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-다음과 같은 항목들을 포함하여 보안성이 반영된 구성 절차를 수립한다.
-* 재사용 가능한 하드닝 프로세스를 구축하여 필요한 보안 통제가 적용된 동일한 형태의 신규 환경을 빠르고 쉽게 배포 가능해야 한다. 개발, QA, 운영 환경은 모두 동일한 구성으로 설정하며, 각각의 환경에서 서로 다른 자격증명을 사용한다. 이 프로세스는 자동화하여 요구되는 새로운 보안환경을 구성하는 데 필요한 노력을 최소화한다.
-* 사용하지 않은 기능, 컴포넌트, 문서, 샘플을 포함하지 않는 최소한의 플랫폼을 구현한다. 사용하지 않는 기능과 프레임워크는 삭제하거나 설치되지 않아야 한다.
-* 패치 관리 프로세스(참고: [A03 소프트웨어 공급망 체인 실패](A03_2025-Software_Supply_Chain_Failures.md)) 수행 시 모든 보안 공지, 업데이트, 패치에 따른 적절한 검토 및 업데이트를 한다. 또한, 클라우드 스토리지 권한(예: S3 버킷 권한)을 점검한다.
-* 구성 요소 간 또는 테넌트 간 효과적으로 격리할 수 있도록 세분화, 컨테이너화, 클라우드 보안 그룹(ACL)을 활용해 애플리케이션 아키텍쳐를 설계함으로써 효과적이고 안전한 분리 구조를 보장한다.
-* 보안 지시문을 클라이언트로 보내야 한다. (예: 보안 헤더)
-* 자동화된 프로세스를 구축하여 모든 환경에서 해당 설정들의 안전성을 검증한다.
-* 만일의 경우를 대비해, 과도한 에러 메시지가 사용자에게 노출되지 않도록 공통 설정을 사전에 구성한다.
-* 만약 이런 검증사항들이 자동화되지 않았다면, 최소한 매년 1회는 수동으로 검증한다.
-* 코드, 설정 파일, 파이프 라인 내 정적인 키나 시크릿을 저장하는 대신 플랫폼에서 제공하는 아이덴티티 페더레이션, 단기 유효 자격 증명, 또는 역할 기반 접근 매커니즘을 사용한다.
-## Example attack scenarios
-**시나리오 1:** 운영 서버에서 테스트용 애플리케이션이 지워지지 않았다. 테스트용 애플리케이션은 공격자가 해당 서버를 공격할 수 있는 보안 취약점이 존재한다고 알려져 있으며, 그중 하나의 애플리케이션은 관리자용 콘솔이라 가정해 보겠다. 그리고 기본 계정은 변경되지 않았다. 이런 경우 공격자는 기본 계정으로 로그인 한 뒤 시스템 장악이 가능하다.
-**시나리오 2:** 서버에서 디렉토리 리스팅이 활성화 되었을 때 공격자는 단순하게 디렉토리 목록을 탐색할 수 있다. 공격자는 컴파일된 자바 클래스들을 찾거나 다운로드 할 수 있고, 이런 클래스들을 디컴파일 하거나 리버싱 엔지니어링을 통해 코드를 볼 수 있다. 그 뒤 공격자는 애플리케이션 내에서 서버 접근 제어 취약점을 찾은 뒤 악용 가능하다.
-**시나리오 3:** 사용자에게 반환되는 스택 트레이스(Stack trace) 같은 자세한 에러 메시지가 표시되도록 설정되어 있는 경우 민감한 정보나 해당 컴포넌트 버전에 알려진 취약점 같은 근본적 취약점이 노출될 가능성이 있다.
-**시나리오 4:** 클라우드 서비스 제공자(Cloud service provider, CSP)는 인터넷에 자원을 공유하는 권한이 기본 설정이다. 이는 민감한 정보가 공개된 클라우드 스토리지 내 저장될 시 관계자 외 접근을 허용할 수 있다.
-참고 자료와 매핑된 CWE 목록에 대한 자세한 정보: https://top10.owasp.org/2025/ko/A02_2025-Security_Misconfiguration/</t>
-  </si>
-  <si>
     <t>Configuração Insegura (Security Misconfiguration)</t>
   </si>
   <si>
@@ -1668,68 +1246,6 @@
 Sem um processo de endurecimento (_hardening_) de configuração de segurança de aplicação concentrado e repetível, os sistemas correm um risco maior.</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWEs Mapeadas 
-   &lt;/td&gt;
-   &lt;td&gt;Taxa Máx. de Incidência
-   &lt;/td&gt;
-   &lt;td&gt;Taxa Média de Incidência
-   &lt;/td&gt;
-   &lt;td&gt;Cobertura Máxima
-   &lt;/td&gt;
-   &lt;td&gt;Cobertura Média
-   &lt;/td&gt;
-   &lt;td&gt;Exploit Médio Ponderado
-   &lt;/td&gt;
-   &lt;td&gt;Impacto Médio Ponderado
-   &lt;/td&gt;
-   &lt;td&gt;Total de Ocorrências
-   &lt;/td&gt;
-   &lt;td&gt;Total de CVEs
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;16
-   &lt;/td&gt;
-   &lt;td&gt;27.70%
-   &lt;/td&gt;
-   &lt;td&gt;3.00%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;52.35%
-   &lt;/td&gt;
-   &lt;td&gt;7.96
-   &lt;/td&gt;
-   &lt;td&gt;3.97
-   &lt;/td&gt;
-   &lt;td&gt;719,084
-   &lt;/td&gt;
-   &lt;td&gt;1,375
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Processos de instalação seguros devem ser implementados, incluindo:
-- Um processo de _hardening_ repetível que permita a implantação rápida e fácil de outro ambiente devidamente bloqueado. Os ambientes de desenvolvimento, QA e produção devem ser configurados de forma idêntica, com credenciais diferentes usadas em cada um. Este processo deve ser automatizado para minimizar o esforço necessário para configurar um novo ambiente seguro.
-- Uma plataforma mínima, sem quaisquer recursos, componentes, documentação ou amostras desnecessárias. Remova ou não instale recursos e **frameworks** não utilizados.
-- Uma tarefa para revisar e atualizar as configurações de acordo com todas as notas de segurança, atualizações e **patches** como parte do processo de gerenciamento de **patches** (veja [A03 Falhas na Cadeia de Suprimentos de Software](A03_2025-Software_Supply_Chain_Failures.md)). Revise as permissões de armazenamento em nuvem (ex: permissões de buckets S3).
-- Uma arquitetura de aplicação segmentada que forneça separação eficaz e segura entre componentes ou usuários (_tenants_), com segmentação, conteinerização ou grupos de segurança de nuvem (ACLs).
-- Envio de diretivas de segurança para os clientes, ex: **headers** de segurança.
-- Um processo automatizado para verificar a eficácia das configurações e definições em todos os ambientes.
-- Adição proativa de uma configuração central para interceptar mensagens de erro excessivas como reserva (_backup_).
-- Se essas verificações não forem automatizadas, elas devem ser verificadas manualmente, no mínimo, anualmente.
-- Utilize federação de identidade, credenciais de curta duração ou mecanismos de acesso baseados em funções (RBAC) fornecidos pela plataforma subjacente, em vez de incorporar chaves estáticas ou segredos (_secrets_) no código, arquivos de configuração ou **pipelines**.
-## Example attack scenarios
-**Cenário #1:** O servidor de aplicação vem com aplicações de exemplo não removidas do servidor de produção. Essas aplicações de exemplo têm falhas de segurança conhecidas que os **atacantes** usam para comprometer o servidor. Suponha que uma dessas aplicações seja o console de administração e as contas padrão não foram alteradas. Nesse caso, o **atacante** faz o login com a senha padrão e assume o controle.
-**Cenário #2:** A listagem de diretórios não está desativada no servidor. Um **atacante** descobre que pode simplesmente listar os diretórios. O **atacante** encontra e baixa as classes Java compiladas, que ele descompila e faz engenharia reversa para visualizar o código. O **atacante**, então, encontra uma falha grave de controle de acesso na aplicação.
-**Cenário #3:** A configuração do servidor de aplicação permite que mensagens de erro detalhadas, como _stack traces_, sejam retornadas aos usuários. Isso potencialmente expõe informações sensíveis ou falhas subjacentes, como versões de componentes que são conhecidamente vulneráveis.
-**Cenário #4:** Um provedor de serviços de nuvem (CSP) define por padrão permissões de compartilhamento abertas para a Internet. Isso permite que dados sensíveis armazenados no armazenamento em nuvem sejam acessados.
-Para mais informações sobre as referências e a lista de CWEs mapeadas: https://top10.owasp.org/2025/pt-BR/A02_2025-Security_Misconfiguration/</t>
-  </si>
-  <si>
     <t>安全配置错误</t>
   </si>
   <si>
@@ -1744,68 +1260,6 @@
 * 应用服务器、应用框架（例如 Struts、Spring、ASP.NET）、库、数据库等的安全设置未设为安全值。
 * 服务器没有发送安全头或安全指令，或者它们未设为安全值。
 如果没有协调一致、可重复的应用安全配置加固流程，系统会面临更高风险。</t>
-  </si>
-  <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;映射的 CWE 数量
-   &lt;/td&gt;
-   &lt;td&gt;最大发生率
-   &lt;/td&gt;
-   &lt;td&gt;平均发生率
-   &lt;/td&gt;
-   &lt;td&gt;最大覆盖率
-   &lt;/td&gt;
-   &lt;td&gt;平均覆盖率
-   &lt;/td&gt;
-   &lt;td&gt;平均加权可利用性
-   &lt;/td&gt;
-   &lt;td&gt;平均加权影响
-   &lt;/td&gt;
-   &lt;td&gt;发生总数
-   &lt;/td&gt;
-   &lt;td&gt;CVE 总数
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;16
-   &lt;/td&gt;
-   &lt;td&gt;27.70%
-   &lt;/td&gt;
-   &lt;td&gt;3.00%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;52.35%
-   &lt;/td&gt;
-   &lt;td&gt;7.96
-   &lt;/td&gt;
-   &lt;td&gt;3.97
-   &lt;/td&gt;
-   &lt;td&gt;719,084
-   &lt;/td&gt;
-   &lt;td&gt;1,375
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-应实施安全安装流程，包括：
-* 建立可重复的加固流程，能够快速、轻松地部署另一个经过适当锁定的环境。开发、QA 和生产环境应以相同方式配置，但各环境使用不同凭据。该流程应自动化，以减少搭建新安全环境所需的工作量。
-* 使用最小化平台，不包含任何不必要的功能、组件、文档或示例。移除或不要安装未使用的功能和框架。
-* 将审查和更新配置作为补丁管理流程的一部分，确保配置符合所有安全公告、更新和补丁要求（参见 [A03 软件供应链失效](A03_2025-Software_Supply_Chain_Failures.md)）。审查云存储权限（例如 S3 bucket 权限）。
-* 采用分段应用架构，通过分段、容器化或云安全组（ACL）在组件或租户之间实现有效且安全的隔离。
-* 向客户端发送安全指令，例如安全头。
-* 建立自动化流程，验证所有环境中的配置和设置是否有效。
-* 主动增加集中配置，作为拦截过多错误消息的备用措施。
-* 如果这些验证没有自动化，至少应每年手动验证一次。
-* 使用底层平台提供的身份联合、短期凭据或基于角色的访问机制，而不是在代码、配置文件或流水线中嵌入静态密钥或 secret。
-## Example attack scenarios
-**场景 #1：** 应用服务器附带的示例应用没有从生产服务器中移除。这些示例应用存在已知安全缺陷，攻击者可利用它们攻陷服务器。假设其中一个示例应用是管理控制台，且默认账户没有修改。攻击者就能使用默认密码登录并接管系统。
-**场景 #2：** 服务器未禁用目录列表。攻击者发现可以直接列出目录。他找到并下载编译后的 Java 类文件，反编译并逆向工程查看代码。随后攻击者在应用中发现严重访问控制缺陷。
-**场景 #3：** 应用服务器配置允许向用户返回详细错误消息，例如堆栈跟踪。这可能暴露敏感信息或底层缺陷，例如已知易受攻击的组件版本。
-**场景 #4：** 云服务提供商（CSP）默认将共享权限开放到互联网。这会允许云存储中的敏感数据被访问。
-有關參考資料及已對應 CWE 清單的更多資訊： https://top10.owasp.org/2025/zh-Hant/A02_2025-Security_Misconfiguration/</t>
   </si>
   <si>
     <t>A03:2025</t>
@@ -5506,20 +4960,6 @@
     <t>認証の不備 (Authentication Failures)</t>
   </si>
   <si>
-    <t>本脆弱性は、攻撃者がシステムを欺き、無効なユーザーや誤ったユーザーを正当なものとして認識させた場合に発生します。
-以下の項目に当てはまる場合、アプリケーションに認証上の不備が存在する可能性があります。
-* **自動化攻撃の許容：** クレデンシャルスタッフィング (Credential Stuffing) や、流出した資格情報のバリエーションを試すパスワードスプレー攻撃 (Password Spray Attacks) を許容している。
-* **ブルートフォース攻撃への脆弱性：** ブルートフォースやその他の自動化・スクリプト化された攻撃を迅速にブロックしていない。
-* **脆弱なパスワードの許可：** デフォルト設定、脆弱な、あるいは広く知られたパスワード（「Password1」や admin/admin など）の使用を許可している。
-* **漏洩済み情報の利用：** 既に侵害が確認されている資格情報を用いて新規アカウントを作成できてしまう。
-* **不適切なリカバリプロセス：** 「秘密の質問」のような、安全性を確保できない知識ベースの回答に依存したパスワード復旧プロセスを採用している。
-* **不十分なデータ保護：** パスワードをプレーンテキスト、あるいは脆弱なハッシュ形式で保存している（[A04:2025 暗号化の失敗](A04_2025-Cryptographic_Failures.md) 参照）。
-* **MFA の欠如：** 多要素認証 (MFA) が実装されていない、あるいはそのフォールバック手段が脆弱である。
-* **セッション管理の不備：** URL や安全でない場所へセッション ID を露出させている、あるいはログイン後にセッション ID を再利用している。
-* **不完全なログアウト：** ログアウト時や一定時間の無活動後に、セッションや認証トークン（特に SSO トークン）が正しく無効化されない。
-* **検証の不足：** 提供された資格情報の適用範囲 (Scope) や意図された対象 (Audience) を正しく検証していない。</t>
-  </si>
-  <si>
     <t>## Score table
 &lt;table&gt;
   &lt;tr&gt;
@@ -6403,23 +5843,6 @@
     <t>Security Logging &amp; Alerting Failures</t>
   </si>
   <si>
-    <t>Without logging and monitoring, attacks and breaches cannot be detected, and without alerting it is very difficult to respond quickly and effectively during a security incident. Insufficient logging, continuous monitoring, detection, and alerting to initiate active responses occurs any time:
-* Auditable events, such as logins, failed logins, and high-value transactions, are not logged or logged inconsistently (for instance, only logging successful logins, but not failed attempts).
-* Warnings and errors generate no, inadequate, or unclear log messages.
-* The integrity of logs is not properly protected from tampering.
-* Logs of applications and APIs are not monitored for suspicious activity.
-* Logs are only stored locally, and not properly backedup.
-* Appropriate alerting thresholds and response escalation processes are not in place or effective. Alerts are not received or reviewed within a reasonable amount of time.
-* Penetration testing and scans by dynamic application security testing (DAST) tools (such as Burp or ZAP) do not trigger alerts.
-* The application cannot detect, escalate, or alert for active attacks in real-time or near real-time.
-* You are vulnerable to sensitive information leakage by making logging and alerting events visible to a user or an attacker (see [A01:2025-Broken Access Control](A01_2025-Broken_Access_Control.md)), or by logging sensitive information that should not be logged (such as PII or PHI).
-* You are vulnerable to injections or attacks on the logging or monitoring systems if log data is not correctly encoded.
-* The application is missing or mishandling errors and other exceptional conditions, such that the system is unaware there was an error, and is therefore unable to log there was a problem.
-* Adequate ‘use cases’ for issuing alerts are missing or outdated to recognize a special situation.
-* Too many false positive alerts make it impossible to distinguish important alerts from unimportant ones, resulting in them being recognized too late or not at all (physical overload of the SOC team).
-* Detected alerts cannot be processed correctly because the playbook for the use case is incomplete, out of date, or missing.</t>
-  </si>
-  <si>
     <t>## Score table
 &lt;table&gt;
   &lt;tr&gt;
@@ -6490,23 +5913,6 @@
     <t>Selhání bezpečnostního logování a upozorňování (Security Logging &amp; Alerting Failures)</t>
   </si>
   <si>
-    <t>Bez logování a monitorování nelze útoky a narušení zabezpečení odhalit a bez upozorňování je během bezpečnostního incidentu velmi obtížné reagovat rychle a účinně. K nedostatkům v logování, průběžném monitorování, detekci a upozorňování, které mají vést k zahájení aktivní reakce, dochází vždy, když:
-* Auditovatelné události, jako jsou přihlášení, neúspěšná přihlášení a transakce s vysokou hodnotou, nejsou logovány vůbec nebo jsou logovány nekonzistentně (například se logují pouze úspěšná přihlášení, nikoli neúspěšné pokusy).
-* Varování a chyby negenerují žádné, dostatečné nebo srozumitelné logovací záznamy.
-* Integrita logů není řádně chráněna před manipulací.
-* Logy aplikací a rozhraní API nejsou monitorovány z hlediska podezřelé aktivity.
-* Logy jsou ukládány pouze lokálně a nejsou řádně zálohovány.
-* Vhodné prahové hodnoty pro upozorňování a procesy eskalace reakce nejsou zavedeny nebo nejsou účinné. Upozornění nejsou přijímána ani vyhodnocována v přiměřené době.
-* Penetrační testování a skeny prováděné nástroji pro dynamické testování bezpečnosti aplikací (DAST), jako jsou Burp nebo ZAP, nespouštějí upozornění.
-* Aplikace nedokáže aktivní útoky detekovat, eskalovat ani na ně upozornit v reálném čase nebo téměř v reálném čase.
-* Jste zranitelní vůči úniku citlivých informací tím, že události logování a upozorňování zpřístupníte uživateli nebo útočníkovi (viz [A01:2025 Nedostatečné řízení přístupu (Broken Access Control)](A01_2025-Broken_Access_Control.md)), nebo tím, že logujete citlivé informace, které by logovány být neměly (například PII nebo PHI).
-* Pokud nejsou data v logu správně zakódována, jste zranitelní vůči injektážím nebo útokům na systémy logování či monitorování.
-* Aplikace opomíjí chyby a jiné výjimečné stavy nebo je zpracovává nesprávně, takže systém neví, že k chybě došlo, a není proto schopen zaznamenat, že nastal problém.
-* Odpovídající „use cases“ pro vyvolání upozornění chybějí nebo jsou zastaralé, a proto nelze rozpoznat zvláštní situaci.
-* Příliš velké množství falešně pozitivních upozornění znemožňuje odlišit důležitá upozornění od nedůležitých, v důsledku čehož jsou rozpoznána příliš pozdě, nebo vůbec ne (fyzické přetížení týmu SOC).
-* Zjištěná upozornění nelze správně zpracovat, protože playbook pro daný use case je neúplný, zastaralý nebo chybí.</t>
-  </si>
-  <si>
     <t>## Score table
 &lt;table&gt;
   &lt;tr&gt;
@@ -6574,23 +5980,6 @@
     <t>Unzureichendes Sicherheitslogging und Alarmierung</t>
   </si>
   <si>
-    <t>Ohne Protokollierung und Überwachung lassen sich Angriffe und Sicherheitsverletzungen nicht erkennen, und ohne Warnmeldungen ist es sehr schwierig, bei einem Sicherheitsvorfall schnell und effektiv zu reagieren. Eine unzureichende Protokollierung, kontinuierliche Überwachung, Erkennung und Warnmeldung zur Einleitung aktiver Maßnahmen kommt immer dann vor, wenn Folgendes zutrifft:
-* Nachvollziehbare Ereignisse, wie Anmeldungen, fehlgeschlagene Anmeldungen und wertvolle Transaktionen, werden nicht protokolliert (zum Beispiel nur erfolgreiche Anmeldungen protokollieren, nicht aber fehlgeschlagene Versuche).
-* Warnungen und Fehler erzeugen keine, unangemessene oder unklare Log-Einträge.
-* Die Integrität der Protokolle ist nicht ausreichend vor Manipulationen geschützt.
-* Die Logs von Anwendungen und APIs werden nicht auf verdächtige Aktivitäten überwacht.
-* Protokolle werden nur lokal gespeichert und nicht angemessen gesichert.
-* Geeignete Schwellenwerte für Warnmeldungen und Eskalationsprozesse für Gegenmaßnahmen sind nicht vorhanden oder nicht wirksam. Benachrichtigungen werden nicht innerhalb einer angemessenen Frist empfangen oder geprüft.
-* Penetrationstests und Scans durch DAST-Tools (Dynamic Application Security Testing) (wie Burp oder ZAP) lösen keine Alarme aus.
-* Die Anwendung kann Angriffe weder in Echtzeit noch nahezu in Echtzeit erkennen, eskalieren oder Alarm schlagen.
-* Sie sind anfällig für den Verlust sensibler Informationen, wenn Sie Protokollierungs- und Warnereignisse für eine:n Benutzer:in oder eine:n Angreifer:in sichtbar machen (siehe [A01:2025-Mangelhafte Zugriffskontrolle](A01_2025-Broken_Access_Control.md)) oder wenn Sie sensible Informationen protokollieren, die nicht protokolliert werden sollten (wie z. B. personenbezogene Daten oder geschützte Gesundheitsdaten).
-* Sie sind anfällig für Injection oder Angriffe auf die Protokollierungs- oder Überwachungssysteme, wenn Protokolldaten nicht encoded sind.
-* Die Anwendung erkennt Fehler und andere Ausnahmebedingungen nicht oder sie behandelt diese falsch, sodass das System nicht erkennt, dass ein Fehler aufgetreten ist, und daher nicht protokollieren kann, dass ein Problem vorlag.
-* Es fehlen angemessene „Anwendungsfälle“ für die Ausgabe von Warnmeldungen oder diese sind veraltet, um eine besondere Situation zu erkennen.
-* Zu viele Fehlalarme machen es unmöglich, wichtige Warnmeldungen von unwichtigen zu unterscheiden, was dazu führt, dass sie zu spät oder gar nicht erkannt werden (physische Überlastung des SOC-Teams).
-* Erkannte Warnmeldungen können nicht korrekt verarbeitet werden, da das Handbuch für den Anwendungsfall unvollständig, veraltet oder nicht vorhanden ist.</t>
-  </si>
-  <si>
     <t>## Score table
 &lt;table&gt;
   &lt;tr&gt;
@@ -6656,23 +6045,6 @@
   </si>
   <si>
     <t>Fallas en el Registro, Alerta y Monitoreo de Seguridad</t>
-  </si>
-  <si>
-    <t>Sin registro (logging) y monitoreo (monitoring), los ataques y las brechas de seguridad no pueden detectarse, y sin alertas (alerting) es muy difícil responder de forma rápida y eficaz durante un incidente de seguridad. Las fallas por registro, monitoreo continuo, detección y alertas insuficientes para iniciar respuestas activas se producen siempre que:
-* No se registran eventos auditables, como los inicios de sesión, las fallas de inicio de sesión y las transacciones de alto valor, o se registran de forma incoherente (por ejemplo, registrando solo los inicios de sesión correctos, pero no los intentos fallidos).
-* Las advertencias y los errores no generan mensajes de registro, o estos son inadecuados o poco claros.
-* La integridad de los registros no está debidamente protegida contra la manipulación.
-* Los registros de las aplicaciones y las API no se monitorean para detectar actividades sospechosas.
-* Los registros solo se almacenan localmente y no se dispone de las copias de seguridad adecuadas.
-* No existen o no son efectivos los umbrales de alerta y los procesos de escalado de respuesta adecuados. Las alertas no se reciben o no se revisan en un tiempo razonable.
-* Las pruebas de penetración (pentesting) y los escaneos mediante herramientas de pruebas de seguridad de aplicaciones dinámicas (DAST) (como Burp Suite o ZAP) no activan alertas.
-* La aplicación no puede detectar, escalar o alertar sobre ataques activos en tiempo real o casi en tiempo real.
-* Se es vulnerable a la filtración de información sensible al hacer visibles los eventos de registro y alerta para un usuario o un atacante (ver [A01:2025-Pérdida de Control de Acceso](A01_2025-Broken_Access_Control.md)), o al registrar información sensible que no debería registrarse (como PII o PHI).
-* Se es vulnerable a inyecciones o ataques a los sistemas de registro o monitoreo si los datos de los registros no están correctamente codificados.
-* La aplicación carece de errores u otras condiciones excepcionales, o los gestiona de forma inadecuada, de modo que el sistema no es consciente de que se ha producido un error y, por tanto, no puede registrar que ha habido un problema.
-* Faltan "casos de uso" adecuados para la emisión de alertas o estos están desactualizados para reconocer una situación especial.
-* Demasiadas alertas de falsos positivos hacen imposible distinguir las alertas importantes de las que no lo son, lo que provoca que se reconozcan demasiado tarde o no se reconozcan en absoluto (sobrecarga física del equipo del SOC).
-* Las alertas detectadas no pueden procesarse correctamente porque el manual de procedimientos (playbook) para el caso de uso es incompleto, está desactualizado o no existe.</t>
   </si>
   <si>
     <t>## Score table
@@ -6788,23 +6160,6 @@
 برای اطلاعات بیشتر درباره منابع و فهرست CWEهای نگاشت‌شده: https://top10.owasp.org/2025/fa/A09_2025-Security_Logging_and_Alerting_Failures/</t>
   </si>
   <si>
-    <t>Senza logging e monitoraggio, gli attacchi e le violazioni non possono essere rilevati, e senza alerting è molto difficile rispondere in modo rapido ed efficace durante un incidente di sicurezza. Un logging insufficiente, un monitoraggio continuo, il rilevamento e l'alerting per avviare risposte attive si verificano ogni volta che:
-* Gli eventi verificabili, come i login, i login falliti e le transazioni di alto valore, non vengono registrati o vengono registrati in modo incoerente (ad esempio, vengono registrati solo i login riusciti, ma non i tentativi falliti).
-* Gli avvisi e gli errori generano messaggi di log assenti, inadeguati o poco chiari.
-* L'integrità dei log non è adeguatamente protetta dalla manomissione.
-* I log delle applicazioni e delle API non vengono monitorati per attività sospette.
-* I log vengono archiviati solo localmente e non vengono adeguatamente sottoposti a backup.
-* Soglie di alerting appropriate e processi di escalation delle risposte non sono in atto o efficaci. Gli alert non vengono ricevuti o esaminati entro un tempo ragionevole.
-* I penetration test e le scansioni degli strumenti di dynamic application security testing (DAST) (come Burp o ZAP) non attivano alert.
-* L'applicazione non è in grado di rilevare, escalare o avvisare per attacchi attivi in tempo reale o quasi in tempo reale.
-* Sei vulnerabile alla fuga di informazioni sensibili rendendo visibili gli eventi di logging e alerting a un utente o a un attaccante (vedi [A01:2025-Broken Access Control](A01_2025-Broken_Access_Control.md)), o registrando informazioni sensibili che non dovrebbero essere registrate (come PII o PHI).
-* Sei vulnerabile a injection o attacchi ai sistemi di logging o monitoraggio se i dati dei log non sono correttamente codificati.
-* L'applicazione manca o gestisce male gli errori e altre condizioni eccezionali, in modo tale che il sistema non sia consapevole che si è verificato un errore e quindi non sia in grado di registrare che c'è stato un problema.
-* Mancano o sono obsoleti adeguati 'use case' per l'emissione di alert per riconoscere una situazione speciale.
-* Troppi alert falsi positivi rendono impossibile distinguere gli alert importanti da quelli non importanti, con il risultato che vengono riconosciuti troppo tardi o per niente (sovraccarico fisico del team SOC).
-* Gli alert rilevati non possono essere elaborati correttamente perché il playbook per il caso d'uso è incompleto, obsoleto o mancante.</t>
-  </si>
-  <si>
     <t>## Score table
 &lt;table&gt;
   &lt;tr&gt;
@@ -6870,24 +6225,6 @@
   </si>
   <si>
     <t>セキュリティログとアラートの不備 (Security Logging and Alerting Failures)</t>
-  </si>
-  <si>
-    <t>ロギングと監視 (Monitoring) がなければ攻撃や侵害を検知できず、適切なアラート (Alerting) がなければ、セキュリティインシデント発生時に迅速かつ効果的な対応をとることが困難になります。
-以下のような状況にある場合、アプリケーションは脆弱です。
-* ログイン、ログイン失敗、および高価値な取引などの監査可能なイベントが記録されていない、あるいは不整合である（例：ログイン成功のみを記録し、失敗を記録していない）。
-* 警告やエラーが発生しても、ログメッセージが生成されない、あるいは不適切で不明確である。
-* ログの完全性 (Integrity) が保護されておらず、改ざんのリスクに晒されている。
-* アプリケーションや API のログが、不審なアクティビティに対して監視されていない。
-* ログがローカルに保存されるだけで、適切にバックアップされていない。
-* 適切なアラート閾値やレスポンス・エスカレーションプロセスが機能しておらず、アラートが合理的な時間内に受信・確認されない。
-* ペネトレーションテストや DAST (動的アプリケーションセキュリティテスト) ツール（Burp や ZAP 等）によるスキャンが、アラートをトリガーしない。
-* アプリケーションが進行中の攻撃をリアルタイム、あるいはそれに近い速度で検知・通知・エスカレーションできない。
-* ログやアラートの内容がユーザーや攻撃者に露出している（[A01:2025 アクセス制御の不備](A01_2025-Broken_Access_Control.md) 参照）、あるいは個人識別情報 (PII) や健康情報 (PHI) などの記録すべきでない機密情報がログに含まれている。
-* ログデータが適切にエンコードされておらず、ロギングまたは監視システム自体へのインジェクション攻撃を許容している。
-* エラーや例外的な状況の処理に失敗しているため、システムがエラーを認識できず、結果として問題を記録できない。
-* 特定の異常事態を認識するための適切なアラート用「ユースケース」が不足している、あるいは陳腐化している。
-* 誤検知 (False Positive) が多すぎて重要なアラートを判別できず、SOC (セキュリティ運用センター) チームが物理的な過負荷や「警報疲れ」を起こしている。
-* プレイブック (Playbook)（対応手順書）が不完全、あるいは欠落しているため、検知されたアラートを正しく処理できない。</t>
   </si>
   <si>
     <t>## Score table
@@ -6942,24 +6279,6 @@
     <t>보안 로깅 및 알림 실패</t>
   </si>
   <si>
-    <t>로깅과 모니터링이 없으면 공격 및 침해를 탐지할 수 없으며, 알림이 없으면 보안 인시던트 발생시 신속하고 효과적으로 대응하기가 매우 어렵다. 다음과 같은 경우에는 불충분한 로깅, 지속적인 모니터링, 탐지 및 능동적 대응을 시작하기 위한 알림의 미흡이 발생한다. 아래와 같은 경우, 능동적 대응을 개시하기 위한 로깅, 지속적 모니터링, 탐지, 알림이 부족한 것으로 볼 수 있다.
-* 로그인, 로그인 실패, 중요 거래 데이터 등 감사가 필요한 대상의 이벤트가 누락되거나 기준 없이 들쭉날쭉하게(예: 성공 로그인만 기록) 로깅되는 경우.
-* 경고 및 오류가 로그 메시지를 생성하지 않거나, 부적절하거나, 불명확한 로그를 생성하는 경우.
-* 로그가 위변조되지 않도록 무결성 보호가 적용되지 않는 경우.
-* 애플리케이션 및 API 로그를 기반으로 한 이상징후 모니터링이 수행되지 않는 경우.
-* 로그가 로컬에만 보관되고 백업이 적절히 수행되지 않는 경우.
-* 적절한 알림 임계값 및 대응 에스컬레이션 절차가 마련되어 있지 않거나 효과적이지 않다. 알림이 적시에 확인되지 않거나 검토되지 않는 경우.
-* 동적 애플리케이션 보안 테스트(DAST) 도구(예: Burp 또는 ZAP)에 의한 침투 테스트 및 스캔이 알림을 트리거하지 않는 경우.
-* 진행 중인 공격을 실시간 혹은 준실시간으로 탐지하지 못하거나 상위 단계로 에스컬레이션하거나 알림을 발생시키지 못하는 경우.
-* 로깅 및 알림 이벤트를 사용자 또는 공격자에게 노출 하거나([A01:2025-접근 제어 실패](A01_2025-Broken_Access_Control.md) 참조), 로깅되면 안 되는 민감정보(예: PII 또는 PHI)를 로깅함으로써 민감정보 유출에 취약한 경우.
-* 로그 데이터 인코딩이 부적절해 로깅 또는 모니터링 시스템 자체가 인젝션 등 공격 대상이 되는 경우.
-* 애플리케이션이 오류 및 예외 처리를 누락 또는 오처리하여 시스템이 오류 발생 자체를 인지하지 못하고, 결과적으로 문제를 로그로 남길 수 없는 경우.
-* 특수 상황을 식별하기 위한 알림 '유스케이스'가 없거나 오래되어 현재 환경을 반영하지 못한다.
-* 특정 상황을 탐지해 알림을 발생시키기 위한 인시던트 유스케이스(use case)가 없거나, 갱신이 되지 않아 현행 환경을 충분히 반영하지 못하는 경우.
-* 너무 많은 오탐 알림으로 인해 중요한 알림과 중요하지 않은 알림을 구분할 수 없게 되어, 알림이 너무 늦게 인지되거나 전혀 인지되지 않는 경우(SOC 팀의 물리적 과부하).
-* 유스케이스에 대한 플레이북이 불완전하거나, 최신이 아니거나, 누락되어 감지된 알림을 올바르게 처리할 수 없는 경우.</t>
-  </si>
-  <si>
     <t>## Score table
 &lt;table&gt;
   &lt;tr&gt;
@@ -7028,23 +6347,6 @@
     <t>Falhas de Registro e Monitoramento de Segurança</t>
   </si>
   <si>
-    <t>Sem registro e monitoramento, ataques e violações não podem ser detectados, e sem alertas é muito difícil responder de forma rápida e eficaz durante um incidente de segurança. Registro, monitoramento contínuo, detecção e alertas insuficientes para iniciar respostas ativas ocorrem sempre que:
-- Eventos auditáveis, como logins, falhas de login e transações de alto valor, não são registrados ou são registrados de forma inconsistente (por exemplo, registrando apenas logins bem-sucedidos, mas não tentativas falhas).
-- Avisos e erros geram mensagens de _log_ inexistentes, inadequadas ou confusas.
-- A integridade dos _logs_ não é devidamente protegida contra adulteração.
-- _Logs_ de aplicações e APIs não são monitorados em busca de atividades suspeitas.
-- Os _logs_ são armazenados apenas localmente e não possuem backup adequado.
-- Limiares de alerta e processos de escalonamento de resposta apropriados não estão estabelecidos ou não são eficazes. Os alertas não são recebidos ou revisados em um tempo razoável.
-- Testes de invasão (_penetration testing_) e varreduras por ferramentas de testes dinâmicos de segurança de aplicações (DAST), como Burp ou ZAP, não disparam alertas.
-- A aplicação não consegue detectar, escalar ou alertar sobre ataques ativos em tempo real ou próximo ao tempo real.
-- Você está vulnerável ao vazamento de informações sensíveis ao tornar eventos de registro e alerta visíveis para um usuário ou atacante (veja [A01:2025-Controle de Acesso Quebrado](A01_2025-Broken_Access_Control.md)), ou ao registrar informações sensíveis que não deveriam ser gravadas (como PII ou PHI).
-- Você está vulnerável a injeções ou ataques nos sistemas de registro ou monitoramento se os dados de _log_ não forem codificados corretamente.
-- A aplicação omite ou trata incorretamente erros e outras condições excepcionais, de modo que o sistema não percebe que houve um erro e, portanto, não consegue registrar que houve um problema.
-- "Casos de uso" adequados para emissão de alertas estão ausentes ou desatualizados para reconhecer uma situação especial.
-- O excesso de alertas falsos positivos impossibilita distinguir alertas importantes de irrelevantes, resultando em detecções tardias ou inexistentes (sobrecarga física da equipe do SOC).
-- Alertas detectados não podem ser processados corretamente porque o _playbook_ para o caso de uso está incompleto, desatualizado ou ausente.</t>
-  </si>
-  <si>
     <t>## Score table
 &lt;table&gt;
   &lt;tr&gt;
@@ -7112,23 +6414,6 @@
     <t>安全日志记录和告警失效</t>
   </si>
   <si>
-    <t>没有日志记录和监控，就无法检测攻击和安全事件；没有告警，也很难在安全事件中快速有效响应。当出现以下情况时，就会发生日志记录不足、持续监控不足、检测不足，以及无法通过告警发起主动响应的问题：
-* 可审计事件没有记录或记录不一致，例如登录、登录失败和高价值交易（例如只记录成功登录，不记录失败尝试）。
-* 警告和错误不生成日志消息，或生成的消息不足、不清晰。
-* 日志完整性没有得到妥善保护，容易被篡改。
-* 应用和 API 的日志没有被监控以发现可疑活动。
-* 日志只存储在本地，没有正确备份。
-* 没有建立适当的告警阈值和响应升级流程，或这些流程无效。告警没有在合理时间内被接收或审查。
-* 渗透测试和动态应用安全测试（DAST）工具（例如 Burp 或 ZAP）的扫描没有触发告警。
-* 应用无法实时或近实时检测、升级或告警正在发生的攻击。
-* 通过让日志记录和告警事件对用户或攻击者可见，容易导致敏感信息泄露（参见 [A01:2025-失效的访问控制](A01_2025-Broken_Access_Control.md)），或记录了不应记录的敏感信息（例如 PII 或 PHI）。
-* 如果日志数据没有正确编码，就容易受到针对日志或监控系统的注入或攻击。
-* 应用缺失或错误处理错误及其他异常条件，导致系统不知道发生了错误，因此无法记录问题。
-* 缺少足够的、用于触发告警的“用例”，或用例已经过时，无法识别特殊情况。
-* 过多误报让人无法区分重要告警和不重要告警，导致重要告警被过晚识别或完全没有被识别（SOC 团队实际过载）。
-* 因为该用例的剧本不完整、过时或缺失，检测到的告警无法被正确处理。</t>
-  </si>
-  <si>
     <t>## Score table
 &lt;table&gt;
   &lt;tr&gt;
@@ -7205,63 +6490,6 @@
 such as logic bugs, overflows, race conditions, fraudulent transactions, or issues with memory, state, resource, timing, authentication, and authorization. These types of vulnerabilities can negatively affect the confidentiality, availability, and/or integrity of a system or it’s data. Attackers manipulate an application's flawed error handling to strike this vulnerability. </t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWEs Mapped 
-   &lt;/td&gt;
-   &lt;td&gt;Max Incidence Rate
-   &lt;/td&gt;
-   &lt;td&gt;Avg Incidence Rate
-   &lt;/td&gt;
-   &lt;td&gt;Max Coverage
-   &lt;/td&gt;
-   &lt;td&gt;Avg Coverage
-   &lt;/td&gt;
-   &lt;td&gt;Avg Weighted Exploit
-   &lt;/td&gt;
-   &lt;td&gt;Avg Weighted Impact
-   &lt;/td&gt;
-   &lt;td&gt;Total Occurrences
-   &lt;/td&gt;
-   &lt;td&gt;Total CVEs
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;24
-   &lt;/td&gt;
-   &lt;td&gt;20.67%
-   &lt;/td&gt;
-   &lt;td&gt;2.95%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;37.95%
-   &lt;/td&gt;
-   &lt;td&gt;7.11
-   &lt;/td&gt;
-   &lt;td&gt;3.81
-   &lt;/td&gt;
-   &lt;td&gt;769,581
-   &lt;/td&gt;
-   &lt;td&gt;3,416
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-In order to handle an exceptional condition properly we must plan for such situations (expect the worst). We must ‘catch’ every possible system error directly at the place where they occur and then handle it (which means do something meaningful to solve the problem and ensure we recover from the issue). As part of the handling, we should include throwing an error (to inform the user in an understandable way), logging of the event, as well as issuing an alert if we feel that is justified. We should also have a global exception handler in place in case there is ever something we have missed. Ideally, we would also have monitoring and/or observability tooling or functionality that watches for repeated errors or patterns that indicate an on-going attack, that could issue a response, defense, or blocking of some kind. This can help us block and respond to scripts and bots that focus on our error handling weaknesses.
-Catching and handling exceptional conditions ensures that the underlying infrastructure of our programs are not left to deal with unpredictable situations. If you are part way through a transaction of any kind, it is extremely important that you roll back every part of the transaction and start again (also known as failing closed). Attempting to recover a transaction part way through is often where we create unrecoverable mistakes.
-Whenever possible, add rate limiting, resource quotas, throttling, and other limits wherever possible, to prevent exceptional conditions in the first place. Nothing in information technology should be limitless, as this leads to a lack of application resilience, denial of service, successful brute force attacks, and extraordinary cloud bills. 
-Consider whether identical repeated errors, above a certain rate, should only be outputted as statistics showing how often they have occurred and in what time frame. This information should be appended to the original message so as not to interfere with automated logging and monitoring, see [A09:2025 Security Logging &amp; Alerting Failures](A09_2025-Security_Logging_and_Alerting_Failures.md).
-On top of this, we would want to include strict input validation (with sanitization or escaping for potentially hazardous characters that we must accept), and *centralized* error handling, logging, monitoring, and alerting, and a global exception handler. One application should not multiple functions for handling exceptional conditions, it should be performed in one place, the same way each time. We should also create project security requirements for all the advice in this section, perform threat modelling and/or secure design review activities in the design phase of our projects, perform code review or static analysis, as well as execute stress, performance, and penetration testing of the final system.
-If possible, your entire organization should handle exceptional conditions in the same way, as it makes it easier to review and audit code for errors in this important security control.
-## Example attack scenarios
-**Scenario #1:** Resource exhaustion via mishandling of exceptional conditions (Denial of Service) could be caused if the application catches exceptions when files are uploaded, but doesn’t properly release resources after. Each new exception leaves resources locked or otherwise unavailable, until all resources are used up.
-**Scenario #2:** Sensitive data exposure via improper handling or database errors that reveals the full system error to the user. The attacker continues to force errors in order to use the sensitive system information to create a better SQL injection attack. The sensitive data in the user error messages are reconnaissance.
-**Scenario #3:** State corruption in financial transactions could be caused by an attacker interrupting a multi-step transaction via network disruptions. Imagine the transaction order was: debit user account, credit destination account, log transaction. If the system doesn’t properly roll back the entire transaction (fail closed) when there is an error part way through, the attacker could potentially drain the user’s account, or possibly a race condition that allows the attacker to send money to the destination multiple times.
-For more information about the references and the list of mapped CWEs: https://top10.owasp.org/2025/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
-  </si>
-  <si>
     <t>Mauvaise gestion des exceptions</t>
   </si>
   <si>
@@ -7273,62 +6501,6 @@
 Když výjimečné stavy zpracujeme nesprávně, může dojít k mnoha různým bezpečnostním zranitelnostem, jako jsou logické chyby, přetečení, souběhy (race conditiony; též „závodní stavy“), podvodné transakce nebo problémy s pamětí, stavem, zdroji, načasováním, ověřováním a autorizací. Tyto typy zranitelností mohou negativně ovlivnit důvěrnost, dostupnost a/nebo integritu systému nebo jeho dat. Útočníci manipulují s chybným zpracováním chyb aplikace, aby tyto zranitelnosti využili. </t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;Počet mapovaných CWE 
-   &lt;/td&gt;
-   &lt;td&gt;Max míra výskytu
-   &lt;/td&gt;
-   &lt;td&gt;Průměrná míra výskytu
-   &lt;/td&gt;
-   &lt;td&gt;Max pokrytí
-   &lt;/td&gt;
-   &lt;td&gt;Průměrné pokrytí
-   &lt;/td&gt;
-   &lt;td&gt;Průměrná vážená zneužitelnost
-   &lt;/td&gt;
-   &lt;td&gt;Průměrný vážený dopad
-   &lt;/td&gt;
-   &lt;td&gt;Celkový počet výskytů
-   &lt;/td&gt;
-   &lt;td&gt;Celkový počet CVE
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;24
-   &lt;/td&gt;
-   &lt;td&gt;20,67 %
-   &lt;/td&gt;
-   &lt;td&gt;2,95 %
-   &lt;/td&gt;
-   &lt;td&gt;100,00 %
-   &lt;/td&gt;
-   &lt;td&gt;37,95 %
-   &lt;/td&gt;
-   &lt;td&gt;7,11
-   &lt;/td&gt;
-   &lt;td&gt;3,81
-   &lt;/td&gt;
-   &lt;td&gt;769 581
-   &lt;/td&gt;
-   &lt;td&gt;3 416
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Abychom mohli výjimečný stav správně zpracovat, musíme na takové situace plánovat (očekávat nejhorší). Musíme „zachytit“ každou možnou systémovou chybu přímo v místě, kde k ní dochází, a poté ji zpracovat (tj. udělat něco smysluplného k vyřešení problému a zajistit, že se z něj zotavíme). Součástí zpracování by mělo být vyvolání chyby (aby byl uživatel informován srozumitelným způsobem), logování události a také vyvolání upozornění (alertu), pokud to považujeme za oprávněné. Měli bychom mít také globální handler výjimek (globální obsluhu/zpracování výjimek) pro případ, že nám něco unikne. V ideálním případě bychom měli mít také nástroje nebo funkcionalitu pro monitoring a/nebo observability, které sledují opakované chyby nebo vzorce naznačující probíhající útok a které mohou vyvolat nějakou reakci, obranu nebo blokování. To nám může pomoci blokovat a reagovat na skripty a boty, které se zaměřují na slabiny našeho zpracování chyb.
-Zachytávání a zpracování výjimečných stavů zajišťuje, že základní infrastruktura našich programů není ponechána, aby se vypořádávala s nepředvídatelnými situacemi. Pokud jste uprostřed jakékoli transakce, je mimořádně důležité, abyste provedli rollback každé její části a začali znovu (také známé jako fail closed). Pokus o zotavení transakce uprostřed jejího průběhu je často místem, kde vznikají nevratné chyby.
-Kdykoli je to možné, přidejte rate limiting, kvóty zdrojů, throttling (omezení) a další limity, abyste výjimečným stavům předcházeli už na začátku. V informačních technologiích by nic nemělo být bez limitu, protože to vede k nízké odolnosti aplikací, odmítnutí služby, úspěšným brute force útokům a mimořádně vysokým účtům za cloud. Zvažte, zda by identické opakované chyby nad určitou míru neměly být vypisovány pouze jako statistiky ukazující, jak často nastaly a v jakém časovém rámci. Tyto informace by měly být připojeny k původní zprávě tak, aby nenarušovaly automatizované logování a monitorování, viz [A09:2025 Selhání bezpečnostního logování a upozorňování (Security Logging &amp; Alerting Failures)](A09_2025-Security_Logging_and_Alerting_Failures.md).
-Kromě toho bychom chtěli zahrnout přísnou validaci vstupů (se sanitizací (očištěním) nebo escapováním potenciálně nebezpečných znaků, které musíme akceptovat), centralizované zpracování chyb, logování, monitorování a upozorňování a globální obsluhu výjimek (global exception handler). Jedna aplikace by neměla mít více funkcí pro zpracování výjimečných stavů; mělo by se to provádět na jednom místě, pokaždé stejným způsobem. Měli bychom také vytvořit bezpečnostní požadavky projektu pro všechna doporučení v této části, provést threat modelling (modelování hrozeb) a/nebo aktivity secure design review (bezpečnostní posouzení návrhu) ve fázi návrhu projektů, provést code review (revizi kódu) nebo statickou analýzu a také provést zátěžové, výkonnostní a penetrační testování finálního systému.
-Pokud je to možné, měla by celá vaše organizace zpracovávat výjimečné stavy stejným způsobem, protože to usnadňuje kontrolu a audit kódu z hlediska chyb v této důležité bezpečnostní kontrole.
-## Example attack scenarios
-**Scénář #1:** K vyčerpání zdrojů v důsledku nesprávného zpracování výjimečných stavů (Denial of Service) může dojít, pokud aplikace při nahrávání souborů zachytává výjimky, ale poté řádně neuvolňuje zdroje. Každá nová výjimka zanechává zdroje uzamčené nebo jinak nedostupné, dokud nejsou všechny zdroje vyčerpány.
-**Scénář #2:** Odhalení citlivých údajů v důsledku nesprávného zpracování nebo databázových chyb, které uživateli zobrazí kompletní systémovou chybu. Útočník pokračuje ve vyvolávání chyb, aby mohl citlivé systémové informace využít k vytvoření účinnějšího útoku typu SQL injection. Citlivé údaje v chybových hlášeních pro uživatele jsou součástí průzkumu (reconnaissance).
-**Scénář #3:** Poškození stavu finančních transakcí může být způsobeno útočníkem, který přeruší vícekrokovou transakci narušením síťového spojení. Představte si, že sled kroků transakce je: odepsat z účtu uživatele, připsat na účet příjemce, zaznamenat transakci. Pokud systém při chybě uprostřed transakce správně nevrátí zpět (rollback) celou transakci (fail closed), útočník by mohl potenciálně vyprázdnit účet uživatele, nebo může dojít k souběhu (race condition), který útočníkovi umožní odeslat peníze příjemci vícekrát.
-Další informace o odkazech a seznamu namapovaných CWE: https://top10.owasp.org/2025/cs/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
-  </si>
-  <si>
     <t>Fehlerhafte Behandlung von Ausnahmezuständen</t>
   </si>
   <si>
@@ -7337,126 +6509,12 @@
 Bei fehlerhafter Behandlung von Ausnahmezuständen können vielfältige Schwachstellen entstehen, wie logische Fehler, Überläufe, Race Conditions, betrügerische Transaktionen oder Probleme mit Speicher, Zustand, Ressourcen, Timing, Authentifizierung und Autorisierung. Diese Schwachstellen können die Vertraulichkeit, Verfügbarkeit und/oder Integrität eines Systems oder seiner Daten beeinträchtigen. Angreifer:innen nutzen die fehlerhafte Fehlerbehandlung einer Anwendung aus, um diese Schwachstelle auszunutzen.</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;Zugeordnete CWEs
-   &lt;/td&gt;
-   &lt;td&gt;Max. Häufigkeit
-   &lt;/td&gt;
-   &lt;td&gt;Durchschn. Häufigkeit
-   &lt;/td&gt;
-   &lt;td&gt;Max. Abdeckung
-   &lt;/td&gt;
-   &lt;td&gt;Durchschn. Abdeckung
-   &lt;/td&gt;
-   &lt;td&gt;Durchschn. gewichtete Ausnutzbarkeit
-   &lt;/td&gt;
-   &lt;td&gt;Durchschn. gewichtete Auswirkung
-   &lt;/td&gt;
-   &lt;td&gt;Gesamtanzahl
-   &lt;/td&gt;
-   &lt;td&gt;Summe CVEs
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;24
-   &lt;/td&gt;
-   &lt;td&gt;20.67%
-   &lt;/td&gt;
-   &lt;td&gt;2.95%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;37.95%
-   &lt;/td&gt;
-   &lt;td&gt;7.11
-   &lt;/td&gt;
-   &lt;td&gt;3.81
-   &lt;/td&gt;
-   &lt;td&gt;769,581
-   &lt;/td&gt;
-   &lt;td&gt;3,416
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Um Ausnahmezustände korrekt zu behandeln, müssen wir solche Situationen einplanen (vom Schlimmsten ausgehen). Wir müssen jeden möglichen Systemfehler direkt an der Stelle abfangen, an der er auftritt, und ihn dann behandeln (d. h. etwas Sinnvolles tun, um das Problem zu lösen und die Wiederherstellung sicherzustellen). Als Teil der Behandlung sollten wir einen Fehler werfen (um die/den Benutzer:in verständlich zu informieren), das Ereignis protokollieren sowie bei Bedarf einen Alarm auslösen. Wir sollten außerdem einen globalen Exception-Handler einrichten, für den Fall, dass uns etwas entgangen ist. Idealerweise verfügen wir zusätzlich über Monitoring- und/oder Observability-Werkzeuge, die auf wiederholte Fehler oder Muster hinweisen, die auf einen laufenden Angriff hindeuten, und eine Reaktion, Abwehr oder Blockierung auslösen können. Dies hilft uns, Skripte und Bots zu blockieren und darauf zu reagieren, die unsere Schwachstellen in der Fehlerbehandlung ausnutzen.
-Das Abfangen und Behandeln von Ausnahmezuständen stellt sicher, dass die zugrunde liegende Infrastruktur unserer Programme nicht mit unvorhersehbaren Situationen allein gelassen wird. Befindet man sich mitten in einer Transaktion jeglicher Art, ist es äußerst wichtig, die gesamte Transaktion zurückzusetzen und neu zu beginnen (auch bekannt als „Failing Closed"). Der Versuch, eine Transaktion mittendrin wiederherzustellen, ist oft der Punkt, an dem unbehebbare Fehler entstehen.
-Wo immer möglich sollten Rate Limiting, Ressourcenkontingente, Throttling und andere Begrenzungen eingesetzt werden, um Ausnahmezustände von vornherein zu verhindern. Nichts in der Informationstechnologie sollte unbegrenzt sein, da dies zu mangelnder Anwendungsresilienz, Denial-of-Service, erfolgreichen Brute-Force-Angriffen und enormen Cloud-Kosten führt.
-Es sollte überlegt werden, ob identische, sich wiederholende Fehler ab einer bestimmten Rate nur noch als Statistik ausgegeben werden sollten, die anzeigt, wie oft und in welchem Zeitraum sie aufgetreten sind. Diese Information sollte an die ursprüngliche Meldung angehängt werden, um automatisiertes Logging und Monitoring nicht zu beeinträchtigen, siehe [A09:2025 Unzureichendes Sicherheitslogging und Alarmierung](A09_2025-Security_Logging_and_Alerting_Failures.md).
-Darüber hinaus sollten wir strikte Eingabevalidierung (mit Bereinigung oder Escaping potenziell gefährlicher Zeichen, die wir akzeptieren müssen) sowie *zentralisierte* Fehlerbehandlung, Logging, Monitoring und Alerting mit einem globalen Exception-Handler einsetzen. Eine Anwendung sollte nicht mehrere Funktionen zur Behandlung von Ausnahmezuständen haben – dies sollte einheitlich an einer Stelle erfolgen. Wir sollten zudem Sicherheitsanforderungen für alle Empfehlungen dieses Abschnitts definieren, Bedrohungsmodellierung und/oder sichere Design-Reviews in der Entwurfsphase durchführen, Code-Reviews oder statische Analysen vornehmen sowie Stress-, Performance- und Penetrationstests am fertigen System ausführen.
-Wenn möglich, sollte die gesamte Organisation Ausnahmezustände einheitlich behandeln, da dies die Überprüfung und Auditierung des Codes auf Fehler in dieser wichtigen Sicherheitsmaßnahme erleichtert.
-## Example attack scenarios
-**Szenario Nr. 1:** Ressourcenerschöpfung durch fehlerhafte Behandlung von Ausnahmezuständen (Denial of Service) kann auftreten, wenn die Anwendung beim Datei-Upload Ausnahmen abfängt, die Ressourcen danach jedoch nicht ordnungsgemäß freigibt. Jede neue Ausnahme hinterlässt gesperrte oder anderweitig nicht verfügbare Ressourcen, bis alle Ressourcen verbraucht sind.
-**Szenario Nr. 2:** Offenlegung sensibler Daten durch fehlerhafte Behandlung von Datenbankfehlern, die den vollständigen Systemfehler an die/den Benutzer:in weitergeben. Die/Der Angreifer:in erzwingt weiterhin Fehler, um die sensiblen Systeminformationen für einen gezielteren SQL-Injection-Angriff zu nutzen. Die sensiblen Daten in den Fehlermeldungen dienen dabei als Aufklärung.
-**Szenario Nr. 3:** Zustandskorruption bei Finanztransaktionen kann durch ein:e Angreifer:in verursacht werden, der eine mehrstufige Transaktion durch Netzwerkunterbrechungen stört. Angenommen, die Transaktionsreihenfolge lautet: Nutzerkonto belasten, Zielkonto gutschreiben, Transaktion protokollieren. Wenn das System bei einem Fehler mittendrin die gesamte Transaktion nicht ordnungsgemäß zurücksetzt (Failing Closed), könnte die/der Angreifer:in das Konto der/des Nutzer:in leeren oder über eine Race Condition Geld mehrfach an das Zielkonto senden.
-Weitere Informationen zu den Referenzen und zur Liste der zugeordneten CWEs: https://top10.owasp.org/2025/de/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
-  </si>
-  <si>
     <t>Manejo Inadecuado de Condiciones Excepcionales</t>
   </si>
   <si>
     <t>El manejo inadecuado de condiciones excepcionales en el software ocurre cuando los programas no logran prevenir, detectar y responder a situaciones inusuales e impredecibles, lo que provoca caídas (crashes), comportamientos inesperados y, a veces, vulnerabilidades. Esto puede implicar uno o más de los siguientes tres fallas: la aplicación no previene que ocurra una situación inusual, no identifica la situación mientras está ocurriendo y/o responde de forma deficiente o no responde en absoluto a la situación posteriormente.
 Las condiciones excepcionales pueden ser causadas por una validación de entradas ausente, deficiente o incompleta; por un manejo de errores de alto nivel tardío en lugar de realizarse en las funciones donde ocurren; por estados ambientales inesperados como problemas de memoria, privilegios o red; por un manejo de excepciones inconsistente o por excepciones que no se manejan en absoluto, permitiendo que el sistema caiga en un estado desconocido e impredecible. Cada vez que una aplicación no está segura de su siguiente instrucción, se ha manejado inadecuadamente una condición excepcional. Los errores y excepciones difíciles de encontrar pueden amenazar la seguridad de toda la aplicación durante mucho tiempo.
 Pueden ocurrir muchas vulnerabilidades de seguridad diferentes cuando manejamos inadecuadamente las condiciones excepcionales, como errores de lógica, desbordamientos (overflows), condiciones de carrera (race conditions), transacciones fraudulentas o problemas de memoria, estado, recursos, tiempos (timing), autenticación y autorización. Estos tipos de vulnerabilidades pueden afectar negativamente la confidencialidad, disponibilidad y/o integridad de un sistema o de sus datos. Los atacantes manipulan el manejo de errores defectuoso de una aplicación para atacar esta vulnerabilidad.</t>
-  </si>
-  <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWEs Mapeadas
-   &lt;/td&gt;
-   &lt;td&gt;Tasa Máxima de Incidencia
-   &lt;/td&gt;
-   &lt;td&gt;Tasa Promedio de Incidencia
-   &lt;/td&gt;
-   &lt;td&gt;Cobertura Máxima
-   &lt;/td&gt;
-   &lt;td&gt;Cobertura Promedio
-   &lt;/td&gt;
-   &lt;td&gt;Promedio Ponderado de Explotación
-   &lt;/td&gt;
-   &lt;td&gt;Promedio Ponderado de Impacto
-   &lt;/td&gt;
-   &lt;td&gt;Ocurrencias Totales
-   &lt;/td&gt;
-   &lt;td&gt;CVEs Totales
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;24
-   &lt;/td&gt;
-   &lt;td&gt;20.67%
-   &lt;/td&gt;
-   &lt;td&gt;2.95%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;37.95%
-   &lt;/td&gt;
-   &lt;td&gt;7.11
-   &lt;/td&gt;
-   &lt;td&gt;3.81
-   &lt;/td&gt;
-   &lt;td&gt;769,581
-   &lt;/td&gt;
-   &lt;td&gt;3,416
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Para manejar adecuadamente una condición excepcional, debemos planificar para tales situaciones (esperar lo peor). Debemos "capturar" (catch) cada posible error del sistema directamente en el lugar donde ocurre y luego manejarlo (lo que significa hacer algo significativo para resolver el problema y asegurar que nos recuperamos del mismo). Como parte del manejo, debemos incluir el lanzamiento de un error (para informar al usuario de forma comprensible), el registro (logging) del evento, así como la emisión de una alerta (alerting) si consideramos que está justificado. También deberíamos tener un manejador de excepciones global por si acaso algo se nos ha pasado por alto. Idealmente, también tendríamos herramientas o funcionalidades de monitoreo y/u observabilidad que vigilen errores repetidos o patrones que indiquen un ataque en curso, que pudieran emitir una respuesta, defensa o bloqueo de algún tipo. Esto puede ayudarnos a bloquear y responder a scripts y bots que se centran en nuestras debilidades de manejo de errores.
-Capturar y manejar las condiciones excepcionales garantiza que la infraestructura subyacente de nuestros programas no se deje a merced de situaciones impredecibles. Si se encuentra a mitad de una transacción de cualquier tipo, es extremadamente importante que revierta (roll back) cada parte de la transacción y comience de nuevo (lo que también se conoce como fallar de forma segura o "fail closed"). Intentar recuperar una transacción a medias es a menudo donde creamos errores irrecuperables.
-Siempre que sea posible, añada limitación de tasa (rate limiting), cuotas de recursos, regulación (throttling) y otros límites para prevenir las condiciones excepcionales en primer lugar. Nada en la tecnología de la información debería ser ilimitado, ya que esto conduce a una falta de resiliencia de la aplicación, denegación de servicio, ataques exitosos de fuerza bruta y facturas extraordinarias en la nube.
-Considere si errores idénticos repetidos, por encima de una cierta tasa, deberían mostrarse únicamente como estadísticas que indiquen con qué frecuencia han ocurrido y en qué intervalo de tiempo. Esta información debería añadirse al mensaje original para no interferir con el registro y monitoreo automatizados, consulte [A09:2025-Fallas en el Registro, Alerta y Monitoreo de Seguridad](A09_2025-Security_Logging_and_Alerting_Failures.md).
-Además de esto, querríamos incluir una validación de entradas estricta (con saneamiento o escape para los caracteres potencialmente peligrosos que debamos aceptar), un manejo de errores, registro, monitoreo y alertas *centralizados*, y un manejador de excepciones global. Una aplicación no debería tener múltiples funciones para manejar condiciones excepcionales; debería realizarse en un solo lugar, de la misma manera cada vez. También deberíamos crear requisitos de seguridad del proyecto para todos los consejos de esta sección, realizar actividades de modelado de amenazas y/o revisión de diseño seguro en la fase de diseño de nuestros proyectos, realizar revisiones de código o análisis estático, así como ejecutar pruebas de estrés, rendimiento y penetración del sistema final.
-Si es posible, toda su organización debería manejar las condiciones excepcionales de la misma manera, ya que esto facilita la revisión y auditoría del código en busca de errores en este importante control de seguridad.
-## Example attack scenarios
-**Escenario #1:** El agotamiento de recursos mediante el manejo inadecuado de condiciones excepcionales (Denegación de Servicio) podría producirse si la aplicación captura excepciones cuando se suben archivos, pero no libera adecuadamente los recursos después. Cada nueva excepción deja los recursos bloqueados o no disponibles de otro modo, hasta que se agotan todos los recursos.
-**Escenario #2:** Exposición de datos sensibles mediante un manejo inadecuado o errores de base de datos que revelan el error completo del sistema al usuario. El atacante continúa forzando errores para utilizar la información sensible del sistema para crear un mejor ataque de inyección SQL. Los datos sensibles en los mensajes de error del usuario sirven de reconocimiento (reconnaissance).
-**Escenario #3:** La corrupción de estado en transacciones financieras podría ser causada por un atacante que interrumpe una transacción de varios pasos mediante interrupciones de red. Imagine que el orden de la transacción fuera: debitar la cuenta del usuario, acreditar la cuenta de destino, registrar la transacción. Si el sistema no revierte adecuadamente toda la transacción (fallar de forma segura o "fail closed") cuando hay un error a mitad del proceso, el atacante podría potencialmente vaciar la cuenta del usuario, o posiblemente una condición de carrera podría permitir al atacante enviar dinero al destino varias veces.
-Para obtener más información sobre las referencias y la lista de CWE asociadas: https://top10.owasp.org/2025/es/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
   </si>
   <si>
     <t xml:space="preserve">Mishandling exceptional conditions زمانی رخ می‌دهد که برنامه‌ها نتوانند شرایط غیرمعمول یا غیرقابل پیش‌بینی را پیش‌بینی، شناسایی یا پاسخ دهند. این موضوع می‌تواند باعث crash، رفتار غیرمنتظره و ایجاد آسیب‌پذیری شود.
@@ -7505,62 +6563,6 @@
 Molte diverse vulnerabilità di sicurezza possono verificarsi quando gestiamo male le condizioni eccezionali, come bug logici, overflow, race condition, transazioni fraudolente, o problemi con memoria, stato, risorse, timing, autenticazione e autorizzazione. Questi tipi di vulnerabilità possono influenzare negativamente la riservatezza, la disponibilità e/o l'integrità di un sistema o dei suoi dati. Gli attaccanti manipolano la gestione degli errori difettosa di un'applicazione per colpire questa vulnerabilità.</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWE Mappati
-   &lt;/td&gt;
-   &lt;td&gt;Tasso di Incidenza Massimo
-   &lt;/td&gt;
-   &lt;td&gt;Tasso di Incidenza Medio
-   &lt;/td&gt;
-   &lt;td&gt;Copertura Massima
-   &lt;/td&gt;
-   &lt;td&gt;Copertura Media
-   &lt;/td&gt;
-   &lt;td&gt;Exploit Ponderato Medio
-   &lt;/td&gt;
-   &lt;td&gt;Impatto Ponderato Medio
-   &lt;/td&gt;
-   &lt;td&gt;Occorrenze Totali
-   &lt;/td&gt;
-   &lt;td&gt;CVE Totali
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;24
-   &lt;/td&gt;
-   &lt;td&gt;20,67%
-   &lt;/td&gt;
-   &lt;td&gt;2,95%
-   &lt;/td&gt;
-   &lt;td&gt;100,00%
-   &lt;/td&gt;
-   &lt;td&gt;37,95%
-   &lt;/td&gt;
-   &lt;td&gt;7,11
-   &lt;/td&gt;
-   &lt;td&gt;3,81
-   &lt;/td&gt;
-   &lt;td&gt;769.581
-   &lt;/td&gt;
-   &lt;td&gt;3.416
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Per gestire correttamente una condizione eccezionale dobbiamo pianificare tali situazioni (aspettarsi il peggio). Dobbiamo "catturare" ogni possibile errore di sistema direttamente nel punto in cui si verifica e poi gestirlo (il che significa fare qualcosa di significativo per risolvere il problema e assicurarci di riprenderci dalla questione). Come parte della gestione, dovremmo includere la generazione di un errore (per informare l'utente in modo comprensibile), la registrazione dell'evento, nonché l'emissione di un alert se riteniamo che sia giustificato. Dovremmo anche avere un gestore globale delle eccezioni nel caso in cui ci sia qualcosa che abbiamo mancato. Idealmente, avremmo anche strumenti o funzionalità di monitoraggio e/o osservabilità che vigilano su errori ripetuti o pattern che indicano un attacco in corso, in grado di emettere una risposta, una difesa o un blocco di qualche tipo. Questo può aiutarci a bloccare e rispondere a script e bot che si concentrano sulle nostre debolezze nella gestione degli errori.
-Catturare e gestire le condizioni eccezionali garantisce che l'infrastruttura sottostante dei nostri programmi non sia lasciata a gestire situazioni imprevedibili. Se siamo nel mezzo di una transazione di qualsiasi tipo, è estremamente importante eseguire il rollback di ogni parte della transazione e ricominciare (noto anche come failing closed). Tentare di recuperare una transazione a metà è spesso il punto in cui creiamo errori irrecuperabili.
-Quando possibile, aggiungere rate limiting, quote di risorse, throttling e altri limiti ovunque sia possibile, per prevenire le condizioni eccezionali in primo luogo. Nulla nell'informatica dovrebbe essere illimitato, poiché questo porta a mancanza di resilienza applicativa, denial of service, attacchi a forza bruta riusciti e bollette cloud straordinarie. Considerare se errori ripetuti identici, al di sopra di un certo tasso, debbano essere emessi solo come statistiche che mostrano con quale frequenza si sono verificati e in quale arco temporale. Queste informazioni dovrebbero essere aggiunte al messaggio originale in modo da non interferire con il logging e il monitoraggio automatizzati, vedere [A09:2025 Security Logging &amp; Alerting Failures](A09_2025-Security_Logging_and_Alerting_Failures.md).
-Oltre a questo, vorremmo includere una validazione rigorosa dell'input (con sanificazione o escaping per caratteri potenzialmente pericolosi che dobbiamo accettare), e gestione degli errori *centralizzata*, logging, monitoraggio e alerting, e un gestore globale delle eccezioni. Un'applicazione non dovrebbe avere più funzioni per la gestione delle condizioni eccezionali, dovrebbe essere eseguita in un unico posto, allo stesso modo ogni volta. Dovremmo anche creare requisiti di sicurezza del progetto per tutti i consigli in questa sezione, eseguire attività di threat modeling e/o revisione del design sicuro nella fase di progettazione dei nostri progetti, eseguire code review o analisi statica, nonché eseguire test di stress, prestazioni e penetration testing del sistema finale.
-Se possibile, l'intera organizzazione dovrebbe gestire le condizioni eccezionali allo stesso modo, poiché rende più facile rivedere e verificare il codice per errori in questo importante controllo di sicurezza.
-## Example attack scenarios
-**Scenario #1:** L'esaurimento delle risorse dovuto alla gestione impropria delle condizioni eccezionali (Denial of Service) potrebbe essere causato se l'applicazione cattura le eccezioni quando i file vengono caricati, ma non rilascia correttamente le risorse dopo. Ogni nuova eccezione lascia risorse bloccate o altrimenti non disponibili, finché tutte le risorse non sono esaurite.
-**Scenario #2:** L'esposizione di dati sensibili tramite la gestione impropria degli errori del database che rivela l'errore di sistema completo all'utente. L'attaccante continua a forzare errori al fine di utilizzare le informazioni di sistema sensibili per creare un attacco SQL injection migliore. I dati sensibili nei messaggi di errore all'utente sono ricognizione.
-**Scenario #3:** La corruzione dello stato nelle transazioni finanziarie potrebbe essere causata da un attaccante che interrompe una transazione multi-step tramite interruzioni di rete. Immaginate che l'ordine della transazione fosse: addebitare l'account utente, accreditare l'account di destinazione, registrare la transazione. Se il sistema non esegue correttamente il rollback dell'intera transazione (failing closed) quando si verifica un errore a metà, l'attaccante potrebbe potenzialmente prosciugare l'account dell'utente, o possibilmente una race condition che consente all'attaccante di inviare denaro alla destinazione più volte.
-Per maggiori informazioni sui riferimenti e sull'elenco delle CWE mappate: https://top10.owasp.org/2025/it/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
-  </si>
-  <si>
     <t>例外的な状況への不適切な対応 (Mishandling of Exceptional Conditions)</t>
   </si>
   <si>
@@ -7569,63 +6571,6 @@
 例外的な状況の処理を誤ると、ロジックの不具合、オーバーフロー、競合状態 (Race conditions)、不正な取引、あるいはメモリ、状態、リソース、タイミング、認証、および認可に関する問題など、多くの異なるセキュリティ脆弱性が発生する可能性があります。これらのタイプの脆弱性は、システムまたはそのデータの機密性、可用性、および完全性に悪影響を及ぼす可能性があります。攻撃者は、アプリケーションの欠陥のあるエラー処理を操作して、この脆弱性を突いてきます。</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;紐付けられた CWE 数
-   &lt;/td&gt;
-   &lt;td&gt;最大出現率
-   &lt;/td&gt;
-   &lt;td&gt;平均出現率
-   &lt;/td&gt;
-   &lt;td&gt;最大網羅率
-   &lt;/td&gt;
-   &lt;td&gt;平均網羅率
-   &lt;/td&gt;
-   &lt;td&gt;平均加重悪用スコア
-   &lt;/td&gt;
-   &lt;td&gt;平均加重影響スコア
-   &lt;/td&gt;
-   &lt;td&gt;出現総数
-   &lt;/td&gt;
-   &lt;td&gt;CVE 総数
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;24
-   &lt;/td&gt;
-   &lt;td&gt;20.67%
-   &lt;/td&gt;
-   &lt;td&gt;2.95%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;37.95%
-   &lt;/td&gt;
-   &lt;td&gt;7.11
-   &lt;/td&gt;
-   &lt;td&gt;3.81
-   &lt;/td&gt;
-   &lt;td&gt;769,581
-   &lt;/td&gt;
-   &lt;td&gt;3,416
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-例外的な状況を適切に処理するには、そのような状況を計画しておく必要があります（最悪の事態を想定 (Expect the worst) する）。すべてのシステムエラーを、それが発生した場所で直接「キャッチ (Catch)」し、それを処理しなければなりません（つまり、問題を解決し、その問題から確実に回復するために意味のある何かを行うことを意味します）。処理の一環として、エラーをスローすること（ユーザーに理解可能な方法で通知する）、イベントをログに記録すること、および正当であると判断した場合にはアラートを発行することを含めるべきです。また、何かを見落とした場合に備えて、グローバルな例外ハンドラーを設置しておくべきです。理想的には、継続的な攻撃を示す繰り返されるエラーやパターンを監視し、何らかの応答、防御、またはブロックを発行できる、監視 (Monitoring) または可観測性 (Observability) のツールや機能を備えることです。これは、私たちのエラー処理の弱点に焦点を当てたスクリプトやボットをブロックし、それらに応答するのに役立ちます。
-例外的な状況をキャッチして処理することで、プログラムの基盤となるインフラストラクチャが予測不能な状況に対処したまま放置されないようにします。いかなる種類のトランザクションであっても、その途中でエラーが発生した場合は、トランザクションのすべての部分をロールバックしてやり直すことが非常に重要です（フェイルクローズ (Fail closed) とも呼ばれます）。途中でトランザクションを回復しようとすると、回復不可能な間違いを犯してしまうことがよくあります。
-可能な限り、レート制限 (Rate limiting)、リソース制限 (Resource quotas)、スロットリング (Throttling)、およびその他の制限を追加して、そもそも例外的な状況が発生するのを防いでください。情報技術において無制限なものは何一つあってはなりません。それはアプリケーションのレジリエンス (Resilience)（回復力）の欠如、サービス拒否、ブルートフォース攻撃の成功、および莫大なクラウド利用料に繋がるからです。
-特定のレートを超える同一の繰り返されるエラーについては、それらがいつ、どの程度の頻度で発生したかを示す統計としてのみ出力することを検討してください。この情報は、自動化されたロギングや監視を妨げないように、元のメッセージに追加されるべきです（[A09:2025 セキュリティログとアラートの不備](A09_2025-Security_Logging_and_Alerting_Failures.md) 参照）。
-これに加えて、厳格な入力検証（受け入れなければならない潜在的に危険な文字については無害化 (Sanitization) またはエスケープを行う）、および「集約された (Centralized)」エラー処理、ロギング、監視、アラート、ならびにグローバル例外ハンドラーを含めるべきです。一つのアプリケーションに例外的な状況を処理するための複数の関数を持たせるべきではなく、一箇所で、毎回同じ方法で実行されるべきです。また、このセクションのすべてのアドバイスについてプロジェクトのセキュリティ要件を作成し、プロジェクトの設計フェーズで脅威モデリング (Threat modeling) や安全な設計レビューを実施し、コードレビューや静的解析を実施し、最終的なシステムに対してストレス、パフォーマンス、およびペネトレーションテストを実行すべきです。
-可能であれば、組織全体で例外的な状況を同じ方法で処理すべきです。そうすることで、この重要なセキュリティ制御におけるエラーのコードレビューや監査が容易になります。
-## Example attack scenarios
-**シナリオ #1：例外的な状況の誤処理によるリソースの枯渇 (サービス拒否)** アプリケーションがファイルのアップロード時に例外をキャッチするものの、その後にリソースを適切に解放しない場合に発生する可能性があります。新しい例外が発生するたびにリソースがロックされるか利用不可のままになり、最終的にすべてのリソースが使い果たされます。
-**シナリオ #2：不適切な処理またはデータベースエラーによる機密データの露出** ユーザーにシステムの完全なエラーを明らかにしてしまうケースです。攻撃者は、機密性の高いシステム情報を利用してより優れた SQL インジェクション攻撃を作成するために、意図的にエラーを発生させ続けます。ユーザーへのエラーメッセージに含まれる機密データは偵察 (Reconnaissance) 活動に利用されます。
-**シナリオ #3：金融取引における状態の破損** 攻撃者がネットワークの中断を介して多段階のトランザクションを妨害することによって引き起こされる可能性があります。トランザクションの順序が「ユーザーアカウントの引き落とし、宛先アカウントへの入金、トランザクションのログ記録」であったと仮定します。途中でエラーが発生したときにシステムがトランザクション全体を適切にロールバック（フェイルクローズ）しない場合、攻撃者はユーザーのアカウントを枯渇させたり、あるいは攻撃者が宛先に何度も送金できてしまう競合状態が発生したりする可能性があります。
-参考資料およびマッピングされたCWEの一覧について、詳しくはこちら： https://top10.owasp.org/2025/ja/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
-  </si>
-  <si>
     <t>부적절한 예외 처리</t>
   </si>
   <si>
@@ -7634,63 +6579,6 @@
 부적절한 예외 처리로 인해 다양한 보안 취약점이 발생할 수 있다. 예를 들어 논리 버그, 오버플로우, 레이스 컨디션, 부정 거래, 메모리·상태·리소스·타이밍·인증·인가 관련 문제 등이 있다. 이러한 유형의 취약점은 시스템 또는 데이터의 기밀성, 가용성, 무결성에 부정적인 영향을 미칠 수 있다. 공격자는 애플리케이션의 결함 있는 오류 처리를 악용하여 이 취약점을 공격한다.</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;해당되는 CWE 개수
-   &lt;/td&gt;
-   &lt;td&gt;최대 취약점 발생률
-   &lt;/td&gt;
-   &lt;td&gt;평균 취약점 발생률
-   &lt;/td&gt;
-   &lt;td&gt;최대 테스트 커버리지
-   &lt;/td&gt;
-   &lt;td&gt;평균 테스트 커버리지
-   &lt;/td&gt;
-   &lt;td&gt;가중 평균 악용도
-   &lt;/td&gt;
-   &lt;td&gt;가중 평균 영향도
-   &lt;/td&gt;
-   &lt;td&gt;총 발생 건수
-   &lt;/td&gt;
-   &lt;td&gt;총 CVE 건수
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;24
-   &lt;/td&gt;
-   &lt;td&gt;20.67%
-   &lt;/td&gt;
-   &lt;td&gt;2.95%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;37.95%
-   &lt;/td&gt;
-   &lt;td&gt;7.11
-   &lt;/td&gt;
-   &lt;td&gt;3.81
-   &lt;/td&gt;
-   &lt;td&gt;769,581
-   &lt;/td&gt;
-   &lt;td&gt;3,416
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-예외 상황을 적절히 처리하려면 이러한 상황에 대비한 계획을 세워야 한다(최악의 상황을 예상하라). 모든 시스템 오류를 발생 지점에서 직접 캐치(catch)하고, 이를 처리해야 한다. 여기서 처리란 문제 해결을 위한 의미 있는 조치를 취하고 정상 상태로 복구하는 것을 의미한다. 처리 과정에는 오류 발생 시 사용자에게 이해하기 쉬운 방식으로 알리고, 이벤트를 로깅하며, 필요하다고 판단되면 알림을 발송하는 것이 포함되어야 한다. 또한 놓친 예외가 있을 경우를 대비해 전역 예외 핸들러(Global Exception Handler)를 구현해야 한다. 이상적으로는 반복되는 오류나 진행 중인 공격을 나타내는 패턴을 감시하고, 이에 대응·방어·차단할 수 있는 모니터링 또는 옵저버빌리티 도구를 갖추는 것이 좋다. 이를 통해 오류 처리 취약점을 악용하는 스크립트와 봇에 대응하고 차단할 수 있다.
-예외 상황을 캐치하고 처리하면 프로그램의 기반 인프라가 예측 불가능한 상황에 노출되는 것을 방지할 수 있다. 트랜잭션 처리 도중이라면, 트랜잭션의 모든 부분을 롤백하고 처음부터 다시 시작하는 것이 매우 중요하다(이를 안전한 실패[Failing Closed]라고 한다). 트랜잭션을 중간 상태에서 복구하려는 시도는 종종 복구 불가능한 오류를 만들어낸다.
-가능하다면 속도 제한(Rate Limiting), 리소스 쿼터, 스로틀링 등 다양한 제한을 적용하여 애초에 예외 상황이 발생하지 않도록 예방하라. 정보 기술에서 무제한이어야 하는 것은 없다. 제한이 없으면 애플리케이션 복원력 저하, 서비스 거부(DoS), 무차별 대입 공격 성공, 과도한 클라우드 비용 등의 문제가 발생할 수 있다.
-특정 빈도 이상으로 동일한 오류가 반복될 경우, 개별 오류 메시지 대신 발생 횟수와 시간대를 보여주는 통계 형태로 출력하는 것을 고려하라. 이 정보는 자동화된 로깅 및 모니터링을 방해하지 않도록 원본 메시지에 추가하는 방식으로 처리해야 한다. [A09:2025 보안 로깅 및 알림 실패](A09_2025-Security_Logging_and_Alerting_Failures.md)를 참고하라.
-이 외에도 다음 사항을 포함해야 한다: 엄격한 입력 검증(허용해야 하는 위험 문자에 대한 새니타이징 또는 이스케이프 처리 포함), 중앙 집중화된 오류 처리·로깅·모니터링·알림 체계, 그리고 전역 예외 핸들러다. 하나의 애플리케이션에서 예외 처리를 위한 여러 함수를 두어서는 안 되며, 한 곳에서 동일한 방식으로 처리해야 한다. 또한 이 섹션의 모든 권고 사항에 대해 프로젝트 보안 요구사항을 수립하고, 설계 단계에서 위협 모델링 또는 보안 설계 검토를 수행하며, 코드 리뷰나 정적 분석을 실시하고, 최종 시스템에 대해 스트레스·성능·침투 테스트를 수행해야 한다.
-가능하다면 조직 전체가 동일한 방식으로 예외 상황을 처리하는 것이 좋다. 이렇게 하면 이 중요한 보안 통제에 대한 코드 리뷰와 감사가 더 쉬워진다.
-## Example attack scenarios
-**시나리오 1:** 애플리케이션이 파일 업로드 시 예외를 캐치하되 리소스를 해제하지 않으면, 예외가 발생할 때마다 리소스가 잠긴 채로 남는다. 이로 인해 리소스가 고갈되어 서비스 거부(DoS)로 이어질 수 있다.
-**시나리오 2:** 데이터베이스 오류가 사용자에게 그대로 노출되면 민감한 시스템 정보가 유출된다. 공격자는 이를 악용해 의도적으로 오류를 유발하고, 수집한 정보를 기반으로 더 정교한 SQL 인젝션 공격을 구성할 수 있다.
-**시나리오 3:** 공격자가 네트워크 중단을 일으켜 다단계 금융 트랜잭션을 방해할 수 있다. 예를 들어 트랜잭션이 "출금 → 입금 → 로깅" 순서로 처리될 때, 중간에 오류가 발생해도 시스템이 전체를 롤백(안전한 실패)하지 않으면 문제가 생긴다. 공격자는 이를 악용해 사용자 계좌에서 돈만 빠져나가게 하거나, 레이스 컨디션을 이용해 대상 계좌로 여러 번 송금할 수 있다.
-참고 자료와 매핑된 CWE 목록에 대한 자세한 정보: https://top10.owasp.org/2025/ko/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
-  </si>
-  <si>
     <t>Tratamento Incorreto de Condições Excepcionais</t>
   </si>
   <si>
@@ -7699,126 +6587,12 @@
 Muitas vulnerabilidades de segurança diferentes podem ocorrer quando tratamos incorretamente condições excepcionais, como _bugs_ de lógica, _overflows_, condições de corrida (_race conditions_), transações fraudulentas ou problemas com memória, estado, recurso, tempo, autenticação e autorização. Esses tipos de vulnerabilidades podem afetar negativamente a confidencialidade, disponibilidade e/ou integridade de um sistema ou de seus dados. Atacantes manipulam o tratamento de erros falho de uma aplicação para explorar essa vulnerabilidade.</t>
   </si>
   <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWEs Mapeadas 
-   &lt;/td&gt;
-   &lt;td&gt;Taxa Máx. de Incidência
-   &lt;/td&gt;
-   &lt;td&gt;Taxa Média de Incidência
-   &lt;/td&gt;
-   &lt;td&gt;Cobertura Máxima
-   &lt;/td&gt;
-   &lt;td&gt;Cobertura Média
-   &lt;/td&gt;
-   &lt;td&gt;Exploit Médio Ponderado
-   &lt;/td&gt;
-   &lt;td&gt;Impacto Médio Ponderado
-   &lt;/td&gt;
-   &lt;td&gt;Total de Ocorrências
-   &lt;/td&gt;
-   &lt;td&gt;Total de CVEs
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;24
-   &lt;/td&gt;
-   &lt;td&gt;20,67%
-   &lt;/td&gt;
-   &lt;td&gt;2,95%
-   &lt;/td&gt;
-   &lt;td&gt;100,00%
-   &lt;/td&gt;
-   &lt;td&gt;37,95%
-   &lt;/td&gt;
-   &lt;td&gt;7,11
-   &lt;/td&gt;
-   &lt;td&gt;3,81
-   &lt;/td&gt;
-   &lt;td&gt;769.581
-   &lt;/td&gt;
-   &lt;td&gt;3.416
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-Para tratar uma condição excepcional adequadamente, devemos planejar para tais situações (esperar o pior). Devemos "capturar" (_catch_) cada erro de sistema possível diretamente no local onde ocorrem e, então, tratá-lo (o que significa fazer algo significativo para resolver o problema e garantir a recuperação da falha). Como parte do tratamento, devemos incluir o lançamento de um erro (para informar o usuário de forma compreensível), o registro do evento (_log_), bem como a emissão de um alerta se considerarmos justificado. Também devemos ter um manipulador de exceções global para o caso de algo ter passado despercebido. Idealmente, também teríamos ferramentas ou funcionalidades de monitoramento e/ou observabilidade que vigiam erros repetidos ou padrões que indiquem um ataque em andamento, podendo emitir uma resposta, defesa ou bloqueio de algum tipo. Isso pode nos ajudar a bloquear e responder a scripts e bots que focam em nossas fraquezas de tratamento de erros.
-Capturar e tratar condições excepcionais garante que a infraestrutura subjacente de nossos programas não seja deixada para lidar com situações imprevisíveis. Se você estiver no meio de uma transação de qualquer tipo, é extremamente importante realizar o _rollback_ de cada parte da transação e começar de novo (também conhecido como falha segura ou _failing closed_). Tentar recuperar uma transação pela metade é frequentemente onde criamos erros irrecuperáveis.
-Sempre que possível, adicione limites de taxa (_rate limiting_), cotas de recursos, _throttling_ e outras restrições para prevenir condições excepcionais antes de tudo. Nada em tecnologia da informação deve ser ilimitado, pois isso leva à falta de resiliência da aplicação, negação de serviço, ataques de força bruta bem-sucedidos e faturas de nuvem extraordinárias.
-Considere se erros repetidos idênticos, acima de uma certa taxa, devem ser exibidos apenas como estatísticas mostrando a frequência com que ocorreram e em qual período. Esta informação deve ser anexada à mensagem original para não interferir no registro e monitoramento automatizados, veja [A09:2025 Falhas de Registro e Monitoramento de Segurança](A09_2025-Security_Logging_and_Alerting_Failures.md).
-Além disso, queremos incluir uma validação de entrada rigorosa (com sanitização ou _escaping_ para caracteres potencialmente perigosos que precisamos aceitar) e um tratamento de erros, registro, monitoramento e alerta _centralizados_, além de um manipulador de exceções global. Uma aplicação não deve ter múltiplas funções para tratar condições excepcionais; isso deve ser realizado em um único lugar, da mesma forma todas as vezes. Também devemos criar requisitos de segurança de projeto para todos os conselhos desta seção, realizar atividades de modelagem de ameaças e/ou revisão de design seguro na fase de design de nossos projetos, realizar revisão de código ou análise estática, bem como executar testes de estresse, desempenho e invasão do sistema final.
-Se possível, toda a sua organização deve tratar condições excepcionais da mesma maneira, pois isso facilita a revisão e a auditoria de código em busca de erros neste importante controle de segurança.
-## Example attack scenarios
-**Cenário 1:** Exaustão de recursos via tratamento incorreto de condições excepcionais (Negação de Serviço) poderia ser causada se a aplicação captura exceções quando arquivos são carregados, mas não libera adequadamente os recursos depois. Cada nova exceção deixa recursos bloqueados ou indisponíveis, até que todos os recursos sejam esgotados.
-**Cenário 2:** Exposição de dados sensíveis via tratamento inadequado ou erros de banco de dados que revelam o erro completo do sistema ao usuário. O atacante continua a forçar erros para usar as informações sensíveis do sistema para criar um ataque de _SQL injection_ melhor. Os dados sensíveis nas mensagens de erro do usuário servem como reconhecimento (_reconnaissance_).
-**Cenário 3:** Corrupção de estado em transações financeiras poderia ser causada por um atacante interrompendo uma transação de múltiplas etapas via interrupções de rede. Imagine que a ordem da transação fosse: debitar conta do usuário, creditar conta de destino, registrar transação. Se o sistema não realizar o _rollback_ adequadamente de toda a transação (falha segura) quando houver um erro no meio do caminho, o atacante poderia potencialmente esvaziar a conta do usuário, ou possivelmente gerar uma condição de corrida que permita ao atacante enviar dinheiro para o destino várias vezes.
-Para mais informações sobre as referências e a lista de CWEs mapeadas: https://top10.owasp.org/2025/pt-BR/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
-  </si>
-  <si>
     <t>异常条件处理不当</t>
   </si>
   <si>
     <t>软件中异常条件处理不当，是指程序未能预防、检测和响应异常且不可预测的情况，从而导致崩溃、意外行为，有时还会造成漏洞。这可能涉及以下三类失败中的一种或多种：应用没有阻止异常情况发生，没有在异常情况发生时识别它，和/或在事后响应不佳或完全不响应。
 异常条件可能由缺失、薄弱或不完整的输入验证造成，也可能由没有在错误发生的函数处处理，而是在较晚、更高层级处理错误造成；还可能来自内存、权限或网络问题等意外环境状态、不一致的异常处理，或完全未处理的异常，使系统进入未知且不可预测的状态。任何时候，只要应用不确定下一条指令是什么，就已经对异常条件处理不当。难以发现的错误和异常可能长期威胁整个应用的安全。
 当我们对异常条件处理不当时，可能出现许多不同安全漏洞，例如逻辑缺陷、溢出、竞争条件、欺诈交易，或与内存、状态、资源、时序、认证和授权有关的问题。这些类型的漏洞可能负面影响系统或其数据的机密性、可用性和/或完整性。攻击者会操纵应用有缺陷的错误处理来利用此类漏洞。</t>
-  </si>
-  <si>
-    <t>## Score table
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;映射的 CWE 数量
-   &lt;/td&gt;
-   &lt;td&gt;最大发生率
-   &lt;/td&gt;
-   &lt;td&gt;平均发生率
-   &lt;/td&gt;
-   &lt;td&gt;最大覆盖率
-   &lt;/td&gt;
-   &lt;td&gt;平均覆盖率
-   &lt;/td&gt;
-   &lt;td&gt;平均加权可利用性
-   &lt;/td&gt;
-   &lt;td&gt;平均加权影响
-   &lt;/td&gt;
-   &lt;td&gt;发生总数
-   &lt;/td&gt;
-   &lt;td&gt;CVE 总数
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;24
-   &lt;/td&gt;
-   &lt;td&gt;20.67%
-   &lt;/td&gt;
-   &lt;td&gt;2.95%
-   &lt;/td&gt;
-   &lt;td&gt;100.00%
-   &lt;/td&gt;
-   &lt;td&gt;37.95%
-   &lt;/td&gt;
-   &lt;td&gt;7.11
-   &lt;/td&gt;
-   &lt;td&gt;3.81
-   &lt;/td&gt;
-   &lt;td&gt;769,581
-   &lt;/td&gt;
-   &lt;td&gt;3,416
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## How to prevent
-为了正确处理异常条件，我们必须提前为这类情况做计划（预期最坏情况）。我们必须在每个可能发生系统错误的位置直接“捕获”错误，然后处理它，也就是采取有意义的行动来解决问题，并确保系统从问题中恢复。作为处理的一部分，应包括抛出错误（以用户能理解的方式告知用户）、记录事件日志，并在我们认为有必要时发出告警。还应设置全局异常处理器，以应对可能遗漏的情况。理想情况下，我们还应具备监控和/或可观测性工具或功能，用于发现重复错误或表明正在发生攻击的模式，并能触发某种响应、防御或阻断。这可以帮助我们阻止并响应专门针对错误处理弱点的脚本和机器人。
-捕获并处理异常条件可以确保程序的底层基础设施不会被迫处理不可预测的情况。如果你正处于任何类型交易的中途，非常重要的一点是回滚交易的每个部分并重新开始（也称为故障关闭，failing closed）。试图从交易中途恢复，往往会造成无法恢复的错误。
-在可能的情况下，尽量加入速率限制、资源配额、节流和其他限制，从源头预防异常条件。信息技术中不应存在无限制的东西，因为这会导致应用韧性不足、拒绝服务、成功的暴力破解攻击以及异常高昂的云账单。
-请考虑是否应将超过一定频率的相同重复错误只输出为统计信息，显示发生次数和时间范围。该信息应追加到原始消息中，以免干扰自动化日志记录和监控，参见 [A09:2025 安全日志记录和告警失效](A09_2025-Security_Logging_and_Alerting_Failures.md)。
-除此之外，我们还希望加入严格输入验证（对必须接受的潜在危险字符进行清理或转义），以及*集中式*错误处理、日志记录、监控、告警和全局异常处理器。一个应用不应有多个处理异常条件的函数，应在一个地方以相同方式执行。我们还应为本节所有建议创建项目安全需求，在项目设计阶段执行威胁建模和/或安全设计审查活动，执行代码审查或静态分析，并对最终系统执行压力、性能和渗透测试。
-如果可能，整个组织应以同一种方式处理异常条件，因为这会让这项重要安全控制的代码审查和审计更容易。
-## Example attack scenarios
-**场景 #1：** 异常条件处理不当导致资源耗尽（拒绝服务）。如果应用在上传文件时捕获异常，但事后没有正确释放资源，每次新异常都会让资源保持锁定或不可用，直到所有资源耗尽。
-**场景 #2：** 错误处理不当或数据库错误把完整系统错误暴露给用户，导致敏感数据泄露。攻击者持续制造错误，以利用敏感系统信息构造更好的 SQL 注入攻击。用户错误消息中的敏感数据成为侦察信息。
-**场景 #3：** 攻击者通过网络中断打断多步骤交易，可能导致金融交易状态损坏。假设交易顺序为：扣减用户账户、增加目标账户余额、记录交易。如果系统在中途出错时没有正确回滚整个交易（故障关闭），攻击者可能耗尽用户账户，或可能利用竞争条件多次向目标账户转账。
-有關參考資料及已對應 CWE 清單的更多資訊： https://top10.owasp.org/2025/zh-Hant/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
   </si>
   <si>
     <t>= Non official translation</t>
@@ -7905,23 +6679,6 @@
   </si>
   <si>
     <t>Les défaillances d’intégrité logicielle et des données concernent du code et une infrastructure qui ne protègent pas contre le traitement de code ou de données invalides ou non fiables. Un exemple est lorsqu’une application s’appuie sur des plugins, bibliothèques ou modules provenant de sources, dépôts et réseaux de diffusion de contenu (CDN) non fiables. Un pipeline CI/CD non sécurisé sans consommer ni fournir de vérifications d’intégrité logicielle peut introduire un risque d’accès non autorisé, de code non sécurisé ou malveillant, ou de compromission système. Un autre exemple est un CI/CD qui extrait du code ou des artefacts de lieux non fiables et/ou ne les vérifie pas avant utilisation (en vérifiant la signature ou un mécanisme similaire). Enfin, de nombreuses applications incluent désormais la fonctionnalité de mise à jour automatique, où les mises à jour sont téléchargées sans vérification suffisante de l’intégrité et appliquées à l’application précédemment fiable. Un autre exemple est celui où des objets ou des données sont encodés ou sérialisés dans une structure qu’un attaquant peut voir et modifier vulnérable à la désérialisation non sécurisée.</t>
-  </si>
-  <si>
-    <t>Sans journalisation et surveillance, les attaques et violations ne peuvent pas être détectées, et sans alerte, il est très difficile de réagir rapidement et efficacement lors d’un incident de sécurité. Un journalage insuffisant, une surveillance continue, une détection et une alerte pour initier des réponses actives surviennent à tout moment : 
-* Les événements auditables, tels que les connexions, les échecs de connexion et les transactions de grande valeur, ne sont pas enregistrés ou enregistrés de manière incohérente (par exemple, seulement les connexions réussies, mais pas les tentatives ratées). 
-* Les avertissements et erreurs ne génèrent aucun message de journal, inadéquat ou flou. 
-* L’intégrité des billots n’est pas correctement protégée contre toute altération des documents. 
-* Les journaux des applications et des API ne sont pas surveillés pour toute activité suspecte. 
-* Les journaux ne sont stockés que localement, et non correctement sauvegardés. 
-* Les seuils d’alerte appropriés et les processus d’escalade de réponse ne sont pas en place ni efficaces. Les alertes ne sont pas reçues ou examinées dans un délai raisonnable. 
-* Les tests d’intrusion et les analyses par des outils de test dynamique de sécurité des applications (DAST) (tels que Burp ou ZAP) ne déclenchent pas d’alertes. 
-* L’application ne peut pas détecter, escalader ou alerter pour des attaques actives en temps réel ou quasi-temps réel. 
-* Vous êtes vulnérable à la fuite d’informations sensibles en rendant les événements de journalisation et d’alerte visibles pour un utilisateur ou un attaquant (voir [A01:2025-Broken Access Control](A01_2025-Broken_Access_Control.md)), ou en enregistrant des informations sensibles qui ne devraient pas être enregistrées (comme les PII ou les informations PHI). 
-* Vous êtes vulnérable aux injections ou attaques sur les systèmes de journalisation ou de surveillance si les données de journal ne sont pas correctement codées. 
-* L’application manque ou ne gère pas les erreurs et autres conditions exceptionnelles, de sorte que le système ignore qu’il y a eu une erreur, et ne peut donc pas enregistrer qu’il y a eu un problème. 
-* Des « cas d’utilisation » adéquats pour l’émission d’alertes manquent ou sont dépassés pour reconnaître une situation particulière. 
-* Trop d’alertes fausses positives rendent impossible la distinction des alertes importantes des non-importantes, ce qui les conduit à être reconnues trop tard ou pas du tout (surcharge physique de l’équipe SOC). 
-* Les alertes détectées ne peuvent pas être traitées correctement car le playbook pour le cas d’utilisation est incomplet, obsolète ou manquant.</t>
   </si>
   <si>
     <t>La mauvaise gestion de conditions exceptionnelles dans les logiciels survient lorsque les programmes ne préviennent pas, détectent et ne répondent pas à des situations inhabituelles et imprévisibles, ce qui entraîne des plantages, des comportements inattendus et parfois des vulnérabilités. Cela peut impliquer une ou plusieurs des trois défaillances suivantes ; l’application ne prévient pas qu’une situation inhabituelle se produise, elle n’identifie pas la situation au moment où elle se produit, et/ou elle réagit mal ou pas du tout à la situation par la suite. 
@@ -8021,68 +6778,6 @@
 ```
 depuis la ligne de commande. 
 Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A01_2025-Broken_Access_Control/</t>
-  </si>
-  <si>
-    <t>## Tableau des scores
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWEs cartographiées 
-   &lt;/td&gt;
-   &lt;td&gt;Taux d’incidence maximal
-   &lt;/td&gt;
-   &lt;td&gt;Taux moyen d’incidence
-   &lt;/td&gt;
-   &lt;td&gt;Couverture maximale
-   &lt;/td&gt;
-   &lt;td&gt;Couverture moyenne
-   &lt;/td&gt;
-   &lt;td&gt;Exploit pondéré moyen
-   &lt;/td&gt;
-   &lt;td&gt;Impact pondéré moyen
-   &lt;/td&gt;
-   &lt;td&gt;Occurrences totales
-   &lt;/td&gt;
-   &lt;td&gt;Total des CVE
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;16
-   &lt;/td&gt;
-   &lt;td&gt;27,70 % 
-   &lt;/td&gt;
-   &lt;td&gt;3,00 % 
-   &lt;/td&gt;
-   &lt;td&gt;100,00 % 
-   &lt;/td&gt;
-   &lt;td&gt;52,35 % 
-   &lt;/td&gt;
-   &lt;td&gt;7,96
-   &lt;/td&gt;
-   &lt;td&gt;3,97
-   &lt;/td&gt;
-   &lt;td&gt;719 084
-   &lt;/td&gt;
-   &lt;td&gt;1 375
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## Comment prévenir
-Des processus d’installation sécurisés doivent être mis en œuvre, notamment : 
-* Un processus de durcissement répétable permettant un déploiement rapide et facile d’un autre environnement suffisamment verrouillé. Les environnements de développement, d’assurance qualité et de production doivent tous être configurés de manière identique, avec des identifiants différents utilisés dans chaque environnement. Ce processus doit être automatisé pour minimiser l’effort nécessaire à la mise en place d’un nouvel environnement sécurisé. 
-* Une plateforme minimale sans fonctionnalités, composants, documentations ou exemples inutiles. Supprimez ou n’installez pas les fonctionnalités et frameworks inutilisés. 
-* Une tâche visant à revoir et mettre à jour les configurations appropriées à toutes les notes de sécurité, mises à jour et correctifs dans le cadre du processus de gestion des correctifs (voir [A03 Défaillances de la chaîne d’approvisionnement logicielle](A03_2025-Software_Supply_Chain_Failures.md)). Revoir les permissions de stockage cloud (par exemple, les permissions de bucket S3). 
-* Une architecture d’application segmentée offre une séparation efficace et sécurisée entre composants ou locataires, avec segmentation, conteneurisation ou groupes de sécurité cloud (ACL). 
-* Envoi de directives de sécurité aux clients, par exemple, les en-têtes de sécurité. 
-* Un processus automatisé pour vérifier l’efficacité des configurations et des réglages dans tous les environnements. 
-* Ajouter proactivement une configuration centrale pour intercepter les messages d’erreur excessifs en tant que sauvegarde. 
-* Si ces vérifications ne sont pas automatisées, elles doivent être vérifiées manuellement au minimum chaque année. 
-* Utiliser la fédération d’identité, des identifiants de courte durée ou des mécanismes d’accès basés sur des rôles fournis par la plateforme sous-jacente au lieu d’intégrer des clés statiques ou des secrets dans le code, les fichiers de configuration ou les pipelines.
-## Exemples de scénarios d’attaque
-**Scénario #1 :** Le serveur d’applications d’applications d’exemple n’est pas supprimé du serveur de production. Ces applications d’exemple présentent des failles de sécurité connues que les attaquants utilisent pour compromettre le serveur. Supposons que l’une de ces applications soit la console d’administration, et que les comptes par défaut n’aient pas été modifiés. Dans ce cas, l’attaquant se connecte avec le mot de passe par défaut et prend le relais. 
-**Scénario #2 :** La liste des répertoires n’est pas désactivée sur le serveur. Un attaquant découvre qu’il peut simplement lister les répertoires. L’attaquant trouve et télécharge les classes Java compilées, qu’il décompile et rétro-ingénierie pour visualiser le code. L’attaquant découvre alors une grave faille de contrôle d’accès dans l’application. 
-**Scénario #3 :** La configuration du serveur d’applications permet de renvoyer des messages d’erreur détaillés, tels que des traces de pile. Cela expose potentiellement des informations sensibles ou des failles sous-jacentes, comme des versions de composants connues pour être vulnérables. 
-**Scénario #4 :** Un fournisseur de services cloud (CSP) a par défaut des permissions de partage ouvertes à Internet. Cela permet d’accéder aux données sensibles stockées dans le stockage cloud. 
-Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A02_2025-Security_Misconfiguration/</t>
   </si>
   <si>
     <t>## Tableau des scores
@@ -8348,63 +7043,6 @@
 **Scénario #3 Utilisation d’un paquet à partir d’une source non fiable :** Un développeur a du mal à trouver la version mise à jour d’un paquet qu’il recherche, il la télécharge donc non pas depuis le gestionnaire de paquets fiable classique, mais depuis un site web en ligne. Le paquet n’est pas signé, et il n’y a donc aucune possibilité d’en garantir l’intégrité. Le paquet inclut du code malveillant. 
 **Scénario #4 Désérialisation insécurisée :** Une application React appelle un ensemble de microservices Spring Boot. En tant que programmeurs fonctionnels, ils ont essayé de s’assurer que leur code reste immuable. La solution qu’ils ont trouvée est de sérialiser l’état utilisateur et de le transmettre à chaque requête. Un attaquant remarque la signature d’objet Java « rO0 » (en base64) et utilise le [Java Deserialization Scanner](https://github.com/federicodotta/Java-Deserialization-Scanner) pour obtenir une exécution de code à distance sur le serveur d’applications. 
 Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A08_2025-Software_or_Data_Integrity_Failures/</t>
-  </si>
-  <si>
-    <t>## Tableau des scores
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWEs cartographiées 
-   &lt;/td&gt;
-   &lt;td&gt;Taux d’incidence maximal
-   &lt;/td&gt;
-   &lt;td&gt;Taux moyen d’incidence
-   &lt;/td&gt;
-   &lt;td&gt;Couverture maximale
-   &lt;/td&gt;
-   &lt;td&gt;Couverture moyenne
-   &lt;/td&gt;
-   &lt;td&gt;Exploit pondéré moyen
-   &lt;/td&gt;
-   &lt;td&gt;Impact pondéré moyen
-   &lt;/td&gt;
-   &lt;td&gt;Occurrences totales
-   &lt;/td&gt;
-   &lt;td&gt;Total des CVE
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;24
-   &lt;/td&gt;
-   &lt;td&gt;20,67 % 
-   &lt;/td&gt;
-   &lt;td&gt;2,95 % 
-   &lt;/td&gt;
-   &lt;td&gt;100,00 % 
-   &lt;/td&gt;
-   &lt;td&gt;37,95 % 
-   &lt;/td&gt;
-   &lt;td&gt;7.11
-   &lt;/td&gt;
-   &lt;td&gt;3.81
-   &lt;/td&gt;
-   &lt;td&gt;769 581
-   &lt;/td&gt;
-   &lt;td&gt;3 416
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## Comment prévenir
-Pour gérer correctement une condition exceptionnelle, nous devons planifier de telles situations (attendez-vous au pire). Nous devons « détecter » chaque erreur système possible directement à l’endroit où elle survient puis la traiter (ce qui signifie faire quelque chose de significatif pour résoudre le problème et nous assurer de nous en remettre). Dans le cadre de la gestion, nous devrions inclure l’envoi d’une erreur (pour informer l’utilisateur de manière compréhensible), la consignation de l’événement, ainsi que l’émission d’une alerte si cela est justifié. Nous devrions également avoir un gestionnaire global d’exceptions en place au cas où quelque chose serait manqué. Idéalement, nous aurions aussi des outils ou fonctionnalités de surveillance et/ou d’observabilité qui surveillent les erreurs répétées ou les schémas indiquant une attaque en cours, qui pourrait fournir une réponse, une défense ou un blocage quelconque. Cela peut nous aider à bloquer et à répondre aux scripts et bots qui se concentrent sur nos faiblesses en gestion des erreurs. 
-Détecter et gérer des conditions exceptionnelles garantit que l’infrastructure sous-jacente de nos programmes ne doit pas gérer des situations imprévisibles. Si vous êtes en cours de transaction de quelque nature que ce soit, il est extrêmement important de revenir en arrière sur chaque partie de la transaction et de recommencer (ce qu’on appelle également échec de clôture). Tenter de récupérer une transaction en cours de route est souvent l’occasion de créer des erreurs irrémédiables. 
-Dans la mesure du possible, ajoutez des limites de vitesse, des quotas de ressources, des limitations de puissance et d’autres limites autant que possible, pour prévenir des conditions exceptionnelles dès le départ. Rien dans les technologies de l’information ne devrait être illimité, car cela conduit à un manque de résilience des applications, au déni de service, à des attaques par force brute réussies et à des factures cloud extraordinaires. 
-Considérez si des erreurs répétées identiques, au-delà d’un certain débit, ne doivent être produites que sous forme de statistiques montrant la fréquence et dans quel délai ils se sont produits. Ces informations doivent être ajoutées au message original afin de ne pas interférer avec la journalisation et la surveillance automatisées, voir [A09:2025 Défaillances de journalisation et alertes de sécurité](A09_2025-Security_Logging_and_Alerting_Failures.md).
-En plus de cela, nous voudrions inclure une validation stricte des entrées (avec nettoyage ou échappement pour les caractères potentiellement dangereux que nous devons accepter), une gestion centralisée des erreurs, la journalisation, la surveillance et l’alerte, ainsi qu’un gestionnaire global d’exceptions. Une application ne doit pas avoir plusieurs fonctions pour gérer des conditions exceptionnelles, elle doit être effectuée en un seul endroit, de la même manière à chaque fois. Nous devrions également créer des exigences de sécurité du projet pour tous les conseils de cette section, effectuer la modélisation des menaces et/ou des activités de revue de conception sécurisée lors de la phase de conception de nos projets, effectuer des revues de code ou des analyses statiques, ainsi que réaliser des tests de stress, de performance et d’intrusion du système final. 
-Si possible, toute votre organisation devrait gérer les conditions exceptionnelles de la même manière, car cela facilite la relecture et l’audit du code pour détecter des erreurs dans ce contrôle de sécurité important.
-## Exemples de scénarios d’attaque
-**Scénario #1 : Une épuisement des ressources dû à une mauvaise gestion de conditions exceptionnelles (déni de service) peut être causé si l’application détecte des exceptions lors du téléchargement des fichiers, mais ne libère pas correctement les ressources ensuite. Chaque nouvelle exception laisse les ressources bloquées ou indisponibles, jusqu’à ce que toutes les ressources soient épuisées. 
-**Scénario #2 :** Exposition de données sensibles via une mauvaise gestion ou des erreurs de base de données qui révèlent l’erreur système complète à l’utilisateur. L’attaquant continue de forcer des erreurs afin d’utiliser les informations sensibles du système pour créer une meilleure attaque d’injection SQL. Les données sensibles dans les messages d’erreur utilisateur sont de la reconnaissance. 
-**Scénario #3 :** La corruption d’état dans les transactions financières pourrait être causée par un attaquant interrompant une transaction en plusieurs étapes via des perturbations réseau. Imaginez que l’ordre de la transaction soit : débiter un compte utilisateur, créditer le compte de destination, enregistrer la transaction. Si le système ne revient pas correctement sur l’intégralité de la transaction (échec fermé) en cas d’erreur en cours de route, l’attaquant pourrait potentiellement vider le compte de l’utilisateur, ou peut-être une condition de course permettant à l’attaquant d’envoyer de l’argent à destination plusieurs fois. 
-Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
   </si>
   <si>
     <t>## Tableau des scores
@@ -8649,6 +7287,1368 @@
   </si>
   <si>
     <t>A10</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs Mapped 
+   &lt;/td&gt;
+   &lt;td&gt;Max Incidence Rate
+   &lt;/td&gt;
+   &lt;td&gt;Avg Incidence Rate
+   &lt;/td&gt;
+   &lt;td&gt;Max Coverage
+   &lt;/td&gt;
+   &lt;td&gt;Avg Coverage
+   &lt;/td&gt;
+   &lt;td&gt;Avg Weighted Exploit
+   &lt;/td&gt;
+   &lt;td&gt;Avg Weighted Impact
+   &lt;/td&gt;
+   &lt;td&gt;Total Occurrences
+   &lt;/td&gt;
+   &lt;td&gt;Total CVEs
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16
+   &lt;/td&gt;
+   &lt;td&gt;27.70%
+   &lt;/td&gt;
+   &lt;td&gt;3.00%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;52.35%
+   &lt;/td&gt;
+   &lt;td&gt;7.96
+   &lt;/td&gt;
+   &lt;td&gt;3.97
+   &lt;/td&gt;
+   &lt;td&gt;719,084
+   &lt;/td&gt;
+   &lt;td&gt;1,375
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Secure installation processes should be implemented, including:
+* A repeatable hardening process enabling the fast and easy deployment of another environment that is appropriately locked down. Development, QA, and production environments should all be configured identically, with different credentials used in each environment. This process should be automated to minimize the effort required to set up a new secure environment.
+* A minimal platform without any unnecessary features, components, documentation, or samples. Remove or do not install unused features and frameworks.
+* A task to review and update the configurations appropriate to all security notes, updates, and patches as part of the patch management process (see **A03 Software Supply Chain Failures**). Review cloud storage permissions (e.g., S3 bucket permissions).
+* A segmented application architecture provides effective and secure separation between components or tenants, with segmentation, containerization, or cloud security groups (ACLs).
+* Sending security directives to clients, e.g., Security Headers.
+* An automated process to verify the effectiveness of the configurations and settings in all environments.
+* Proactively add a central configuration to intercept excessive error messages as a backup.
+* If these verifications are not automated, they should be manually verified annually at a minimum.
+* Use identity federation, short-lived credentials, or role-based access mechanisms provided by the underlying platform instead of embedding static keys or secrets in code, configuration files, or pipelines.
+## Example attack scenarios
+**Scenario #1:** The application server comes with sample applications not removed from the production server. These sample applications have known security flaws that attackers use to compromise the server. Suppose one of these applications is the admin console, and default accounts weren't changed. In that case, the attacker logs in with the default password and takes over.
+**Scenario #2:** Directory listing is not disabled on the server. An attacker discovers they can simply list directories. The attacker finds and downloads the compiled Java classes, which they decompile and reverse engineer to view the code. The attacker then finds a severe access control flaw in the application.
+**Scenario #3:** The application server's configuration allows detailed error messages, such as stack traces to be returned to users. This potentially exposes sensitive information or underlying flaws, such as component versions that are known to be vulnerable.
+**Scenario #4:** A cloud service provider (CSP) defaults to having sharing permissions open to the Internet. This allows sensitive data stored within cloud storage to be accessed.
+For more information about the references and the list of mapped CWEs: https://top10.owasp.org/2025/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>Without logging and monitoring, attacks and breaches cannot be detected, and without alerting it is very difficult to respond quickly and effectively during a security incident. Insufficient logging, continuous monitoring, detection, and alerting to initiate active responses occurs any time:
+* Auditable events, such as logins, failed logins, and high-value transactions, are not logged or logged inconsistently (for instance, only logging successful logins, but not failed attempts).
+* Warnings and errors generate no, inadequate, or unclear log messages.
+* The integrity of logs is not properly protected from tampering.
+* Logs of applications and APIs are not monitored for suspicious activity.
+* Logs are only stored locally, and not properly backedup.
+* Appropriate alerting thresholds and response escalation processes are not in place or effective. Alerts are not received or reviewed within a reasonable amount of time.
+* Penetration testing and scans by dynamic application security testing (DAST) tools (such as Burp or ZAP) do not trigger alerts.
+* The application cannot detect, escalate, or alert for active attacks in real-time or near real-time.
+* You are vulnerable to sensitive information leakage by making logging and alerting events visible to a user or an attacker (see **A01:2025-Broken Access Control**), or by logging sensitive information that should not be logged (such as PII or PHI).
+* You are vulnerable to injections or attacks on the logging or monitoring systems if log data is not correctly encoded.
+* The application is missing or mishandling errors and other exceptional conditions, such that the system is unaware there was an error, and is therefore unable to log there was a problem.
+* Adequate ‘use cases’ for issuing alerts are missing or outdated to recognize a special situation.
+* Too many false positive alerts make it impossible to distinguish important alerts from unimportant ones, resulting in them being recognized too late or not at all (physical overload of the SOC team).
+* Detected alerts cannot be processed correctly because the playbook for the use case is incomplete, out of date, or missing.</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs Mapped 
+   &lt;/td&gt;
+   &lt;td&gt;Max Incidence Rate
+   &lt;/td&gt;
+   &lt;td&gt;Avg Incidence Rate
+   &lt;/td&gt;
+   &lt;td&gt;Max Coverage
+   &lt;/td&gt;
+   &lt;td&gt;Avg Coverage
+   &lt;/td&gt;
+   &lt;td&gt;Avg Weighted Exploit
+   &lt;/td&gt;
+   &lt;td&gt;Avg Weighted Impact
+   &lt;/td&gt;
+   &lt;td&gt;Total Occurrences
+   &lt;/td&gt;
+   &lt;td&gt;Total CVEs
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20.67%
+   &lt;/td&gt;
+   &lt;td&gt;2.95%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;37.95%
+   &lt;/td&gt;
+   &lt;td&gt;7.11
+   &lt;/td&gt;
+   &lt;td&gt;3.81
+   &lt;/td&gt;
+   &lt;td&gt;769,581
+   &lt;/td&gt;
+   &lt;td&gt;3,416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+In order to handle an exceptional condition properly we must plan for such situations (expect the worst). We must ‘catch’ every possible system error directly at the place where they occur and then handle it (which means do something meaningful to solve the problem and ensure we recover from the issue). As part of the handling, we should include throwing an error (to inform the user in an understandable way), logging of the event, as well as issuing an alert if we feel that is justified. We should also have a global exception handler in place in case there is ever something we have missed. Ideally, we would also have monitoring and/or observability tooling or functionality that watches for repeated errors or patterns that indicate an on-going attack, that could issue a response, defense, or blocking of some kind. This can help us block and respond to scripts and bots that focus on our error handling weaknesses.
+Catching and handling exceptional conditions ensures that the underlying infrastructure of our programs are not left to deal with unpredictable situations. If you are part way through a transaction of any kind, it is extremely important that you roll back every part of the transaction and start again (also known as failing closed). Attempting to recover a transaction part way through is often where we create unrecoverable mistakes.
+Whenever possible, add rate limiting, resource quotas, throttling, and other limits wherever possible, to prevent exceptional conditions in the first place. Nothing in information technology should be limitless, as this leads to a lack of application resilience, denial of service, successful brute force attacks, and extraordinary cloud bills. 
+Consider whether identical repeated errors, above a certain rate, should only be outputted as statistics showing how often they have occurred and in what time frame. This information should be appended to the original message so as not to interfere with automated logging and monitoring, see **A09:2025 Security Logging &amp; Alerting Failures**.
+On top of this, we would want to include strict input validation (with sanitization or escaping for potentially hazardous characters that we must accept), and *centralized* error handling, logging, monitoring, and alerting, and a global exception handler. One application should not multiple functions for handling exceptional conditions, it should be performed in one place, the same way each time. We should also create project security requirements for all the advice in this section, perform threat modelling and/or secure design review activities in the design phase of our projects, perform code review or static analysis, as well as execute stress, performance, and penetration testing of the final system.
+If possible, your entire organization should handle exceptional conditions in the same way, as it makes it easier to review and audit code for errors in this important security control.
+## Example attack scenarios
+**Scenario #1:** Resource exhaustion via mishandling of exceptional conditions (Denial of Service) could be caused if the application catches exceptions when files are uploaded, but doesn’t properly release resources after. Each new exception leaves resources locked or otherwise unavailable, until all resources are used up.
+**Scenario #2:** Sensitive data exposure via improper handling or database errors that reveals the full system error to the user. The attacker continues to force errors in order to use the sensitive system information to create a better SQL injection attack. The sensitive data in the user error messages are reconnaissance.
+**Scenario #3:** State corruption in financial transactions could be caused by an attacker interrupting a multi-step transaction via network disruptions. Imagine the transaction order was: debit user account, credit destination account, log transaction. If the system doesn’t properly roll back the entire transaction (fail closed) when there is an error part way through, the attacker could potentially drain the user’s account, or possibly a race condition that allows the attacker to send money to the destination multiple times.
+For more information about the references and the list of mapped CWEs: https://top10.owasp.org/2025/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;Počet mapovaných CWE 
+   &lt;/td&gt;
+   &lt;td&gt;Max míra výskytu
+   &lt;/td&gt;
+   &lt;td&gt;Průměrná míra výskytu
+   &lt;/td&gt;
+   &lt;td&gt;Max pokrytí
+   &lt;/td&gt;
+   &lt;td&gt;Průměrné pokrytí
+   &lt;/td&gt;
+   &lt;td&gt;Průměrná vážená zneužitelnost
+   &lt;/td&gt;
+   &lt;td&gt;Průměrný vážený dopad
+   &lt;/td&gt;
+   &lt;td&gt;Celkový počet výskytů
+   &lt;/td&gt;
+   &lt;td&gt;Celkový počet CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16
+   &lt;/td&gt;
+   &lt;td&gt;27,70 %
+   &lt;/td&gt;
+   &lt;td&gt;3,00 %
+   &lt;/td&gt;
+   &lt;td&gt;100,00 %
+   &lt;/td&gt;
+   &lt;td&gt;52,35 %
+   &lt;/td&gt;
+   &lt;td&gt;7,96
+   &lt;/td&gt;
+   &lt;td&gt;3,97
+   &lt;/td&gt;
+   &lt;td&gt;719 084
+   &lt;/td&gt;
+   &lt;td&gt;1 375
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Měly by být implementovány bezpečné instalační procesy, včetně:
+* Opakovatelný proces hardeningu umožňující rychlé a snadné nasazení dalšího prostředí s odpovídajícím zabezpečením. Vývojové, testovací (QA) a produkční prostředí by měla být konfigurována shodně, přičemž v každém prostředí by se měly používat odlišné přihlašovací údaje. Tento proces by měl být automatizován, aby se minimalizovalo úsilí potřebné k nastavení nového bezpečného prostředí.
+* Minimální platforma bez zbytečných funkcí, komponent, dokumentace nebo ukázek. Odstraňte nebo neinstalujte nepoužívané funkce a frameworky.
+* Revize a aktualizace konfigurací v návaznosti na všechna bezpečnostní upozornění, aktualizace a záplaty jako součást procesu správy záplat (viz **A03:2025 Selhání dodavatelského řetězce softwaru**). Kontrola oprávnění cloudových úložišť (např. oprávnění S3 bucketů).
+* Segmentovanou architekturu aplikace, která zajišťuje účinné a bezpečné oddělení komponent nebo tenantů pomocí segmentace, kontejnerizace nebo cloudových bezpečnostních skupin (ACL).
+* Zasílání bezpečnostních direktiv klientům, např. bezpečnostních hlaviček (Security Headers).
+* Automatizovaný proces ověřování účinnosti konfigurací a nastavení ve všech prostředích.
+* Proaktivní zavedení centrální konfigurace pro zachytávání příliš informativních chybových hlášení jako záložního opatření.
+* Pokud tyto kontroly nejsou automatizované, měly by být alespoň jednou ročně prováděny manuálně.
+* Využívání federace identit, krátkodobě platných přihlašovacích údajů nebo mechanismů řízení přístupu založených na rolích poskytovaných podkladovou platformou namísto ukládání statických klíčů nebo tajných údajů (secrets) do zdrojového kódu, konfiguračních souborů nebo CI/CD pipeline.
+## Example attack scenarios
+**Scénář #1:** Na aplikačním serveru zůstaly nasazeny ukázkové aplikace, které nebyly z produkčního prostředí odstraněny. Tyto aplikace obsahují známé bezpečnostní chyby, které mohou útočníci zneužít ke kompromitaci serveru. Pokud je jednou z těchto aplikací administrační konzole a výchozí účty nebyly změněny, útočník se přihlásí pomocí výchozích přihlašovacích údajů a převezme kontrolu.
+**Scénář #2:** Na serveru není zakázán výpis adresářů. Útočník zjistí, že může zobrazit seznam adresářů, nalezne a stáhne zkompilované třídy Java, které následně dekompiluje a analyzuje. Na základě toho odhalí závažnou chybu v řízení přístupu aplikace.
+**Scénář #3:** Konfigurace aplikačního serveru umožňuje zobrazování detailních chybových informací, například výpisů zásobníku (stack trace). Tím může dojít ke zpřístupnění citlivých informací nebo vnitřních nedostatků, například verzí použitých komponent, o nichž je známo, že jsou zranitelné.
+**Scénář #4:** Poskytovatel cloudových služeb (CSP) má ve výchozím nastavení povolena oprávnění ke sdílení otevřená do Internetu. To umožňuje přístup k citlivým datům uloženým v cloudovém úložišti.
+Další informace o odkazech a seznamu namapovaných CWE: https://top10.owasp.org/2025/cs/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>Die Anwendung besitzt möglicherweise Schwachstellen, wenn Folgendes zutrifft:
+* Mangelhafte Sicherheitshärtung des Anwendungsstacks oder ungeeignet konfigurierte Berechtigungen auf Cloud-Diensten.
+* Nicht benötigte Features sind aktiviert oder installiert (z. B. unnötige Ports, Dienste, Seiten, Accounts oder Rechte).
+* Standardkonten und -passwörter sind aktiviert bzw. unverändert.
+* Die Fehlerbehandlung gibt Stack-Traces oder andere interne technische Fehlermeldungen an Anwender:innen preis.
+* Für aktualisierte Systeme sind die neuesten Sicherheitsfeatures deaktiviert oder nicht sicher konfiguriert.
+* Die Sicherheitseinstellungen in den Anwendungsservern und -frameworks (z. B. Struts, Spring, ASP.NET), Bibliotheken, Datenbanken etc. sind nicht auf sichere Werte gesetzt.
+* Der Server sendet keine Sicherheits-Header oder -Direktiven, bzw. diese sind nicht sicher konfiguriert.
+* Die Software ist veraltet oder verwundbar (siehe **A06:2025-Unsichere oder veraltete Komponenten**).
+Ohne einen abgestimmten und reproduzierbaren Prozess zur sicheren Konfiguration sind Systeme einem höheren Risiko ausgesetzt!</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+&lt;tr&gt;
+   &lt;td&gt;Zugeordnete CWEs
+   &lt;/td&gt;
+   &lt;td&gt;Max. Häufigkeit
+   &lt;/td&gt;
+   &lt;td&gt;Durchschn. Häufigkeit
+   &lt;/td&gt;
+   &lt;td&gt;Max. Abdeckung
+   &lt;/td&gt;
+   &lt;td&gt;Durchschn. Abdeckung
+   &lt;/td&gt;
+   &lt;td&gt;Durchschn. gewichtete Ausnutzbarkeit
+   &lt;/td&gt;
+   &lt;td&gt;Durchschn. gewichtete Auswirkung
+   &lt;/td&gt;
+   &lt;td&gt;Gesamtanzahl
+   &lt;/td&gt;
+   &lt;td&gt;Summe CVEs
+   &lt;/td&gt;
+&lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16
+   &lt;/td&gt;
+   &lt;td&gt;27.70%
+   &lt;/td&gt;
+   &lt;td&gt;3.00%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;52.35%
+   &lt;/td&gt;
+   &lt;td&gt;7.96
+   &lt;/td&gt;
+   &lt;td&gt;3.97
+   &lt;/td&gt;
+   &lt;td&gt;719,084
+   &lt;/td&gt;
+   &lt;td&gt;1,375
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Es sollten sichere Installationsprozesse implementiert werden, darunter:
+* Ein wiederholbarer Härtungsprozess, welcher die schnelle und einfache Bereitstellung zusätzlicher Umgebungen, die entsprechend abgesichert sind, ermöglicht. Entwicklungs-, Qualitätssicherungs- und Produktionsumgebungen sollten alle identisch konfiguriert sein, wobei in jeder Umgebung unterschiedliche Zugangsdaten verwendet werden sollten. Dieser Prozess sollte automatisiert werden, um den Aufwand für die Einrichtung einer neuen sicheren Umgebung zu minimieren.
+* Eine minimale Plattform ohne unnötige Funktionen, Komponenten, Dokumentation oder Beispiele: Entfernen Sie Funktionen und Frameworks die Sie nicht verwenden oder installieren Sie diese erst gar nicht.
+* Überprüfen und Aktualisieren der Konfigurationen, die für alle Sicherheitshinweise, Updates und Patches im Rahmen des Patch-Verwaltungsprozesses geeignet sind (siehe **A03:2025 – Schwachstellen in der Software-Lieferkette**). Überprüfen Sie die Cloud-Speicherberechtigungen (z. B. S3-Bucket-Berechtigungen).
+## Example attack scenarios
+**Szenario Nr. 1:** Der Anwendungsserver wird mit Beispielanwendungen geliefert, die nicht vom Produktionsserver entfernt wurden. Diese Beispielanwendungen weisen bekannte Schwachstellen auf, die Angreifer:innen nutzen, um den Server zu gefährden. Angenommen, eine dieser Anwendungen ist die Admin-Konsole und die Standardkonten wurden nicht geändert. In diesem Fall meldet sich die/der Angreifer:in mit einem Standardkennwort an und übernimmt die Kontrolle.
+**Szenario Nr. 2:** Die Directory Listings wurden nicht auf dem Server deaktiviert. Angreifer:innen entdecken, dass Verzeichnisse einfach aufgelistet werden können. Die/Der Angreifer:in findet die kompilierten Java-Klassen und lädt sie herunter, dekompiliert sie und betreibt Reverse Engineering, um den Code anzuzeigen. Dies ermöglicht das Findet eines schwerwiegenden Fehlers in der Zugriffskontrolle in der Anwendung.
+**Szenario Nr. 3:** Die Konfiguration des Anwendungsservers ermöglicht die Rückgabe detaillierter Fehlermeldungen an Anwender:innen, wie z. B. Stack-Traces. Dadurch werden möglicherweise vertrauliche Informationen oder zugrunde liegende Fehler wie Komponentenversionen offengelegt, die als angreifbar bekannt sind.
+**Szenario Nr. 4:** Ein Cloud-Dienstanbieter (CSP) gewährt standardmäßig Freigabeberechtigungen zum Internet und ermöglicht dadurch Zugriff auf sensible Daten in der Cloud.
+Weitere Informationen zu den Referenzen und zur Liste der zugeordneten CWEs: https://top10.owasp.org/2025/de/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWE Mapeados 
+   &lt;/td&gt;
+   &lt;td&gt;Tasa de Incidencia Máx.
+   &lt;/td&gt;
+   &lt;td&gt;Tasa de Incidencia Prom.
+   &lt;/td&gt;
+   &lt;td&gt;Cobertura Máx.
+   &lt;/td&gt;
+   &lt;td&gt;Cobertura Prom.
+   &lt;/td&gt;
+   &lt;td&gt;Explotación Ponderada Prom.
+   &lt;/td&gt;
+   &lt;td&gt;Impacto Ponderado Prom.
+   &lt;/td&gt;
+   &lt;td&gt;Ocurrencias Totales
+   &lt;/td&gt;
+   &lt;td&gt;CVE Totales
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16
+   &lt;/td&gt;
+   &lt;td&gt;27.70%
+   &lt;/td&gt;
+   &lt;td&gt;3.00%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;52.35%
+   &lt;/td&gt;
+   &lt;td&gt;7.96
+   &lt;/td&gt;
+   &lt;td&gt;3.97
+   &lt;/td&gt;
+   &lt;td&gt;719,084
+   &lt;/td&gt;
+   &lt;td&gt;1,375
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Deben implementarse procesos de instalación seguros, que incluyan:
+* Un proceso de bastionado (hardening) repetible que permita el despliegue rápido y sencillo de otro entorno que esté bloqueado adecuadamente. Los entornos de desarrollo, QA y producción deben estar configurados de forma idéntica, con credenciales diferentes en cada uno. Este proceso debe estar automatizado para minimizar el esfuerzo requerido para configurar un nuevo entorno seguro.
+* Una plataforma mínima sin funciones, componentes, documentación o ejemplos innecesarios. Elimine o no instale funciones y frameworks que no utilice.
+* Una tarea para revisar y actualizar las configuraciones de acuerdo con todas las notas de seguridad, actualizaciones y parches como parte del proceso de gestión de parches (consulte **A03 Fallas en la Cadena de Suministro de Software**). Revise los permisos de almacenamiento en la nube (por ejemplo, los permisos de los buckets S3).
+* Una arquitectura de aplicación segmentada que proporcione una separación efectiva y segura entre componentes o inquilinos (tenants), con segmentación, contenedorización o grupos de seguridad en la nube (ACLs).
+* Envío de directivas de seguridad a los clientes, por ejemplo, Cabeceras de Seguridad (Security Headers).
+* Un proceso automatizado para verificar la eficacia de las configuraciones y ajustes en todos los entornos.
+* Añadir proactivamente una configuración central para interceptar mensajes de error excesivos como medida de respaldo.
+* Si estas verificaciones no están automatizadas, deben verificarse manualmente al menos una vez al año.
+* Utilizar federación de identidades, credenciales de corta duración o mecanismos de acceso basados en roles proporcionados por la plataforma subyacente en lugar de incrustar claves estáticas o secretos en el código, los archivos de configuración o los flujos de trabajo (pipelines).
+## Example attack scenarios
+**Escenario #1:** El servidor de aplicaciones viene con aplicaciones de ejemplo que no se eliminaron del servidor de producción. Estas aplicaciones de ejemplo tienen fallas de seguridad conocidas que los atacantes utilizan para comprometer el servidor. Supongamos que una de estas aplicaciones es la consola de administración y las cuentas predeterminadas no se cambiaron. En ese caso, el atacante inicia sesión con la contraseña predeterminada y toma el control.
+**Escenario #2:** El listado de directorios no está desactivado en el servidor. Un atacante descubre que puede simplemente listar los directorios. El atacante encuentra y descarga las clases Java compiladas, las cuales descompila y les aplica ingeniería inversa para ver el código. El atacante encuentra entonces una falla grave de control de acceso en la aplicación.
+**Escenario #3:** La configuración del servidor de aplicaciones permite que se devuelvan mensajes de error detallados, como trazas de la pila, a los usuarios. Esto expone potencialmente información sensible o fallas subyacentes, como versiones de componentes que se sabe que son vulnerables.
+**Escenario #4:** Un proveedor de servicios en la nube (CSP) tiene por defecto permisos de compartición abiertos a Internet. Esto permite el acceso a datos sensibles almacenados en el almacenamiento en la nube.
+Para obtener más información sobre las referencias y la lista de CWE asociadas: https://top10.owasp.org/2025/es/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWE Mappate 
+   &lt;/td&gt;
+   &lt;td&gt;Tasso Massimo di Incidenza
+   &lt;/td&gt;
+   &lt;td&gt;Tasso Medio di Incidenza
+   &lt;/td&gt;
+   &lt;td&gt;Copertura Massima
+   &lt;/td&gt;
+   &lt;td&gt;Copertura Media
+   &lt;/td&gt;
+   &lt;td&gt;Exploit Medio Ponderato
+   &lt;/td&gt;
+   &lt;td&gt;Impatto Medio Ponderato
+   &lt;/td&gt;
+   &lt;td&gt;Totale Occorrenze
+   &lt;/td&gt;
+   &lt;td&gt;Totale CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16
+   &lt;/td&gt;
+   &lt;td&gt;27,70%
+   &lt;/td&gt;
+   &lt;td&gt;3,00%
+   &lt;/td&gt;
+   &lt;td&gt;100,00%
+   &lt;/td&gt;
+   &lt;td&gt;52,35%
+   &lt;/td&gt;
+   &lt;td&gt;7,96
+   &lt;/td&gt;
+   &lt;td&gt;3,97
+   &lt;/td&gt;
+   &lt;td&gt;719.084
+   &lt;/td&gt;
+   &lt;td&gt;1.375
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Devono essere implementati processi di installazione sicuri, incluso:
+* Un processo di hardening ripetibile che consenta la distribuzione rapida e semplice di un altro ambiente adeguatamente protetto. Gli ambienti di sviluppo, QA e produzione devono essere configurati in modo identico, con credenziali diverse utilizzate in ciascun ambiente. Questo processo deve essere automatizzato per minimizzare lo sforzo necessario per configurare un nuovo ambiente sicuro.
+* Una piattaforma minimale senza funzionalità, componenti, documentazione o campioni non necessari. Rimuovere o non installare funzionalità e framework non utilizzati.
+* Un'attività di revisione e aggiornamento delle configurazioni appropriate a tutte le note di sicurezza, aggiornamenti e patch come parte del processo di gestione delle patch (vedi **A03 Software Supply Chain Failures**). Revisionare i permessi dello storage cloud (es. permessi dei bucket S3).
+* Un'architettura applicativa segmentata che fornisca una separazione efficace e sicura tra componenti o tenant, con segmentazione, containerizzazione o gruppi di sicurezza cloud (ACL).
+* Invio di direttive di sicurezza ai client, es. Security Headers.
+* Un processo automatizzato per verificare l'efficacia delle configurazioni e delle impostazioni in tutti gli ambienti.
+* Aggiungere proattivamente una configurazione centrale per intercettare messaggi di errore eccessivi come backup.
+* Se queste verifiche non sono automatizzate, devono essere verificate manualmente almeno annualmente.
+* Utilizzare la federazione di identità, credenziali di breve durata o meccanismi di accesso basati sui ruoli forniti dalla piattaforma sottostante anziché incorporare chiavi o segreti statici nel codice, nei file di configurazione o nelle pipeline.
+## Example attack scenarios
+**Scenario #1:** Il server applicativo include applicazioni di esempio non rimosse dal server di produzione. Queste applicazioni di esempio hanno falle di sicurezza note che gli attaccanti utilizzano per compromettere il server. Supponiamo che una di queste applicazioni sia la console di amministrazione e che le credenziali predefinite non siano state cambiate. In tal caso, l'attaccante accede con la password predefinita e prende il controllo.
+**Scenario #2:** Il directory listing non è disabilitato sul server. Un attaccante scopre che può semplicemente elencare le directory. L'attaccante trova e scarica le classi Java compilate, che decompila e fa reverse engineering per visualizzare il codice. L'attaccante trova quindi una grave falla nel controllo degli accessi nell'applicazione.
+**Scenario #3:** La configurazione del server applicativo consente la restituzione di messaggi di errore dettagliati, come stack trace, agli utenti. Ciò potrebbe esporre informazioni sensibili o falle sottostanti, come le versioni dei componenti note per essere vulnerabili.
+**Scenario #4:** Un cloud service provider (CSP) ha come default i permessi di condivisione aperti a Internet. Ciò consente l'accesso ai dati sensibili archiviati nello storage cloud.
+Per maggiori informazioni sui riferimenti e sull'elenco delle CWE mappate: https://top10.owasp.org/2025/it/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;紐付けられた CWE 数&lt;/td&gt;
+   &lt;td&gt;最大出現率&lt;/td&gt;
+   &lt;td&gt;平均出現率&lt;/td&gt;
+   &lt;td&gt;最大網羅率&lt;/td&gt;
+   &lt;td&gt;平均網羅率&lt;/td&gt;
+   &lt;td&gt;平均加重悪用スコア&lt;/td&gt;
+   &lt;td&gt;平均加重影響スコア&lt;/td&gt;
+   &lt;td&gt;出現総数&lt;/td&gt;
+   &lt;td&gt;CVE 総数&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16&lt;/td&gt;
+   &lt;td&gt;27.70%&lt;/td&gt;
+   &lt;td&gt;3.00%&lt;/td&gt;
+   &lt;td&gt;100.00%&lt;/td&gt;
+   &lt;td&gt;52.35%&lt;/td&gt;
+   &lt;td&gt;7.96&lt;/td&gt;
+   &lt;td&gt;3.97&lt;/td&gt;
+   &lt;td&gt;719,084&lt;/td&gt;
+   &lt;td&gt;1,375&lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+安全なインストールプロセスを実装する必要があります。これには以下の対策が含まれます。
+* **反復可能な要塞化プロセス：** 適切にロックダウンされた環境を、迅速かつ容易にデプロイできるプロセスを確立してください。開発、QA、本番の各環境は同一の設定とし、認証情報のみを環境ごとに使い分けるべきです。このプロセスを自動化し、安全な環境構築の負荷を最小限に抑えてください。
+* **最小限のプラットフォーム：** 不要な機能、コンポーネント、ドキュメント、サンプルを含まない最小限のプラットフォームを構成してください。使用していない機能やフレームワークは削除するか、インストールしないでください。
+* **設定レビューとパッチ管理：** パッチ管理プロセスの一環として、セキュリティノートやアップデート、パッチに基づき設定をレビュー・更新してください（**A03 ソフトウェアサプライチェーンの不備** を参照）。クラウドストレージ（S3 バケット等）の権限設定も定期的にレビューしてください。
+* **セグメント化されたアーキテクチャ：** コンテナ化、セグメンテーション、あるいはクラウドのセキュリティグループ (ACL) を活用し、コンポーネント間やテナント間を安全に分離してください。
+* **セキュリティディレクティブの送信：** セキュリティヘッダーなどのディレクティブをクライアントへ送信してください。
+* **自動検証プロセス：** すべての環境において、設定の有効性を自動で検証するプロセスを導入してください。
+* **中央集中型のエラー管理：** 過剰なエラーメッセージをインターセプトする中央設定を、バックアップとして事前に導入してください。
+* **手動検証の実施：** 検証が自動化されていない場合は、少なくとも年に一度は手動で検証を実施してください。
+* **プラットフォーム機能の活用：** コードや設定ファイル、パイプラインに静的なキーやシークレットを埋め込むのではなく、プラットフォームが提供するアイデンティティ連携 (Identity Federation)、短命な認証情報 (Short-lived Credentials)、またはロールベースのアクセス制御を活用してください。
+## Example attack scenarios
+**シナリオ #1：** 本番サーバーからサンプルアプリケーションが削除されていなかった。攻撃者は、これらのサンプルに含まれる既知の脆弱性を悪用してサーバーを侵害した。さらに、管理コンソールのデフォルトパスワードが変更されていなかったため、攻撃者は管理者としてログインし、システムを完全に乗っ取った。
+**シナリオ #2：** サーバーのディレクトリ一覧表示が無効化されていなかった。攻撃者はディレクトリ構造を把握し、コンパイル済みの Java クラスファイルをダウンロードした。これをデコンパイルしてソースコードをリバースエンジニアリングした結果、アプリケーションに重大なアクセス制御の欠陥があることを突き止めた。
+**シナリオ #3：** アプリケーションサーバーの設定により、スタックトレースを含む詳細なエラーメッセージがユーザーに返されていた。これにより、機密情報や、使用されているコンポーネントのバージョン（脆弱性が既知のものを含む）といった内部情報が攻撃者に露呈した。
+**シナリオ #4：** クラウドサービスプロバイダー (CSP) のデフォルト設定により、共有権限がインターネットに公開されていた。これにより、クラウドストレージ内に保存されていた機密データが第三者に奪取された。
+参考資料およびマッピングされたCWEの一覧について、詳しくはこちら： https://top10.owasp.org/2025/ja/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;해당되는 CWE 개수
+   &lt;/td&gt;
+   &lt;td&gt;최대 취약점 발생률
+   &lt;/td&gt;
+   &lt;td&gt;평균 취약점 발생률
+   &lt;/td&gt;
+   &lt;td&gt;최대 테스트 커버리지
+   &lt;/td&gt;
+   &lt;td&gt;평균 테스트 커버리지
+   &lt;/td&gt;
+   &lt;td&gt;평균 가중 악용도
+   &lt;/td&gt;
+   &lt;td&gt;평균 가중 영향도
+   &lt;/td&gt;
+   &lt;td&gt;총 발생 건수
+   &lt;/td&gt;
+   &lt;td&gt;총 CVE 건수
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16
+   &lt;/td&gt;
+   &lt;td&gt;27.70%
+   &lt;/td&gt;
+   &lt;td&gt;3.00%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;52.35%
+   &lt;/td&gt;
+   &lt;td&gt;7.96
+   &lt;/td&gt;
+   &lt;td&gt;3.97
+   &lt;/td&gt;
+   &lt;td&gt;719,084
+   &lt;/td&gt;
+   &lt;td&gt;1,375
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+다음과 같은 항목들을 포함하여 보안성이 반영된 구성 절차를 수립한다.
+* 재사용 가능한 하드닝 프로세스를 구축하여 필요한 보안 통제가 적용된 동일한 형태의 신규 환경을 빠르고 쉽게 배포 가능해야 한다. 개발, QA, 운영 환경은 모두 동일한 구성으로 설정하며, 각각의 환경에서 서로 다른 자격증명을 사용한다. 이 프로세스는 자동화하여 요구되는 새로운 보안환경을 구성하는 데 필요한 노력을 최소화한다.
+* 사용하지 않은 기능, 컴포넌트, 문서, 샘플을 포함하지 않는 최소한의 플랫폼을 구현한다. 사용하지 않는 기능과 프레임워크는 삭제하거나 설치되지 않아야 한다.
+* 패치 관리 프로세스(참고: **A03 소프트웨어 공급망 체인 실패**) 수행 시 모든 보안 공지, 업데이트, 패치에 따른 적절한 검토 및 업데이트를 한다. 또한, 클라우드 스토리지 권한(예: S3 버킷 권한)을 점검한다.
+* 구성 요소 간 또는 테넌트 간 효과적으로 격리할 수 있도록 세분화, 컨테이너화, 클라우드 보안 그룹(ACL)을 활용해 애플리케이션 아키텍쳐를 설계함으로써 효과적이고 안전한 분리 구조를 보장한다.
+* 보안 지시문을 클라이언트로 보내야 한다. (예: 보안 헤더)
+* 자동화된 프로세스를 구축하여 모든 환경에서 해당 설정들의 안전성을 검증한다.
+* 만일의 경우를 대비해, 과도한 에러 메시지가 사용자에게 노출되지 않도록 공통 설정을 사전에 구성한다.
+* 만약 이런 검증사항들이 자동화되지 않았다면, 최소한 매년 1회는 수동으로 검증한다.
+* 코드, 설정 파일, 파이프 라인 내 정적인 키나 시크릿을 저장하는 대신 플랫폼에서 제공하는 아이덴티티 페더레이션, 단기 유효 자격 증명, 또는 역할 기반 접근 매커니즘을 사용한다.
+## Example attack scenarios
+**시나리오 1:** 운영 서버에서 테스트용 애플리케이션이 지워지지 않았다. 테스트용 애플리케이션은 공격자가 해당 서버를 공격할 수 있는 보안 취약점이 존재한다고 알려져 있으며, 그중 하나의 애플리케이션은 관리자용 콘솔이라 가정해 보겠다. 그리고 기본 계정은 변경되지 않았다. 이런 경우 공격자는 기본 계정으로 로그인 한 뒤 시스템 장악이 가능하다.
+**시나리오 2:** 서버에서 디렉토리 리스팅이 활성화 되었을 때 공격자는 단순하게 디렉토리 목록을 탐색할 수 있다. 공격자는 컴파일된 자바 클래스들을 찾거나 다운로드 할 수 있고, 이런 클래스들을 디컴파일 하거나 리버싱 엔지니어링을 통해 코드를 볼 수 있다. 그 뒤 공격자는 애플리케이션 내에서 서버 접근 제어 취약점을 찾은 뒤 악용 가능하다.
+**시나리오 3:** 사용자에게 반환되는 스택 트레이스(Stack trace) 같은 자세한 에러 메시지가 표시되도록 설정되어 있는 경우 민감한 정보나 해당 컴포넌트 버전에 알려진 취약점 같은 근본적 취약점이 노출될 가능성이 있다.
+**시나리오 4:** 클라우드 서비스 제공자(Cloud service provider, CSP)는 인터넷에 자원을 공유하는 권한이 기본 설정이다. 이는 민감한 정보가 공개된 클라우드 스토리지 내 저장될 시 관계자 외 접근을 허용할 수 있다.
+참고 자료와 매핑된 CWE 목록에 대한 자세한 정보: https://top10.owasp.org/2025/ko/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs Mapeadas 
+   &lt;/td&gt;
+   &lt;td&gt;Taxa Máx. de Incidência
+   &lt;/td&gt;
+   &lt;td&gt;Taxa Média de Incidência
+   &lt;/td&gt;
+   &lt;td&gt;Cobertura Máxima
+   &lt;/td&gt;
+   &lt;td&gt;Cobertura Média
+   &lt;/td&gt;
+   &lt;td&gt;Exploit Médio Ponderado
+   &lt;/td&gt;
+   &lt;td&gt;Impacto Médio Ponderado
+   &lt;/td&gt;
+   &lt;td&gt;Total de Ocorrências
+   &lt;/td&gt;
+   &lt;td&gt;Total de CVEs
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16
+   &lt;/td&gt;
+   &lt;td&gt;27.70%
+   &lt;/td&gt;
+   &lt;td&gt;3.00%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;52.35%
+   &lt;/td&gt;
+   &lt;td&gt;7.96
+   &lt;/td&gt;
+   &lt;td&gt;3.97
+   &lt;/td&gt;
+   &lt;td&gt;719,084
+   &lt;/td&gt;
+   &lt;td&gt;1,375
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Processos de instalação seguros devem ser implementados, incluindo:
+- Um processo de _hardening_ repetível que permita a implantação rápida e fácil de outro ambiente devidamente bloqueado. Os ambientes de desenvolvimento, QA e produção devem ser configurados de forma idêntica, com credenciais diferentes usadas em cada um. Este processo deve ser automatizado para minimizar o esforço necessário para configurar um novo ambiente seguro.
+- Uma plataforma mínima, sem quaisquer recursos, componentes, documentação ou amostras desnecessárias. Remova ou não instale recursos e **frameworks** não utilizados.
+- Uma tarefa para revisar e atualizar as configurações de acordo com todas as notas de segurança, atualizações e **patches** como parte do processo de gerenciamento de **patches** (veja **A03 Falhas na Cadeia de Suprimentos de Software**). Revise as permissões de armazenamento em nuvem (ex: permissões de buckets S3).
+- Uma arquitetura de aplicação segmentada que forneça separação eficaz e segura entre componentes ou usuários (_tenants_), com segmentação, conteinerização ou grupos de segurança de nuvem (ACLs).
+- Envio de diretivas de segurança para os clientes, ex: **headers** de segurança.
+- Um processo automatizado para verificar a eficácia das configurações e definições em todos os ambientes.
+- Adição proativa de uma configuração central para interceptar mensagens de erro excessivas como reserva (_backup_).
+- Se essas verificações não forem automatizadas, elas devem ser verificadas manualmente, no mínimo, anualmente.
+- Utilize federação de identidade, credenciais de curta duração ou mecanismos de acesso baseados em funções (RBAC) fornecidos pela plataforma subjacente, em vez de incorporar chaves estáticas ou segredos (_secrets_) no código, arquivos de configuração ou **pipelines**.
+## Example attack scenarios
+**Cenário #1:** O servidor de aplicação vem com aplicações de exemplo não removidas do servidor de produção. Essas aplicações de exemplo têm falhas de segurança conhecidas que os **atacantes** usam para comprometer o servidor. Suponha que uma dessas aplicações seja o console de administração e as contas padrão não foram alteradas. Nesse caso, o **atacante** faz o login com a senha padrão e assume o controle.
+**Cenário #2:** A listagem de diretórios não está desativada no servidor. Um **atacante** descobre que pode simplesmente listar os diretórios. O **atacante** encontra e baixa as classes Java compiladas, que ele descompila e faz engenharia reversa para visualizar o código. O **atacante**, então, encontra uma falha grave de controle de acesso na aplicação.
+**Cenário #3:** A configuração do servidor de aplicação permite que mensagens de erro detalhadas, como _stack traces_, sejam retornadas aos usuários. Isso potencialmente expõe informações sensíveis ou falhas subjacentes, como versões de componentes que são conhecidamente vulneráveis.
+**Cenário #4:** Um provedor de serviços de nuvem (CSP) define por padrão permissões de compartilhamento abertas para a Internet. Isso permite que dados sensíveis armazenados no armazenamento em nuvem sejam acessados.
+Para mais informações sobre as referências e a lista de CWEs mapeadas: https://top10.owasp.org/2025/pt-BR/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;映射的 CWE 数量
+   &lt;/td&gt;
+   &lt;td&gt;最大发生率
+   &lt;/td&gt;
+   &lt;td&gt;平均发生率
+   &lt;/td&gt;
+   &lt;td&gt;最大覆盖率
+   &lt;/td&gt;
+   &lt;td&gt;平均覆盖率
+   &lt;/td&gt;
+   &lt;td&gt;平均加权可利用性
+   &lt;/td&gt;
+   &lt;td&gt;平均加权影响
+   &lt;/td&gt;
+   &lt;td&gt;发生总数
+   &lt;/td&gt;
+   &lt;td&gt;CVE 总数
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16
+   &lt;/td&gt;
+   &lt;td&gt;27.70%
+   &lt;/td&gt;
+   &lt;td&gt;3.00%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;52.35%
+   &lt;/td&gt;
+   &lt;td&gt;7.96
+   &lt;/td&gt;
+   &lt;td&gt;3.97
+   &lt;/td&gt;
+   &lt;td&gt;719,084
+   &lt;/td&gt;
+   &lt;td&gt;1,375
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+应实施安全安装流程，包括：
+* 建立可重复的加固流程，能够快速、轻松地部署另一个经过适当锁定的环境。开发、QA 和生产环境应以相同方式配置，但各环境使用不同凭据。该流程应自动化，以减少搭建新安全环境所需的工作量。
+* 使用最小化平台，不包含任何不必要的功能、组件、文档或示例。移除或不要安装未使用的功能和框架。
+* 将审查和更新配置作为补丁管理流程的一部分，确保配置符合所有安全公告、更新和补丁要求（参见 **A03 软件供应链失效**）。审查云存储权限（例如 S3 bucket 权限）。
+* 采用分段应用架构，通过分段、容器化或云安全组（ACL）在组件或租户之间实现有效且安全的隔离。
+* 向客户端发送安全指令，例如安全头。
+* 建立自动化流程，验证所有环境中的配置和设置是否有效。
+* 主动增加集中配置，作为拦截过多错误消息的备用措施。
+* 如果这些验证没有自动化，至少应每年手动验证一次。
+* 使用底层平台提供的身份联合、短期凭据或基于角色的访问机制，而不是在代码、配置文件或流水线中嵌入静态密钥或 secret。
+## Example attack scenarios
+**场景 #1：** 应用服务器附带的示例应用没有从生产服务器中移除。这些示例应用存在已知安全缺陷，攻击者可利用它们攻陷服务器。假设其中一个示例应用是管理控制台，且默认账户没有修改。攻击者就能使用默认密码登录并接管系统。
+**场景 #2：** 服务器未禁用目录列表。攻击者发现可以直接列出目录。他找到并下载编译后的 Java 类文件，反编译并逆向工程查看代码。随后攻击者在应用中发现严重访问控制缺陷。
+**场景 #3：** 应用服务器配置允许向用户返回详细错误消息，例如堆栈跟踪。这可能暴露敏感信息或底层缺陷，例如已知易受攻击的组件版本。
+**场景 #4：** 云服务提供商（CSP）默认将共享权限开放到互联网。这会允许云存储中的敏感数据被访问。
+有關參考資料及已對應 CWE 清單的更多資訊： https://top10.owasp.org/2025/zh-Hant/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>本脆弱性は、攻撃者がシステムを欺き、無効なユーザーや誤ったユーザーを正当なものとして認識させた場合に発生します。
+以下の項目に当てはまる場合、アプリケーションに認証上の不備が存在する可能性があります。
+* **自動化攻撃の許容：** クレデンシャルスタッフィング (Credential Stuffing) や、流出した資格情報のバリエーションを試すパスワードスプレー攻撃 (Password Spray Attacks) を許容している。
+* **ブルートフォース攻撃への脆弱性：** ブルートフォースやその他の自動化・スクリプト化された攻撃を迅速にブロックしていない。
+* **脆弱なパスワードの許可：** デフォルト設定、脆弱な、あるいは広く知られたパスワード（「Password1」や admin/admin など）の使用を許可している。
+* **漏洩済み情報の利用：** 既に侵害が確認されている資格情報を用いて新規アカウントを作成できてしまう。
+* **不適切なリカバリプロセス：** 「秘密の質問」のような、安全性を確保できない知識ベースの回答に依存したパスワード復旧プロセスを採用している。
+* **不十分なデータ保護：** パスワードをプレーンテキスト、あるいは脆弱なハッシュ形式で保存している（**A04:2025 暗号化の失敗** 参照）。
+* **MFA の欠如：** 多要素認証 (MFA) が実装されていない、あるいはそのフォールバック手段が脆弱である。
+* **セッション管理の不備：** URL や安全でない場所へセッション ID を露出させている、あるいはログイン後にセッション ID を再利用している。
+* **不完全なログアウト：** ログアウト時や一定時間の無活動後に、セッションや認証トークン（特に SSO トークン）が正しく無効化されない。
+* **検証の不足：** 提供された資格情報の適用範囲 (Scope) や意図された対象 (Audience) を正しく検証していない。</t>
+  </si>
+  <si>
+    <t>Bez logování a monitorování nelze útoky a narušení zabezpečení odhalit a bez upozorňování je během bezpečnostního incidentu velmi obtížné reagovat rychle a účinně. K nedostatkům v logování, průběžném monitorování, detekci a upozorňování, které mají vést k zahájení aktivní reakce, dochází vždy, když:
+* Auditovatelné události, jako jsou přihlášení, neúspěšná přihlášení a transakce s vysokou hodnotou, nejsou logovány vůbec nebo jsou logovány nekonzistentně (například se logují pouze úspěšná přihlášení, nikoli neúspěšné pokusy).
+* Varování a chyby negenerují žádné, dostatečné nebo srozumitelné logovací záznamy.
+* Integrita logů není řádně chráněna před manipulací.
+* Logy aplikací a rozhraní API nejsou monitorovány z hlediska podezřelé aktivity.
+* Logy jsou ukládány pouze lokálně a nejsou řádně zálohovány.
+* Vhodné prahové hodnoty pro upozorňování a procesy eskalace reakce nejsou zavedeny nebo nejsou účinné. Upozornění nejsou přijímána ani vyhodnocována v přiměřené době.
+* Penetrační testování a skeny prováděné nástroji pro dynamické testování bezpečnosti aplikací (DAST), jako jsou Burp nebo ZAP, nespouštějí upozornění.
+* Aplikace nedokáže aktivní útoky detekovat, eskalovat ani na ně upozornit v reálném čase nebo téměř v reálném čase.
+* Jste zranitelní vůči úniku citlivých informací tím, že události logování a upozorňování zpřístupníte uživateli nebo útočníkovi (viz **A01:2025 Nedostatečné řízení přístupu (Broken Access Control)**), nebo tím, že logujete citlivé informace, které by logovány být neměly (například PII nebo PHI).
+* Pokud nejsou data v logu správně zakódována, jste zranitelní vůči injektážím nebo útokům na systémy logování či monitorování.
+* Aplikace opomíjí chyby a jiné výjimečné stavy nebo je zpracovává nesprávně, takže systém neví, že k chybě došlo, a není proto schopen zaznamenat, že nastal problém.
+* Odpovídající „use cases“ pro vyvolání upozornění chybějí nebo jsou zastaralé, a proto nelze rozpoznat zvláštní situaci.
+* Příliš velké množství falešně pozitivních upozornění znemožňuje odlišit důležitá upozornění od nedůležitých, v důsledku čehož jsou rozpoznána příliš pozdě, nebo vůbec ne (fyzické přetížení týmu SOC).
+* Zjištěná upozornění nelze správně zpracovat, protože playbook pro daný use case je neúplný, zastaralý nebo chybí.</t>
+  </si>
+  <si>
+    <t>Ohne Protokollierung und Überwachung lassen sich Angriffe und Sicherheitsverletzungen nicht erkennen, und ohne Warnmeldungen ist es sehr schwierig, bei einem Sicherheitsvorfall schnell und effektiv zu reagieren. Eine unzureichende Protokollierung, kontinuierliche Überwachung, Erkennung und Warnmeldung zur Einleitung aktiver Maßnahmen kommt immer dann vor, wenn Folgendes zutrifft:
+* Nachvollziehbare Ereignisse, wie Anmeldungen, fehlgeschlagene Anmeldungen und wertvolle Transaktionen, werden nicht protokolliert (zum Beispiel nur erfolgreiche Anmeldungen protokollieren, nicht aber fehlgeschlagene Versuche).
+* Warnungen und Fehler erzeugen keine, unangemessene oder unklare Log-Einträge.
+* Die Integrität der Protokolle ist nicht ausreichend vor Manipulationen geschützt.
+* Die Logs von Anwendungen und APIs werden nicht auf verdächtige Aktivitäten überwacht.
+* Protokolle werden nur lokal gespeichert und nicht angemessen gesichert.
+* Geeignete Schwellenwerte für Warnmeldungen und Eskalationsprozesse für Gegenmaßnahmen sind nicht vorhanden oder nicht wirksam. Benachrichtigungen werden nicht innerhalb einer angemessenen Frist empfangen oder geprüft.
+* Penetrationstests und Scans durch DAST-Tools (Dynamic Application Security Testing) (wie Burp oder ZAP) lösen keine Alarme aus.
+* Die Anwendung kann Angriffe weder in Echtzeit noch nahezu in Echtzeit erkennen, eskalieren oder Alarm schlagen.
+* Sie sind anfällig für den Verlust sensibler Informationen, wenn Sie Protokollierungs- und Warnereignisse für eine:n Benutzer:in oder eine:n Angreifer:in sichtbar machen (siehe **A01:2025-Mangelhafte Zugriffskontrolle**) oder wenn Sie sensible Informationen protokollieren, die nicht protokolliert werden sollten (wie z. B. personenbezogene Daten oder geschützte Gesundheitsdaten).
+* Sie sind anfällig für Injection oder Angriffe auf die Protokollierungs- oder Überwachungssysteme, wenn Protokolldaten nicht encoded sind.
+* Die Anwendung erkennt Fehler und andere Ausnahmebedingungen nicht oder sie behandelt diese falsch, sodass das System nicht erkennt, dass ein Fehler aufgetreten ist, und daher nicht protokollieren kann, dass ein Problem vorlag.
+* Es fehlen angemessene „Anwendungsfälle“ für die Ausgabe von Warnmeldungen oder diese sind veraltet, um eine besondere Situation zu erkennen.
+* Zu viele Fehlalarme machen es unmöglich, wichtige Warnmeldungen von unwichtigen zu unterscheiden, was dazu führt, dass sie zu spät oder gar nicht erkannt werden (physische Überlastung des SOC-Teams).
+* Erkannte Warnmeldungen können nicht korrekt verarbeitet werden, da das Handbuch für den Anwendungsfall unvollständig, veraltet oder nicht vorhanden ist.</t>
+  </si>
+  <si>
+    <t>Sin registro (logging) y monitoreo (monitoring), los ataques y las brechas de seguridad no pueden detectarse, y sin alertas (alerting) es muy difícil responder de forma rápida y eficaz durante un incidente de seguridad. Las fallas por registro, monitoreo continuo, detección y alertas insuficientes para iniciar respuestas activas se producen siempre que:
+* No se registran eventos auditables, como los inicios de sesión, las fallas de inicio de sesión y las transacciones de alto valor, o se registran de forma incoherente (por ejemplo, registrando solo los inicios de sesión correctos, pero no los intentos fallidos).
+* Las advertencias y los errores no generan mensajes de registro, o estos son inadecuados o poco claros.
+* La integridad de los registros no está debidamente protegida contra la manipulación.
+* Los registros de las aplicaciones y las API no se monitorean para detectar actividades sospechosas.
+* Los registros solo se almacenan localmente y no se dispone de las copias de seguridad adecuadas.
+* No existen o no son efectivos los umbrales de alerta y los procesos de escalado de respuesta adecuados. Las alertas no se reciben o no se revisan en un tiempo razonable.
+* Las pruebas de penetración (pentesting) y los escaneos mediante herramientas de pruebas de seguridad de aplicaciones dinámicas (DAST) (como Burp Suite o ZAP) no activan alertas.
+* La aplicación no puede detectar, escalar o alertar sobre ataques activos en tiempo real o casi en tiempo real.
+* Se es vulnerable a la filtración de información sensible al hacer visibles los eventos de registro y alerta para un usuario o un atacante (ver **A01:2025-Pérdida de Control de Acceso**), o al registrar información sensible que no debería registrarse (como PII o PHI).
+* Se es vulnerable a inyecciones o ataques a los sistemas de registro o monitoreo si los datos de los registros no están correctamente codificados.
+* La aplicación carece de errores u otras condiciones excepcionales, o los gestiona de forma inadecuada, de modo que el sistema no es consciente de que se ha producido un error y, por tanto, no puede registrar que ha habido un problema.
+* Faltan "casos de uso" adecuados para la emisión de alertas o estos están desactualizados para reconocer una situación especial.
+* Demasiadas alertas de falsos positivos hacen imposible distinguir las alertas importantes de las que no lo son, lo que provoca que se reconozcan demasiado tarde o no se reconozcan en absoluto (sobrecarga física del equipo del SOC).
+* Las alertas detectadas no pueden procesarse correctamente porque el manual de procedimientos (playbook) para el caso de uso es incompleto, está desactualizado o no existe.</t>
+  </si>
+  <si>
+    <t>Senza logging e monitoraggio, gli attacchi e le violazioni non possono essere rilevati, e senza alerting è molto difficile rispondere in modo rapido ed efficace durante un incidente di sicurezza. Un logging insufficiente, un monitoraggio continuo, il rilevamento e l'alerting per avviare risposte attive si verificano ogni volta che:
+* Gli eventi verificabili, come i login, i login falliti e le transazioni di alto valore, non vengono registrati o vengono registrati in modo incoerente (ad esempio, vengono registrati solo i login riusciti, ma non i tentativi falliti).
+* Gli avvisi e gli errori generano messaggi di log assenti, inadeguati o poco chiari.
+* L'integrità dei log non è adeguatamente protetta dalla manomissione.
+* I log delle applicazioni e delle API non vengono monitorati per attività sospette.
+* I log vengono archiviati solo localmente e non vengono adeguatamente sottoposti a backup.
+* Soglie di alerting appropriate e processi di escalation delle risposte non sono in atto o efficaci. Gli alert non vengono ricevuti o esaminati entro un tempo ragionevole.
+* I penetration test e le scansioni degli strumenti di dynamic application security testing (DAST) (come Burp o ZAP) non attivano alert.
+* L'applicazione non è in grado di rilevare, escalare o avvisare per attacchi attivi in tempo reale o quasi in tempo reale.
+* Sei vulnerabile alla fuga di informazioni sensibili rendendo visibili gli eventi di logging e alerting a un utente o a un attaccante (vedi **A01:2025-Broken Access Control**), o registrando informazioni sensibili che non dovrebbero essere registrate (come PII o PHI).
+* Sei vulnerabile a injection o attacchi ai sistemi di logging o monitoraggio se i dati dei log non sono correttamente codificati.
+* L'applicazione manca o gestisce male gli errori e altre condizioni eccezionali, in modo tale che il sistema non sia consapevole che si è verificato un errore e quindi non sia in grado di registrare che c'è stato un problema.
+* Mancano o sono obsoleti adeguati 'use case' per l'emissione di alert per riconoscere una situazione speciale.
+* Troppi alert falsi positivi rendono impossibile distinguere gli alert importanti da quelli non importanti, con il risultato che vengono riconosciuti troppo tardi o per niente (sovraccarico fisico del team SOC).
+* Gli alert rilevati non possono essere elaborati correttamente perché il playbook per il caso d'uso è incompleto, obsoleto o mancante.</t>
+  </si>
+  <si>
+    <t>ロギングと監視 (Monitoring) がなければ攻撃や侵害を検知できず、適切なアラート (Alerting) がなければ、セキュリティインシデント発生時に迅速かつ効果的な対応をとることが困難になります。
+以下のような状況にある場合、アプリケーションは脆弱です。
+* ログイン、ログイン失敗、および高価値な取引などの監査可能なイベントが記録されていない、あるいは不整合である（例：ログイン成功のみを記録し、失敗を記録していない）。
+* 警告やエラーが発生しても、ログメッセージが生成されない、あるいは不適切で不明確である。
+* ログの完全性 (Integrity) が保護されておらず、改ざんのリスクに晒されている。
+* アプリケーションや API のログが、不審なアクティビティに対して監視されていない。
+* ログがローカルに保存されるだけで、適切にバックアップされていない。
+* 適切なアラート閾値やレスポンス・エスカレーションプロセスが機能しておらず、アラートが合理的な時間内に受信・確認されない。
+* ペネトレーションテストや DAST (動的アプリケーションセキュリティテスト) ツール（Burp や ZAP 等）によるスキャンが、アラートをトリガーしない。
+* アプリケーションが進行中の攻撃をリアルタイム、あるいはそれに近い速度で検知・通知・エスカレーションできない。
+* ログやアラートの内容がユーザーや攻撃者に露出している（**A01:2025 アクセス制御の不備** 参照）、あるいは個人識別情報 (PII) や健康情報 (PHI) などの記録すべきでない機密情報がログに含まれている。
+* ログデータが適切にエンコードされておらず、ロギングまたは監視システム自体へのインジェクション攻撃を許容している。
+* エラーや例外的な状況の処理に失敗しているため、システムがエラーを認識できず、結果として問題を記録できない。
+* 特定の異常事態を認識するための適切なアラート用「ユースケース」が不足している、あるいは陳腐化している。
+* 誤検知 (False Positive) が多すぎて重要なアラートを判別できず、SOC (セキュリティ運用センター) チームが物理的な過負荷や「警報疲れ」を起こしている。
+* プレイブック (Playbook)（対応手順書）が不完全、あるいは欠落しているため、検知されたアラートを正しく処理できない。</t>
+  </si>
+  <si>
+    <t>로깅과 모니터링이 없으면 공격 및 침해를 탐지할 수 없으며, 알림이 없으면 보안 인시던트 발생시 신속하고 효과적으로 대응하기가 매우 어렵다. 다음과 같은 경우에는 불충분한 로깅, 지속적인 모니터링, 탐지 및 능동적 대응을 시작하기 위한 알림의 미흡이 발생한다. 아래와 같은 경우, 능동적 대응을 개시하기 위한 로깅, 지속적 모니터링, 탐지, 알림이 부족한 것으로 볼 수 있다.
+* 로그인, 로그인 실패, 중요 거래 데이터 등 감사가 필요한 대상의 이벤트가 누락되거나 기준 없이 들쭉날쭉하게(예: 성공 로그인만 기록) 로깅되는 경우.
+* 경고 및 오류가 로그 메시지를 생성하지 않거나, 부적절하거나, 불명확한 로그를 생성하는 경우.
+* 로그가 위변조되지 않도록 무결성 보호가 적용되지 않는 경우.
+* 애플리케이션 및 API 로그를 기반으로 한 이상징후 모니터링이 수행되지 않는 경우.
+* 로그가 로컬에만 보관되고 백업이 적절히 수행되지 않는 경우.
+* 적절한 알림 임계값 및 대응 에스컬레이션 절차가 마련되어 있지 않거나 효과적이지 않다. 알림이 적시에 확인되지 않거나 검토되지 않는 경우.
+* 동적 애플리케이션 보안 테스트(DAST) 도구(예: Burp 또는 ZAP)에 의한 침투 테스트 및 스캔이 알림을 트리거하지 않는 경우.
+* 진행 중인 공격을 실시간 혹은 준실시간으로 탐지하지 못하거나 상위 단계로 에스컬레이션하거나 알림을 발생시키지 못하는 경우.
+* 로깅 및 알림 이벤트를 사용자 또는 공격자에게 노출 하거나(**A01:2025-접근 제어 실패** 참조), 로깅되면 안 되는 민감정보(예: PII 또는 PHI)를 로깅함으로써 민감정보 유출에 취약한 경우.
+* 로그 데이터 인코딩이 부적절해 로깅 또는 모니터링 시스템 자체가 인젝션 등 공격 대상이 되는 경우.
+* 애플리케이션이 오류 및 예외 처리를 누락 또는 오처리하여 시스템이 오류 발생 자체를 인지하지 못하고, 결과적으로 문제를 로그로 남길 수 없는 경우.
+* 특수 상황을 식별하기 위한 알림 '유스케이스'가 없거나 오래되어 현재 환경을 반영하지 못한다.
+* 특정 상황을 탐지해 알림을 발생시키기 위한 인시던트 유스케이스(use case)가 없거나, 갱신이 되지 않아 현행 환경을 충분히 반영하지 못하는 경우.
+* 너무 많은 오탐 알림으로 인해 중요한 알림과 중요하지 않은 알림을 구분할 수 없게 되어, 알림이 너무 늦게 인지되거나 전혀 인지되지 않는 경우(SOC 팀의 물리적 과부하).
+* 유스케이스에 대한 플레이북이 불완전하거나, 최신이 아니거나, 누락되어 감지된 알림을 올바르게 처리할 수 없는 경우.</t>
+  </si>
+  <si>
+    <t>Sem registro e monitoramento, ataques e violações não podem ser detectados, e sem alertas é muito difícil responder de forma rápida e eficaz durante um incidente de segurança. Registro, monitoramento contínuo, detecção e alertas insuficientes para iniciar respostas ativas ocorrem sempre que:
+- Eventos auditáveis, como logins, falhas de login e transações de alto valor, não são registrados ou são registrados de forma inconsistente (por exemplo, registrando apenas logins bem-sucedidos, mas não tentativas falhas).
+- Avisos e erros geram mensagens de _log_ inexistentes, inadequadas ou confusas.
+- A integridade dos _logs_ não é devidamente protegida contra adulteração.
+- _Logs_ de aplicações e APIs não são monitorados em busca de atividades suspeitas.
+- Os _logs_ são armazenados apenas localmente e não possuem backup adequado.
+- Limiares de alerta e processos de escalonamento de resposta apropriados não estão estabelecidos ou não são eficazes. Os alertas não são recebidos ou revisados em um tempo razoável.
+- Testes de invasão (_penetration testing_) e varreduras por ferramentas de testes dinâmicos de segurança de aplicações (DAST), como Burp ou ZAP, não disparam alertas.
+- A aplicação não consegue detectar, escalar ou alertar sobre ataques ativos em tempo real ou próximo ao tempo real.
+- Você está vulnerável ao vazamento de informações sensíveis ao tornar eventos de registro e alerta visíveis para um usuário ou atacante (veja **A01:2025-Controle de Acesso Quebrado**), ou ao registrar informações sensíveis que não deveriam ser gravadas (como PII ou PHI).
+- Você está vulnerável a injeções ou ataques nos sistemas de registro ou monitoramento se os dados de _log_ não forem codificados corretamente.
+- A aplicação omite ou trata incorretamente erros e outras condições excepcionais, de modo que o sistema não percebe que houve um erro e, portanto, não consegue registrar que houve um problema.
+- "Casos de uso" adequados para emissão de alertas estão ausentes ou desatualizados para reconhecer uma situação especial.
+- O excesso de alertas falsos positivos impossibilita distinguir alertas importantes de irrelevantes, resultando em detecções tardias ou inexistentes (sobrecarga física da equipe do SOC).
+- Alertas detectados não podem ser processados corretamente porque o _playbook_ para o caso de uso está incompleto, desatualizado ou ausente.</t>
+  </si>
+  <si>
+    <t>没有日志记录和监控，就无法检测攻击和安全事件；没有告警，也很难在安全事件中快速有效响应。当出现以下情况时，就会发生日志记录不足、持续监控不足、检测不足，以及无法通过告警发起主动响应的问题：
+* 可审计事件没有记录或记录不一致，例如登录、登录失败和高价值交易（例如只记录成功登录，不记录失败尝试）。
+* 警告和错误不生成日志消息，或生成的消息不足、不清晰。
+* 日志完整性没有得到妥善保护，容易被篡改。
+* 应用和 API 的日志没有被监控以发现可疑活动。
+* 日志只存储在本地，没有正确备份。
+* 没有建立适当的告警阈值和响应升级流程，或这些流程无效。告警没有在合理时间内被接收或审查。
+* 渗透测试和动态应用安全测试（DAST）工具（例如 Burp 或 ZAP）的扫描没有触发告警。
+* 应用无法实时或近实时检测、升级或告警正在发生的攻击。
+* 通过让日志记录和告警事件对用户或攻击者可见，容易导致敏感信息泄露（参见 **A01:2025-失效的访问控制**），或记录了不应记录的敏感信息（例如 PII 或 PHI）。
+* 如果日志数据没有正确编码，就容易受到针对日志或监控系统的注入或攻击。
+* 应用缺失或错误处理错误及其他异常条件，导致系统不知道发生了错误，因此无法记录问题。
+* 缺少足够的、用于触发告警的“用例”，或用例已经过时，无法识别特殊情况。
+* 过多误报让人无法区分重要告警和不重要告警，导致重要告警被过晚识别或完全没有被识别（SOC 团队实际过载）。
+* 因为该用例的剧本不完整、过时或缺失，检测到的告警无法被正确处理。</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;Počet mapovaných CWE 
+   &lt;/td&gt;
+   &lt;td&gt;Max míra výskytu
+   &lt;/td&gt;
+   &lt;td&gt;Průměrná míra výskytu
+   &lt;/td&gt;
+   &lt;td&gt;Max pokrytí
+   &lt;/td&gt;
+   &lt;td&gt;Průměrné pokrytí
+   &lt;/td&gt;
+   &lt;td&gt;Průměrná vážená zneužitelnost
+   &lt;/td&gt;
+   &lt;td&gt;Průměrný vážený dopad
+   &lt;/td&gt;
+   &lt;td&gt;Celkový počet výskytů
+   &lt;/td&gt;
+   &lt;td&gt;Celkový počet CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20,67 %
+   &lt;/td&gt;
+   &lt;td&gt;2,95 %
+   &lt;/td&gt;
+   &lt;td&gt;100,00 %
+   &lt;/td&gt;
+   &lt;td&gt;37,95 %
+   &lt;/td&gt;
+   &lt;td&gt;7,11
+   &lt;/td&gt;
+   &lt;td&gt;3,81
+   &lt;/td&gt;
+   &lt;td&gt;769 581
+   &lt;/td&gt;
+   &lt;td&gt;3 416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Abychom mohli výjimečný stav správně zpracovat, musíme na takové situace plánovat (očekávat nejhorší). Musíme „zachytit“ každou možnou systémovou chybu přímo v místě, kde k ní dochází, a poté ji zpracovat (tj. udělat něco smysluplného k vyřešení problému a zajistit, že se z něj zotavíme). Součástí zpracování by mělo být vyvolání chyby (aby byl uživatel informován srozumitelným způsobem), logování události a také vyvolání upozornění (alertu), pokud to považujeme za oprávněné. Měli bychom mít také globální handler výjimek (globální obsluhu/zpracování výjimek) pro případ, že nám něco unikne. V ideálním případě bychom měli mít také nástroje nebo funkcionalitu pro monitoring a/nebo observability, které sledují opakované chyby nebo vzorce naznačující probíhající útok a které mohou vyvolat nějakou reakci, obranu nebo blokování. To nám může pomoci blokovat a reagovat na skripty a boty, které se zaměřují na slabiny našeho zpracování chyb.
+Zachytávání a zpracování výjimečných stavů zajišťuje, že základní infrastruktura našich programů není ponechána, aby se vypořádávala s nepředvídatelnými situacemi. Pokud jste uprostřed jakékoli transakce, je mimořádně důležité, abyste provedli rollback každé její části a začali znovu (také známé jako fail closed). Pokus o zotavení transakce uprostřed jejího průběhu je často místem, kde vznikají nevratné chyby.
+Kdykoli je to možné, přidejte rate limiting, kvóty zdrojů, throttling (omezení) a další limity, abyste výjimečným stavům předcházeli už na začátku. V informačních technologiích by nic nemělo být bez limitu, protože to vede k nízké odolnosti aplikací, odmítnutí služby, úspěšným brute force útokům a mimořádně vysokým účtům za cloud. Zvažte, zda by identické opakované chyby nad určitou míru neměly být vypisovány pouze jako statistiky ukazující, jak často nastaly a v jakém časovém rámci. Tyto informace by měly být připojeny k původní zprávě tak, aby nenarušovaly automatizované logování a monitorování, viz **A09:2025 Selhání bezpečnostního logování a upozorňování (Security Logging &amp; Alerting Failures)**.
+Kromě toho bychom chtěli zahrnout přísnou validaci vstupů (se sanitizací (očištěním) nebo escapováním potenciálně nebezpečných znaků, které musíme akceptovat), centralizované zpracování chyb, logování, monitorování a upozorňování a globální obsluhu výjimek (global exception handler). Jedna aplikace by neměla mít více funkcí pro zpracování výjimečných stavů; mělo by se to provádět na jednom místě, pokaždé stejným způsobem. Měli bychom také vytvořit bezpečnostní požadavky projektu pro všechna doporučení v této části, provést threat modelling (modelování hrozeb) a/nebo aktivity secure design review (bezpečnostní posouzení návrhu) ve fázi návrhu projektů, provést code review (revizi kódu) nebo statickou analýzu a také provést zátěžové, výkonnostní a penetrační testování finálního systému.
+Pokud je to možné, měla by celá vaše organizace zpracovávat výjimečné stavy stejným způsobem, protože to usnadňuje kontrolu a audit kódu z hlediska chyb v této důležité bezpečnostní kontrole.
+## Example attack scenarios
+**Scénář #1:** K vyčerpání zdrojů v důsledku nesprávného zpracování výjimečných stavů (Denial of Service) může dojít, pokud aplikace při nahrávání souborů zachytává výjimky, ale poté řádně neuvolňuje zdroje. Každá nová výjimka zanechává zdroje uzamčené nebo jinak nedostupné, dokud nejsou všechny zdroje vyčerpány.
+**Scénář #2:** Odhalení citlivých údajů v důsledku nesprávného zpracování nebo databázových chyb, které uživateli zobrazí kompletní systémovou chybu. Útočník pokračuje ve vyvolávání chyb, aby mohl citlivé systémové informace využít k vytvoření účinnějšího útoku typu SQL injection. Citlivé údaje v chybových hlášeních pro uživatele jsou součástí průzkumu (reconnaissance).
+**Scénář #3:** Poškození stavu finančních transakcí může být způsobeno útočníkem, který přeruší vícekrokovou transakci narušením síťového spojení. Představte si, že sled kroků transakce je: odepsat z účtu uživatele, připsat na účet příjemce, zaznamenat transakci. Pokud systém při chybě uprostřed transakce správně nevrátí zpět (rollback) celou transakci (fail closed), útočník by mohl potenciálně vyprázdnit účet uživatele, nebo může dojít k souběhu (race condition), který útočníkovi umožní odeslat peníze příjemci vícekrát.
+Další informace o odkazech a seznamu namapovaných CWE: https://top10.owasp.org/2025/cs/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;Zugeordnete CWEs
+   &lt;/td&gt;
+   &lt;td&gt;Max. Häufigkeit
+   &lt;/td&gt;
+   &lt;td&gt;Durchschn. Häufigkeit
+   &lt;/td&gt;
+   &lt;td&gt;Max. Abdeckung
+   &lt;/td&gt;
+   &lt;td&gt;Durchschn. Abdeckung
+   &lt;/td&gt;
+   &lt;td&gt;Durchschn. gewichtete Ausnutzbarkeit
+   &lt;/td&gt;
+   &lt;td&gt;Durchschn. gewichtete Auswirkung
+   &lt;/td&gt;
+   &lt;td&gt;Gesamtanzahl
+   &lt;/td&gt;
+   &lt;td&gt;Summe CVEs
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20.67%
+   &lt;/td&gt;
+   &lt;td&gt;2.95%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;37.95%
+   &lt;/td&gt;
+   &lt;td&gt;7.11
+   &lt;/td&gt;
+   &lt;td&gt;3.81
+   &lt;/td&gt;
+   &lt;td&gt;769,581
+   &lt;/td&gt;
+   &lt;td&gt;3,416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Um Ausnahmezustände korrekt zu behandeln, müssen wir solche Situationen einplanen (vom Schlimmsten ausgehen). Wir müssen jeden möglichen Systemfehler direkt an der Stelle abfangen, an der er auftritt, und ihn dann behandeln (d. h. etwas Sinnvolles tun, um das Problem zu lösen und die Wiederherstellung sicherzustellen). Als Teil der Behandlung sollten wir einen Fehler werfen (um die/den Benutzer:in verständlich zu informieren), das Ereignis protokollieren sowie bei Bedarf einen Alarm auslösen. Wir sollten außerdem einen globalen Exception-Handler einrichten, für den Fall, dass uns etwas entgangen ist. Idealerweise verfügen wir zusätzlich über Monitoring- und/oder Observability-Werkzeuge, die auf wiederholte Fehler oder Muster hinweisen, die auf einen laufenden Angriff hindeuten, und eine Reaktion, Abwehr oder Blockierung auslösen können. Dies hilft uns, Skripte und Bots zu blockieren und darauf zu reagieren, die unsere Schwachstellen in der Fehlerbehandlung ausnutzen.
+Das Abfangen und Behandeln von Ausnahmezuständen stellt sicher, dass die zugrunde liegende Infrastruktur unserer Programme nicht mit unvorhersehbaren Situationen allein gelassen wird. Befindet man sich mitten in einer Transaktion jeglicher Art, ist es äußerst wichtig, die gesamte Transaktion zurückzusetzen und neu zu beginnen (auch bekannt als „Failing Closed"). Der Versuch, eine Transaktion mittendrin wiederherzustellen, ist oft der Punkt, an dem unbehebbare Fehler entstehen.
+Wo immer möglich sollten Rate Limiting, Ressourcenkontingente, Throttling und andere Begrenzungen eingesetzt werden, um Ausnahmezustände von vornherein zu verhindern. Nichts in der Informationstechnologie sollte unbegrenzt sein, da dies zu mangelnder Anwendungsresilienz, Denial-of-Service, erfolgreichen Brute-Force-Angriffen und enormen Cloud-Kosten führt.
+Es sollte überlegt werden, ob identische, sich wiederholende Fehler ab einer bestimmten Rate nur noch als Statistik ausgegeben werden sollten, die anzeigt, wie oft und in welchem Zeitraum sie aufgetreten sind. Diese Information sollte an die ursprüngliche Meldung angehängt werden, um automatisiertes Logging und Monitoring nicht zu beeinträchtigen, siehe **A09:2025 Unzureichendes Sicherheitslogging und Alarmierung**.
+Darüber hinaus sollten wir strikte Eingabevalidierung (mit Bereinigung oder Escaping potenziell gefährlicher Zeichen, die wir akzeptieren müssen) sowie *zentralisierte* Fehlerbehandlung, Logging, Monitoring und Alerting mit einem globalen Exception-Handler einsetzen. Eine Anwendung sollte nicht mehrere Funktionen zur Behandlung von Ausnahmezuständen haben – dies sollte einheitlich an einer Stelle erfolgen. Wir sollten zudem Sicherheitsanforderungen für alle Empfehlungen dieses Abschnitts definieren, Bedrohungsmodellierung und/oder sichere Design-Reviews in der Entwurfsphase durchführen, Code-Reviews oder statische Analysen vornehmen sowie Stress-, Performance- und Penetrationstests am fertigen System ausführen.
+Wenn möglich, sollte die gesamte Organisation Ausnahmezustände einheitlich behandeln, da dies die Überprüfung und Auditierung des Codes auf Fehler in dieser wichtigen Sicherheitsmaßnahme erleichtert.
+## Example attack scenarios
+**Szenario Nr. 1:** Ressourcenerschöpfung durch fehlerhafte Behandlung von Ausnahmezuständen (Denial of Service) kann auftreten, wenn die Anwendung beim Datei-Upload Ausnahmen abfängt, die Ressourcen danach jedoch nicht ordnungsgemäß freigibt. Jede neue Ausnahme hinterlässt gesperrte oder anderweitig nicht verfügbare Ressourcen, bis alle Ressourcen verbraucht sind.
+**Szenario Nr. 2:** Offenlegung sensibler Daten durch fehlerhafte Behandlung von Datenbankfehlern, die den vollständigen Systemfehler an die/den Benutzer:in weitergeben. Die/Der Angreifer:in erzwingt weiterhin Fehler, um die sensiblen Systeminformationen für einen gezielteren SQL-Injection-Angriff zu nutzen. Die sensiblen Daten in den Fehlermeldungen dienen dabei als Aufklärung.
+**Szenario Nr. 3:** Zustandskorruption bei Finanztransaktionen kann durch ein:e Angreifer:in verursacht werden, der eine mehrstufige Transaktion durch Netzwerkunterbrechungen stört. Angenommen, die Transaktionsreihenfolge lautet: Nutzerkonto belasten, Zielkonto gutschreiben, Transaktion protokollieren. Wenn das System bei einem Fehler mittendrin die gesamte Transaktion nicht ordnungsgemäß zurücksetzt (Failing Closed), könnte die/der Angreifer:in das Konto der/des Nutzer:in leeren oder über eine Race Condition Geld mehrfach an das Zielkonto senden.
+Weitere Informationen zu den Referenzen und zur Liste der zugeordneten CWEs: https://top10.owasp.org/2025/de/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs Mapeadas
+   &lt;/td&gt;
+   &lt;td&gt;Tasa Máxima de Incidencia
+   &lt;/td&gt;
+   &lt;td&gt;Tasa Promedio de Incidencia
+   &lt;/td&gt;
+   &lt;td&gt;Cobertura Máxima
+   &lt;/td&gt;
+   &lt;td&gt;Cobertura Promedio
+   &lt;/td&gt;
+   &lt;td&gt;Promedio Ponderado de Explotación
+   &lt;/td&gt;
+   &lt;td&gt;Promedio Ponderado de Impacto
+   &lt;/td&gt;
+   &lt;td&gt;Ocurrencias Totales
+   &lt;/td&gt;
+   &lt;td&gt;CVEs Totales
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20.67%
+   &lt;/td&gt;
+   &lt;td&gt;2.95%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;37.95%
+   &lt;/td&gt;
+   &lt;td&gt;7.11
+   &lt;/td&gt;
+   &lt;td&gt;3.81
+   &lt;/td&gt;
+   &lt;td&gt;769,581
+   &lt;/td&gt;
+   &lt;td&gt;3,416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Para manejar adecuadamente una condición excepcional, debemos planificar para tales situaciones (esperar lo peor). Debemos "capturar" (catch) cada posible error del sistema directamente en el lugar donde ocurre y luego manejarlo (lo que significa hacer algo significativo para resolver el problema y asegurar que nos recuperamos del mismo). Como parte del manejo, debemos incluir el lanzamiento de un error (para informar al usuario de forma comprensible), el registro (logging) del evento, así como la emisión de una alerta (alerting) si consideramos que está justificado. También deberíamos tener un manejador de excepciones global por si acaso algo se nos ha pasado por alto. Idealmente, también tendríamos herramientas o funcionalidades de monitoreo y/u observabilidad que vigilen errores repetidos o patrones que indiquen un ataque en curso, que pudieran emitir una respuesta, defensa o bloqueo de algún tipo. Esto puede ayudarnos a bloquear y responder a scripts y bots que se centran en nuestras debilidades de manejo de errores.
+Capturar y manejar las condiciones excepcionales garantiza que la infraestructura subyacente de nuestros programas no se deje a merced de situaciones impredecibles. Si se encuentra a mitad de una transacción de cualquier tipo, es extremadamente importante que revierta (roll back) cada parte de la transacción y comience de nuevo (lo que también se conoce como fallar de forma segura o "fail closed"). Intentar recuperar una transacción a medias es a menudo donde creamos errores irrecuperables.
+Siempre que sea posible, añada limitación de tasa (rate limiting), cuotas de recursos, regulación (throttling) y otros límites para prevenir las condiciones excepcionales en primer lugar. Nada en la tecnología de la información debería ser ilimitado, ya que esto conduce a una falta de resiliencia de la aplicación, denegación de servicio, ataques exitosos de fuerza bruta y facturas extraordinarias en la nube.
+Considere si errores idénticos repetidos, por encima de una cierta tasa, deberían mostrarse únicamente como estadísticas que indiquen con qué frecuencia han ocurrido y en qué intervalo de tiempo. Esta información debería añadirse al mensaje original para no interferir con el registro y monitoreo automatizados, consulte **A09:2025-Fallas en el Registro, Alerta y Monitoreo de Seguridad**.
+Además de esto, querríamos incluir una validación de entradas estricta (con saneamiento o escape para los caracteres potencialmente peligrosos que debamos aceptar), un manejo de errores, registro, monitoreo y alertas *centralizados*, y un manejador de excepciones global. Una aplicación no debería tener múltiples funciones para manejar condiciones excepcionales; debería realizarse en un solo lugar, de la misma manera cada vez. También deberíamos crear requisitos de seguridad del proyecto para todos los consejos de esta sección, realizar actividades de modelado de amenazas y/o revisión de diseño seguro en la fase de diseño de nuestros proyectos, realizar revisiones de código o análisis estático, así como ejecutar pruebas de estrés, rendimiento y penetración del sistema final.
+Si es posible, toda su organización debería manejar las condiciones excepcionales de la misma manera, ya que esto facilita la revisión y auditoría del código en busca de errores en este importante control de seguridad.
+## Example attack scenarios
+**Escenario #1:** El agotamiento de recursos mediante el manejo inadecuado de condiciones excepcionales (Denegación de Servicio) podría producirse si la aplicación captura excepciones cuando se suben archivos, pero no libera adecuadamente los recursos después. Cada nueva excepción deja los recursos bloqueados o no disponibles de otro modo, hasta que se agotan todos los recursos.
+**Escenario #2:** Exposición de datos sensibles mediante un manejo inadecuado o errores de base de datos que revelan el error completo del sistema al usuario. El atacante continúa forzando errores para utilizar la información sensible del sistema para crear un mejor ataque de inyección SQL. Los datos sensibles en los mensajes de error del usuario sirven de reconocimiento (reconnaissance).
+**Escenario #3:** La corrupción de estado en transacciones financieras podría ser causada por un atacante que interrumpe una transacción de varios pasos mediante interrupciones de red. Imagine que el orden de la transacción fuera: debitar la cuenta del usuario, acreditar la cuenta de destino, registrar la transacción. Si el sistema no revierte adecuadamente toda la transacción (fallar de forma segura o "fail closed") cuando hay un error a mitad del proceso, el atacante podría potencialmente vaciar la cuenta del usuario, o posiblemente una condición de carrera podría permitir al atacante enviar dinero al destino varias veces.
+Para obtener más información sobre las referencias y la lista de CWE asociadas: https://top10.owasp.org/2025/es/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWE Mappati
+   &lt;/td&gt;
+   &lt;td&gt;Tasso di Incidenza Massimo
+   &lt;/td&gt;
+   &lt;td&gt;Tasso di Incidenza Medio
+   &lt;/td&gt;
+   &lt;td&gt;Copertura Massima
+   &lt;/td&gt;
+   &lt;td&gt;Copertura Media
+   &lt;/td&gt;
+   &lt;td&gt;Exploit Ponderato Medio
+   &lt;/td&gt;
+   &lt;td&gt;Impatto Ponderato Medio
+   &lt;/td&gt;
+   &lt;td&gt;Occorrenze Totali
+   &lt;/td&gt;
+   &lt;td&gt;CVE Totali
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20,67%
+   &lt;/td&gt;
+   &lt;td&gt;2,95%
+   &lt;/td&gt;
+   &lt;td&gt;100,00%
+   &lt;/td&gt;
+   &lt;td&gt;37,95%
+   &lt;/td&gt;
+   &lt;td&gt;7,11
+   &lt;/td&gt;
+   &lt;td&gt;3,81
+   &lt;/td&gt;
+   &lt;td&gt;769.581
+   &lt;/td&gt;
+   &lt;td&gt;3.416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Per gestire correttamente una condizione eccezionale dobbiamo pianificare tali situazioni (aspettarsi il peggio). Dobbiamo "catturare" ogni possibile errore di sistema direttamente nel punto in cui si verifica e poi gestirlo (il che significa fare qualcosa di significativo per risolvere il problema e assicurarci di riprenderci dalla questione). Come parte della gestione, dovremmo includere la generazione di un errore (per informare l'utente in modo comprensibile), la registrazione dell'evento, nonché l'emissione di un alert se riteniamo che sia giustificato. Dovremmo anche avere un gestore globale delle eccezioni nel caso in cui ci sia qualcosa che abbiamo mancato. Idealmente, avremmo anche strumenti o funzionalità di monitoraggio e/o osservabilità che vigilano su errori ripetuti o pattern che indicano un attacco in corso, in grado di emettere una risposta, una difesa o un blocco di qualche tipo. Questo può aiutarci a bloccare e rispondere a script e bot che si concentrano sulle nostre debolezze nella gestione degli errori.
+Catturare e gestire le condizioni eccezionali garantisce che l'infrastruttura sottostante dei nostri programmi non sia lasciata a gestire situazioni imprevedibili. Se siamo nel mezzo di una transazione di qualsiasi tipo, è estremamente importante eseguire il rollback di ogni parte della transazione e ricominciare (noto anche come failing closed). Tentare di recuperare una transazione a metà è spesso il punto in cui creiamo errori irrecuperabili.
+Quando possibile, aggiungere rate limiting, quote di risorse, throttling e altri limiti ovunque sia possibile, per prevenire le condizioni eccezionali in primo luogo. Nulla nell'informatica dovrebbe essere illimitato, poiché questo porta a mancanza di resilienza applicativa, denial of service, attacchi a forza bruta riusciti e bollette cloud straordinarie. Considerare se errori ripetuti identici, al di sopra di un certo tasso, debbano essere emessi solo come statistiche che mostrano con quale frequenza si sono verificati e in quale arco temporale. Queste informazioni dovrebbero essere aggiunte al messaggio originale in modo da non interferire con il logging e il monitoraggio automatizzati, vedere **A09:2025 Security Logging &amp; Alerting Failures**.
+Oltre a questo, vorremmo includere una validazione rigorosa dell'input (con sanificazione o escaping per caratteri potenzialmente pericolosi che dobbiamo accettare), e gestione degli errori *centralizzata*, logging, monitoraggio e alerting, e un gestore globale delle eccezioni. Un'applicazione non dovrebbe avere più funzioni per la gestione delle condizioni eccezionali, dovrebbe essere eseguita in un unico posto, allo stesso modo ogni volta. Dovremmo anche creare requisiti di sicurezza del progetto per tutti i consigli in questa sezione, eseguire attività di threat modeling e/o revisione del design sicuro nella fase di progettazione dei nostri progetti, eseguire code review o analisi statica, nonché eseguire test di stress, prestazioni e penetration testing del sistema finale.
+Se possibile, l'intera organizzazione dovrebbe gestire le condizioni eccezionali allo stesso modo, poiché rende più facile rivedere e verificare il codice per errori in questo importante controllo di sicurezza.
+## Example attack scenarios
+**Scenario #1:** L'esaurimento delle risorse dovuto alla gestione impropria delle condizioni eccezionali (Denial of Service) potrebbe essere causato se l'applicazione cattura le eccezioni quando i file vengono caricati, ma non rilascia correttamente le risorse dopo. Ogni nuova eccezione lascia risorse bloccate o altrimenti non disponibili, finché tutte le risorse non sono esaurite.
+**Scenario #2:** L'esposizione di dati sensibili tramite la gestione impropria degli errori del database che rivela l'errore di sistema completo all'utente. L'attaccante continua a forzare errori al fine di utilizzare le informazioni di sistema sensibili per creare un attacco SQL injection migliore. I dati sensibili nei messaggi di errore all'utente sono ricognizione.
+**Scenario #3:** La corruzione dello stato nelle transazioni finanziarie potrebbe essere causata da un attaccante che interrompe una transazione multi-step tramite interruzioni di rete. Immaginate che l'ordine della transazione fosse: addebitare l'account utente, accreditare l'account di destinazione, registrare la transazione. Se il sistema non esegue correttamente il rollback dell'intera transazione (failing closed) quando si verifica un errore a metà, l'attaccante potrebbe potenzialmente prosciugare l'account dell'utente, o possibilmente una race condition che consente all'attaccante di inviare denaro alla destinazione più volte.
+Per maggiori informazioni sui riferimenti e sull'elenco delle CWE mappate: https://top10.owasp.org/2025/it/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;紐付けられた CWE 数
+   &lt;/td&gt;
+   &lt;td&gt;最大出現率
+   &lt;/td&gt;
+   &lt;td&gt;平均出現率
+   &lt;/td&gt;
+   &lt;td&gt;最大網羅率
+   &lt;/td&gt;
+   &lt;td&gt;平均網羅率
+   &lt;/td&gt;
+   &lt;td&gt;平均加重悪用スコア
+   &lt;/td&gt;
+   &lt;td&gt;平均加重影響スコア
+   &lt;/td&gt;
+   &lt;td&gt;出現総数
+   &lt;/td&gt;
+   &lt;td&gt;CVE 総数
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20.67%
+   &lt;/td&gt;
+   &lt;td&gt;2.95%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;37.95%
+   &lt;/td&gt;
+   &lt;td&gt;7.11
+   &lt;/td&gt;
+   &lt;td&gt;3.81
+   &lt;/td&gt;
+   &lt;td&gt;769,581
+   &lt;/td&gt;
+   &lt;td&gt;3,416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+例外的な状況を適切に処理するには、そのような状況を計画しておく必要があります（最悪の事態を想定 (Expect the worst) する）。すべてのシステムエラーを、それが発生した場所で直接「キャッチ (Catch)」し、それを処理しなければなりません（つまり、問題を解決し、その問題から確実に回復するために意味のある何かを行うことを意味します）。処理の一環として、エラーをスローすること（ユーザーに理解可能な方法で通知する）、イベントをログに記録すること、および正当であると判断した場合にはアラートを発行することを含めるべきです。また、何かを見落とした場合に備えて、グローバルな例外ハンドラーを設置しておくべきです。理想的には、継続的な攻撃を示す繰り返されるエラーやパターンを監視し、何らかの応答、防御、またはブロックを発行できる、監視 (Monitoring) または可観測性 (Observability) のツールや機能を備えることです。これは、私たちのエラー処理の弱点に焦点を当てたスクリプトやボットをブロックし、それらに応答するのに役立ちます。
+例外的な状況をキャッチして処理することで、プログラムの基盤となるインフラストラクチャが予測不能な状況に対処したまま放置されないようにします。いかなる種類のトランザクションであっても、その途中でエラーが発生した場合は、トランザクションのすべての部分をロールバックしてやり直すことが非常に重要です（フェイルクローズ (Fail closed) とも呼ばれます）。途中でトランザクションを回復しようとすると、回復不可能な間違いを犯してしまうことがよくあります。
+可能な限り、レート制限 (Rate limiting)、リソース制限 (Resource quotas)、スロットリング (Throttling)、およびその他の制限を追加して、そもそも例外的な状況が発生するのを防いでください。情報技術において無制限なものは何一つあってはなりません。それはアプリケーションのレジリエンス (Resilience)（回復力）の欠如、サービス拒否、ブルートフォース攻撃の成功、および莫大なクラウド利用料に繋がるからです。
+特定のレートを超える同一の繰り返されるエラーについては、それらがいつ、どの程度の頻度で発生したかを示す統計としてのみ出力することを検討してください。この情報は、自動化されたロギングや監視を妨げないように、元のメッセージに追加されるべきです（**A09:2025 セキュリティログとアラートの不備** 参照）。
+これに加えて、厳格な入力検証（受け入れなければならない潜在的に危険な文字については無害化 (Sanitization) またはエスケープを行う）、および「集約された (Centralized)」エラー処理、ロギング、監視、アラート、ならびにグローバル例外ハンドラーを含めるべきです。一つのアプリケーションに例外的な状況を処理するための複数の関数を持たせるべきではなく、一箇所で、毎回同じ方法で実行されるべきです。また、このセクションのすべてのアドバイスについてプロジェクトのセキュリティ要件を作成し、プロジェクトの設計フェーズで脅威モデリング (Threat modeling) や安全な設計レビューを実施し、コードレビューや静的解析を実施し、最終的なシステムに対してストレス、パフォーマンス、およびペネトレーションテストを実行すべきです。
+可能であれば、組織全体で例外的な状況を同じ方法で処理すべきです。そうすることで、この重要なセキュリティ制御におけるエラーのコードレビューや監査が容易になります。
+## Example attack scenarios
+**シナリオ #1：例外的な状況の誤処理によるリソースの枯渇 (サービス拒否)** アプリケーションがファイルのアップロード時に例外をキャッチするものの、その後にリソースを適切に解放しない場合に発生する可能性があります。新しい例外が発生するたびにリソースがロックされるか利用不可のままになり、最終的にすべてのリソースが使い果たされます。
+**シナリオ #2：不適切な処理またはデータベースエラーによる機密データの露出** ユーザーにシステムの完全なエラーを明らかにしてしまうケースです。攻撃者は、機密性の高いシステム情報を利用してより優れた SQL インジェクション攻撃を作成するために、意図的にエラーを発生させ続けます。ユーザーへのエラーメッセージに含まれる機密データは偵察 (Reconnaissance) 活動に利用されます。
+**シナリオ #3：金融取引における状態の破損** 攻撃者がネットワークの中断を介して多段階のトランザクションを妨害することによって引き起こされる可能性があります。トランザクションの順序が「ユーザーアカウントの引き落とし、宛先アカウントへの入金、トランザクションのログ記録」であったと仮定します。途中でエラーが発生したときにシステムがトランザクション全体を適切にロールバック（フェイルクローズ）しない場合、攻撃者はユーザーのアカウントを枯渇させたり、あるいは攻撃者が宛先に何度も送金できてしまう競合状態が発生したりする可能性があります。
+参考資料およびマッピングされたCWEの一覧について、詳しくはこちら： https://top10.owasp.org/2025/ja/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;해당되는 CWE 개수
+   &lt;/td&gt;
+   &lt;td&gt;최대 취약점 발생률
+   &lt;/td&gt;
+   &lt;td&gt;평균 취약점 발생률
+   &lt;/td&gt;
+   &lt;td&gt;최대 테스트 커버리지
+   &lt;/td&gt;
+   &lt;td&gt;평균 테스트 커버리지
+   &lt;/td&gt;
+   &lt;td&gt;가중 평균 악용도
+   &lt;/td&gt;
+   &lt;td&gt;가중 평균 영향도
+   &lt;/td&gt;
+   &lt;td&gt;총 발생 건수
+   &lt;/td&gt;
+   &lt;td&gt;총 CVE 건수
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20.67%
+   &lt;/td&gt;
+   &lt;td&gt;2.95%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;37.95%
+   &lt;/td&gt;
+   &lt;td&gt;7.11
+   &lt;/td&gt;
+   &lt;td&gt;3.81
+   &lt;/td&gt;
+   &lt;td&gt;769,581
+   &lt;/td&gt;
+   &lt;td&gt;3,416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+예외 상황을 적절히 처리하려면 이러한 상황에 대비한 계획을 세워야 한다(최악의 상황을 예상하라). 모든 시스템 오류를 발생 지점에서 직접 캐치(catch)하고, 이를 처리해야 한다. 여기서 처리란 문제 해결을 위한 의미 있는 조치를 취하고 정상 상태로 복구하는 것을 의미한다. 처리 과정에는 오류 발생 시 사용자에게 이해하기 쉬운 방식으로 알리고, 이벤트를 로깅하며, 필요하다고 판단되면 알림을 발송하는 것이 포함되어야 한다. 또한 놓친 예외가 있을 경우를 대비해 전역 예외 핸들러(Global Exception Handler)를 구현해야 한다. 이상적으로는 반복되는 오류나 진행 중인 공격을 나타내는 패턴을 감시하고, 이에 대응·방어·차단할 수 있는 모니터링 또는 옵저버빌리티 도구를 갖추는 것이 좋다. 이를 통해 오류 처리 취약점을 악용하는 스크립트와 봇에 대응하고 차단할 수 있다.
+예외 상황을 캐치하고 처리하면 프로그램의 기반 인프라가 예측 불가능한 상황에 노출되는 것을 방지할 수 있다. 트랜잭션 처리 도중이라면, 트랜잭션의 모든 부분을 롤백하고 처음부터 다시 시작하는 것이 매우 중요하다(이를 안전한 실패[Failing Closed]라고 한다). 트랜잭션을 중간 상태에서 복구하려는 시도는 종종 복구 불가능한 오류를 만들어낸다.
+가능하다면 속도 제한(Rate Limiting), 리소스 쿼터, 스로틀링 등 다양한 제한을 적용하여 애초에 예외 상황이 발생하지 않도록 예방하라. 정보 기술에서 무제한이어야 하는 것은 없다. 제한이 없으면 애플리케이션 복원력 저하, 서비스 거부(DoS), 무차별 대입 공격 성공, 과도한 클라우드 비용 등의 문제가 발생할 수 있다.
+특정 빈도 이상으로 동일한 오류가 반복될 경우, 개별 오류 메시지 대신 발생 횟수와 시간대를 보여주는 통계 형태로 출력하는 것을 고려하라. 이 정보는 자동화된 로깅 및 모니터링을 방해하지 않도록 원본 메시지에 추가하는 방식으로 처리해야 한다. **A09:2025 보안 로깅 및 알림 실패**를 참고하라.
+이 외에도 다음 사항을 포함해야 한다: 엄격한 입력 검증(허용해야 하는 위험 문자에 대한 새니타이징 또는 이스케이프 처리 포함), 중앙 집중화된 오류 처리·로깅·모니터링·알림 체계, 그리고 전역 예외 핸들러다. 하나의 애플리케이션에서 예외 처리를 위한 여러 함수를 두어서는 안 되며, 한 곳에서 동일한 방식으로 처리해야 한다. 또한 이 섹션의 모든 권고 사항에 대해 프로젝트 보안 요구사항을 수립하고, 설계 단계에서 위협 모델링 또는 보안 설계 검토를 수행하며, 코드 리뷰나 정적 분석을 실시하고, 최종 시스템에 대해 스트레스·성능·침투 테스트를 수행해야 한다.
+가능하다면 조직 전체가 동일한 방식으로 예외 상황을 처리하는 것이 좋다. 이렇게 하면 이 중요한 보안 통제에 대한 코드 리뷰와 감사가 더 쉬워진다.
+## Example attack scenarios
+**시나리오 1:** 애플리케이션이 파일 업로드 시 예외를 캐치하되 리소스를 해제하지 않으면, 예외가 발생할 때마다 리소스가 잠긴 채로 남는다. 이로 인해 리소스가 고갈되어 서비스 거부(DoS)로 이어질 수 있다.
+**시나리오 2:** 데이터베이스 오류가 사용자에게 그대로 노출되면 민감한 시스템 정보가 유출된다. 공격자는 이를 악용해 의도적으로 오류를 유발하고, 수집한 정보를 기반으로 더 정교한 SQL 인젝션 공격을 구성할 수 있다.
+**시나리오 3:** 공격자가 네트워크 중단을 일으켜 다단계 금융 트랜잭션을 방해할 수 있다. 예를 들어 트랜잭션이 "출금 → 입금 → 로깅" 순서로 처리될 때, 중간에 오류가 발생해도 시스템이 전체를 롤백(안전한 실패)하지 않으면 문제가 생긴다. 공격자는 이를 악용해 사용자 계좌에서 돈만 빠져나가게 하거나, 레이스 컨디션을 이용해 대상 계좌로 여러 번 송금할 수 있다.
+참고 자료와 매핑된 CWE 목록에 대한 자세한 정보: https://top10.owasp.org/2025/ko/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs Mapeadas 
+   &lt;/td&gt;
+   &lt;td&gt;Taxa Máx. de Incidência
+   &lt;/td&gt;
+   &lt;td&gt;Taxa Média de Incidência
+   &lt;/td&gt;
+   &lt;td&gt;Cobertura Máxima
+   &lt;/td&gt;
+   &lt;td&gt;Cobertura Média
+   &lt;/td&gt;
+   &lt;td&gt;Exploit Médio Ponderado
+   &lt;/td&gt;
+   &lt;td&gt;Impacto Médio Ponderado
+   &lt;/td&gt;
+   &lt;td&gt;Total de Ocorrências
+   &lt;/td&gt;
+   &lt;td&gt;Total de CVEs
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20,67%
+   &lt;/td&gt;
+   &lt;td&gt;2,95%
+   &lt;/td&gt;
+   &lt;td&gt;100,00%
+   &lt;/td&gt;
+   &lt;td&gt;37,95%
+   &lt;/td&gt;
+   &lt;td&gt;7,11
+   &lt;/td&gt;
+   &lt;td&gt;3,81
+   &lt;/td&gt;
+   &lt;td&gt;769.581
+   &lt;/td&gt;
+   &lt;td&gt;3.416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+Para tratar uma condição excepcional adequadamente, devemos planejar para tais situações (esperar o pior). Devemos "capturar" (_catch_) cada erro de sistema possível diretamente no local onde ocorrem e, então, tratá-lo (o que significa fazer algo significativo para resolver o problema e garantir a recuperação da falha). Como parte do tratamento, devemos incluir o lançamento de um erro (para informar o usuário de forma compreensível), o registro do evento (_log_), bem como a emissão de um alerta se considerarmos justificado. Também devemos ter um manipulador de exceções global para o caso de algo ter passado despercebido. Idealmente, também teríamos ferramentas ou funcionalidades de monitoramento e/ou observabilidade que vigiam erros repetidos ou padrões que indiquem um ataque em andamento, podendo emitir uma resposta, defesa ou bloqueio de algum tipo. Isso pode nos ajudar a bloquear e responder a scripts e bots que focam em nossas fraquezas de tratamento de erros.
+Capturar e tratar condições excepcionais garante que a infraestrutura subjacente de nossos programas não seja deixada para lidar com situações imprevisíveis. Se você estiver no meio de uma transação de qualquer tipo, é extremamente importante realizar o _rollback_ de cada parte da transação e começar de novo (também conhecido como falha segura ou _failing closed_). Tentar recuperar uma transação pela metade é frequentemente onde criamos erros irrecuperáveis.
+Sempre que possível, adicione limites de taxa (_rate limiting_), cotas de recursos, _throttling_ e outras restrições para prevenir condições excepcionais antes de tudo. Nada em tecnologia da informação deve ser ilimitado, pois isso leva à falta de resiliência da aplicação, negação de serviço, ataques de força bruta bem-sucedidos e faturas de nuvem extraordinárias.
+Considere se erros repetidos idênticos, acima de uma certa taxa, devem ser exibidos apenas como estatísticas mostrando a frequência com que ocorreram e em qual período. Esta informação deve ser anexada à mensagem original para não interferir no registro e monitoramento automatizados, veja **A09:2025 Falhas de Registro e Monitoramento de Segurança**.
+Além disso, queremos incluir uma validação de entrada rigorosa (com sanitização ou _escaping_ para caracteres potencialmente perigosos que precisamos aceitar) e um tratamento de erros, registro, monitoramento e alerta _centralizados_, além de um manipulador de exceções global. Uma aplicação não deve ter múltiplas funções para tratar condições excepcionais; isso deve ser realizado em um único lugar, da mesma forma todas as vezes. Também devemos criar requisitos de segurança de projeto para todos os conselhos desta seção, realizar atividades de modelagem de ameaças e/ou revisão de design seguro na fase de design de nossos projetos, realizar revisão de código ou análise estática, bem como executar testes de estresse, desempenho e invasão do sistema final.
+Se possível, toda a sua organização deve tratar condições excepcionais da mesma maneira, pois isso facilita a revisão e a auditoria de código em busca de erros neste importante controle de segurança.
+## Example attack scenarios
+**Cenário 1:** Exaustão de recursos via tratamento incorreto de condições excepcionais (Negação de Serviço) poderia ser causada se a aplicação captura exceções quando arquivos são carregados, mas não libera adequadamente os recursos depois. Cada nova exceção deixa recursos bloqueados ou indisponíveis, até que todos os recursos sejam esgotados.
+**Cenário 2:** Exposição de dados sensíveis via tratamento inadequado ou erros de banco de dados que revelam o erro completo do sistema ao usuário. O atacante continua a forçar erros para usar as informações sensíveis do sistema para criar um ataque de _SQL injection_ melhor. Os dados sensíveis nas mensagens de erro do usuário servem como reconhecimento (_reconnaissance_).
+**Cenário 3:** Corrupção de estado em transações financeiras poderia ser causada por um atacante interrompendo uma transação de múltiplas etapas via interrupções de rede. Imagine que a ordem da transação fosse: debitar conta do usuário, creditar conta de destino, registrar transação. Se o sistema não realizar o _rollback_ adequadamente de toda a transação (falha segura) quando houver um erro no meio do caminho, o atacante poderia potencialmente esvaziar a conta do usuário, ou possivelmente gerar uma condição de corrida que permita ao atacante enviar dinheiro para o destino várias vezes.
+Para mais informações sobre as referências e a lista de CWEs mapeadas: https://top10.owasp.org/2025/pt-BR/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## Score table
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;映射的 CWE 数量
+   &lt;/td&gt;
+   &lt;td&gt;最大发生率
+   &lt;/td&gt;
+   &lt;td&gt;平均发生率
+   &lt;/td&gt;
+   &lt;td&gt;最大覆盖率
+   &lt;/td&gt;
+   &lt;td&gt;平均覆盖率
+   &lt;/td&gt;
+   &lt;td&gt;平均加权可利用性
+   &lt;/td&gt;
+   &lt;td&gt;平均加权影响
+   &lt;/td&gt;
+   &lt;td&gt;发生总数
+   &lt;/td&gt;
+   &lt;td&gt;CVE 总数
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20.67%
+   &lt;/td&gt;
+   &lt;td&gt;2.95%
+   &lt;/td&gt;
+   &lt;td&gt;100.00%
+   &lt;/td&gt;
+   &lt;td&gt;37.95%
+   &lt;/td&gt;
+   &lt;td&gt;7.11
+   &lt;/td&gt;
+   &lt;td&gt;3.81
+   &lt;/td&gt;
+   &lt;td&gt;769,581
+   &lt;/td&gt;
+   &lt;td&gt;3,416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## How to prevent
+为了正确处理异常条件，我们必须提前为这类情况做计划（预期最坏情况）。我们必须在每个可能发生系统错误的位置直接“捕获”错误，然后处理它，也就是采取有意义的行动来解决问题，并确保系统从问题中恢复。作为处理的一部分，应包括抛出错误（以用户能理解的方式告知用户）、记录事件日志，并在我们认为有必要时发出告警。还应设置全局异常处理器，以应对可能遗漏的情况。理想情况下，我们还应具备监控和/或可观测性工具或功能，用于发现重复错误或表明正在发生攻击的模式，并能触发某种响应、防御或阻断。这可以帮助我们阻止并响应专门针对错误处理弱点的脚本和机器人。
+捕获并处理异常条件可以确保程序的底层基础设施不会被迫处理不可预测的情况。如果你正处于任何类型交易的中途，非常重要的一点是回滚交易的每个部分并重新开始（也称为故障关闭，failing closed）。试图从交易中途恢复，往往会造成无法恢复的错误。
+在可能的情况下，尽量加入速率限制、资源配额、节流和其他限制，从源头预防异常条件。信息技术中不应存在无限制的东西，因为这会导致应用韧性不足、拒绝服务、成功的暴力破解攻击以及异常高昂的云账单。
+请考虑是否应将超过一定频率的相同重复错误只输出为统计信息，显示发生次数和时间范围。该信息应追加到原始消息中，以免干扰自动化日志记录和监控，参见 **A09:2025 安全日志记录和告警失效**。
+除此之外，我们还希望加入严格输入验证（对必须接受的潜在危险字符进行清理或转义），以及*集中式*错误处理、日志记录、监控、告警和全局异常处理器。一个应用不应有多个处理异常条件的函数，应在一个地方以相同方式执行。我们还应为本节所有建议创建项目安全需求，在项目设计阶段执行威胁建模和/或安全设计审查活动，执行代码审查或静态分析，并对最终系统执行压力、性能和渗透测试。
+如果可能，整个组织应以同一种方式处理异常条件，因为这会让这项重要安全控制的代码审查和审计更容易。
+## Example attack scenarios
+**场景 #1：** 异常条件处理不当导致资源耗尽（拒绝服务）。如果应用在上传文件时捕获异常，但事后没有正确释放资源，每次新异常都会让资源保持锁定或不可用，直到所有资源耗尽。
+**场景 #2：** 错误处理不当或数据库错误把完整系统错误暴露给用户，导致敏感数据泄露。攻击者持续制造错误，以利用敏感系统信息构造更好的 SQL 注入攻击。用户错误消息中的敏感数据成为侦察信息。
+**场景 #3：** 攻击者通过网络中断打断多步骤交易，可能导致金融交易状态损坏。假设交易顺序为：扣减用户账户、增加目标账户余额、记录交易。如果系统在中途出错时没有正确回滚整个交易（故障关闭），攻击者可能耗尽用户账户，或可能利用竞争条件多次向目标账户转账。
+有關參考資料及已對應 CWE 清單的更多資訊： https://top10.owasp.org/2025/zh-Hant/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;16
+   &lt;/td&gt;
+   &lt;td&gt;27,70 % 
+   &lt;/td&gt;
+   &lt;td&gt;3,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;100,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;52,35 % 
+   &lt;/td&gt;
+   &lt;td&gt;7,96
+   &lt;/td&gt;
+   &lt;td&gt;3,97
+   &lt;/td&gt;
+   &lt;td&gt;719 084
+   &lt;/td&gt;
+   &lt;td&gt;1 375
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+Des processus d’installation sécurisés doivent être mis en œuvre, notamment : 
+* Un processus de durcissement répétable permettant un déploiement rapide et facile d’un autre environnement suffisamment verrouillé. Les environnements de développement, d’assurance qualité et de production doivent tous être configurés de manière identique, avec des identifiants différents utilisés dans chaque environnement. Ce processus doit être automatisé pour minimiser l’effort nécessaire à la mise en place d’un nouvel environnement sécurisé. 
+* Une plateforme minimale sans fonctionnalités, composants, documentations ou exemples inutiles. Supprimez ou n’installez pas les fonctionnalités et frameworks inutilisés. 
+* Une tâche visant à revoir et mettre à jour les configurations appropriées à toutes les notes de sécurité, mises à jour et correctifs dans le cadre du processus de gestion des correctifs (voir **A03 Défaillances de la chaîne d’approvisionnement logicielle**). Revoir les permissions de stockage cloud (par exemple, les permissions de bucket S3). 
+* Une architecture d’application segmentée offre une séparation efficace et sécurisée entre composants ou locataires, avec segmentation, conteneurisation ou groupes de sécurité cloud (ACL). 
+* Envoi de directives de sécurité aux clients, par exemple, les en-têtes de sécurité. 
+* Un processus automatisé pour vérifier l’efficacité des configurations et des réglages dans tous les environnements. 
+* Ajouter proactivement une configuration centrale pour intercepter les messages d’erreur excessifs en tant que sauvegarde. 
+* Si ces vérifications ne sont pas automatisées, elles doivent être vérifiées manuellement au minimum chaque année. 
+* Utiliser la fédération d’identité, des identifiants de courte durée ou des mécanismes d’accès basés sur des rôles fournis par la plateforme sous-jacente au lieu d’intégrer des clés statiques ou des secrets dans le code, les fichiers de configuration ou les pipelines.
+## Exemples de scénarios d’attaque
+**Scénario #1 :** Le serveur d’applications d’applications d’exemple n’est pas supprimé du serveur de production. Ces applications d’exemple présentent des failles de sécurité connues que les attaquants utilisent pour compromettre le serveur. Supposons que l’une de ces applications soit la console d’administration, et que les comptes par défaut n’aient pas été modifiés. Dans ce cas, l’attaquant se connecte avec le mot de passe par défaut et prend le relais. 
+**Scénario #2 :** La liste des répertoires n’est pas désactivée sur le serveur. Un attaquant découvre qu’il peut simplement lister les répertoires. L’attaquant trouve et télécharge les classes Java compilées, qu’il décompile et rétro-ingénierie pour visualiser le code. L’attaquant découvre alors une grave faille de contrôle d’accès dans l’application. 
+**Scénario #3 :** La configuration du serveur d’applications permet de renvoyer des messages d’erreur détaillés, tels que des traces de pile. Cela expose potentiellement des informations sensibles ou des failles sous-jacentes, comme des versions de composants connues pour être vulnérables. 
+**Scénario #4 :** Un fournisseur de services cloud (CSP) a par défaut des permissions de partage ouvertes à Internet. Cela permet d’accéder aux données sensibles stockées dans le stockage cloud. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A02_2025-Security_Misconfiguration/</t>
+  </si>
+  <si>
+    <t>Sans journalisation et surveillance, les attaques et violations ne peuvent pas être détectées, et sans alerte, il est très difficile de réagir rapidement et efficacement lors d’un incident de sécurité. Un journalage insuffisant, une surveillance continue, une détection et une alerte pour initier des réponses actives surviennent à tout moment : 
+* Les événements auditables, tels que les connexions, les échecs de connexion et les transactions de grande valeur, ne sont pas enregistrés ou enregistrés de manière incohérente (par exemple, seulement les connexions réussies, mais pas les tentatives ratées). 
+* Les avertissements et erreurs ne génèrent aucun message de journal, inadéquat ou flou. 
+* L’intégrité des billots n’est pas correctement protégée contre toute altération des documents. 
+* Les journaux des applications et des API ne sont pas surveillés pour toute activité suspecte. 
+* Les journaux ne sont stockés que localement, et non correctement sauvegardés. 
+* Les seuils d’alerte appropriés et les processus d’escalade de réponse ne sont pas en place ni efficaces. Les alertes ne sont pas reçues ou examinées dans un délai raisonnable. 
+* Les tests d’intrusion et les analyses par des outils de test dynamique de sécurité des applications (DAST) (tels que Burp ou ZAP) ne déclenchent pas d’alertes. 
+* L’application ne peut pas détecter, escalader ou alerter pour des attaques actives en temps réel ou quasi-temps réel. 
+* Vous êtes vulnérable à la fuite d’informations sensibles en rendant les événements de journalisation et d’alerte visibles pour un utilisateur ou un attaquant (voir **A01:2025-Broken Access Control**), ou en enregistrant des informations sensibles qui ne devraient pas être enregistrées (comme les PII ou les informations PHI). 
+* Vous êtes vulnérable aux injections ou attaques sur les systèmes de journalisation ou de surveillance si les données de journal ne sont pas correctement codées. 
+* L’application manque ou ne gère pas les erreurs et autres conditions exceptionnelles, de sorte que le système ignore qu’il y a eu une erreur, et ne peut donc pas enregistrer qu’il y a eu un problème. 
+* Des « cas d’utilisation » adéquats pour l’émission d’alertes manquent ou sont dépassés pour reconnaître une situation particulière. 
+* Trop d’alertes fausses positives rendent impossible la distinction des alertes importantes des non-importantes, ce qui les conduit à être reconnues trop tard ou pas du tout (surcharge physique de l’équipe SOC). 
+* Les alertes détectées ne peuvent pas être traitées correctement car le playbook pour le cas d’utilisation est incomplet, obsolète ou manquant.</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;24
+   &lt;/td&gt;
+   &lt;td&gt;20,67 % 
+   &lt;/td&gt;
+   &lt;td&gt;2,95 % 
+   &lt;/td&gt;
+   &lt;td&gt;100,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;37,95 % 
+   &lt;/td&gt;
+   &lt;td&gt;7.11
+   &lt;/td&gt;
+   &lt;td&gt;3.81
+   &lt;/td&gt;
+   &lt;td&gt;769 581
+   &lt;/td&gt;
+   &lt;td&gt;3 416
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+Pour gérer correctement une condition exceptionnelle, nous devons planifier de telles situations (attendez-vous au pire). Nous devons « détecter » chaque erreur système possible directement à l’endroit où elle survient puis la traiter (ce qui signifie faire quelque chose de significatif pour résoudre le problème et nous assurer de nous en remettre). Dans le cadre de la gestion, nous devrions inclure l’envoi d’une erreur (pour informer l’utilisateur de manière compréhensible), la consignation de l’événement, ainsi que l’émission d’une alerte si cela est justifié. Nous devrions également avoir un gestionnaire global d’exceptions en place au cas où quelque chose serait manqué. Idéalement, nous aurions aussi des outils ou fonctionnalités de surveillance et/ou d’observabilité qui surveillent les erreurs répétées ou les schémas indiquant une attaque en cours, qui pourrait fournir une réponse, une défense ou un blocage quelconque. Cela peut nous aider à bloquer et à répondre aux scripts et bots qui se concentrent sur nos faiblesses en gestion des erreurs. 
+Détecter et gérer des conditions exceptionnelles garantit que l’infrastructure sous-jacente de nos programmes ne doit pas gérer des situations imprévisibles. Si vous êtes en cours de transaction de quelque nature que ce soit, il est extrêmement important de revenir en arrière sur chaque partie de la transaction et de recommencer (ce qu’on appelle également échec de clôture). Tenter de récupérer une transaction en cours de route est souvent l’occasion de créer des erreurs irrémédiables. 
+Dans la mesure du possible, ajoutez des limites de vitesse, des quotas de ressources, des limitations de puissance et d’autres limites autant que possible, pour prévenir des conditions exceptionnelles dès le départ. Rien dans les technologies de l’information ne devrait être illimité, car cela conduit à un manque de résilience des applications, au déni de service, à des attaques par force brute réussies et à des factures cloud extraordinaires. 
+Considérez si des erreurs répétées identiques, au-delà d’un certain débit, ne doivent être produites que sous forme de statistiques montrant la fréquence et dans quel délai ils se sont produits. Ces informations doivent être ajoutées au message original afin de ne pas interférer avec la journalisation et la surveillance automatisées, voir **A09:2025 Défaillances de journalisation et alertes de sécurité**.
+En plus de cela, nous voudrions inclure une validation stricte des entrées (avec nettoyage ou échappement pour les caractères potentiellement dangereux que nous devons accepter), une gestion centralisée des erreurs, la journalisation, la surveillance et l’alerte, ainsi qu’un gestionnaire global d’exceptions. Une application ne doit pas avoir plusieurs fonctions pour gérer des conditions exceptionnelles, elle doit être effectuée en un seul endroit, de la même manière à chaque fois. Nous devrions également créer des exigences de sécurité du projet pour tous les conseils de cette section, effectuer la modélisation des menaces et/ou des activités de revue de conception sécurisée lors de la phase de conception de nos projets, effectuer des revues de code ou des analyses statiques, ainsi que réaliser des tests de stress, de performance et d’intrusion du système final. 
+Si possible, toute votre organisation devrait gérer les conditions exceptionnelles de la même manière, car cela facilite la relecture et l’audit du code pour détecter des erreurs dans ce contrôle de sécurité important.
+## Exemples de scénarios d’attaque
+**Scénario #1 : Une épuisement des ressources dû à une mauvaise gestion de conditions exceptionnelles (déni de service) peut être causé si l’application détecte des exceptions lors du téléchargement des fichiers, mais ne libère pas correctement les ressources ensuite. Chaque nouvelle exception laisse les ressources bloquées ou indisponibles, jusqu’à ce que toutes les ressources soient épuisées. 
+**Scénario #2 :** Exposition de données sensibles via une mauvaise gestion ou des erreurs de base de données qui révèlent l’erreur système complète à l’utilisateur. L’attaquant continue de forcer des erreurs afin d’utiliser les informations sensibles du système pour créer une meilleure attaque d’injection SQL. Les données sensibles dans les messages d’erreur utilisateur sont de la reconnaissance. 
+**Scénario #3 :** La corruption d’état dans les transactions financières pourrait être causée par un attaquant interrompant une transaction en plusieurs étapes via des perturbations réseau. Imaginez que l’ordre de la transaction soit : débiter un compte utilisateur, créditer le compte de destination, enregistrer la transaction. Si le système ne revient pas correctement sur l’intégralité de la transaction (échec fermé) en cas d’erreur en cours de route, l’attaquant pourrait potentiellement vider le compte de l’utilisateur, ou peut-être une condition de course permettant à l’attaquant d’envoyer de l’argent à destination plusieurs fois. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
   </si>
 </sst>
 </file>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="3" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -10628,7 +10628,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>386</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -10683,7 +10683,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>387</v>
+        <v>355</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>10</v>
@@ -10790,7 +10790,7 @@
         <v>63</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>64</v>
@@ -10805,10 +10805,10 @@
         <v>67</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>376</v>
+        <v>346</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>68</v>
@@ -10897,7 +10897,7 @@
         <v>94</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>389</v>
+        <v>357</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>95</v>
@@ -10906,953 +10906,953 @@
         <v>96</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="M3" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="Q3" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="R3" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="S3" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="T3" s="8" t="s">
         <v>105</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="U3" s="8" t="s">
         <v>95</v>
       </c>
       <c r="V3" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z3" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="AA3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="AD3" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="AE3" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="X3" s="8" t="s">
+      <c r="AF3" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="AG3" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="Y3" s="8" t="s">
+      <c r="AH3" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="Z3" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA3" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD3" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="AE3" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF3" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="AG3" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="AH3" s="8" t="s">
-        <v>123</v>
-      </c>
       <c r="AI3" s="8" t="s">
-        <v>124</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="O4" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="Q4" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="R4" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="S4" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="T4" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="U4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="W4" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="X4" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="Y4" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="AA4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC4" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="AE4" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="AF4" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="AG4" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="U4" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="V4" s="5" t="s">
+      <c r="AH4" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="AI4" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y4" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z4" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="AC4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="AD4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AE4" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="AF4" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="AG4" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="AH4" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="AI4" s="5" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="O5" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="P5" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="Q5" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="R5" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="I5" s="8" t="s">
+      <c r="S5" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="T5" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="U5" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="V5" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="W5" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="X5" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="Y5" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="Z5" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="AA5" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="AB5" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="AC5" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="AD5" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="T5" s="8" t="s">
+      <c r="AE5" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="U5" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="V5" s="8" t="s">
+      <c r="AF5" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="W5" s="8" t="s">
+      <c r="AG5" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="X5" s="8" t="s">
+      <c r="AH5" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="AI5" s="8" t="s">
         <v>174</v>
-      </c>
-      <c r="Z5" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA5" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB5" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC5" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="AD5" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE5" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF5" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="AG5" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="AH5" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI5" s="8" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="P6" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="Q6" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="R6" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="S6" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="T6" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="U6" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="V6" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="W6" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="L6" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="M6" s="5" t="s">
+      <c r="X6" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="Y6" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="Z6" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="AA6" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="Q6" s="5" t="s">
+      <c r="AB6" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="R6" s="5" t="s">
+      <c r="AC6" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="S6" s="5" t="s">
+      <c r="AD6" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="T6" s="5" t="s">
+      <c r="AE6" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="U6" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="V6" s="5" t="s">
+      <c r="AF6" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="AG6" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="X6" s="5" t="s">
+      <c r="AH6" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="Y6" s="5" t="s">
+      <c r="AI6" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="Z6" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="AA6" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB6" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC6" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD6" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE6" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="AF6" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="AG6" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AH6" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="AI6" s="5" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="O7" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="Q7" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="R7" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="S7" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="T7" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="U7" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="V7" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="W7" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="X7" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="Y7" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="Z7" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="AA7" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="AB7" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="AC7" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="R7" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="S7" s="8" t="s">
+      <c r="AD7" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="T7" s="8" t="s">
+      <c r="AE7" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="U7" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="V7" s="8" t="s">
+      <c r="AF7" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="W7" s="8" t="s">
+      <c r="AG7" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="X7" s="8" t="s">
+      <c r="AH7" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="Y7" s="8" t="s">
+      <c r="AI7" s="8" t="s">
         <v>233</v>
-      </c>
-      <c r="Z7" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA7" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="AB7" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC7" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="AD7" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="AE7" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="AF7" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="AG7" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="AH7" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="AI7" s="8" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="O8" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="P8" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="Q8" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="R8" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="S8" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="I8" s="5" t="s">
+      <c r="T8" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="U8" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="V8" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="W8" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="X8" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="Y8" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="Z8" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="N8" s="5" t="s">
+      <c r="AA8" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="AB8" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="AC8" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="Q8" s="5" t="s">
+      <c r="AD8" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="R8" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="S8" s="5" t="s">
+      <c r="AE8" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="T8" s="5" t="s">
+      <c r="AF8" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="U8" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="V8" s="5" t="s">
+      <c r="AG8" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="W8" s="5" t="s">
+      <c r="AH8" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="X8" s="5" t="s">
+      <c r="AI8" s="5" t="s">
         <v>262</v>
-      </c>
-      <c r="Y8" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="Z8" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="AA8" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="AB8" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="AC8" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="AD8" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="AE8" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="AF8" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="AG8" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="AH8" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="AI8" s="5" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="O9" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="P9" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="Q9" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="R9" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="S9" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="T9" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="I9" s="8" t="s">
+      <c r="U9" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="V9" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="W9" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="X9" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="Y9" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="Z9" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="AA9" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="AB9" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="AC9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="AD9" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="R9" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="S9" s="8" t="s">
+      <c r="AE9" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="T9" s="8" t="s">
+      <c r="AF9" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="U9" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="V9" s="8" t="s">
+      <c r="AG9" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="W9" s="8" t="s">
+      <c r="AH9" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="X9" s="8" t="s">
+      <c r="AI9" s="8" t="s">
         <v>292</v>
-      </c>
-      <c r="Y9" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z9" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA9" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="AB9" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="AC9" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="AD9" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="AE9" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="AF9" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="AG9" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="AH9" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="AI9" s="8" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="S10" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="T10" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="U10" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="W10" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="X10" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="Y10" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="Z10" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="AA10" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="AB10" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="AC10" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="AD10" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="AE10" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="L10" s="5" t="s">
+      <c r="AF10" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="AG10" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="AH10" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="AI10" s="5" t="s">
         <v>314</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="W10" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="Y10" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="Z10" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="AB10" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="AC10" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="AD10" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="AE10" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="AF10" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="AH10" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="AI10" s="5" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="T11" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="W11" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="X11" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="Y11" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="Z11" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="AA11" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="AB11" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="AC11" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="AD11" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="AE11" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="AF11" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="AG11" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="AH11" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="T11" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="U11" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="V11" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="W11" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="X11" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="Y11" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="Z11" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="AA11" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="AB11" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="AC11" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="AD11" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="AE11" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="AF11" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="AG11" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="AH11" s="8" t="s">
-        <v>363</v>
-      </c>
       <c r="AI11" s="8" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/owasp/owasp-top-10-web_2025.xlsx
+++ b/tools/excel/owasp/owasp-top-10-web_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\owasp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140E4654-EA3E-44CC-8C8A-81CCC0E8CBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7576D0A9-DAF0-4F00-B213-8E4FFF4B879D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="-14475" windowWidth="20280" windowHeight="11790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1650" yWindow="-15870" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -84,10 +84,6 @@
   </si>
   <si>
     <t>description[fr]</t>
-  </si>
-  <si>
-    <t>Le Top 10 de l'OWASP est un document de sensibilisation destiné aux développeurs et à la sécurité des applications web. Il représente un large consensus sur les risques de sécurité les plus critiques pour les applications web.
-Source: https://top10.owasp.org/2025/fr/0x00_2025-Introduction/</t>
   </si>
   <si>
     <t>copyright</t>
@@ -1367,9 +1363,6 @@
 For more information about the references and the list of mapped CWEs: https://top10.owasp.org/2025/A03_2025-Software_Supply_Chain_Failures/</t>
   </si>
   <si>
-    <t>Défaillances de la nomenclature logicielle</t>
-  </si>
-  <si>
     <t>Selhání dodavatelského řetězce softwaru (Software Supply Chain Failures)</t>
   </si>
   <si>
@@ -5316,9 +5309,6 @@
 For more information about the references and the list of mapped CWEs: https://top10.owasp.org/2025/A08_2025-Software_or_Data_Integrity_Failures/</t>
   </si>
   <si>
-    <t>Manque d'intégrité des données ou du logiciel</t>
-  </si>
-  <si>
     <t>Selhání integrity softwaru nebo dat (Software or Data Integrity Failures)</t>
   </si>
   <si>
@@ -5905,9 +5895,6 @@
 **Scenario #2:** A major Indian airline had a data breach involving more than ten years' worth of personal data of millions of passengers, including passport and credit card data. The data breach occurred at a third-party cloud hosting provider, who notified the airline of the breach after some time.
 **Scenario #3:** A major European airline suffered a GDPR reportable breach. The breach was reportedly caused by payment application security vulnerabilities exploited by attackers, who harvested more than 400,000 customer payment records. The airline was fined 20 million pounds as a result by the privacy regulator.
 For more information about the references and the list of mapped CWEs: https://top10.owasp.org/2025/A09_2025-Security_Logging_and_Alerting_Failures/</t>
-  </si>
-  <si>
-    <t>Carence des systèmes de contrôle et d'alerte</t>
   </si>
   <si>
     <t>Selhání bezpečnostního logování a upozorňování (Security Logging &amp; Alerting Failures)</t>
@@ -6488,9 +6475,6 @@
 Exceptional conditions can be caused by missing, poor, or incomplete input validation, or late, high level error handling instead at the functions where they occur, or unexpected environmental states such as memory, privilege, or network issues, inconsistent exception handling, or exceptions that are not handled at all, allowing the system to fall into an unknown and unpredictable state. Any time an application is unsure of its next instruction, an exceptional condition has been mishandled. Hard-to-find errors and exceptions can threaten the security of the whole application for a long time.
 Many different security vulnerabilities can happen when we mishandle exceptional conditions,
 such as logic bugs, overflows, race conditions, fraudulent transactions, or issues with memory, state, resource, timing, authentication, and authorization. These types of vulnerabilities can negatively affect the confidentiality, availability, and/or integrity of a system or it’s data. Attackers manipulate an application's flawed error handling to strike this vulnerability. </t>
-  </si>
-  <si>
-    <t>Mauvaise gestion des exceptions</t>
   </si>
   <si>
     <t>Nesprávné zpracování výjimečných stavů (Mishandling of Exceptional Conditions)</t>
@@ -8650,6 +8634,22 @@
 **Scénario #3 :** La corruption d’état dans les transactions financières pourrait être causée par un attaquant interrompant une transaction en plusieurs étapes via des perturbations réseau. Imaginez que l’ordre de la transaction soit : débiter un compte utilisateur, créditer le compte de destination, enregistrer la transaction. Si le système ne revient pas correctement sur l’intégralité de la transaction (échec fermé) en cas d’erreur en cours de route, l’attaquant pourrait potentiellement vider le compte de l’utilisateur, ou peut-être une condition de course permettant à l’attaquant d’envoyer de l’argent à destination plusieurs fois. 
 Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
   </si>
+  <si>
+    <t>Défaillances de la chaîne d’approvisionnement logicielle</t>
+  </si>
+  <si>
+    <t>Défaillances de la journalisation et de l'alerte de sécurité</t>
+  </si>
+  <si>
+    <t>Mauvaise gestion des conditions exceptionnelles</t>
+  </si>
+  <si>
+    <t>Défaillances logicielles ou d'intégrité des données</t>
+  </si>
+  <si>
+    <t>Le Top 10 de l'OWASP est un document de sensibilisation destiné aux développeurs et à la sécurité des applications web. Il représente un large consensus sur les risques de sécurité les plus critiques pour les applications web.
+Source: https://top10.owasp.org/2025/0x00_2025-Introduction/</t>
+  </si>
 </sst>
 </file>
 
@@ -8678,7 +8678,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8700,6 +8700,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
@@ -8771,7 +8777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -8802,6 +8808,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10366,7 +10378,7 @@
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -10426,40 +10438,40 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
+      <c r="B9" s="14" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
@@ -10467,15 +10479,15 @@
     </row>
     <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
@@ -10483,15 +10495,15 @@
     </row>
     <row r="16" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>11</v>
@@ -10499,15 +10511,15 @@
     </row>
     <row r="18" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>11</v>
@@ -10515,15 +10527,15 @@
     </row>
     <row r="20" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>11</v>
@@ -10531,15 +10543,15 @@
     </row>
     <row r="22" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>11</v>
@@ -10547,15 +10559,15 @@
     </row>
     <row r="24" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>11</v>
@@ -10563,15 +10575,15 @@
     </row>
     <row r="26" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>11</v>
@@ -10579,15 +10591,15 @@
     </row>
     <row r="28" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>11</v>
@@ -10595,10 +10607,10 @@
     </row>
     <row r="30" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -10620,15 +10632,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -10683,7 +10695,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>10</v>
@@ -10692,7 +10704,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>14</v>
@@ -10701,1158 +10713,1158 @@
         <v>15</v>
       </c>
       <c r="H1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="12" t="s">
+      <c r="O1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="O1" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q1" s="12" t="s">
+      <c r="R1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="R1" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="S1" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" s="12" t="s">
+      <c r="U1" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="W1" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="U1" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="V1" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="W1" s="12" t="s">
+      <c r="X1" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z1" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="X1" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y1" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z1" s="12" t="s">
+      <c r="AA1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC1" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="AA1" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB1" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC1" s="12" t="s">
+      <c r="AD1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF1" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="AD1" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE1" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF1" s="12" t="s">
+      <c r="AG1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI1" s="12" t="s">
         <v>61</v>
-      </c>
-      <c r="AG1" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH1" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI1" s="12" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="U2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="U2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="V2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AB2" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AC2" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AC2" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AE2" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AF2" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AF2" s="5" t="s">
+      <c r="AG2" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="AG2" s="5" t="s">
+      <c r="AH2" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="AH2" s="5" t="s">
+      <c r="AI2" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="AI2" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="G3" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="N3" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="O3" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y3" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z3" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="M3" s="8" t="s">
+      <c r="AA3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AC3" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="AD3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF3" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q3" s="8" t="s">
+      <c r="AG3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH3" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI3" s="8" t="s">
         <v>372</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="V3" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="W3" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z3" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="AA3" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="AD3" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="AE3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AF3" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="AG3" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="AH3" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AI3" s="8" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="O4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="Q4" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="R4" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="S4" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="T4" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="U4" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="W4" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="X4" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB4" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="V4" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="AA4" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AE4" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="AD4" s="5" t="s">
+      <c r="AF4" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AG4" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AH4" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="AG4" s="5" t="s">
+      <c r="AI4" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="AH4" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AI4" s="5" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="G5" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="J5" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="I5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="M5" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="N5" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="O5" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="P5" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="Q5" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="R5" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="S5" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="T5" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="U5" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="V5" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="T5" s="8" t="s">
+      <c r="W5" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="U5" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="V5" s="8" t="s">
+      <c r="X5" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="W5" s="8" t="s">
+      <c r="Y5" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="X5" s="8" t="s">
+      <c r="Z5" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="AA5" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="Z5" s="8" t="s">
+      <c r="AB5" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="AA5" s="8" t="s">
+      <c r="AC5" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="AB5" s="8" t="s">
+      <c r="AD5" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="AC5" s="8" t="s">
+      <c r="AE5" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="AD5" s="8" t="s">
+      <c r="AF5" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="AE5" s="8" t="s">
+      <c r="AG5" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="AF5" s="8" t="s">
+      <c r="AH5" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="AG5" s="8" t="s">
+      <c r="AI5" s="8" t="s">
         <v>172</v>
-      </c>
-      <c r="AH5" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="AI5" s="8" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="F6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="L6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="M6" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="N6" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L6" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="M6" s="5" t="s">
+      <c r="O6" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="P6" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="Q6" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="R6" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="Q6" s="5" t="s">
+      <c r="S6" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="R6" s="5" t="s">
+      <c r="T6" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="S6" s="5" t="s">
+      <c r="U6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="V6" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="T6" s="5" t="s">
+      <c r="W6" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="U6" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="V6" s="5" t="s">
+      <c r="X6" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="Y6" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="X6" s="5" t="s">
+      <c r="Z6" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="Y6" s="5" t="s">
+      <c r="AA6" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="Z6" s="5" t="s">
+      <c r="AB6" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AA6" s="5" t="s">
+      <c r="AC6" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="AB6" s="5" t="s">
+      <c r="AD6" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="AC6" s="5" t="s">
+      <c r="AE6" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="AD6" s="5" t="s">
+      <c r="AF6" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="AE6" s="5" t="s">
+      <c r="AG6" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="AF6" s="5" t="s">
+      <c r="AH6" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="AG6" s="5" t="s">
+      <c r="AI6" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="AH6" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="AI6" s="5" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="G7" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="J7" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="M7" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="N7" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="O7" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="Q7" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="R7" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="S7" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="T7" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="R7" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="S7" s="8" t="s">
+      <c r="U7" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="V7" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="T7" s="8" t="s">
+      <c r="W7" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="U7" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="V7" s="8" t="s">
+      <c r="X7" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="W7" s="8" t="s">
+      <c r="Y7" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="X7" s="8" t="s">
+      <c r="Z7" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="Y7" s="8" t="s">
+      <c r="AA7" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="Z7" s="8" t="s">
+      <c r="AB7" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AA7" s="8" t="s">
+      <c r="AC7" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="AB7" s="8" t="s">
+      <c r="AD7" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="AC7" s="8" t="s">
+      <c r="AE7" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="AD7" s="8" t="s">
+      <c r="AF7" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="AE7" s="8" t="s">
+      <c r="AG7" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="AF7" s="8" t="s">
+      <c r="AH7" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="AG7" s="8" t="s">
+      <c r="AI7" s="8" t="s">
         <v>231</v>
-      </c>
-      <c r="AH7" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="AI7" s="8" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="G8" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="I8" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="L8" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="N8" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="O8" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="N8" s="5" t="s">
+      <c r="P8" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="Q8" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="R8" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="S8" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="Q8" s="5" t="s">
+      <c r="T8" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="R8" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="S8" s="5" t="s">
+      <c r="U8" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="V8" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="T8" s="5" t="s">
+      <c r="W8" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="U8" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="V8" s="5" t="s">
+      <c r="X8" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="W8" s="5" t="s">
+      <c r="Y8" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="Z8" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="X8" s="5" t="s">
+      <c r="AA8" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="Y8" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="Z8" s="5" t="s">
+      <c r="AB8" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="AA8" s="5" t="s">
+      <c r="AC8" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="AB8" s="5" t="s">
+      <c r="AD8" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="AC8" s="5" t="s">
+      <c r="AE8" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="AD8" s="5" t="s">
+      <c r="AF8" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="AE8" s="5" t="s">
+      <c r="AG8" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="AF8" s="5" t="s">
+      <c r="AH8" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="AG8" s="5" t="s">
+      <c r="AI8" s="5" t="s">
         <v>260</v>
-      </c>
-      <c r="AH8" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="AI8" s="5" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="F9" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="I9" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="M9" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="N9" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="O9" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="P9" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="Q9" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="R9" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="S9" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="T9" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="U9" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="V9" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="R9" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="S9" s="8" t="s">
+      <c r="W9" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="T9" s="8" t="s">
+      <c r="X9" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="U9" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="V9" s="8" t="s">
+      <c r="Y9" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="W9" s="8" t="s">
+      <c r="Z9" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="X9" s="8" t="s">
+      <c r="AA9" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="Y9" s="8" t="s">
+      <c r="AB9" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="Z9" s="8" t="s">
+      <c r="AC9" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="AA9" s="8" t="s">
+      <c r="AD9" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="AB9" s="8" t="s">
+      <c r="AE9" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="AC9" s="8" t="s">
+      <c r="AF9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="AD9" s="8" t="s">
+      <c r="AG9" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="AE9" s="8" t="s">
+      <c r="AH9" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="AF9" s="8" t="s">
+      <c r="AI9" s="8" t="s">
         <v>289</v>
-      </c>
-      <c r="AG9" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="AH9" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="AI9" s="8" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="J10" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="L10" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="M10" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="N10" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="O10" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="P10" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="AB10" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="M10" s="5" t="s">
+      <c r="AC10" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="AD10" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="AE10" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="N10" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="P10" s="5" t="s">
+      <c r="AF10" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="AG10" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="AH10" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="Q10" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="W10" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="Y10" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="Z10" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="AB10" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="AC10" s="5" t="s">
+      <c r="AI10" s="5" t="s">
         <v>310</v>
-      </c>
-      <c r="AD10" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="AE10" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="AF10" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="AH10" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="AI10" s="5" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="K11" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="M11" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="N11" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="O11" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="I11" s="8" t="s">
+      <c r="P11" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="Q11" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="S11" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="T11" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="W11" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="X11" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="Y11" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="Z11" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="AA11" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="AB11" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC11" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="N11" s="8" t="s">
+      <c r="AD11" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="AE11" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="AF11" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="O11" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q11" s="8" t="s">
+      <c r="AG11" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="AH11" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="AI11" s="8" t="s">
         <v>389</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="T11" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="U11" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="V11" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="W11" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="X11" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="Y11" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="Z11" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="AA11" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="AB11" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="AC11" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="AD11" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="AE11" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="AF11" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="AG11" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="AH11" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="AI11" s="8" t="s">
-        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/owasp/owasp-top-10-web_2025.xlsx
+++ b/tools/excel/owasp/owasp-top-10-web_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\owasp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7576D0A9-DAF0-4F00-B213-8E4FFF4B879D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71B3F9D-F0D8-4E55-94F0-5D283A780488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="-15870" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1650" yWindow="-15870" windowWidth="25440" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -6471,12 +6471,6 @@
     <t>Mishandling of Exceptional Conditions</t>
   </si>
   <si>
-    <t xml:space="preserve">Mishandling exceptional conditions in software happens when programs fail to prevent, detect, and respond to unusual and unpredictable situations, which leads to crashes, unexpected behavior, and sometimes vulnerabilities. This can involve one or more of the following 3 failings; the application doesn’t prevent an unusual situation from happening, it doesn’t identify the situation as it is happening, and/or it responds poorly or not at all to the situation afterwards.
-Exceptional conditions can be caused by missing, poor, or incomplete input validation, or late, high level error handling instead at the functions where they occur, or unexpected environmental states such as memory, privilege, or network issues, inconsistent exception handling, or exceptions that are not handled at all, allowing the system to fall into an unknown and unpredictable state. Any time an application is unsure of its next instruction, an exceptional condition has been mishandled. Hard-to-find errors and exceptions can threaten the security of the whole application for a long time.
-Many different security vulnerabilities can happen when we mishandle exceptional conditions,
-such as logic bugs, overflows, race conditions, fraudulent transactions, or issues with memory, state, resource, timing, authentication, and authorization. These types of vulnerabilities can negatively affect the confidentiality, availability, and/or integrity of a system or it’s data. Attackers manipulate an application's flawed error handling to strike this vulnerability. </t>
-  </si>
-  <si>
     <t>Nesprávné zpracování výjimečných stavů (Mishandling of Exceptional Conditions)</t>
   </si>
   <si>
@@ -6663,12 +6657,6 @@
   </si>
   <si>
     <t>Les défaillances d’intégrité logicielle et des données concernent du code et une infrastructure qui ne protègent pas contre le traitement de code ou de données invalides ou non fiables. Un exemple est lorsqu’une application s’appuie sur des plugins, bibliothèques ou modules provenant de sources, dépôts et réseaux de diffusion de contenu (CDN) non fiables. Un pipeline CI/CD non sécurisé sans consommer ni fournir de vérifications d’intégrité logicielle peut introduire un risque d’accès non autorisé, de code non sécurisé ou malveillant, ou de compromission système. Un autre exemple est un CI/CD qui extrait du code ou des artefacts de lieux non fiables et/ou ne les vérifie pas avant utilisation (en vérifiant la signature ou un mécanisme similaire). Enfin, de nombreuses applications incluent désormais la fonctionnalité de mise à jour automatique, où les mises à jour sont téléchargées sans vérification suffisante de l’intégrité et appliquées à l’application précédemment fiable. Un autre exemple est celui où des objets ou des données sont encodés ou sérialisés dans une structure qu’un attaquant peut voir et modifier vulnérable à la désérialisation non sécurisée.</t>
-  </si>
-  <si>
-    <t>La mauvaise gestion de conditions exceptionnelles dans les logiciels survient lorsque les programmes ne préviennent pas, détectent et ne répondent pas à des situations inhabituelles et imprévisibles, ce qui entraîne des plantages, des comportements inattendus et parfois des vulnérabilités. Cela peut impliquer une ou plusieurs des trois défaillances suivantes ; l’application ne prévient pas qu’une situation inhabituelle se produise, elle n’identifie pas la situation au moment où elle se produit, et/ou elle réagit mal ou pas du tout à la situation par la suite. 
-Des conditions exceptionnelles peuvent être causées par une validation d’entrée manquante, mauvaise ou incomplète, ou une gestion tardive et de haut niveau des erreurs aux fonctions où elles se produisent, ou des états environnementaux inattendus tels que des problèmes de mémoire, de privilèges ou de réseau, une gestion incohérente des exceptions ou des exceptions qui ne sont pas du tout traitées, permettant au système de tomber dans un état inconnu et imprévisible. Chaque fois qu’une application n’est pas sûre de sa prochaine instruction, une condition exceptionnelle a été mal gérée. Les erreurs et exceptions difficiles à trouver peuvent menacer la sécurité de l’ensemble de l’application pendant longtemps. 
-De nombreuses vulnérabilités de sécurité peuvent survenir lorsque nous gérons mal des conditions exceptionnelles, 
-tels que des bugs logiques, des débordements, des conditions de course, des transactions frauduleuses ou des problèmes de mémoire, d’état, de ressources, de timing, d’authentification et d’autorisation. Ce type de vulnérabilités peut nuire à la confidentialité, à la disponibilité et/ou à l’intégrité d’un système ou de ses données. Les attaquants manipulent la gestion des erreurs défaillantes d’une application pour corriger cette vulnérabilité.</t>
   </si>
   <si>
     <t>La conception non sécurisée est une catégorie large représentant différentes faiblesses, exprimées par « conception de contrôle manquante ou inefficace ». La conception non sécurisée n’est pas la source pour toutes les autres catégories de risque Top 10. Notez qu’il existe une différence entre conception non sécurisée et implémentation non sécurisée. Nous différencions les défauts de conception et les défauts d’implémentation pour une raison : ils ont des causes profondes différentes, surviennent à des moments différents du processus de développement et comportent des corrections différentes. Une conception sécurisée peut tout de même présenter des défauts d’implémentation entraînant des vulnérabilités qui peuvent être exploitées. Une conception non sécurisée ne peut être corrigée par une implémentation parfaite car les contrôles de sécurité nécessaires n’ont jamais été créés pour se défendre contre des attaques spécifiques. L’un des facteurs qui contribue à la conception non sécurisée est l’absence de profilage des risques métier inhérent au logiciel ou au système développé, et donc l’échec à déterminer quel niveau de conception de sécurité est requis. 
@@ -8649,6 +8637,16 @@
   <si>
     <t>Le Top 10 de l'OWASP est un document de sensibilisation destiné aux développeurs et à la sécurité des applications web. Il représente un large consensus sur les risques de sécurité les plus critiques pour les applications web.
 Source: https://top10.owasp.org/2025/0x00_2025-Introduction/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mishandling exceptional conditions in software happens when programs fail to prevent, detect, and respond to unusual and unpredictable situations, which leads to crashes, unexpected behavior, and sometimes vulnerabilities. This can involve one or more of the following 3 failings; the application doesn’t prevent an unusual situation from happening, it doesn’t identify the situation as it is happening, and/or it responds poorly or not at all to the situation afterwards.
+Exceptional conditions can be caused by missing, poor, or incomplete input validation, or late, high level error handling instead at the functions where they occur, or unexpected environmental states such as memory, privilege, or network issues, inconsistent exception handling, or exceptions that are not handled at all, allowing the system to fall into an unknown and unpredictable state. Any time an application is unsure of its next instruction, an exceptional condition has been mishandled. Hard-to-find errors and exceptions can threaten the security of the whole application for a long time.
+Many different security vulnerabilities can happen when we mishandle exceptional conditions, such as logic bugs, overflows, race conditions, fraudulent transactions, or issues with memory, state, resource, timing, authentication, and authorization. These types of vulnerabilities can negatively affect the confidentiality, availability, and/or integrity of a system or it’s data. Attackers manipulate an application's flawed error handling to strike this vulnerability. </t>
+  </si>
+  <si>
+    <t>La mauvaise gestion de conditions exceptionnelles dans les logiciels survient lorsque les programmes ne préviennent pas, détectent et ne répondent pas à des situations inhabituelles et imprévisibles, ce qui entraîne des plantages, des comportements inattendus et parfois des vulnérabilités. Cela peut impliquer une ou plusieurs des trois défaillances suivantes ; l’application ne prévient pas qu’une situation inhabituelle se produise, elle n’identifie pas la situation au moment où elle se produit, et/ou elle réagit mal ou pas du tout à la situation par la suite. 
+Des conditions exceptionnelles peuvent être causées par une validation d’entrée manquante, mauvaise ou incomplète, ou une gestion tardive et de haut niveau des erreurs aux fonctions où elles se produisent, ou des états environnementaux inattendus tels que des problèmes de mémoire, de privilèges ou de réseau, une gestion incohérente des exceptions ou des exceptions qui ne sont pas du tout traitées, permettant au système de tomber dans un état inconnu et imprévisible. Chaque fois qu’une application n’est pas sûre de sa prochaine instruction, une condition exceptionnelle a été mal gérée. Les erreurs et exceptions difficiles à trouver peuvent menacer la sécurité de l’ensemble de l’application pendant longtemps. 
+De nombreuses vulnérabilités de sécurité peuvent survenir lorsque nous gérons mal des conditions exceptionnelles, tels que des bugs logiques, des débordements, des conditions de course, des transactions frauduleuses ou des problèmes de mémoire, d’état, de ressources, de timing, d’authentification et d’autorisation. Ce type de vulnérabilités peut nuire à la confidentialité, à la disponibilité et/ou à l’intégrité d’un système ou de ses données. Les attaquants manipulent la gestion des erreurs défaillantes d’une application pour corriger cette vulnérabilité.</t>
   </si>
 </sst>
 </file>
@@ -10378,7 +10376,7 @@
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -10442,7 +10440,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -10640,7 +10638,7 @@
         <v>50</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -10695,7 +10693,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>10</v>
@@ -10802,7 +10800,7 @@
         <v>62</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>63</v>
@@ -10817,10 +10815,10 @@
         <v>66</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>67</v>
@@ -10909,7 +10907,7 @@
         <v>93</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>94</v>
@@ -10918,16 +10916,16 @@
         <v>95</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>96</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>97</v>
@@ -10936,16 +10934,16 @@
         <v>98</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>99</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>100</v>
@@ -10954,7 +10952,7 @@
         <v>101</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="R3" s="8" t="s">
         <v>102</v>
@@ -10972,7 +10970,7 @@
         <v>105</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X3" s="8" t="s">
         <v>106</v>
@@ -10981,7 +10979,7 @@
         <v>107</v>
       </c>
       <c r="Z3" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AA3" s="8" t="s">
         <v>108</v>
@@ -10990,7 +10988,7 @@
         <v>109</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AD3" s="8" t="s">
         <v>110</v>
@@ -10999,7 +10997,7 @@
         <v>111</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG3" s="8" t="s">
         <v>112</v>
@@ -11008,7 +11006,7 @@
         <v>113</v>
       </c>
       <c r="AI3" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
@@ -11016,7 +11014,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>115</v>
@@ -11028,13 +11026,13 @@
         <v>117</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>118</v>
@@ -11123,7 +11121,7 @@
         <v>142</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>143</v>
@@ -11138,10 +11136,10 @@
         <v>146</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>147</v>
@@ -11230,7 +11228,7 @@
         <v>173</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>174</v>
@@ -11245,10 +11243,10 @@
         <v>174</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>177</v>
@@ -11337,7 +11335,7 @@
         <v>202</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>203</v>
@@ -11352,10 +11350,10 @@
         <v>206</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>207</v>
@@ -11444,7 +11442,7 @@
         <v>232</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>233</v>
@@ -11459,10 +11457,10 @@
         <v>236</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>237</v>
@@ -11513,7 +11511,7 @@
         <v>250</v>
       </c>
       <c r="Y8" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="Z8" s="5" t="s">
         <v>251</v>
@@ -11551,7 +11549,7 @@
         <v>261</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>262</v>
@@ -11563,13 +11561,13 @@
         <v>264</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>265</v>
@@ -11658,31 +11656,31 @@
         <v>290</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>291</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>293</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>294</v>
@@ -11691,7 +11689,7 @@
         <v>295</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N10" s="5" t="s">
         <v>296</v>
@@ -11700,7 +11698,7 @@
         <v>297</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>298</v>
@@ -11718,7 +11716,7 @@
         <v>291</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="W10" s="5" t="s">
         <v>302</v>
@@ -11727,7 +11725,7 @@
         <v>303</v>
       </c>
       <c r="Y10" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="Z10" s="5" t="s">
         <v>304</v>
@@ -11736,7 +11734,7 @@
         <v>305</v>
       </c>
       <c r="AB10" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AC10" s="5" t="s">
         <v>306</v>
@@ -11745,7 +11743,7 @@
         <v>307</v>
       </c>
       <c r="AE10" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AF10" s="5" t="s">
         <v>308</v>
@@ -11754,7 +11752,7 @@
         <v>309</v>
       </c>
       <c r="AH10" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AI10" s="5" t="s">
         <v>310</v>
@@ -11765,106 +11763,106 @@
         <v>311</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>312</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="I11" s="8" t="s">
+      <c r="J11" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="K11" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="M11" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q11" s="8" t="s">
         <v>382</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>384</v>
       </c>
       <c r="R11" s="8" t="s">
         <v>312</v>
       </c>
       <c r="S11" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="T11" s="8" t="s">
         <v>320</v>
-      </c>
-      <c r="T11" s="8" t="s">
-        <v>321</v>
       </c>
       <c r="U11" s="8" t="s">
         <v>312</v>
       </c>
       <c r="V11" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="W11" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="X11" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="W11" s="8" t="s">
+      <c r="Y11" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="Z11" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="AA11" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="AB11" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="AC11" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="X11" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="Y11" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="Z11" s="8" t="s">
+      <c r="AD11" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="AE11" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="AF11" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="AA11" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="AB11" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC11" s="8" t="s">
+      <c r="AG11" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="AH11" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="AI11" s="8" t="s">
         <v>387</v>
-      </c>
-      <c r="AD11" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="AE11" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="AF11" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="AG11" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="AH11" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="AI11" s="8" t="s">
-        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/owasp/owasp-top-10-web_2025.xlsx
+++ b/tools/excel/owasp/owasp-top-10-web_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\owasp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294CA6D2-75F6-4A1C-BA8F-D6C3D42439A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284B60DC-2255-4389-A01C-20E826156023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="-15870" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1650" yWindow="-15870" windowWidth="25440" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -2509,69 +2509,6 @@
    &lt;/td&gt;
   &lt;/tr&gt;
   &lt;tr&gt;
-   &lt;td&gt;36
-   &lt;/td&gt;
-   &lt;td&gt;15,80 % 
-   &lt;/td&gt;
-   &lt;td&gt;2,92 % 
-   &lt;/td&gt;
-   &lt;td&gt;100,00 % 
-   &lt;/td&gt;
-   &lt;td&gt;37,14 % 
-   &lt;/td&gt;
-   &lt;td&gt;7,69
-   &lt;/td&gt;
-   &lt;td&gt;4,44
-   &lt;/td&gt;
-   &lt;td&gt;1 120 673
-   &lt;/td&gt;
-   &lt;td&gt;7 147
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## Comment prévenir
-* Lorsque possible, implémenter et faire respecter l’utilisation de l’authentification multifactorielle pour prévenir le bourrage automatisé des identifiants, la force brute et les attaques de réutilisation de crédents volées. 
-* Lorsque possible, encourager et activer l’utilisation de gestionnaires de mots de passe pour aider les utilisateurs à faire de meilleurs choix. 
-* Ne pas livrer ni déployer avec des identifiants par défaut, en particulier pour les utilisateurs administrateurs. 
-* Mettre en place des vérifications de mots de passe faibles, comme tester de nouveaux mots de passe ou modifiés dans la liste des 10 000 pires mots de passe. 
-* Lors de la création d’un nouveau compte et des changements de mot de passe, validez contre les listes d’identifiants connus pour violation (par exemple : utiliser [haveibeenpwned.com](https://haveibeenpwned.com)). 
-* Aligner les politiques de longueur, de complexité et de rotation des mots de passe avec les directives du [National Institute of Standards and Technology (NIST) 800-63b dans la section 5.1.1] (https://pages.nist.gov/800-63-3/sp800-63b.html#:~:text=5.1.1%20Memorized%20Secrets) pour les secrets mémorisés ou d’autres politiques modernes fondées sur des mots de passe fondées sur des preuves. 
-* Ne forcez pas les êtres humains à faire tourner les mots de passe sauf si vous suspectez une faille. Si vous soupçonnez une fuite, forcez immédiatement la réinitialisation du mot de passe.  
-* S’assurer que l’enregistrement, la récupération des identifiants et les voies API sont renforcés contre les attaques d’énumération de comptes en utilisant les mêmes messages pour tous les résultats (« Nom d’utilisateur ou mot de passe invalides. »). 
-* Limiter ou retarder de plus en plus les tentatives de connexion ratées, mais veillez à ne pas créer un scénario de déni de service. Consignez toutes les défaillances et alertez les administrateurs lorsque des attaques de type « credentialsal stuffing, de force brute » ou d’autres attaques sont détectées ou suspectées. 
-* Utiliser un gestionnaire de session intégré sécurisé côté serveur qui génère un nouvel ID de session aléatoire avec une forte entropie après la connexion. Les identifiants de session ne doivent pas être dans l’URL, être stockés de manière sécurisée dans un cookie sécurisé, et invalidés après déconnexion, inactivité et délais absolus.  
-* Idéalement, utiliser un système préfabriqué et bien fiable pour gérer l’authentification, l’identité et la gestion des sessions. Transférez ce risque autant que possible en achetant et en utilisant un système renforcé et bien testé. 
-* Vérifier l’utilisation prévue des identifiants fournis, par exemple pour les JWT, valider les affirmations « aud », « iss » et les périmètres
-## Exemples de scénarios d’attaque
-**Scénario #1 :** Le remplissage de crédentiaux, l’utilisation de listes de combinaisons de noms d’utilisateur et de mots de passe connus, est désormais une attaque très courante. Plus récemment, les attaquants ont été observés « incrémentant » ou ajustant autrement les mots de passe, en fonction du comportement humain courant. Par exemple, changer « Winter2025 » en « Hiver 2026 », ou « ILoveMyDog6 » en « ILoveMyDog7 » ou « ILoveMyDog5 ». Cet ajustement des tentatives de mot de passe est appelé attaque hybride de remplissage de crédibles ou attaque par pulvérisation de mots de passe, et ils peuvent être encore plus efficaces que la version traditionnelle. Si une application ne met pas en place de défenses contre les menaces automatisées (force brute, scripts ou bots) ou bourrage de crédents, l’application peut être utilisée comme oracle de mot de passe pour déterminer si les identifiants sont valides et obtenir un accès non autorisé. 
-**Scénario #2 :** La plupart des attaques d’authentification réussies surviennent en raison de l’utilisation continue des mots de passe comme seul facteur d’authentification. Une fois considérées comme les meilleures pratiques, la rotation des mots de passe et les exigences de complexité encouragent les utilisateurs à réutiliser les mots de passe et à utiliser des mots de passe faibles. Il est recommandé aux organisations d’arrêter ces pratiques conformément au NIST 800-63 et d’imposer l’utilisation de l’authentification multifacteur sur tous les systèmes importants. 
-**Scénario #3 :** Les délais d’expiration des sessions d’application ne sont pas correctement implémentés. Un utilisateur utilise un ordinateur public pour accéder à une application et au lieu de sélectionner « déconnexion », il ferme simplement l’onglet du navigateur et s’en va. Un autre exemple est si une session de connexion unique (SSO) ne peut pas être fermée par un seul déconnexion (SLO). C’est-à-dire qu’une seule connexion vous connecte, par exemple, à votre lecteur de messagerie, à votre système de documents et à votre système de chat. Mais la déconnexion ne se produit qu’au système actuel. Si un attaquant utilise le même navigateur après que la victime pense s’être déconnectée avec succès, mais avec l’utilisateur toujours authentifié sur certaines applications, il peut alors accéder au compte de la victime. Le même problème peut survenir dans les bureaux et les entreprises lorsqu’une application sensible n’a pas été correctement fermée et qu’un collègue a un accès (temporaire) à l’ordinateur déverrouillé. 
-Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A07_2025-Authentication_Failures/</t>
-  </si>
-  <si>
-    <t>## Tableau des scores
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWEs cartographiées 
-   &lt;/td&gt;
-   &lt;td&gt;Taux d’incidence maximal
-   &lt;/td&gt;
-   &lt;td&gt;Taux moyen d’incidence
-   &lt;/td&gt;
-   &lt;td&gt;Couverture maximale
-   &lt;/td&gt;
-   &lt;td&gt;Couverture moyenne
-   &lt;/td&gt;
-   &lt;td&gt;Exploit pondéré moyen
-   &lt;/td&gt;
-   &lt;td&gt;Impact pondéré moyen
-   &lt;/td&gt;
-   &lt;td&gt;Occurrences totales
-   &lt;/td&gt;
-   &lt;td&gt;Total des CVE
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
    &lt;td&gt;14
    &lt;/td&gt;
    &lt;td&gt;8,98 % 
@@ -2604,90 +2541,6 @@
 **Scénario #3 Utilisation d’un paquet à partir d’une source non fiable :** Un développeur a du mal à trouver la version mise à jour d’un paquet qu’il recherche, il la télécharge donc non pas depuis le gestionnaire de paquets fiable classique, mais depuis un site web en ligne. Le paquet n’est pas signé, et il n’y a donc aucune possibilité d’en garantir l’intégrité. Le paquet inclut du code malveillant. 
 **Scénario #4 Désérialisation insécurisée :** Une application React appelle un ensemble de microservices Spring Boot. En tant que programmeurs fonctionnels, ils ont essayé de s’assurer que leur code reste immuable. La solution qu’ils ont trouvée est de sérialiser l’état utilisateur et de le transmettre à chaque requête. Un attaquant remarque la signature d’objet Java « rO0 » (en base64) et utilise le [Java Deserialization Scanner](https://github.com/federicodotta/Java-Deserialization-Scanner) pour obtenir une exécution de code à distance sur le serveur d’applications. 
 Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A08_2025-Software_or_Data_Integrity_Failures/</t>
-  </si>
-  <si>
-    <t>## Tableau des scores
-&lt;table&gt;
-  &lt;tr&gt;
-   &lt;td&gt;CWEs cartographiées
-   &lt;/td&gt;
-   &lt;td&gt;Taux d’incidence maximal
-   &lt;/td&gt;
-   &lt;td&gt;Taux moyen d’incidence
-   &lt;/td&gt;
-   &lt;td&gt;Couverture maximale
-   &lt;/td&gt;
-   &lt;td&gt;Couverture moyenne
-   &lt;/td&gt;
-   &lt;td&gt;Exploit pondéré moyen
-   &lt;/td&gt;
-   &lt;td&gt;Impact pondéré moyen
-   &lt;/td&gt;
-   &lt;td&gt;Occurrences totales
-   &lt;/td&gt;
-   &lt;td&gt;Total des CVE
-   &lt;/td&gt;
-  &lt;/tr&gt;
-  &lt;tr&gt;
-   &lt;td&gt;6
-   &lt;/td&gt;
-   &lt;td&gt;9,56 % 
-   &lt;/td&gt;
-   &lt;td&gt;5,72 % 
-   &lt;/td&gt;
-   &lt;td&gt;65,42 % 
-   &lt;/td&gt;
-   &lt;td&gt;27,47 % 
-   &lt;/td&gt;
-   &lt;td&gt;8.17
-   &lt;/td&gt;
-   &lt;td&gt;5.23
-   &lt;/td&gt;
-   &lt;td&gt;215 248
-   &lt;/td&gt;
-   &lt;td&gt;11
-   &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;
-## Comment prévenir
-Il devrait y avoir un processus de gestion des correctifs pour : 
-* Générer et gérer centralisément la liste des documents logiciels (SBOM) de l’ensemble de votre logiciel. 
-* Suivre non seulement vos dépendances directes, mais aussi leurs dépendances (transitives), et ainsi de suite. 
-* Réduire la surface d’attaque en supprimant les dépendances inutilisées, les fonctionnalités, les composants, les fichiers et la documentation inutiles. 
-* Inventorier continuellement les versions des composants côté client et côté serveur (par exemple, frameworks, bibliothèques) et leurs dépendances à l’aide d’outils comme OWASP Dependency Track, OWASP Dependency Check, retire.js, etc. 
-* Surveillez en continu des sources telles que Common Vulnerability and Exposures (CVE), National Vulnerability Database (NVD) et [Open Source Vulnerabilities (OSV)](https://osv.dev/) pour les vulnérabilités des composants que vous utilisez. Utilisez l’analyse de composition logicielle, la chaîne d’approvisionnement logicielle ou des outils SBOM axés sur la sécurité pour automatiser le processus. Abonnez-vous aux alertes concernant les vulnérabilités de sécurité liées aux composants que vous utilisez. 
-* N’obtenir les composants que de sources officielles (fiables) via des liens sécurisés. Privilégier les paquets signés pour réduire le risque d’inclure un composant modifié et malveillant (voir [A08:2025 - Défaillances d’intégrité logicielle et des données](https://owasp.org/Top10/2025/A08_2025-Software_or_Data_Integrity_Failures/)). 
-* Choisissez délibérément la version d’une dépendance que vous utilisez et ne mettez à jour que lorsqu’il y a un besoin. 
-* Surveillez les bibliothèques et composants non maintenus ou qui ne créent pas de correctifs de sécurité pour les versions précédentes. Si le patch n’est pas possible, envisagez de migrer vers une alternative. Si cela n’est pas possible, envisagez de déployer un correctif virtuel pour surveiller, détecter ou protéger contre le problème découvert. 
-* Mettez régulièrement à jour votre CI/CD, IDE et tout autre outil de développement
-* Éviter de déployer des mises à jour simultanément sur tous les systèmes. Utiliser des déploiements par étapes ou des déploiements canari pour limiter l’exposition au cas où un fournisseur de confiance serait compromis. 
-Il devrait y avoir un processus de gestion des changements ou un système de suivi pour suivre les modifications sur :
-* Paramètres CI/CD (tous les outils de compilation et pipelines)
-* Dépôts de code
-* Zones de bac à sable
-* IDE développeurs
-* Outils SBOM et artefacts créés
-* Systèmes de journalisation et journaux
-* Intégrations tierces, telles que le SaaS
-* Dépôts d’artefacts
-* Registres de conteneurs
-Renforcez les systèmes suivants, ce qui inclut la mise en service de la MFA et la fermeture de l’IAM : 
-* Votre dépôt de code (ce qui inclut de ne pas vérifier les secrets, protéger les branches, sauvegarder)
-* Stations de travail développeurs (correctifs réguliers, MFA, surveillance, et plus encore)
-* Votre serveur de compilation &amp; CI/CD (séparation des fonctions, contrôle d’accès, compilations signées, secrets à portée d’environnement, journaux inviolables, plus encore)
-* Vos artefacts (assurez l’intégrité via la provenance, la signature et l’horodatage, promouvez les artefacts plutôt que les reconstruisez pour chaque environnement, assurez-vous que les builds restent immuables)
-* Infrastructure en tant que code (géré comme tout le code, y compris l’utilisation des PR et le contrôle de versions)
-Chaque organisation doit s’assurer d’un plan continu pour la surveillance, le tri et l’application des mises à jour ou modifications de configuration tout au long de la durée de vie de l’application ou du portefeuille.
-## Exemples de scénarios d’attaque
-**Scénario #1 :** Un fournisseur de confiance est compromis par des logiciels malveillants, ce qui entraîne la compromission de vos systèmes informatiques lors de la mise à jour. L’exemple le plus célèbre est probablement : 
-* Le compromis SolarWinds de 2019 qui a conduit à la compromission de ~18 000 organisations. [https://www.npr.org/2021/04/16/985439655/a-worst-nightmare-cyberattack-the-untold-story-of-the-solarwinds-hack] (https://www.npr.org/2021/04/16/985439655/a-worst-nightmare-cyberattack-the-untold-story-of-the-solarwinds-hack)
-**Scénario #2 :** Un fournisseur de confiance est compromis au point de ne se comporter de manière malveillante que dans une condition spécifique. 
-* Le vol de 1,5 milliard de dollars par Bybit en 2025 a été causé par [une attaque de chaîne d’approvisionnement dans un logiciel de portefeuille](https://www.sygnia.co/blog/sygnia-investigation-bybit-hack/) qui ne s’est exécutée que lorsque le portefeuille cible était utilisé. 
-**Scénario #3 :** L’attaque de chaîne d’approvisionnement ['Shai-Hulud'](https://www.cisa.gov/news-events/alerts/2025/09/23/widespread-supply-chain-compromise-impacting-npm-ecosystem) en 2025 a été le premier ver npm auto-propagant réussi. Les attaques ont semé des versions malveillantes de paquets populaires, qui utilisaient un script post-installation pour récolter et exfiltrer des données sensibles vers des dépôts publics GitHub. Le malware détectait également les jetons npm dans l’environnement victime et les utilisait automatiquement pour diffuser des versions malveillantes de tout package accessible. Le ver a atteint plus de 500 versions de paquets avant d’être perturbé par npm. Cette attaque de chaîne d’approvisionnement était avancée, se propageait rapidement et causait des dommages, et en ciblant les machines développeurs, elle a démontré que les développeurs eux-mêmes sont désormais des cibles principales pour les attaques de la chaîne d’approvisionnement. 
-**Scénario #4 :** Les composants fonctionnent généralement avec les mêmes privilèges que l’application elle-même, donc des défauts dans n’importe quel composant peuvent avoir un impact sérieux. Ces défauts peuvent être accidentels (par exemple, une erreur de codage) ou intentionnels (par exemple, une porte dérobée dans un composant). Voici quelques exemples de vulnérabilités exploitables de composants découverts : 
-* CVE-2017-5638, une vulnérabilité d’exécution de code à distance Struts 2 qui permet l’exécution de code arbitraire sur le serveur, a été tenue responsable de violations importantes. 
-* CVE-2021-44228 (« Log4Shell »), une vulnérabilité zero-day d’exécution de code à distance Apache Log4j, a été tenue responsable de campagnes de ransomware, de cryptominage et d’autres attaques. 
-Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A03_2025-Software_Supply_Chain_Failures/</t>
   </si>
   <si>
     <t>## Tableau des scores
@@ -5803,29 +5656,6 @@
 Para obtener más información sobre las referencias y la lista de CWE asociadas: https://top10.owasp.org/2025/es/A05_2025-Injection/</t>
   </si>
   <si>
-    <t>## جدول امتیازدهی
-| تعداد CWEهای نگاشت‌شده | بیشترین نرخ بروز | میانگین نرخ بروز | بیشترین پوشش | میانگین پوشش | میانگین امتیاز بهره‌برداری | میانگین امتیاز تأثیر | تعداد کل رخدادها |
-|-----------------------|-----------------|-----------------|---------------|---------------|----------------------------|----------------------|----------------|
-| 37                    | 13.77%          | 3.08%           | 100.00%       | 42.93%        | 7.15                       | 4.32                 | 1,404,249      |
-## چگونه جلوگیری کنیم
-- از API امن استفاده کنید یا از ORMها بهره ببرید تا داده از دستورات جدا شود.  
-- اگر جداسازی ممکن نیست:
-  - اعتبارسنجی مثبت سمت سرور انجام دهید  
-  - برای کوئری‌های باقی‌مانده، کاراکترهای ویژه را با syntax مخصوص interpreter escape کنید  
-  - توجه داشته باشید که ساختار SQL مانند table/column name را نمی‌توان escape کرد  
-⚠️ هشدار: این تکنیک‌ها پیچیده هستند و در صورت تغییرات جزئی سیستم خطاپذیر می‌شوند.
-## نمونه سناریوهای حمله
-**سناریو #1:**
-```java
-String query = "SELECT * FROM accounts WHERE custID='" + request.getParameter("id") + "'";
-سناریو #2:
-Query HQLQuery = session.createQuery("FROM accounts WHERE custID='" + request.getParameter("id") + "'");
-در هر دو، مهاجم مقدار id را به ' UNION SLEEP(10);-- تغییر می‌دهد:
-http://example.com/app/accountView?id=' UNION SELECT SLEEP(10);--
-این باعث بازگرداندن همه رکوردها می‌شود. حملات خطرناک‌تر می‌توانند داده‌ها را تغییر دهند، حذف کنند یا stored procedure اجرا کنند.
-برای اطلاعات بیشتر درباره منابع و فهرست CWEهای نگاشت‌شده: https://top10.owasp.org/2025/fa/A05_2025-Injection/</t>
-  </si>
-  <si>
     <t>## Tabella dei punteggi.
 &lt;table&gt;
   &lt;tr&gt;
@@ -8648,6 +8478,177 @@
 **场景 #2：** 错误处理不当或数据库错误把完整系统错误暴露给用户，导致敏感数据泄露。攻击者持续制造错误，以利用敏感系统信息构造更好的 SQL 注入攻击。用户错误消息中的敏感数据成为侦察信息。
 **场景 #3：** 攻击者通过网络中断打断多步骤交易，可能导致金融交易状态损坏。假设交易顺序为：扣减用户账户、增加目标账户余额、记录交易。如果系统在中途出错时没有正确回滚整个交易（故障关闭），攻击者可能耗尽用户账户，或可能利用竞争条件多次向目标账户转账。
 有關參考資料及已對應 CWE 清單的更多資訊： https://top10.owasp.org/2025/zh-Hant/A10_2025-Mishandling_of_Exceptional_Conditions/</t>
+  </si>
+  <si>
+    <t>## جدول امتیازدهی
+| تعداد CWEهای نگاشت‌شده | بیشترین نرخ بروز | میانگین نرخ بروز | بیشترین پوشش | میانگین پوشش | میانگین امتیاز بهره‌برداری | میانگین امتیاز تأثیر | تعداد کل رخدادها |
+|-----------------------|-----------------|-----------------|---------------|---------------|----------------------------|----------------------|----------------|
+| 37                    | 13.77%          | 3.08%           | 100.00%       | 42.93%        | 7.15                       | 4.32                 | 1,404,249      |
+## چگونه جلوگیری کنیم
+- از API امن استفاده کنید یا از ORMها بهره ببرید تا داده از دستورات جدا شود.  
+- اگر جداسازی ممکن نیست:
+  - اعتبارسنجی مثبت سمت سرور انجام دهید  
+  - برای کوئری‌های باقی‌مانده، کاراکترهای ویژه را با syntax مخصوص interpreter escape کنید  
+  - توجه داشته باشید که ساختار SQL مانند table/column name را نمی‌توان escape کرد  
+⚠️ هشدار: این تکنیک‌ها پیچیده هستند و در صورت تغییرات جزئی سیستم خطاپذیر می‌شوند.
+## نمونه سناریوهای حمله
+**سناریو #1:**
+```java
+String query = "SELECT * FROM accounts WHERE custID='" + request.getParameter("id") + "'";
+```
+سناریو #2:
+Query HQLQuery = session.createQuery("FROM accounts WHERE custID='" + request.getParameter("id") + "'");
+در هر دو، مهاجم مقدار id را به ' UNION SLEEP(10);-- تغییر می‌دهد:
+http://example.com/app/accountView?id=' UNION SELECT SLEEP(10);--
+این باعث بازگرداندن همه رکوردها می‌شود. حملات خطرناک‌تر می‌توانند داده‌ها را تغییر دهند، حذف کنند یا stored procedure اجرا کنند.
+برای اطلاعات بیشتر درباره منابع و فهرست CWEهای نگاشت‌شده: https://top10.owasp.org/2025/fa/A05_2025-Injection/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;6
+   &lt;/td&gt;
+   &lt;td&gt;9,56 % 
+   &lt;/td&gt;
+   &lt;td&gt;5,72 % 
+   &lt;/td&gt;
+   &lt;td&gt;65,42 % 
+   &lt;/td&gt;
+   &lt;td&gt;27,47 % 
+   &lt;/td&gt;
+   &lt;td&gt;8.17
+   &lt;/td&gt;
+   &lt;td&gt;5.23
+   &lt;/td&gt;
+   &lt;td&gt;215 248
+   &lt;/td&gt;
+   &lt;td&gt;11
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+Il devrait y avoir un processus de gestion des correctifs pour : 
+* Générer et gérer centralisément la liste des documents logiciels (SBOM) de l’ensemble de votre logiciel. 
+* Suivre non seulement vos dépendances directes, mais aussi leurs dépendances (transitives), et ainsi de suite. 
+* Réduire la surface d’attaque en supprimant les dépendances inutilisées, les fonctionnalités, les composants, les fichiers et la documentation inutiles. 
+* Inventorier continuellement les versions des composants côté client et côté serveur (par exemple, frameworks, bibliothèques) et leurs dépendances à l’aide d’outils comme OWASP Dependency Track, OWASP Dependency Check, retire.js, etc. 
+* Surveillez en continu des sources telles que Common Vulnerability and Exposures (CVE), National Vulnerability Database (NVD) et [Open Source Vulnerabilities (OSV)](https://osv.dev/) pour les vulnérabilités des composants que vous utilisez. Utilisez l’analyse de composition logicielle, la chaîne d’approvisionnement logicielle ou des outils SBOM axés sur la sécurité pour automatiser le processus. Abonnez-vous aux alertes concernant les vulnérabilités de sécurité liées aux composants que vous utilisez. 
+* N’obtenir les composants que de sources officielles (fiables) via des liens sécurisés. Privilégier les paquets signés pour réduire le risque d’inclure un composant modifié et malveillant (voir [A08:2025 - Défaillances d’intégrité logicielle et des données](https://owasp.org/Top10/2025/A08_2025-Software_or_Data_Integrity_Failures/)). 
+* Choisissez délibérément la version d’une dépendance que vous utilisez et ne mettez à jour que lorsqu’il y a un besoin. 
+* Surveillez les bibliothèques et composants non maintenus ou qui ne créent pas de correctifs de sécurité pour les versions précédentes. Si le patch n’est pas possible, envisagez de migrer vers une alternative. Si cela n’est pas possible, envisagez de déployer un correctif virtuel pour surveiller, détecter ou protéger contre le problème découvert. 
+* Mettez régulièrement à jour votre CI/CD, IDE et tout autre outil de développement
+* Éviter de déployer des mises à jour simultanément sur tous les systèmes. Utiliser des déploiements par étapes ou des déploiements canari pour limiter l’exposition au cas où un fournisseur de confiance serait compromis. 
+Il devrait y avoir un processus de gestion des changements ou un système de suivi pour suivre les modifications sur :
+* Paramètres CI/CD (tous les outils de compilation et pipelines)
+* Dépôts de code
+* Zones de bac à sable
+* IDE développeurs
+* Outils SBOM et artefacts créés
+* Systèmes de journalisation et journaux
+* Intégrations tierces, telles que le SaaS
+* Dépôts d’artefacts
+* Registres de conteneurs
+Renforcez les systèmes suivants, ce qui inclut la mise en service de la MFA et la fermeture de l’IAM : 
+* Votre dépôt de code (ce qui inclut de ne pas vérifier les secrets, protéger les branches, sauvegarder)
+* Stations de travail développeurs (correctifs réguliers, MFA, surveillance, et plus encore)
+* Votre serveur de compilation &amp; CI/CD (séparation des fonctions, contrôle d’accès, compilations signées, secrets à portée d’environnement, journaux inviolables, plus encore)
+* Vos artefacts (assurez l’intégrité via la provenance, la signature et l’horodatage, promouvez les artefacts plutôt que les reconstruisez pour chaque environnement, assurez-vous que les builds restent immuables)
+* Infrastructure en tant que code (géré comme tout le code, y compris l’utilisation des PR et le contrôle de versions)
+Chaque organisation doit s’assurer d’un plan continu pour la surveillance, le tri et l’application des mises à jour ou modifications de configuration tout au long de la durée de vie de l’application ou du portefeuille.
+## Exemples de scénarios d’attaque
+**Scénario #1 :** Un fournisseur de confiance est compromis par des logiciels malveillants, ce qui entraîne la compromission de vos systèmes informatiques lors de la mise à jour. L’exemple le plus célèbre est probablement : 
+* Le compromis SolarWinds de 2019 qui a conduit à la compromission de ~18 000 organisations. [https://www.npr.org/2021/04/16/985439655/a-worst-nightmare-cyberattack-the-untold-story-of-the-solarwinds-hack](https://www.npr.org/2021/04/16/985439655/a-worst-nightmare-cyberattack-the-untold-story-of-the-solarwinds-hack)
+**Scénario #2 :** Un fournisseur de confiance est compromis au point de ne se comporter de manière malveillante que dans une condition spécifique. 
+* Le vol de 1,5 milliard de dollars par Bybit en 2025 a été causé par [une attaque de chaîne d’approvisionnement dans un logiciel de portefeuille](https://www.sygnia.co/blog/sygnia-investigation-bybit-hack/) qui ne s’est exécutée que lorsque le portefeuille cible était utilisé. 
+**Scénario #3 :** L’attaque de chaîne d’approvisionnement ['Shai-Hulud'](https://www.cisa.gov/news-events/alerts/2025/09/23/widespread-supply-chain-compromise-impacting-npm-ecosystem) en 2025 a été le premier ver npm auto-propagant réussi. Les attaques ont semé des versions malveillantes de paquets populaires, qui utilisaient un script post-installation pour récolter et exfiltrer des données sensibles vers des dépôts publics GitHub. Le malware détectait également les jetons npm dans l’environnement victime et les utilisait automatiquement pour diffuser des versions malveillantes de tout package accessible. Le ver a atteint plus de 500 versions de paquets avant d’être perturbé par npm. Cette attaque de chaîne d’approvisionnement était avancée, se propageait rapidement et causait des dommages, et en ciblant les machines développeurs, elle a démontré que les développeurs eux-mêmes sont désormais des cibles principales pour les attaques de la chaîne d’approvisionnement. 
+**Scénario #4 :** Les composants fonctionnent généralement avec les mêmes privilèges que l’application elle-même, donc des défauts dans n’importe quel composant peuvent avoir un impact sérieux. Ces défauts peuvent être accidentels (par exemple, une erreur de codage) ou intentionnels (par exemple, une porte dérobée dans un composant). Voici quelques exemples de vulnérabilités exploitables de composants découverts : 
+* CVE-2017-5638, une vulnérabilité d’exécution de code à distance Struts 2 qui permet l’exécution de code arbitraire sur le serveur, a été tenue responsable de violations importantes. 
+* CVE-2021-44228 (« Log4Shell »), une vulnérabilité zero-day d’exécution de code à distance Apache Log4j, a été tenue responsable de campagnes de ransomware, de cryptominage et d’autres attaques. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A03_2025-Software_Supply_Chain_Failures/</t>
+  </si>
+  <si>
+    <t>## Tableau des scores
+&lt;table&gt;
+  &lt;tr&gt;
+   &lt;td&gt;CWEs cartographiées 
+   &lt;/td&gt;
+   &lt;td&gt;Taux d’incidence maximal
+   &lt;/td&gt;
+   &lt;td&gt;Taux moyen d’incidence
+   &lt;/td&gt;
+   &lt;td&gt;Couverture maximale
+   &lt;/td&gt;
+   &lt;td&gt;Couverture moyenne
+   &lt;/td&gt;
+   &lt;td&gt;Exploit pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Impact pondéré moyen
+   &lt;/td&gt;
+   &lt;td&gt;Occurrences totales
+   &lt;/td&gt;
+   &lt;td&gt;Total des CVE
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td&gt;36
+   &lt;/td&gt;
+   &lt;td&gt;15,80 % 
+   &lt;/td&gt;
+   &lt;td&gt;2,92 % 
+   &lt;/td&gt;
+   &lt;td&gt;100,00 % 
+   &lt;/td&gt;
+   &lt;td&gt;37,14 % 
+   &lt;/td&gt;
+   &lt;td&gt;7,69
+   &lt;/td&gt;
+   &lt;td&gt;4,44
+   &lt;/td&gt;
+   &lt;td&gt;1 120 673
+   &lt;/td&gt;
+   &lt;td&gt;7 147
+   &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;
+## Comment prévenir
+* Lorsque possible, implémenter et faire respecter l’utilisation de l’authentification multifactorielle pour prévenir le bourrage automatisé des identifiants, la force brute et les attaques de réutilisation de crédents volées. 
+* Lorsque possible, encourager et activer l’utilisation de gestionnaires de mots de passe pour aider les utilisateurs à faire de meilleurs choix. 
+* Ne pas livrer ni déployer avec des identifiants par défaut, en particulier pour les utilisateurs administrateurs. 
+* Mettre en place des vérifications de mots de passe faibles, comme tester de nouveaux mots de passe ou modifiés dans la liste des 10 000 pires mots de passe. 
+* Lors de la création d’un nouveau compte et des changements de mot de passe, validez contre les listes d’identifiants connus pour violation (par exemple : utiliser [haveibeenpwned.com](https://haveibeenpwned.com)). 
+* Aligner les politiques de longueur, de complexité et de rotation des mots de passe avec les directives du [National Institute of Standards and Technology (NIST) 800-63b dans la section 5.1.1](https://pages.nist.gov/800-63-3/sp800-63b.html#:~:text=5.1.1%20Memorized%20Secrets) pour les secrets mémorisés ou d’autres politiques modernes fondées sur des mots de passe fondées sur des preuves. 
+* Ne forcez pas les êtres humains à faire tourner les mots de passe sauf si vous suspectez une faille. Si vous soupçonnez une fuite, forcez immédiatement la réinitialisation du mot de passe.  
+* S’assurer que l’enregistrement, la récupération des identifiants et les voies API sont renforcés contre les attaques d’énumération de comptes en utilisant les mêmes messages pour tous les résultats (« Nom d’utilisateur ou mot de passe invalides. »). 
+* Limiter ou retarder de plus en plus les tentatives de connexion ratées, mais veillez à ne pas créer un scénario de déni de service. Consignez toutes les défaillances et alertez les administrateurs lorsque des attaques de type « credentialsal stuffing, de force brute » ou d’autres attaques sont détectées ou suspectées. 
+* Utiliser un gestionnaire de session intégré sécurisé côté serveur qui génère un nouvel ID de session aléatoire avec une forte entropie après la connexion. Les identifiants de session ne doivent pas être dans l’URL, être stockés de manière sécurisée dans un cookie sécurisé, et invalidés après déconnexion, inactivité et délais absolus.  
+* Idéalement, utiliser un système préfabriqué et bien fiable pour gérer l’authentification, l’identité et la gestion des sessions. Transférez ce risque autant que possible en achetant et en utilisant un système renforcé et bien testé. 
+* Vérifier l’utilisation prévue des identifiants fournis, par exemple pour les JWT, valider les affirmations « aud », « iss » et les périmètres
+## Exemples de scénarios d’attaque
+**Scénario #1 :** Le remplissage de crédentiaux, l’utilisation de listes de combinaisons de noms d’utilisateur et de mots de passe connus, est désormais une attaque très courante. Plus récemment, les attaquants ont été observés « incrémentant » ou ajustant autrement les mots de passe, en fonction du comportement humain courant. Par exemple, changer « Winter2025 » en « Hiver 2026 », ou « ILoveMyDog6 » en « ILoveMyDog7 » ou « ILoveMyDog5 ». Cet ajustement des tentatives de mot de passe est appelé attaque hybride de remplissage de crédibles ou attaque par pulvérisation de mots de passe, et ils peuvent être encore plus efficaces que la version traditionnelle. Si une application ne met pas en place de défenses contre les menaces automatisées (force brute, scripts ou bots) ou bourrage de crédents, l’application peut être utilisée comme oracle de mot de passe pour déterminer si les identifiants sont valides et obtenir un accès non autorisé. 
+**Scénario #2 :** La plupart des attaques d’authentification réussies surviennent en raison de l’utilisation continue des mots de passe comme seul facteur d’authentification. Une fois considérées comme les meilleures pratiques, la rotation des mots de passe et les exigences de complexité encouragent les utilisateurs à réutiliser les mots de passe et à utiliser des mots de passe faibles. Il est recommandé aux organisations d’arrêter ces pratiques conformément au NIST 800-63 et d’imposer l’utilisation de l’authentification multifacteur sur tous les systèmes importants. 
+**Scénario #3 :** Les délais d’expiration des sessions d’application ne sont pas correctement implémentés. Un utilisateur utilise un ordinateur public pour accéder à une application et au lieu de sélectionner « déconnexion », il ferme simplement l’onglet du navigateur et s’en va. Un autre exemple est si une session de connexion unique (SSO) ne peut pas être fermée par un seul déconnexion (SLO). C’est-à-dire qu’une seule connexion vous connecte, par exemple, à votre lecteur de messagerie, à votre système de documents et à votre système de chat. Mais la déconnexion ne se produit qu’au système actuel. Si un attaquant utilise le même navigateur après que la victime pense s’être déconnectée avec succès, mais avec l’utilisateur toujours authentifié sur certaines applications, il peut alors accéder au compte de la victime. Le même problème peut survenir dans les bureaux et les entreprises lorsqu’une application sensible n’a pas été correctement fermée et qu’un collègue a un accès (temporaire) à l’ordinateur déverrouillé. 
+Pour plus d’informations sur les références et la liste des CWE cartographiées : https://top10.owasp.org/2025/A07_2025-Authentication_Failures/</t>
   </si>
 </sst>
 </file>
@@ -10441,7 +10442,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -10639,7 +10640,7 @@
         <v>50</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -10694,7 +10695,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>10</v>
@@ -10801,7 +10802,7 @@
         <v>62</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>63</v>
@@ -10828,7 +10829,7 @@
         <v>68</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>69</v>
@@ -10837,7 +10838,7 @@
         <v>70</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>71</v>
@@ -10846,7 +10847,7 @@
         <v>72</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>73</v>
@@ -10855,7 +10856,7 @@
         <v>74</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>63</v>
@@ -10864,7 +10865,7 @@
         <v>75</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="X2" s="5" t="s">
         <v>76</v>
@@ -10873,7 +10874,7 @@
         <v>77</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AA2" s="5" t="s">
         <v>78</v>
@@ -10882,7 +10883,7 @@
         <v>79</v>
       </c>
       <c r="AC2" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AD2" s="5" t="s">
         <v>80</v>
@@ -10891,7 +10892,7 @@
         <v>81</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG2" s="5" t="s">
         <v>82</v>
@@ -10900,7 +10901,7 @@
         <v>83</v>
       </c>
       <c r="AI2" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
@@ -10908,7 +10909,7 @@
         <v>84</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>85</v>
@@ -10917,7 +10918,7 @@
         <v>86</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>87</v>
@@ -10926,7 +10927,7 @@
         <v>259</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>88</v>
@@ -10935,16 +10936,16 @@
         <v>89</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>90</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>91</v>
@@ -10953,7 +10954,7 @@
         <v>92</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="R3" s="8" t="s">
         <v>93</v>
@@ -10962,7 +10963,7 @@
         <v>94</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="U3" s="8" t="s">
         <v>85</v>
@@ -10971,7 +10972,7 @@
         <v>95</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="X3" s="8" t="s">
         <v>96</v>
@@ -10980,7 +10981,7 @@
         <v>97</v>
       </c>
       <c r="Z3" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AA3" s="8" t="s">
         <v>98</v>
@@ -10989,7 +10990,7 @@
         <v>99</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AD3" s="8" t="s">
         <v>100</v>
@@ -10998,7 +10999,7 @@
         <v>101</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG3" s="8" t="s">
         <v>102</v>
@@ -11007,7 +11008,7 @@
         <v>103</v>
       </c>
       <c r="AI3" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
@@ -11015,7 +11016,7 @@
         <v>104</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>105</v>
@@ -11027,13 +11028,13 @@
         <v>107</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>260</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>271</v>
+        <v>396</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>108</v>
@@ -11042,7 +11043,7 @@
         <v>109</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>110</v>
@@ -11051,7 +11052,7 @@
         <v>111</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>112</v>
@@ -11060,7 +11061,7 @@
         <v>113</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>114</v>
@@ -11069,7 +11070,7 @@
         <v>115</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>105</v>
@@ -11078,7 +11079,7 @@
         <v>116</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="X4" s="5" t="s">
         <v>117</v>
@@ -11087,7 +11088,7 @@
         <v>118</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AA4" s="5" t="s">
         <v>105</v>
@@ -11105,7 +11106,7 @@
         <v>121</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG4" s="5" t="s">
         <v>122</v>
@@ -11114,7 +11115,7 @@
         <v>123</v>
       </c>
       <c r="AI4" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
@@ -11122,7 +11123,7 @@
         <v>124</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>125</v>
@@ -11149,7 +11150,7 @@
         <v>130</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>131</v>
@@ -11158,7 +11159,7 @@
         <v>132</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>133</v>
@@ -11167,7 +11168,7 @@
         <v>134</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="R5" s="8" t="s">
         <v>135</v>
@@ -11176,7 +11177,7 @@
         <v>136</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="U5" s="8" t="s">
         <v>125</v>
@@ -11185,7 +11186,7 @@
         <v>137</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="X5" s="8" t="s">
         <v>138</v>
@@ -11194,7 +11195,7 @@
         <v>139</v>
       </c>
       <c r="Z5" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AA5" s="8" t="s">
         <v>140</v>
@@ -11203,7 +11204,7 @@
         <v>141</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AD5" s="8" t="s">
         <v>142</v>
@@ -11212,7 +11213,7 @@
         <v>143</v>
       </c>
       <c r="AF5" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AG5" s="8" t="s">
         <v>144</v>
@@ -11221,7 +11222,7 @@
         <v>145</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
@@ -11229,7 +11230,7 @@
         <v>146</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>147</v>
@@ -11256,7 +11257,7 @@
         <v>151</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>147</v>
@@ -11265,7 +11266,7 @@
         <v>152</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>153</v>
@@ -11274,7 +11275,7 @@
         <v>154</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="R6" s="5" t="s">
         <v>155</v>
@@ -11283,7 +11284,7 @@
         <v>156</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>347</v>
+        <v>395</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>147</v>
@@ -11292,7 +11293,7 @@
         <v>157</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="X6" s="5" t="s">
         <v>158</v>
@@ -11301,7 +11302,7 @@
         <v>159</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AA6" s="5" t="s">
         <v>160</v>
@@ -11310,7 +11311,7 @@
         <v>161</v>
       </c>
       <c r="AC6" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AD6" s="5" t="s">
         <v>162</v>
@@ -11319,7 +11320,7 @@
         <v>163</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AG6" s="5" t="s">
         <v>164</v>
@@ -11328,7 +11329,7 @@
         <v>165</v>
       </c>
       <c r="AI6" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
@@ -11336,7 +11337,7 @@
         <v>166</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>167</v>
@@ -11354,7 +11355,7 @@
         <v>265</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>171</v>
@@ -11363,7 +11364,7 @@
         <v>172</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>173</v>
@@ -11372,7 +11373,7 @@
         <v>174</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>175</v>
@@ -11381,7 +11382,7 @@
         <v>176</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="R7" s="8" t="s">
         <v>167</v>
@@ -11390,7 +11391,7 @@
         <v>177</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="U7" s="8" t="s">
         <v>167</v>
@@ -11399,7 +11400,7 @@
         <v>178</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="X7" s="8" t="s">
         <v>179</v>
@@ -11408,7 +11409,7 @@
         <v>180</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AA7" s="8" t="s">
         <v>181</v>
@@ -11417,7 +11418,7 @@
         <v>182</v>
       </c>
       <c r="AC7" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AD7" s="8" t="s">
         <v>183</v>
@@ -11426,7 +11427,7 @@
         <v>184</v>
       </c>
       <c r="AF7" s="8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="AG7" s="8" t="s">
         <v>185</v>
@@ -11435,7 +11436,7 @@
         <v>186</v>
       </c>
       <c r="AI7" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
@@ -11443,7 +11444,7 @@
         <v>187</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>188</v>
@@ -11461,7 +11462,7 @@
         <v>263</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>192</v>
@@ -11470,7 +11471,7 @@
         <v>193</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>194</v>
@@ -11479,7 +11480,7 @@
         <v>195</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>196</v>
@@ -11488,7 +11489,7 @@
         <v>197</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="R8" s="5" t="s">
         <v>188</v>
@@ -11497,7 +11498,7 @@
         <v>198</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>188</v>
@@ -11506,16 +11507,16 @@
         <v>199</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="X8" s="5" t="s">
         <v>200</v>
       </c>
       <c r="Y8" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Z8" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AA8" s="5" t="s">
         <v>201</v>
@@ -11524,7 +11525,7 @@
         <v>202</v>
       </c>
       <c r="AC8" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AD8" s="5" t="s">
         <v>203</v>
@@ -11533,7 +11534,7 @@
         <v>204</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG8" s="5" t="s">
         <v>205</v>
@@ -11542,7 +11543,7 @@
         <v>206</v>
       </c>
       <c r="AI8" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
@@ -11550,7 +11551,7 @@
         <v>207</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>208</v>
@@ -11562,13 +11563,13 @@
         <v>210</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>264</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>211</v>
@@ -11577,7 +11578,7 @@
         <v>212</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>213</v>
@@ -11586,7 +11587,7 @@
         <v>214</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>215</v>
@@ -11595,7 +11596,7 @@
         <v>216</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="R9" s="8" t="s">
         <v>208</v>
@@ -11604,7 +11605,7 @@
         <v>217</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="U9" s="8" t="s">
         <v>208</v>
@@ -11613,7 +11614,7 @@
         <v>218</v>
       </c>
       <c r="W9" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="X9" s="8" t="s">
         <v>219</v>
@@ -11622,7 +11623,7 @@
         <v>220</v>
       </c>
       <c r="Z9" s="8" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AA9" s="8" t="s">
         <v>221</v>
@@ -11631,7 +11632,7 @@
         <v>222</v>
       </c>
       <c r="AC9" s="8" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AD9" s="8" t="s">
         <v>223</v>
@@ -11640,7 +11641,7 @@
         <v>224</v>
       </c>
       <c r="AF9" s="8" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AG9" s="8" t="s">
         <v>225</v>
@@ -11649,7 +11650,7 @@
         <v>226</v>
       </c>
       <c r="AI9" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
@@ -11657,52 +11658,52 @@
         <v>227</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>228</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>229</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>230</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>231</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>232</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="R10" s="5" t="s">
         <v>233</v>
@@ -11711,52 +11712,52 @@
         <v>234</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="U10" s="5" t="s">
         <v>228</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="W10" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="X10" s="5" t="s">
         <v>235</v>
       </c>
       <c r="Y10" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="Z10" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AA10" s="5" t="s">
         <v>236</v>
       </c>
       <c r="AB10" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AC10" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AD10" s="5" t="s">
         <v>237</v>
       </c>
       <c r="AE10" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG10" s="5" t="s">
         <v>238</v>
       </c>
       <c r="AH10" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AI10" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="409.6" x14ac:dyDescent="0.3">
@@ -11764,25 +11765,25 @@
         <v>239</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>240</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>241</v>
@@ -11791,7 +11792,7 @@
         <v>242</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>243</v>
@@ -11800,7 +11801,7 @@
         <v>244</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>245</v>
@@ -11809,7 +11810,7 @@
         <v>246</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="R11" s="8" t="s">
         <v>240</v>
@@ -11818,7 +11819,7 @@
         <v>247</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="U11" s="8" t="s">
         <v>240</v>
@@ -11827,7 +11828,7 @@
         <v>248</v>
       </c>
       <c r="W11" s="8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="X11" s="8" t="s">
         <v>249</v>
@@ -11836,7 +11837,7 @@
         <v>250</v>
       </c>
       <c r="Z11" s="8" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AA11" s="8" t="s">
         <v>251</v>
@@ -11845,7 +11846,7 @@
         <v>252</v>
       </c>
       <c r="AC11" s="8" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AD11" s="8" t="s">
         <v>253</v>
@@ -11854,7 +11855,7 @@
         <v>254</v>
       </c>
       <c r="AF11" s="8" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AG11" s="8" t="s">
         <v>255</v>
@@ -11863,7 +11864,7 @@
         <v>256</v>
       </c>
       <c r="AI11" s="8" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
